--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -6221,12 +6221,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6292,17 +6292,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V55" t="n">
@@ -11715,12 +11715,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ca-cioos_7de69ca8-b3f3-4761-b441-dfc9e63b1fbc</t>
+          <t>ca-cioos_7e0f0bbc-507a-4ca0-bafc-1cc3e56db028</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rocky Intertidal RPAS Mapping Project - BC Central Coast - Canada</t>
+          <t>Hakai physical plan and utility lines – Calvert Island Field Station - 2006</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11772,16 +11772,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6286, 48.1332], [-122.8941, 48.1332], [-122.8941, 51.9689], [-128.6286, 51.9689], [-128.6286, 48.1332]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13541603114572, 51.65216411387959], [-128.12786293055976, 51.65216411387959], [-128.12786293055976, 51.6557318761607], [-128.13541603114572, 51.6557318761607], [-128.13541603114572, 51.65216411387959]]]}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11791,12 +11791,12 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>10.21966/mc7v-dx06</t>
+          <t>10.21966/3yew-5r94</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBVWDBQSFpnWjBBS0Q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU9IR0RmSHlkRW1sd2k</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V104" t="n">
@@ -11817,9 +11817,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X104" t="n">
-        <v>3</v>
-      </c>
+      <c r="X104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11827,12 +11825,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ca-cioos_7e0f0bbc-507a-4ca0-bafc-1cc3e56db028</t>
+          <t>ca-cioos_7de69ca8-b3f3-4761-b441-dfc9e63b1fbc</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11842,7 +11840,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hakai physical plan and utility lines – Calvert Island Field Station - 2006</t>
+          <t>Rocky Intertidal RPAS Mapping Project - BC Central Coast - Canada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -11860,7 +11858,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -11884,16 +11882,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13541603114572, 51.65216411387959], [-128.12786293055976, 51.65216411387959], [-128.12786293055976, 51.6557318761607], [-128.13541603114572, 51.6557318761607], [-128.13541603114572, 51.65216411387959]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6286, 48.1332], [-122.8941, 48.1332], [-122.8941, 51.9689], [-128.6286, 51.9689], [-128.6286, 48.1332]]]}</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -11903,12 +11901,12 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>10.21966/3yew-5r94</t>
+          <t>10.21966/mc7v-dx06</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU9IR0RmSHlkRW1sd2k</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBVWDBQSFpnWjBBS0Q</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -11918,7 +11916,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="V105" t="n">
@@ -11929,7 +11927,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr"/>
+      <c r="X105" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13147,12 +13147,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -13204,11 +13204,11 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V117" t="n">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -13257,12 +13257,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -13314,11 +13314,11 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13333,12 +13333,12 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V118" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -15229,7 +15229,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X135" t="inlineStr"/>
+      <c r="X135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16111,7 +16113,9 @@
           <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
-      <c r="X143" t="inlineStr"/>
+      <c r="X143" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16779,12 +16783,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ca-cioos_cec3dcef-8dba-4d91-aee6-b60ce416497c</t>
+          <t>ca-cioos_c89e35df-8a16-4efc-ae29-15f4e3da8a55</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -16794,7 +16798,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mussel Dynamics - Point Intercepts - BC Central Coast</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -16850,17 +16854,17 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>10.21966/ns9h-1126</t>
+          <t>10.21966/0yk3-9b74</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotaGdFmX3xEvWjXQA5</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-Motctf2E7ids9V-6Cfb</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
@@ -16870,7 +16874,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="V150" t="n">
@@ -16889,12 +16893,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ca-cioos_c89e35df-8a16-4efc-ae29-15f4e3da8a55</t>
+          <t>ca-cioos_cec3dcef-8dba-4d91-aee6-b60ce416497c</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -16904,7 +16908,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast</t>
+          <t>Mussel Dynamics - Point Intercepts - BC Central Coast</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -16960,17 +16964,17 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>10.21966/0yk3-9b74</t>
+          <t>10.21966/ns9h-1126</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-Motctf2E7ids9V-6Cfb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotaGdFmX3xEvWjXQA5</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
@@ -16980,7 +16984,7 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V151" t="n">
@@ -18979,12 +18983,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ca-cioos_476204a7-0714-4755-953d-61fa3c5df497</t>
+          <t>ca-cioos_24f1c230-6c37-470c-907d-25b9b022f5c2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -18994,7 +18998,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Hakai Institute Nutrients (Dosser et al., 2021)</t>
+          <t>Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -19012,7 +19016,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -19040,27 +19044,27 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.6, 50.69], [-126.3, 50.8], [-124.8, 50.44], [-123.9, 49.65], [-125.1, 49.65], [-127.6, 50.69]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.87477074, 49.80151064], [-124.30109865, 49.80151064], [-124.30109865, 50.66883255], [-126.87477074, 50.66883255], [-126.87477074, 49.80151064]]]}</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '9.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>nutrients</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>10.21966/j3j5-wt70</t>
+          <t>10.21966/54tw-kh93</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/oOseiEWez6TzqPUIisEXczg6G8y2/-MoZtzH-n9LBy9Bn29Hl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZDeElXT3dpUFNlOGQ</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
@@ -19070,7 +19074,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V170" t="n">
@@ -19089,12 +19093,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ca-cioos_24f1c230-6c37-470c-907d-25b9b022f5c2</t>
+          <t>ca-cioos_476204a7-0714-4755-953d-61fa3c5df497</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -19104,7 +19108,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada</t>
+          <t>Hakai Institute Nutrients (Dosser et al., 2021)</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -19122,7 +19126,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -19150,27 +19154,27 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.87477074, 49.80151064], [-124.30109865, 49.80151064], [-124.30109865, 50.66883255], [-126.87477074, 50.66883255], [-126.87477074, 49.80151064]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.6, 50.69], [-126.3, 50.8], [-124.8, 50.44], [-123.9, 49.65], [-125.1, 49.65], [-127.6, 50.69]]]}</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>[{'max': '9.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>nutrients</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>10.21966/54tw-kh93</t>
+          <t>10.21966/j3j5-wt70</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZDeElXT3dpUFNlOGQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/oOseiEWez6TzqPUIisEXczg6G8y2/-MoZtzH-n9LBy9Bn29Hl</t>
         </is>
       </c>
       <c r="T171" t="inlineStr">
@@ -19180,7 +19184,7 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="V171" t="n">
@@ -19191,9 +19195,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X171" t="n">
-        <v>1</v>
-      </c>
+      <c r="X171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -24471,9 +24473,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X219" t="n">
-        <v>1</v>
-      </c>
+      <c r="X219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V250" t="n">
@@ -30968,7 +30968,7 @@
         </is>
       </c>
       <c r="X278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X284"/>
+  <dimension ref="A1:X300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6292,17 +6292,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V55" t="n">
@@ -13147,12 +13147,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -13204,11 +13204,11 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V117" t="n">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -13257,12 +13257,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -13314,11 +13314,11 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13333,12 +13333,12 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V118" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -13477,12 +13477,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>e1b86825-d43b-47e1-bf45-ab791f44772d</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_0e446321-34f3-4d5a-8c7d-79c89eb76373</t>
+          <t>ca-cioos_0e4f324c-6498-4c89-9e19-f2f9f474a1df</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stream temperature time-series – Calvert Island – 2013 - 2019</t>
+          <t>LiDAR-derived Drainage Network for Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13534,16 +13534,16 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.25940955, 51.55841821], [-127.87488807, 51.55841821], [-127.87488807, 51.75224257], [-128.25940955, 51.75224257], [-128.25940955, 51.55841821]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16, 51.41], [-127.88, 51.41], [-127.88, 51.73], [-128.16, 51.73], [-128.16, 51.41]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/7nb6-zk37</t>
+          <t>10.21966/vavm-b152</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFDT2lYSlBQZ0VNdDg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW5MeGIydVA3U1VKdWo</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>e1b86825-d43b-47e1-bf45-ab791f44772d</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ca-cioos_0e4f324c-6498-4c89-9e19-f2f9f474a1df</t>
+          <t>ca-cioos_0e446321-34f3-4d5a-8c7d-79c89eb76373</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>LiDAR-derived Drainage Network for Calvert Island - British Columbia - Canada</t>
+          <t>Stream temperature time-series – Calvert Island – 2013 - 2019</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -13620,12 +13620,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -13644,16 +13644,16 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16, 51.41], [-127.88, 51.41], [-127.88, 51.73], [-128.16, 51.73], [-128.16, 51.41]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.25940955, 51.55841821], [-127.87488807, 51.55841821], [-127.87488807, 51.75224257], [-128.25940955, 51.75224257], [-128.25940955, 51.55841821]]]}</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>10.21966/vavm-b152</t>
+          <t>10.21966/7nb6-zk37</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW5MeGIydVA3U1VKdWo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFDT2lYSlBQZ0VNdDg</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
@@ -15229,9 +15229,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X135" t="n">
-        <v>1</v>
-      </c>
+      <c r="X135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16113,9 +16111,7 @@
           <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
-      <c r="X143" t="n">
-        <v>1</v>
-      </c>
+      <c r="X143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16783,12 +16779,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ca-cioos_c89e35df-8a16-4efc-ae29-15f4e3da8a55</t>
+          <t>ca-cioos_cec3dcef-8dba-4d91-aee6-b60ce416497c</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -16798,7 +16794,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast</t>
+          <t>Mussel Dynamics - Point Intercepts - BC Central Coast</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -16854,17 +16850,17 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>10.21966/0yk3-9b74</t>
+          <t>10.21966/ns9h-1126</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-Motctf2E7ids9V-6Cfb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotaGdFmX3xEvWjXQA5</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
@@ -16874,7 +16870,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V150" t="n">
@@ -16893,12 +16889,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ca-cioos_cec3dcef-8dba-4d91-aee6-b60ce416497c</t>
+          <t>ca-cioos_c89e35df-8a16-4efc-ae29-15f4e3da8a55</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -16908,7 +16904,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Mussel Dynamics - Point Intercepts - BC Central Coast</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -16964,17 +16960,17 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>10.21966/ns9h-1126</t>
+          <t>10.21966/0yk3-9b74</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotaGdFmX3xEvWjXQA5</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-Motctf2E7ids9V-6Cfb</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
@@ -16984,7 +16980,7 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="V151" t="n">
@@ -30968,7 +30964,7 @@
         </is>
       </c>
       <c r="X278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -31411,12 +31407,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
+          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>ca-cioos_bea3da72-dafe-4e25-b5b2-0176e0ffba44</t>
+          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -31426,7 +31422,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Chemainus River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -31472,7 +31468,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.66843, 48.91641], [-123.6484, 48.90105], [-123.6554, 48.88016], [-123.6751, 48.87641], [-123.68894, 48.88178], [-123.68329, 48.89633], [-123.67928, 48.90316], [-123.67136, 48.91722], [-123.66848, 48.91635]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
@@ -31487,12 +31483,12 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>10.21966/q2e0-j004</t>
+          <t>10.21966/r9zr-xz33</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpszvIrt9OF8-BLQW2N</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
         </is>
       </c>
       <c r="T283" t="inlineStr">
@@ -31502,7 +31498,7 @@
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="V283" t="n">
@@ -31514,7 +31510,7 @@
         </is>
       </c>
       <c r="X283" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -31523,12 +31519,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -31538,7 +31534,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -31556,12 +31552,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Estuary Resilience</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -31576,7 +31572,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N284" t="n">
@@ -31584,44 +31580,1836 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>10.21966/9dbb-5d54</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V284" t="n">
+        <v>0</v>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X284" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>283</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H285" t="b">
+        <v>0</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>1</v>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>10.21966/vpz7-mm73</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V285" t="n">
+        <v>0</v>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X285" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>284</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>0ce3ee5b-425b-4eb0-a201-96bdfb795a3f</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>ca-cioos_354b5b83-e752-4ffb-a740-d1cdc02ac8c6</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Dtlaxsiwè River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H286" t="b">
+        <v>0</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>1</v>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.1721, 50.61011], [-127.17933, 50.612], [-127.1873, 50.6098], [-127.19703, 50.61072], [-127.20524, 50.61585], [-127.19007, 50.61844], [-127.18675, 50.61393], [-127.17744, 50.61359], [-127.17161, 50.61118], [-127.17203, 50.61011], [-127.1721, 50.61011]]]}</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>10.21966/ydm2-m238</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7Dng-ZtRd05hnZCq1</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V286" t="n">
+        <v>0</v>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X286" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>285</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>1a2aa5c8-9a83-46f7-967d-1127436c2084</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>ca-cioos_58a5140a-0b2c-4186-a648-53d9f58e5226</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Kvai River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H287" t="b">
+        <v>0</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>1</v>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.81882, 51.77547], [-127.83122, 51.77986], [-127.85192, 51.781], [-127.86785, 51.78358], [-127.8958, 51.77366], [-127.89418, 51.77118], [-127.87834, 51.77309], [-127.86508, 51.77748], [-127.84009, 51.77519], [-127.82731, 51.77452], [-127.82025, 51.77309], [-127.81853, 51.77566], [-127.81882, 51.77547]]]}</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>10.21966/pm9m-h431</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7QQE3ifLCAPcu3Jih</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V287" t="n">
+        <v>0</v>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X287" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>286</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>c035b81c-0fc3-446e-bec5-8b8933ae874b</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>ca-cioos_7fbc28f7-ee87-4361-bbee-0ed8ce24522d</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Gwa'dzi River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H288" t="b">
+        <v>0</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>1</v>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.46176, 50.74217], [-127.49022, 50.72165], [-127.49167, 50.71188], [-127.4832, 50.70356], [-127.4874, 50.69181], [-127.46443, 50.6928], [-127.47282, 50.70776], [-127.47992, 50.71424], [-127.48305, 50.72058], [-127.45901, 50.74011], [-127.46153, 50.74217], [-127.46176, 50.74217]]]}</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>10.21966/xq99-x273</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7BCRnF2C30YPkxIyd</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V288" t="n">
+        <v>0</v>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X288" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>287</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H289" t="b">
+        <v>0</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>1</v>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>10.21966/kde9-8g12</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V289" t="n">
+        <v>0</v>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>288</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H290" t="b">
+        <v>0</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>1</v>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>10.21966/9a97-2j48</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V290" t="n">
+        <v>0</v>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>289</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H291" t="b">
+        <v>0</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>1</v>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>10.21966/ed9w-2653</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V291" t="n">
+        <v>0</v>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X291" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>290</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>1af6a43a-e73b-4774-8e10-b9f2928ab133</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>ca-cioos_ae7e017c-9211-4f98-b56e-90a4bbac161c</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Snuneymuxw River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H292" t="b">
+        <v>0</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>1</v>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.88685, 49.19332], [-123.92494, 49.1612], [-123.92581, 49.13841], [-123.91159, 49.123], [-123.88023, 49.11117], [-123.85971, 49.12766], [-123.89792, 49.16196], [-123.88099, 49.18866], [-123.88685, 49.19332]]]}</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>10.21966/k01q-wb27</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt459vxCIH7YPRN9fp</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V292" t="n">
+        <v>0</v>
+      </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X292" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>291</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>d320d90e-96bf-4993-81c5-f1f57886b0e6</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>ca-cioos_b922699f-69b6-4d63-b538-7c290086a408</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Quw'utsun/Xwulqw'selu River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H293" t="b">
+        <v>0</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>1</v>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.56201, 48.73508], [-123.59772, 48.75559], [-123.62127, 48.76514], [-123.63885, 48.77426], [-123.66935, 48.78033], [-123.67901, 48.75472], [-123.65155, 48.74322], [-123.63017, 48.7405], [-123.60792, 48.74289], [-123.56494, 48.72987], [-123.56179, 48.73529], [-123.56201, 48.73508]]]}</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>10.21966/2ha7-9p26</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpsCA3ycwZ7bFTDIQxh</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V293" t="n">
+        <v>0</v>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X293" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>292</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>ca-cioos_bea3da72-dafe-4e25-b5b2-0176e0ffba44</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Chemainus River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H294" t="b">
+        <v>0</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>1</v>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.66843, 48.91641], [-123.6484, 48.90105], [-123.6554, 48.88016], [-123.6751, 48.87641], [-123.68894, 48.88178], [-123.68329, 48.89633], [-123.67928, 48.90316], [-123.67136, 48.91722], [-123.66848, 48.91635], [-123.66843, 48.91641]]]}</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>10.21966/q2e0-j004</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpszvIrt9OF8-BLQW2N</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V294" t="n">
+        <v>0</v>
+      </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X294" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>293</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H295" t="b">
+        <v>0</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>1</v>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>10.21966/hjkj-6611</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V295" t="n">
+        <v>0</v>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X295" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>294</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>4c7b7347-767d-45e4-b3ad-7e0133b31e1c</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>ca-cioos_dce15b7b-3772-4106-ab20-c3979c4c3f57</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Fulmore River - Shoal Creek Estuary Complex (Provisional)</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H296" t="b">
+        <v>0</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N296" t="n">
+        <v>1</v>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.08798, 50.4777], [-126.09599, 50.48418], [-126.09046, 50.50918], [-126.0647, 50.52425], [-125.99698, 50.53569], [-125.93459, 50.56717], [-125.93173, 50.56202], [-125.93764, 50.55458], [-125.91055, 50.55134], [-125.89853, 50.54943], [-125.90063, 50.54466], [-125.96416, 50.53989], [-125.98973, 50.52043], [-126.06566, 50.5067], [-126.08779, 50.47789], [-126.08798, 50.4777]]]}</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>10.21966/g1cn-xs92</t>
+        </is>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptdJ8iUmLeOrdmqzrQ</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V296" t="n">
+        <v>0</v>
+      </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X296" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>295</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H297" t="b">
+        <v>0</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N297" t="n">
+        <v>1</v>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>10.21966/npe4-3036</t>
+        </is>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V297" t="n">
+        <v>0</v>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X297" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>296</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>35245eae-e508-47da-bcf7-54346cda086a</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>ca-cioos_e9b72149-8cf1-4000-ae3e-6b29ad60b078</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Malksope River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H298" t="b">
+        <v>0</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N298" t="n">
+        <v>1</v>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.46569, 50.12556], [-127.45723, 50.13142], [-127.43281, 50.13338], [-127.42845, 50.13765], [-127.41181, 50.14408], [-127.40973, 50.14233], [-127.41999, 50.13627], [-127.41803, 50.13195], [-127.43106, 50.12796], [-127.46545, 50.12446], [-127.46569, 50.12548], [-127.46569, 50.12556]]]}</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>10.21966/21sf-ey03</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq77iyWJfPg4z-FvOSb</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V298" t="n">
+        <v>0</v>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X298" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>297</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>5177d019-598e-4415-b778-9688403652c8</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>ca-cioos_ed84df74-5a2d-4a7d-87c8-a7b93f11088e</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>BC Estuary Water Quality Monitoring Data - Nalaxdlala River Estuary (Provisional)</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H299" t="b">
+        <v>0</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Estuary Resilience</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>tentative</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N299" t="n">
+        <v>1</v>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.9489, 50.70902], [-125.9696, 50.70291], [-126.00938, 50.69118], [-126.00108, 50.66848], [-125.98257, 50.68374], [-125.98152, 50.69271], [-125.95462, 50.70263], [-125.94785, 50.70768], [-125.9489, 50.70911], [-125.9489, 50.70902]]]}</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>10.21966/4krv-aw23</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptbxmpkBsfyWWfSxOJ</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V299" t="n">
+        <v>0</v>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X299" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>298</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H300" t="b">
+        <v>0</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory, Geospatial</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>Tula Foundation</t>
+        </is>
+      </c>
+      <c r="N300" t="n">
+        <v>1</v>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
           <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
         </is>
       </c>
-      <c r="P284" t="inlineStr">
+      <c r="P300" t="inlineStr">
         <is>
           <t>[{'max': '3954.0', 'min': '800.0'}]</t>
         </is>
       </c>
-      <c r="Q284" t="inlineStr">
+      <c r="Q300" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="R284" t="inlineStr">
+      <c r="R300" t="inlineStr">
         <is>
           <t>10.21966/w9n0-kn30</t>
         </is>
       </c>
-      <c r="S284" t="inlineStr">
+      <c r="S300" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
         </is>
       </c>
-      <c r="T284" t="inlineStr"/>
-      <c r="U284" t="inlineStr">
+      <c r="T300" t="inlineStr"/>
+      <c r="U300" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="V284" t="n">
-        <v>0</v>
-      </c>
-      <c r="W284" t="inlineStr">
+      <c r="V300" t="n">
+        <v>0</v>
+      </c>
+      <c r="W300" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X284" t="inlineStr"/>
+      <c r="X300" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -5561,12 +5561,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
+          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
+          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10.21966/1.715784</t>
+          <t>10.21966/6zp4-ye07</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V48" t="n">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
+          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10.21966/6zp4-ye07</t>
+          <t>10.21966/zs6a-j496</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
+          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
+          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5852,17 +5852,17 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10.21966/zs6a-j496</t>
+          <t>10.21966/1.715740</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V50" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
+          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
+          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5962,17 +5962,17 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>10.21966/1.715740</t>
+          <t>10.21966/1.715784</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V51" t="n">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8580,16 +8580,16 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10.21966/awsk-my87</t>
+          <t>10.21966/5rp3-3207</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V75" t="n">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>10.21966/5rp3-3207</t>
+          <t>10.21966/awsk-my87</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V76" t="n">
@@ -14577,12 +14577,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Skeena Fisheries Commission</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -14638,27 +14638,27 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="V130" t="n">
@@ -14687,12 +14687,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Skeena Fisheries Commission</t>
         </is>
       </c>
       <c r="N131" t="n">
@@ -14748,27 +14748,27 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V131" t="n">
@@ -16779,12 +16779,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ca-cioos_cec3dcef-8dba-4d91-aee6-b60ce416497c</t>
+          <t>ca-cioos_c89e35df-8a16-4efc-ae29-15f4e3da8a55</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mussel Dynamics - Point Intercepts - BC Central Coast</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -16850,17 +16850,17 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>10.21966/ns9h-1126</t>
+          <t>10.21966/0yk3-9b74</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotaGdFmX3xEvWjXQA5</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-Motctf2E7ids9V-6Cfb</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="V150" t="n">
@@ -16889,12 +16889,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ca-cioos_c89e35df-8a16-4efc-ae29-15f4e3da8a55</t>
+          <t>ca-cioos_cec3dcef-8dba-4d91-aee6-b60ce416497c</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast</t>
+          <t>Mussel Dynamics - Point Intercepts - BC Central Coast</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -16960,17 +16960,17 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>10.21966/0yk3-9b74</t>
+          <t>10.21966/ns9h-1126</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-Motctf2E7ids9V-6Cfb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotaGdFmX3xEvWjXQA5</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V151" t="n">
@@ -21623,12 +21623,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
+          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -21638,7 +21638,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
+          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -21680,16 +21680,16 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -21699,12 +21699,12 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>10.21966/thq7-0g08</t>
+          <t>10.21966/e4b8-vp48</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
@@ -21714,15 +21714,15 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="V194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
@@ -21733,12 +21733,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
+          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -21748,7 +21748,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -21790,16 +21790,16 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
@@ -21809,12 +21809,12 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>10.21966/e4b8-vp48</t>
+          <t>10.21966/bzr6-er66</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
@@ -21824,15 +21824,15 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
@@ -21843,12 +21843,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
+          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -21858,7 +21858,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -21904,12 +21904,12 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -21919,12 +21919,12 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>10.21966/bzr6-er66</t>
+          <t>10.21966/thq7-0g08</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="V196" t="n">
@@ -21945,7 +21945,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X196" t="inlineStr"/>
+      <c r="X196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -31195,12 +31197,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
+          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
+          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -31210,17 +31212,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
+          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H281" t="b">
@@ -31233,7 +31235,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -31256,27 +31258,23 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>[{'max': '2.5', 'min': '2.5'}]</t>
+          <t>[{'max': '0.0', 'min': '600.0'}]</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R281" t="inlineStr">
-        <is>
-          <t>10.21966/rrzq-yw32</t>
-        </is>
-      </c>
+          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
         </is>
       </c>
       <c r="T281" t="inlineStr">
@@ -31289,15 +31287,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="V281" t="n">
-        <v>0</v>
-      </c>
-      <c r="W281" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X281" t="inlineStr"/>
+      <c r="V281" t="inlineStr"/>
+      <c r="W281" t="inlineStr"/>
+      <c r="X281" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31305,12 +31299,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
+          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
+          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -31320,17 +31314,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
+          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H282" t="b">
@@ -31343,7 +31337,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -31366,23 +31360,27 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '600.0'}]</t>
+          <t>[{'max': '2.5', 'min': '2.5'}]</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R282" t="inlineStr"/>
+          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>10.21966/rrzq-yw32</t>
+        </is>
+      </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
         </is>
       </c>
       <c r="T282" t="inlineStr">
@@ -31395,10 +31393,16 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="V282" t="inlineStr"/>
-      <c r="W282" t="inlineStr"/>
+      <c r="V282" t="n">
+        <v>0</v>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="X282" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -32294,7 +32298,7 @@
         </is>
       </c>
       <c r="X290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X300"/>
+  <dimension ref="A1:X301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
+          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
+          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10.21966/6zp4-ye07</t>
+          <t>10.21966/1.715784</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V48" t="n">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
+          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
+          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10.21966/zs6a-j496</t>
+          <t>10.21966/6zp4-ye07</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
+          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5852,17 +5852,17 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10.21966/1.715740</t>
+          <t>10.21966/zs6a-j496</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V50" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
+          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
+          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5962,17 +5962,17 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>10.21966/1.715784</t>
+          <t>10.21966/1.715740</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V51" t="n">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6292,17 +6292,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V55" t="n">
@@ -11715,12 +11715,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ca-cioos_7e0f0bbc-507a-4ca0-bafc-1cc3e56db028</t>
+          <t>ca-cioos_7de69ca8-b3f3-4761-b441-dfc9e63b1fbc</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hakai physical plan and utility lines – Calvert Island Field Station - 2006</t>
+          <t>Rocky Intertidal RPAS Mapping Project - BC Central Coast - Canada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11772,16 +11772,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13541603114572, 51.65216411387959], [-128.12786293055976, 51.65216411387959], [-128.12786293055976, 51.6557318761607], [-128.13541603114572, 51.6557318761607], [-128.13541603114572, 51.65216411387959]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6286, 48.1332], [-122.8941, 48.1332], [-122.8941, 51.9689], [-128.6286, 51.9689], [-128.6286, 48.1332]]]}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11791,12 +11791,12 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>10.21966/3yew-5r94</t>
+          <t>10.21966/mc7v-dx06</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU9IR0RmSHlkRW1sd2k</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBVWDBQSFpnWjBBS0Q</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="V104" t="n">
@@ -11817,7 +11817,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr"/>
+      <c r="X104" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11825,12 +11827,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ca-cioos_7de69ca8-b3f3-4761-b441-dfc9e63b1fbc</t>
+          <t>ca-cioos_7e0f0bbc-507a-4ca0-bafc-1cc3e56db028</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11840,7 +11842,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rocky Intertidal RPAS Mapping Project - BC Central Coast - Canada</t>
+          <t>Hakai physical plan and utility lines – Calvert Island Field Station - 2006</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -11858,7 +11860,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -11882,16 +11884,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6286, 48.1332], [-122.8941, 48.1332], [-122.8941, 51.9689], [-128.6286, 51.9689], [-128.6286, 48.1332]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13541603114572, 51.65216411387959], [-128.12786293055976, 51.65216411387959], [-128.12786293055976, 51.6557318761607], [-128.13541603114572, 51.6557318761607], [-128.13541603114572, 51.65216411387959]]]}</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -11901,12 +11903,12 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>10.21966/mc7v-dx06</t>
+          <t>10.21966/3yew-5r94</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBVWDBQSFpnWjBBS0Q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU9IR0RmSHlkRW1sd2k</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -11916,7 +11918,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V105" t="n">
@@ -11927,9 +11929,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X105" t="n">
-        <v>3</v>
-      </c>
+      <c r="X105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -14577,12 +14577,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Skeena Fisheries Commission</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -14638,27 +14638,27 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V130" t="n">
@@ -14687,12 +14687,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Skeena Fisheries Commission</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N131" t="n">
@@ -14748,27 +14748,27 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="V131" t="n">
@@ -21623,12 +21623,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
+          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -21638,7 +21638,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -21680,16 +21680,16 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -21699,12 +21699,12 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>10.21966/e4b8-vp48</t>
+          <t>10.21966/thq7-0g08</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
@@ -21714,15 +21714,15 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="V194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
@@ -21733,12 +21733,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
+          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -21748,7 +21748,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -21790,16 +21790,16 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
@@ -21809,12 +21809,12 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>10.21966/bzr6-er66</t>
+          <t>10.21966/e4b8-vp48</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
@@ -21824,15 +21824,15 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="V195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
@@ -21843,12 +21843,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
+          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -21858,7 +21858,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
+          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -21904,12 +21904,12 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -21919,12 +21919,12 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>10.21966/thq7-0g08</t>
+          <t>10.21966/bzr6-er66</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V196" t="n">
@@ -21945,9 +21945,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X196" t="n">
-        <v>1</v>
-      </c>
+      <c r="X196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22596,7 +22594,7 @@
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V202" t="n">
@@ -23047,7 +23045,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X206" t="inlineStr"/>
+      <c r="X206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -31146,7 +31146,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.343, 51.8489], [-126.3333, 51.815], [-122.6652, 49.5126], [-123.9831, 49.2554], [-128.343, 51.8489]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.0471, 52.2577], [-128.9141, 51.7033], [-127.6841, 50.7687], [-123.7744, 48.9864], [-122.764, 49.331], [-122.8299, 49.9706], [-127.0471, 52.2577]]]}</t>
         </is>
       </c>
       <c r="P280" t="inlineStr">
@@ -31176,7 +31176,7 @@
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V280" t="n">
@@ -31197,12 +31197,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
+          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
+          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -31212,17 +31212,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
+          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H281" t="b">
@@ -31235,7 +31235,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -31258,23 +31258,27 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '600.0'}]</t>
+          <t>[{'max': '2.5', 'min': '2.5'}]</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R281" t="inlineStr"/>
+          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>10.21966/rrzq-yw32</t>
+        </is>
+      </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
         </is>
       </c>
       <c r="T281" t="inlineStr">
@@ -31287,11 +31291,15 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="V281" t="inlineStr"/>
-      <c r="W281" t="inlineStr"/>
-      <c r="X281" t="n">
-        <v>2</v>
-      </c>
+      <c r="V281" t="n">
+        <v>0</v>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31299,12 +31307,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
+          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
+          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -31314,17 +31322,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
+          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H282" t="b">
@@ -31337,7 +31345,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -31360,27 +31368,23 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>[{'max': '2.5', 'min': '2.5'}]</t>
+          <t>[{'max': '0.0', 'min': '600.0'}]</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R282" t="inlineStr">
-        <is>
-          <t>10.21966/rrzq-yw32</t>
-        </is>
-      </c>
+          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
         </is>
       </c>
       <c r="T282" t="inlineStr">
@@ -31393,16 +31397,10 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="V282" t="n">
-        <v>0</v>
-      </c>
-      <c r="W282" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="V282" t="inlineStr"/>
+      <c r="W282" t="inlineStr"/>
       <c r="X282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
@@ -32298,7 +32296,7 @@
         </is>
       </c>
       <c r="X290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -33315,105 +33313,215 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
+          <t>dd471e82-a6b8-4f32-891c-bbea26e9998e</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>ca-cioos_aeb30028-a7eb-462e-ac0f-6c5fe101d4a2</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>DNA Metabarcoding Captures Temporal and Vertical Dynamics of Mesozooplankton Communities</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H300" t="b">
+        <v>0</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Genomics, Oceanography</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>University of British Columbia</t>
+        </is>
+      </c>
+      <c r="N300" t="n">
+        <v>2</v>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>{'type': 'Point', 'coordinates': [-125.0992, 50.0307]}</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>[{'max': '260.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>zooplanktonBiomassAndDiversity</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>10.21966/6b20-7r76</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OvzbmseH_syBXg1RXKd</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="V300" t="n">
+        <v>0</v>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>299</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
           <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
+      <c r="C301" t="inlineStr">
         <is>
           <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
         <is>
           <t>Mount Robson Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
         <is>
           <t>CC-BY-4.0</t>
         </is>
       </c>
-      <c r="H300" t="b">
-        <v>0</v>
-      </c>
-      <c r="I300" t="inlineStr">
+      <c r="H301" t="b">
+        <v>0</v>
+      </c>
+      <c r="I301" t="inlineStr">
         <is>
           <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
-      <c r="J300" t="inlineStr">
+      <c r="J301" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
+      <c r="K301" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="M300" t="inlineStr">
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
         <is>
           <t>Tula Foundation</t>
         </is>
       </c>
-      <c r="N300" t="n">
+      <c r="N301" t="n">
         <v>1</v>
       </c>
-      <c r="O300" t="inlineStr">
+      <c r="O301" t="inlineStr">
         <is>
           <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
         </is>
       </c>
-      <c r="P300" t="inlineStr">
+      <c r="P301" t="inlineStr">
         <is>
           <t>[{'max': '3954.0', 'min': '800.0'}]</t>
         </is>
       </c>
-      <c r="Q300" t="inlineStr">
+      <c r="Q301" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="R300" t="inlineStr">
+      <c r="R301" t="inlineStr">
         <is>
           <t>10.21966/w9n0-kn30</t>
         </is>
       </c>
-      <c r="S300" t="inlineStr">
+      <c r="S301" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
         </is>
       </c>
-      <c r="T300" t="inlineStr"/>
-      <c r="U300" t="inlineStr">
+      <c r="T301" t="inlineStr"/>
+      <c r="U301" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="V300" t="n">
-        <v>0</v>
-      </c>
-      <c r="W300" t="inlineStr">
+      <c r="V301" t="n">
+        <v>0</v>
+      </c>
+      <c r="W301" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X300" t="inlineStr"/>
+      <c r="X301" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -5561,12 +5561,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
+          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
+          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10.21966/1.715784</t>
+          <t>10.21966/6zp4-ye07</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V48" t="n">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
+          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10.21966/6zp4-ye07</t>
+          <t>10.21966/zs6a-j496</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
+          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
+          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5852,17 +5852,17 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10.21966/zs6a-j496</t>
+          <t>10.21966/1.715740</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V50" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
+          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
+          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5962,17 +5962,17 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>10.21966/1.715740</t>
+          <t>10.21966/1.715784</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V51" t="n">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6292,17 +6292,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V55" t="n">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8580,16 +8580,16 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10.21966/5rp3-3207</t>
+          <t>10.21966/awsk-my87</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V75" t="n">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>10.21966/awsk-my87</t>
+          <t>10.21966/5rp3-3207</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V76" t="n">
@@ -15127,12 +15127,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15180,20 +15180,20 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>10.21966/1.135248</t>
+          <t>10.21966/x6q2-me90</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V135" t="n">
@@ -15237,12 +15237,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15290,20 +15290,20 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -15313,12 +15313,12 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>10.21966/x6q2-me90</t>
+          <t>10.21966/1.135248</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="V136" t="n">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="V192" t="n">
@@ -21505,7 +21505,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X192" t="inlineStr"/>
+      <c r="X192" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -23045,9 +23047,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X206" t="n">
-        <v>1</v>
-      </c>
+      <c r="X206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8580,16 +8580,16 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10.21966/awsk-my87</t>
+          <t>10.21966/5rp3-3207</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V75" t="n">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>10.21966/5rp3-3207</t>
+          <t>10.21966/awsk-my87</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V76" t="n">
@@ -14577,12 +14577,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Skeena Fisheries Commission</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -14638,27 +14638,27 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="V130" t="n">
@@ -14687,12 +14687,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Skeena Fisheries Commission</t>
         </is>
       </c>
       <c r="N131" t="n">
@@ -14748,27 +14748,27 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V131" t="n">
@@ -15127,12 +15127,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15180,20 +15180,20 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>10.21966/x6q2-me90</t>
+          <t>10.21966/1.135248</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="V135" t="n">
@@ -15237,12 +15237,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15290,20 +15290,20 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -15313,12 +15313,12 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>10.21966/1.135248</t>
+          <t>10.21966/x6q2-me90</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V136" t="n">
@@ -27333,7 +27333,9 @@
           <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
-      <c r="X245" t="inlineStr"/>
+      <c r="X245" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -4569,12 +4569,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ca-cioos_26a09a27-7f16-4944-b88d-8c3bf2d36f03</t>
+          <t>ca-cioos_33c870b8-3b4c-429d-bc10-99dd4c7f4c7d</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wind Fetch - BC Central Coast - Canada</t>
+          <t>Nearshore elevation and imagery models - Quadra Island Hakai Institute Facility Shoreline - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4626,16 +4626,16 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.7578125, 50.16193379], [-126.22070312, 50.16193379], [-126.22070312, 52.84175491], [-131.7578125, 52.84175491], [-131.7578125, 50.16193379]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.2229327, 50.11245881], [-125.21821201, 50.11245881], [-125.21821201, 50.1172472], [-125.2229327, 50.1172472], [-125.2229327, 50.11245881]]]}</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>10.21966/845b-yn81</t>
+          <t>10.21966/ebd6-yd93</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXNDOU8zYXhRdDA3RWM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXN1MUhmRE9GRndsSko</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V39" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ca-cioos_33c870b8-3b4c-429d-bc10-99dd4c7f4c7d</t>
+          <t>ca-cioos_3f40326a-23f9-4e30-a16a-f332ace14e2f</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nearshore elevation and imagery models - Quadra Island Hakai Institute Facility Shoreline - British Columbia - Canada</t>
+          <t>Nereocystis kelp canopy productivity data from BC Central Coast</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4736,31 +4736,31 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.2229327, 50.11245881], [-125.21821201, 50.11245881], [-125.21821201, 50.1172472], [-125.2229327, 50.1172472], [-125.2229327, 50.11245881]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.19], [-127.1, 51.19], [-127.1, 52.28], [-128.6, 52.28], [-128.6, 51.19]]]}</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>10.21966/ebd6-yd93</t>
+          <t>10.21966/d1s2-s530</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXN1MUhmRE9GRndsSko</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtG8b48aDAEdJoqNT6N</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -4770,18 +4770,20 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr"/>
+          <t>[{'year': '2024', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4789,12 +4791,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ca-cioos_3f40326a-23f9-4e30-a16a-f332ace14e2f</t>
+          <t>ca-cioos_26a09a27-7f16-4944-b88d-8c3bf2d36f03</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4804,7 +4806,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nereocystis kelp canopy productivity data from BC Central Coast</t>
+          <t>Wind Fetch - BC Central Coast - Canada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4822,12 +4824,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4850,27 +4852,27 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.19], [-127.1, 51.19], [-127.1, 52.28], [-128.6, 52.28], [-128.6, 51.19]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.7578125, 50.16193379], [-126.22070312, 50.16193379], [-126.22070312, 52.84175491], [-131.7578125, 52.84175491], [-131.7578125, 50.16193379]]]}</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>10.21966/d1s2-s530</t>
+          <t>10.21966/845b-yn81</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtG8b48aDAEdJoqNT6N</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXNDOU8zYXhRdDA3RWM</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -4880,20 +4882,18 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
-        </is>
-      </c>
-      <c r="X41" t="n">
-        <v>3</v>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
+          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
+          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10.21966/6zp4-ye07</t>
+          <t>10.21966/1.715784</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V48" t="n">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
+          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
+          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10.21966/zs6a-j496</t>
+          <t>10.21966/6zp4-ye07</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
+          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5852,17 +5852,17 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10.21966/1.715740</t>
+          <t>10.21966/zs6a-j496</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V50" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
+          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
+          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5962,17 +5962,17 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>10.21966/1.715784</t>
+          <t>10.21966/1.715740</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V51" t="n">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6292,17 +6292,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V55" t="n">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8580,16 +8580,16 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10.21966/5rp3-3207</t>
+          <t>10.21966/awsk-my87</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V75" t="n">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>10.21966/awsk-my87</t>
+          <t>10.21966/5rp3-3207</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V76" t="n">
@@ -14577,12 +14577,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Skeena Fisheries Commission</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -14638,27 +14638,27 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V130" t="n">
@@ -14687,12 +14687,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Skeena Fisheries Commission</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N131" t="n">
@@ -14748,27 +14748,27 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="V131" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -5447,12 +5447,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
+          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
+          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5518,17 +5518,17 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>10.21966/1.715784</t>
+          <t>10.21966/6zp4-ye07</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V47" t="n">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
+          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10.21966/6zp4-ye07</t>
+          <t>10.21966/zs6a-j496</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
+          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
+          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5738,17 +5738,17 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10.21966/zs6a-j496</t>
+          <t>10.21966/1.715740</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V49" t="n">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
+          <t>ca-cioos_4624baf9-ec39-4538-83fe-1563511b722c</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
+          <t>High-resolution record of surface seawater CO2 content from June 2017 to April 2019 collected in Sitka Harbor, Alaska, USA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-135.62915433, 56.79541908], [-135.02059329, 56.79541908], [-135.02059329, 57.22157626], [-135.62915433, 57.22157626], [-135.62915433, 56.79541908]]]}</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5848,17 +5848,17 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10.21966/1.715740</t>
+          <t>10.21966/fwk1-a364</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXFtYXJjVDZ5V3UxcTk</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V50" t="n">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ca-cioos_4624baf9-ec39-4538-83fe-1563511b722c</t>
+          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>High-resolution record of surface seawater CO2 content from June 2017 to April 2019 collected in Sitka Harbor, Alaska, USA</t>
+          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-135.62915433, 56.79541908], [-135.02059329, 56.79541908], [-135.02059329, 57.22157626], [-135.62915433, 57.22157626], [-135.62915433, 56.79541908]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5963,12 +5963,12 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>10.21966/fwk1-a364</t>
+          <t>10.21966/1.715784</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXFtYXJjVDZ5V3UxcTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -13359,12 +13359,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>e1b86825-d43b-47e1-bf45-ab791f44772d</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ca-cioos_0e4f324c-6498-4c89-9e19-f2f9f474a1df</t>
+          <t>ca-cioos_0e446321-34f3-4d5a-8c7d-79c89eb76373</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LiDAR-derived Drainage Network for Calvert Island - British Columbia - Canada</t>
+          <t>Stream temperature time-series – Calvert Island – 2013 - 2019</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -13392,12 +13392,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -13416,16 +13416,16 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16, 51.41], [-127.88, 51.41], [-127.88, 51.73], [-128.16, 51.73], [-128.16, 51.41]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.25940955, 51.55841821], [-127.87488807, 51.55841821], [-127.87488807, 51.75224257], [-128.25940955, 51.75224257], [-128.25940955, 51.55841821]]]}</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -13435,12 +13435,12 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>10.21966/vavm-b152</t>
+          <t>10.21966/7nb6-zk37</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW5MeGIydVA3U1VKdWo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFDT2lYSlBQZ0VNdDg</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>e1b86825-d43b-47e1-bf45-ab791f44772d</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_0e446321-34f3-4d5a-8c7d-79c89eb76373</t>
+          <t>ca-cioos_0e4f324c-6498-4c89-9e19-f2f9f474a1df</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stream temperature time-series – Calvert Island – 2013 - 2019</t>
+          <t>LiDAR-derived Drainage Network for Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13502,12 +13502,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13526,16 +13526,16 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.25940955, 51.55841821], [-127.87488807, 51.55841821], [-127.87488807, 51.75224257], [-128.25940955, 51.75224257], [-128.25940955, 51.55841821]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16, 51.41], [-127.88, 51.41], [-127.88, 51.73], [-128.16, 51.73], [-128.16, 51.41]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/7nb6-zk37</t>
+          <t>10.21966/vavm-b152</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFDT2lYSlBQZ0VNdDg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW5MeGIydVA3U1VKdWo</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -14459,12 +14459,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Skeena Fisheries Commission</t>
         </is>
       </c>
       <c r="N129" t="n">
@@ -14520,27 +14520,27 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V129" t="n">
@@ -14569,12 +14569,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Skeena Fisheries Commission</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -14630,27 +14630,27 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="V130" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -5989,7 +5989,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6107,12 +6109,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6122,7 +6124,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6168,7 +6170,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6178,17 +6180,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6198,7 +6200,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -6217,12 +6219,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6232,7 +6234,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6278,7 +6280,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6288,17 +6290,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6308,7 +6310,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -8407,12 +8409,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8422,7 +8424,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8464,16 +8466,16 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8483,12 +8485,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>10.21966/awsk-my87</t>
+          <t>10.21966/5rp3-3207</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -8498,7 +8500,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V74" t="n">
@@ -8517,12 +8519,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8532,7 +8534,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8574,16 +8576,16 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -8593,12 +8595,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10.21966/5rp3-3207</t>
+          <t>10.21966/awsk-my87</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8608,7 +8610,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V75" t="n">
@@ -13359,12 +13361,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>e1b86825-d43b-47e1-bf45-ab791f44772d</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ca-cioos_0e446321-34f3-4d5a-8c7d-79c89eb76373</t>
+          <t>ca-cioos_0e4f324c-6498-4c89-9e19-f2f9f474a1df</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -13374,7 +13376,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Stream temperature time-series – Calvert Island – 2013 - 2019</t>
+          <t>LiDAR-derived Drainage Network for Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -13392,12 +13394,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -13416,16 +13418,16 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.25940955, 51.55841821], [-127.87488807, 51.55841821], [-127.87488807, 51.75224257], [-128.25940955, 51.75224257], [-128.25940955, 51.55841821]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16, 51.41], [-127.88, 51.41], [-127.88, 51.73], [-128.16, 51.73], [-128.16, 51.41]]]}</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -13435,12 +13437,12 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>10.21966/7nb6-zk37</t>
+          <t>10.21966/vavm-b152</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFDT2lYSlBQZ0VNdDg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW5MeGIydVA3U1VKdWo</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -13469,12 +13471,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>e1b86825-d43b-47e1-bf45-ab791f44772d</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_0e4f324c-6498-4c89-9e19-f2f9f474a1df</t>
+          <t>ca-cioos_0e446321-34f3-4d5a-8c7d-79c89eb76373</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13484,7 +13486,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LiDAR-derived Drainage Network for Calvert Island - British Columbia - Canada</t>
+          <t>Stream temperature time-series – Calvert Island – 2013 - 2019</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13502,12 +13504,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13526,16 +13528,16 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16, 51.41], [-127.88, 51.41], [-127.88, 51.73], [-128.16, 51.73], [-128.16, 51.41]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.25940955, 51.55841821], [-127.87488807, 51.55841821], [-127.87488807, 51.75224257], [-128.25940955, 51.75224257], [-128.25940955, 51.55841821]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -13545,12 +13547,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/vavm-b152</t>
+          <t>10.21966/7nb6-zk37</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW5MeGIydVA3U1VKdWo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFDT2lYSlBQZ0VNdDg</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -15009,12 +15011,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15024,7 +15026,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15042,7 +15044,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15062,20 +15064,20 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -15085,12 +15087,12 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/1.135248</t>
+          <t>10.21966/x6q2-me90</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -15100,7 +15102,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V134" t="n">
@@ -15119,12 +15121,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -15134,7 +15136,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -15152,7 +15154,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15172,20 +15174,20 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -15195,12 +15197,12 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>10.21966/x6q2-me90</t>
+          <t>10.21966/1.135248</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -15210,7 +15212,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="V135" t="n">
@@ -16661,12 +16663,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ca-cioos_cec3dcef-8dba-4d91-aee6-b60ce416497c</t>
+          <t>ca-cioos_c89e35df-8a16-4efc-ae29-15f4e3da8a55</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -16676,7 +16678,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Mussel Dynamics - Point Intercepts - BC Central Coast</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -16732,17 +16734,17 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>10.21966/ns9h-1126</t>
+          <t>10.21966/0yk3-9b74</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotaGdFmX3xEvWjXQA5</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-Motctf2E7ids9V-6Cfb</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
@@ -16752,7 +16754,7 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="V149" t="n">
@@ -16771,12 +16773,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ca-cioos_c89e35df-8a16-4efc-ae29-15f4e3da8a55</t>
+          <t>ca-cioos_cec3dcef-8dba-4d91-aee6-b60ce416497c</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -16786,7 +16788,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast</t>
+          <t>Mussel Dynamics - Point Intercepts - BC Central Coast</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -16842,17 +16844,17 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>10.21966/0yk3-9b74</t>
+          <t>10.21966/ns9h-1126</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-Motctf2E7ids9V-6Cfb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotaGdFmX3xEvWjXQA5</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
@@ -16862,7 +16864,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V150" t="n">
@@ -21717,7 +21719,9 @@
           <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
-      <c r="X194" t="inlineStr"/>
+      <c r="X194" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -31490,7 +31494,7 @@
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V283" t="n">
@@ -31501,9 +31505,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X283" t="n">
-        <v>1</v>
-      </c>
+      <c r="X283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -31602,7 +31604,7 @@
       </c>
       <c r="U284" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V284" t="n">
@@ -31613,9 +31615,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X284" t="n">
-        <v>1</v>
-      </c>
+      <c r="X284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -31714,7 +31714,7 @@
       </c>
       <c r="U285" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V285" t="n">
@@ -31725,9 +31725,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X285" t="n">
-        <v>1</v>
-      </c>
+      <c r="X285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31826,7 +31824,7 @@
       </c>
       <c r="U286" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V286" t="n">
@@ -31837,9 +31835,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X286" t="n">
-        <v>1</v>
-      </c>
+      <c r="X286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -31938,7 +31934,7 @@
       </c>
       <c r="U287" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V287" t="n">
@@ -31949,9 +31945,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X287" t="n">
-        <v>1</v>
-      </c>
+      <c r="X287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -32050,7 +32044,7 @@
       </c>
       <c r="U288" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V288" t="n">
@@ -32061,9 +32055,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X288" t="n">
-        <v>1</v>
-      </c>
+      <c r="X288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -32162,7 +32154,7 @@
       </c>
       <c r="U289" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V289" t="n">
@@ -32173,9 +32165,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X289" t="n">
-        <v>1</v>
-      </c>
+      <c r="X289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -32274,7 +32264,7 @@
       </c>
       <c r="U290" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V290" t="n">
@@ -32285,9 +32275,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X290" t="n">
-        <v>1</v>
-      </c>
+      <c r="X290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -32386,7 +32374,7 @@
       </c>
       <c r="U291" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V291" t="n">
@@ -32397,9 +32385,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X291" t="n">
-        <v>1</v>
-      </c>
+      <c r="X291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -32498,7 +32484,7 @@
       </c>
       <c r="U292" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V292" t="n">
@@ -32509,9 +32495,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X292" t="n">
-        <v>1</v>
-      </c>
+      <c r="X292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -32519,12 +32503,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>d320d90e-96bf-4993-81c5-f1f57886b0e6</t>
+          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ca-cioos_b922699f-69b6-4d63-b538-7c290086a408</t>
+          <t>ca-cioos_bea3da72-dafe-4e25-b5b2-0176e0ffba44</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -32534,7 +32518,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Quw'utsun/Xwulqw'selu River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Chemainus River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -32580,7 +32564,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.56201, 48.73508], [-123.59772, 48.75559], [-123.62127, 48.76514], [-123.63885, 48.77426], [-123.66935, 48.78033], [-123.67901, 48.75472], [-123.65155, 48.74322], [-123.63017, 48.7405], [-123.60792, 48.74289], [-123.56494, 48.72987], [-123.56179, 48.73529], [-123.56201, 48.73508]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.66843, 48.91641], [-123.6484, 48.90105], [-123.6554, 48.88016], [-123.6751, 48.87641], [-123.68894, 48.88178], [-123.68329, 48.89633], [-123.67928, 48.90316], [-123.67136, 48.91722], [-123.66848, 48.91635], [-123.66843, 48.91641]]]}</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
@@ -32595,12 +32579,12 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>10.21966/2ha7-9p26</t>
+          <t>10.21966/q2e0-j004</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpsCA3ycwZ7bFTDIQxh</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpszvIrt9OF8-BLQW2N</t>
         </is>
       </c>
       <c r="T293" t="inlineStr">
@@ -32610,7 +32594,7 @@
       </c>
       <c r="U293" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V293" t="n">
@@ -32621,9 +32605,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X293" t="n">
-        <v>1</v>
-      </c>
+      <c r="X293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -32631,12 +32613,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
+          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>ca-cioos_bea3da72-dafe-4e25-b5b2-0176e0ffba44</t>
+          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -32646,7 +32628,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Chemainus River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -32692,7 +32674,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.66843, 48.91641], [-123.6484, 48.90105], [-123.6554, 48.88016], [-123.6751, 48.87641], [-123.68894, 48.88178], [-123.68329, 48.89633], [-123.67928, 48.90316], [-123.67136, 48.91722], [-123.66848, 48.91635], [-123.66843, 48.91641]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
@@ -32707,12 +32689,12 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>10.21966/q2e0-j004</t>
+          <t>10.21966/hjkj-6611</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpszvIrt9OF8-BLQW2N</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
         </is>
       </c>
       <c r="T294" t="inlineStr">
@@ -32722,7 +32704,7 @@
       </c>
       <c r="U294" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V294" t="n">
@@ -32733,9 +32715,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X294" t="n">
-        <v>1</v>
-      </c>
+      <c r="X294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -32743,12 +32723,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
+          <t>4c7b7347-767d-45e4-b3ad-7e0133b31e1c</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
+          <t>ca-cioos_dce15b7b-3772-4106-ab20-c3979c4c3f57</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -32758,7 +32738,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Fulmore River - Shoal Creek Estuary Complex (Provisional)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -32804,7 +32784,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.08798, 50.4777], [-126.09599, 50.48418], [-126.09046, 50.50918], [-126.0647, 50.52425], [-125.99698, 50.53569], [-125.93459, 50.56717], [-125.93173, 50.56202], [-125.93764, 50.55458], [-125.91055, 50.55134], [-125.89853, 50.54943], [-125.90063, 50.54466], [-125.96416, 50.53989], [-125.98973, 50.52043], [-126.06566, 50.5067], [-126.08779, 50.47789], [-126.08798, 50.4777]]]}</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
@@ -32819,12 +32799,12 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>10.21966/hjkj-6611</t>
+          <t>10.21966/g1cn-xs92</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptdJ8iUmLeOrdmqzrQ</t>
         </is>
       </c>
       <c r="T295" t="inlineStr">
@@ -32834,7 +32814,7 @@
       </c>
       <c r="U295" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V295" t="n">
@@ -32845,9 +32825,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X295" t="n">
-        <v>1</v>
-      </c>
+      <c r="X295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -32855,12 +32833,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>4c7b7347-767d-45e4-b3ad-7e0133b31e1c</t>
+          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>ca-cioos_dce15b7b-3772-4106-ab20-c3979c4c3f57</t>
+          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -32870,7 +32848,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Fulmore River - Shoal Creek Estuary Complex (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -32916,7 +32894,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.08798, 50.4777], [-126.09599, 50.48418], [-126.09046, 50.50918], [-126.0647, 50.52425], [-125.99698, 50.53569], [-125.93459, 50.56717], [-125.93173, 50.56202], [-125.93764, 50.55458], [-125.91055, 50.55134], [-125.89853, 50.54943], [-125.90063, 50.54466], [-125.96416, 50.53989], [-125.98973, 50.52043], [-126.06566, 50.5067], [-126.08779, 50.47789], [-126.08798, 50.4777]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
@@ -32931,12 +32909,12 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>10.21966/g1cn-xs92</t>
+          <t>10.21966/npe4-3036</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptdJ8iUmLeOrdmqzrQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
         </is>
       </c>
       <c r="T296" t="inlineStr">
@@ -32946,7 +32924,7 @@
       </c>
       <c r="U296" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V296" t="n">
@@ -32957,9 +32935,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X296" t="n">
-        <v>1</v>
-      </c>
+      <c r="X296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -32967,12 +32943,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
+          <t>35245eae-e508-47da-bcf7-54346cda086a</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
+          <t>ca-cioos_e9b72149-8cf1-4000-ae3e-6b29ad60b078</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -32982,7 +32958,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Malksope River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -33028,7 +33004,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.46569, 50.12556], [-127.45723, 50.13142], [-127.43281, 50.13338], [-127.42845, 50.13765], [-127.41181, 50.14408], [-127.40973, 50.14233], [-127.41999, 50.13627], [-127.41803, 50.13195], [-127.43106, 50.12796], [-127.46545, 50.12446], [-127.46569, 50.12548], [-127.46569, 50.12556]]]}</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
@@ -33043,12 +33019,12 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>10.21966/npe4-3036</t>
+          <t>10.21966/21sf-ey03</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq77iyWJfPg4z-FvOSb</t>
         </is>
       </c>
       <c r="T297" t="inlineStr">
@@ -33058,7 +33034,7 @@
       </c>
       <c r="U297" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V297" t="n">
@@ -33069,9 +33045,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X297" t="n">
-        <v>1</v>
-      </c>
+      <c r="X297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -33079,12 +33053,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>35245eae-e508-47da-bcf7-54346cda086a</t>
+          <t>5177d019-598e-4415-b778-9688403652c8</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>ca-cioos_e9b72149-8cf1-4000-ae3e-6b29ad60b078</t>
+          <t>ca-cioos_ed84df74-5a2d-4a7d-87c8-a7b93f11088e</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -33094,7 +33068,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Malksope River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Nalaxdlala River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -33140,7 +33114,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.46569, 50.12556], [-127.45723, 50.13142], [-127.43281, 50.13338], [-127.42845, 50.13765], [-127.41181, 50.14408], [-127.40973, 50.14233], [-127.41999, 50.13627], [-127.41803, 50.13195], [-127.43106, 50.12796], [-127.46545, 50.12446], [-127.46569, 50.12548], [-127.46569, 50.12556]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.9489, 50.70902], [-125.9696, 50.70291], [-126.00938, 50.69118], [-126.00108, 50.66848], [-125.98257, 50.68374], [-125.98152, 50.69271], [-125.95462, 50.70263], [-125.94785, 50.70768], [-125.9489, 50.70911], [-125.9489, 50.70902]]]}</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
@@ -33155,12 +33129,12 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>10.21966/21sf-ey03</t>
+          <t>10.21966/4krv-aw23</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq77iyWJfPg4z-FvOSb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptbxmpkBsfyWWfSxOJ</t>
         </is>
       </c>
       <c r="T298" t="inlineStr">
@@ -33170,7 +33144,7 @@
       </c>
       <c r="U298" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V298" t="n">
@@ -33181,9 +33155,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X298" t="n">
-        <v>1</v>
-      </c>
+      <c r="X298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -33191,12 +33163,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>5177d019-598e-4415-b778-9688403652c8</t>
+          <t>d320d90e-96bf-4993-81c5-f1f57886b0e6</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>ca-cioos_ed84df74-5a2d-4a7d-87c8-a7b93f11088e</t>
+          <t>ca-cioos_b922699f-69b6-4d63-b538-7c290086a408</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -33206,7 +33178,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Nalaxdlala River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Quw'utsun/Xwulqw'selu River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -33252,7 +33224,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.9489, 50.70902], [-125.9696, 50.70291], [-126.00938, 50.69118], [-126.00108, 50.66848], [-125.98257, 50.68374], [-125.98152, 50.69271], [-125.95462, 50.70263], [-125.94785, 50.70768], [-125.9489, 50.70911], [-125.9489, 50.70902]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.56201, 48.73508], [-123.59772, 48.75559], [-123.62127, 48.76514], [-123.63885, 48.77426], [-123.66935, 48.78033], [-123.67901, 48.75472], [-123.65155, 48.74322], [-123.63017, 48.7405], [-123.60792, 48.74289], [-123.56494, 48.72987], [-123.56179, 48.73529], [-123.56201, 48.73508]]]}</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
@@ -33267,22 +33239,22 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>10.21966/4krv-aw23</t>
+          <t>10.21966/2ha7-9p26</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptbxmpkBsfyWWfSxOJ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpsCA3ycwZ7bFTDIQxh</t>
         </is>
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V299" t="n">
@@ -33293,9 +33265,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X299" t="n">
-        <v>1</v>
-      </c>
+      <c r="X299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -33504,7 +33474,7 @@
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V301" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -5557,12 +5557,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
+          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
+          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5628,17 +5628,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10.21966/zs6a-j496</t>
+          <t>10.21966/1.715784</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V48" t="n">
@@ -5659,7 +5659,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5667,12 +5669,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
+          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5682,7 +5684,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5700,7 +5702,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5728,7 +5730,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5738,17 +5740,17 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10.21966/1.715740</t>
+          <t>10.21966/zs6a-j496</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -5758,7 +5760,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V49" t="n">
@@ -5777,12 +5779,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
+          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5792,7 +5794,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
+          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5838,7 +5840,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5848,17 +5850,17 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10.21966/1.715784</t>
+          <t>10.21966/1.715740</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -5868,7 +5870,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V50" t="n">
@@ -9067,12 +9069,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
+          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9082,7 +9084,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9100,7 +9102,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9128,12 +9130,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -9143,12 +9145,12 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>10.21966/wfcv-n753</t>
+          <t>10.21966/eysg-7a26</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -9177,12 +9179,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
+          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9192,7 +9194,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
+          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9210,7 +9212,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9238,12 +9240,12 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -9253,12 +9255,12 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>10.21966/eysg-7a26</t>
+          <t>10.21966/wfcv-n753</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -11599,12 +11601,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ca-cioos_7de69ca8-b3f3-4761-b441-dfc9e63b1fbc</t>
+          <t>ca-cioos_7e0f0bbc-507a-4ca0-bafc-1cc3e56db028</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -11614,7 +11616,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rocky Intertidal RPAS Mapping Project - BC Central Coast - Canada</t>
+          <t>Hakai physical plan and utility lines – Calvert Island Field Station - 2006</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11632,7 +11634,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -11656,16 +11658,16 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6286, 48.1332], [-122.8941, 48.1332], [-122.8941, 51.9689], [-128.6286, 51.9689], [-128.6286, 48.1332]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13541603114572, 51.65216411387959], [-128.12786293055976, 51.65216411387959], [-128.12786293055976, 51.6557318761607], [-128.13541603114572, 51.6557318761607], [-128.13541603114572, 51.65216411387959]]]}</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -11675,12 +11677,12 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>10.21966/mc7v-dx06</t>
+          <t>10.21966/3yew-5r94</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBVWDBQSFpnWjBBS0Q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU9IR0RmSHlkRW1sd2k</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -11690,7 +11692,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V103" t="n">
@@ -11709,12 +11711,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ca-cioos_7e0f0bbc-507a-4ca0-bafc-1cc3e56db028</t>
+          <t>ca-cioos_7de69ca8-b3f3-4761-b441-dfc9e63b1fbc</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11724,7 +11726,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hakai physical plan and utility lines – Calvert Island Field Station - 2006</t>
+          <t>Rocky Intertidal RPAS Mapping Project - BC Central Coast - Canada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11742,7 +11744,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11766,16 +11768,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13541603114572, 51.65216411387959], [-128.12786293055976, 51.65216411387959], [-128.12786293055976, 51.6557318761607], [-128.13541603114572, 51.6557318761607], [-128.13541603114572, 51.65216411387959]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6286, 48.1332], [-122.8941, 48.1332], [-122.8941, 51.9689], [-128.6286, 51.9689], [-128.6286, 48.1332]]]}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11785,12 +11787,12 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>10.21966/3yew-5r94</t>
+          <t>10.21966/mc7v-dx06</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU9IR0RmSHlkRW1sd2k</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBVWDBQSFpnWjBBS0Q</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11800,7 +11802,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V104" t="n">
@@ -13029,12 +13031,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -13044,7 +13046,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -13067,7 +13069,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -13086,11 +13088,11 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13105,12 +13107,12 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -13120,7 +13122,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V116" t="n">
@@ -13128,7 +13130,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -13139,12 +13141,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -13154,7 +13156,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -13177,7 +13179,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -13196,11 +13198,11 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13215,12 +13217,12 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -13230,7 +13232,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V117" t="n">
@@ -13238,7 +13240,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -13359,12 +13361,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>e1b86825-d43b-47e1-bf45-ab791f44772d</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ca-cioos_0e446321-34f3-4d5a-8c7d-79c89eb76373</t>
+          <t>ca-cioos_0e4f324c-6498-4c89-9e19-f2f9f474a1df</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -13374,7 +13376,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Stream temperature time-series – Calvert Island – 2013 - 2019</t>
+          <t>LiDAR-derived Drainage Network for Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -13392,12 +13394,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -13416,16 +13418,16 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.25940955, 51.55841821], [-127.87488807, 51.55841821], [-127.87488807, 51.75224257], [-128.25940955, 51.75224257], [-128.25940955, 51.55841821]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16, 51.41], [-127.88, 51.41], [-127.88, 51.73], [-128.16, 51.73], [-128.16, 51.41]]]}</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -13435,12 +13437,12 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>10.21966/7nb6-zk37</t>
+          <t>10.21966/vavm-b152</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFDT2lYSlBQZ0VNdDg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW5MeGIydVA3U1VKdWo</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -13469,12 +13471,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>e1b86825-d43b-47e1-bf45-ab791f44772d</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_0e4f324c-6498-4c89-9e19-f2f9f474a1df</t>
+          <t>ca-cioos_0e446321-34f3-4d5a-8c7d-79c89eb76373</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13484,7 +13486,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LiDAR-derived Drainage Network for Calvert Island - British Columbia - Canada</t>
+          <t>Stream temperature time-series – Calvert Island – 2013 - 2019</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13502,12 +13504,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13526,16 +13528,16 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16, 51.41], [-127.88, 51.41], [-127.88, 51.73], [-128.16, 51.73], [-128.16, 51.41]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.25940955, 51.55841821], [-127.87488807, 51.55841821], [-127.87488807, 51.75224257], [-128.25940955, 51.75224257], [-128.25940955, 51.55841821]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -13545,12 +13547,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/vavm-b152</t>
+          <t>10.21966/7nb6-zk37</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW5MeGIydVA3U1VKdWo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFDT2lYSlBQZ0VNdDg</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -15111,7 +15113,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr"/>
+      <c r="X134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -20615,7 +20619,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X184" t="inlineStr"/>
+      <c r="X184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -31183,12 +31189,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
+          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
+          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -31198,17 +31204,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
+          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H281" t="b">
@@ -31221,7 +31227,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -31244,23 +31250,27 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '600.0'}]</t>
+          <t>[{'max': '2.5', 'min': '2.5'}]</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R281" t="inlineStr"/>
+          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>10.21966/rrzq-yw32</t>
+        </is>
+      </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
         </is>
       </c>
       <c r="T281" t="inlineStr">
@@ -31270,14 +31280,18 @@
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="V281" t="inlineStr"/>
-      <c r="W281" t="inlineStr"/>
-      <c r="X281" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="V281" t="n">
+        <v>0</v>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31285,12 +31299,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
+          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
+          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -31300,17 +31314,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
+          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H282" t="b">
@@ -31323,7 +31337,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -31346,27 +31360,23 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>[{'max': '2.5', 'min': '2.5'}]</t>
+          <t>[{'max': '0.0', 'min': '600.0'}]</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R282" t="inlineStr">
-        <is>
-          <t>10.21966/rrzq-yw32</t>
-        </is>
-      </c>
+          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
         </is>
       </c>
       <c r="T282" t="inlineStr">
@@ -31376,19 +31386,13 @@
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="V282" t="n">
-        <v>0</v>
-      </c>
-      <c r="W282" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr"/>
+      <c r="W282" t="inlineStr"/>
       <c r="X282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -5557,12 +5557,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
+          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5628,17 +5628,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10.21966/1.715784</t>
+          <t>10.21966/zs6a-j496</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V48" t="n">
@@ -5659,9 +5659,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X48" t="n">
-        <v>1</v>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5669,12 +5667,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
+          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5684,7 +5682,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
+          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5702,7 +5700,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5730,7 +5728,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5740,17 +5738,17 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10.21966/zs6a-j496</t>
+          <t>10.21966/1.715740</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -5760,7 +5758,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V49" t="n">
@@ -5779,12 +5777,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
+          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5794,7 +5792,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
+          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5840,7 +5838,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5850,17 +5848,17 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10.21966/1.715740</t>
+          <t>10.21966/1.715784</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -5870,7 +5868,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V50" t="n">
@@ -6109,12 +6107,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6124,7 +6122,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6170,7 +6168,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6180,17 +6178,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6200,7 +6198,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -6219,12 +6217,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6234,7 +6232,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6280,7 +6278,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6290,17 +6288,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6310,7 +6308,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -9069,12 +9067,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
+          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9084,7 +9082,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
+          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9102,7 +9100,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9130,12 +9128,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -9145,12 +9143,12 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>10.21966/eysg-7a26</t>
+          <t>10.21966/wfcv-n753</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -9179,12 +9177,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
+          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9194,7 +9192,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9212,7 +9210,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9240,12 +9238,12 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -9255,12 +9253,12 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>10.21966/wfcv-n753</t>
+          <t>10.21966/eysg-7a26</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -11601,12 +11599,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ca-cioos_7e0f0bbc-507a-4ca0-bafc-1cc3e56db028</t>
+          <t>ca-cioos_7de69ca8-b3f3-4761-b441-dfc9e63b1fbc</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -11616,7 +11614,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hakai physical plan and utility lines – Calvert Island Field Station - 2006</t>
+          <t>Rocky Intertidal RPAS Mapping Project - BC Central Coast - Canada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11634,7 +11632,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -11658,16 +11656,16 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13541603114572, 51.65216411387959], [-128.12786293055976, 51.65216411387959], [-128.12786293055976, 51.6557318761607], [-128.13541603114572, 51.6557318761607], [-128.13541603114572, 51.65216411387959]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6286, 48.1332], [-122.8941, 48.1332], [-122.8941, 51.9689], [-128.6286, 51.9689], [-128.6286, 48.1332]]]}</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -11677,12 +11675,12 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>10.21966/3yew-5r94</t>
+          <t>10.21966/mc7v-dx06</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU9IR0RmSHlkRW1sd2k</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBVWDBQSFpnWjBBS0Q</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -11692,7 +11690,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V103" t="n">
@@ -11711,12 +11709,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ca-cioos_7de69ca8-b3f3-4761-b441-dfc9e63b1fbc</t>
+          <t>ca-cioos_7e0f0bbc-507a-4ca0-bafc-1cc3e56db028</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11726,7 +11724,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rocky Intertidal RPAS Mapping Project - BC Central Coast - Canada</t>
+          <t>Hakai physical plan and utility lines – Calvert Island Field Station - 2006</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11744,7 +11742,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11768,16 +11766,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6286, 48.1332], [-122.8941, 48.1332], [-122.8941, 51.9689], [-128.6286, 51.9689], [-128.6286, 48.1332]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13541603114572, 51.65216411387959], [-128.12786293055976, 51.65216411387959], [-128.12786293055976, 51.6557318761607], [-128.13541603114572, 51.6557318761607], [-128.13541603114572, 51.65216411387959]]]}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11787,12 +11785,12 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>10.21966/mc7v-dx06</t>
+          <t>10.21966/3yew-5r94</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBVWDBQSFpnWjBBS0Q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU9IR0RmSHlkRW1sd2k</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11802,7 +11800,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V104" t="n">
@@ -13031,12 +13029,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -13046,7 +13044,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -13069,7 +13067,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -13088,11 +13086,11 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13107,12 +13105,12 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -13122,7 +13120,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V116" t="n">
@@ -13130,7 +13128,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -13141,12 +13139,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -13156,7 +13154,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -13179,7 +13177,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -13198,11 +13196,11 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13217,12 +13215,12 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -13232,7 +13230,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V117" t="n">
@@ -13240,7 +13238,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -15113,9 +15111,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X134" t="n">
-        <v>1</v>
-      </c>
+      <c r="X134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -20619,9 +20615,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X184" t="n">
-        <v>1</v>
-      </c>
+      <c r="X184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X302"/>
+  <dimension ref="A1:X301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V32" t="n">
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
+          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
+          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5738,17 +5738,17 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10.21966/1.715740</t>
+          <t>10.21966/1.715784</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V49" t="n">
@@ -5769,7 +5769,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5777,12 +5779,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
+          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5792,7 +5794,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
+          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5838,7 +5840,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5848,17 +5850,17 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10.21966/1.715784</t>
+          <t>10.21966/1.715740</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -5868,7 +5870,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V50" t="n">
@@ -6107,12 +6109,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6122,7 +6124,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6168,7 +6170,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6178,17 +6180,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6198,7 +6200,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -6217,12 +6219,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6232,7 +6234,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6278,7 +6280,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6288,17 +6290,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6308,7 +6310,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -11338,7 +11340,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -11358,7 +11360,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V100" t="n">
@@ -11369,9 +11371,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X100" t="n">
-        <v>1</v>
-      </c>
+      <c r="X100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -15009,12 +15009,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15062,20 +15062,20 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -15085,12 +15085,12 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/1.135248</t>
+          <t>10.21966/x6q2-me90</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V134" t="n">
@@ -15119,12 +15119,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15172,20 +15172,20 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -15195,12 +15195,12 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>10.21966/x6q2-me90</t>
+          <t>10.21966/1.135248</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="V135" t="n">
@@ -19392,7 +19392,7 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V173" t="n">
@@ -19403,9 +19403,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X173" t="n">
-        <v>1</v>
-      </c>
+      <c r="X173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20714,7 +20712,7 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V185" t="n">
@@ -20725,9 +20723,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X185" t="n">
-        <v>1</v>
-      </c>
+      <c r="X185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21505,12 +21501,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
+          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -21520,7 +21516,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
+          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -21562,16 +21558,16 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -21581,12 +21577,12 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>10.21966/thq7-0g08</t>
+          <t>10.21966/e4b8-vp48</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
@@ -21596,15 +21592,15 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
@@ -21615,12 +21611,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
+          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -21630,7 +21626,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -21672,16 +21668,16 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -21691,12 +21687,12 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>10.21966/e4b8-vp48</t>
+          <t>10.21966/bzr6-er66</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
@@ -21706,15 +21702,15 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
@@ -21725,12 +21721,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
+          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -21740,7 +21736,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -21758,12 +21754,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -21782,41 +21778,41 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+          <t>[{'max': '6.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>10.21966/bzr6-er66</t>
+          <t>10.21966/jv5k-3k59</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nh8VlPQ_m681tso87Gd</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="V195" t="n">
@@ -21835,12 +21831,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
+          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -21850,7 +21846,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -21868,12 +21864,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -21892,41 +21888,41 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '1.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>10.21966/jv5k-3k59</t>
+          <t>10.21966/8mpe-h081</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nh8VlPQ_m681tso87Gd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUR4a1V0N1UxYTc2U3Q</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V196" t="n">
@@ -21945,12 +21941,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
+          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -21960,12 +21956,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
+          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>document</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -21978,7 +21974,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -21998,45 +21994,45 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Hakai Geospatial</t>
         </is>
       </c>
       <c r="N197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>10.21966/8mpe-h081</t>
+          <t>10.21966/xp9x-m243</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUR4a1V0N1UxYTc2U3Q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NTLT7n49Ox3SnVoy6nW</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="V197" t="n">
@@ -22055,12 +22051,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
+          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -22070,12 +22066,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
+          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>document</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -22088,7 +22084,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -22108,7 +22104,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N198" t="n">
@@ -22116,12 +22112,12 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
@@ -22131,22 +22127,22 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>10.21966/xp9x-m243</t>
+          <t>10.21966/qpe8-ay93</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NTLT7n49Ox3SnVoy6nW</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpurN_vwkhOgSJmgBh9</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V198" t="n">
@@ -22165,12 +22161,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
+          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -22180,7 +22176,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
+          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -22198,12 +22194,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -22226,37 +22222,37 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
+          <t>[{'max': '75.0', 'min': '15.0'}]</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>10.21966/qpe8-ay93</t>
+          <t>10.21966/fbv4-th96</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpurN_vwkhOgSJmgBh9</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-O26fyGiVXoF__M22UrP</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="V199" t="n">
@@ -22275,12 +22271,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
+          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -22290,7 +22286,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
+          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -22308,7 +22304,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -22336,37 +22332,37 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>[{'max': '75.0', 'min': '15.0'}]</t>
+          <t>[{'max': '2.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>10.21966/fbv4-th96</t>
+          <t>10.21966/36hp-7f40</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-O26fyGiVXoF__M22UrP</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-N1KAki3SSBEw0aHCoSv</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V200" t="n">
@@ -22385,12 +22381,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
+          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -22400,7 +22396,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
+          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -22418,12 +22414,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -22446,37 +22442,37 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>[{'max': '2.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>10.21966/36hp-7f40</t>
+          <t>10.21966/wxph-tz51</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-N1KAki3SSBEw0aHCoSv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKOQlOxJdTg_BFOoXb</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V201" t="n">
@@ -22495,12 +22491,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
+          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -22510,7 +22506,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
+          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -22528,12 +22524,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -22556,45 +22552,45 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
+          <t>[{'max': '0.5', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>10.21966/wxph-tz51</t>
+          <t>10.21966/4kr2-jc55</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKOQlOxJdTg_BFOoXb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NH0r8ddHNhVJ5bXkyqR</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="V202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
@@ -22605,12 +22601,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
+          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -22620,7 +22616,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
+          <t>Phytoplankton Pigment Time Series from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -22638,7 +22634,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -22666,45 +22662,45 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>[{'max': '0.5', 'min': '0.5'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>10.21966/4kr2-jc55</t>
+          <t>10.21966/bw2d-tg65</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NH0r8ddHNhVJ5bXkyqR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-O25qzW3OpioeACGpRHl</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
@@ -22715,12 +22711,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
+          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -22730,7 +22726,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Phytoplankton Pigment Time Series from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
+          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -22748,12 +22744,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -22768,7 +22764,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N204" t="n">
@@ -22776,37 +22772,37 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>10.21966/bw2d-tg65</t>
+          <t>10.21966/pvy6-nw38</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-O25qzW3OpioeACGpRHl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O0G3gSlISPfB-f0u3Zz</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="V204" t="n">
@@ -22825,12 +22821,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
+          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -22840,7 +22836,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -22858,7 +22854,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -22878,7 +22874,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N205" t="n">
@@ -22886,48 +22882,40 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
-        </is>
-      </c>
-      <c r="R205" t="inlineStr">
-        <is>
-          <t>10.21966/pvy6-nw38</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O0G3gSlISPfB-f0u3Zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OFhFpUJDNDF0hlFiGUV</t>
         </is>
       </c>
       <c r="T205" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
-        </is>
-      </c>
-      <c r="V205" t="n">
-        <v>0</v>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr"/>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr"/>
+      <c r="W205" t="inlineStr"/>
+      <c r="X205" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22935,12 +22923,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
+          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -22950,7 +22938,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
+          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -22968,7 +22956,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -22996,12 +22984,12 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '254.0', 'min': '61.0'}]</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
@@ -23009,27 +22997,35 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R206" t="inlineStr"/>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>10.21966/zfxe-rd73</t>
+        </is>
+      </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OFhFpUJDNDF0hlFiGUV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCe-GBA4i93dk_I9uOR</t>
         </is>
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr"/>
-      <c r="W206" t="inlineStr"/>
-      <c r="X206" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="V206" t="n">
+        <v>0</v>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23037,12 +23033,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
+          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -23052,7 +23048,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
+          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -23070,12 +23066,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -23098,37 +23094,37 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>[{'max': '254.0', 'min': '61.0'}]</t>
+          <t>[{'max': '15.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>10.21966/zfxe-rd73</t>
+          <t>10.21966/jj9p-d309</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCe-GBA4i93dk_I9uOR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtF5vh1GUMdwtJdYjoJ</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V207" t="n">
@@ -23147,12 +23143,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
+          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -23162,7 +23158,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
+          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -23180,12 +23176,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -23208,45 +23204,45 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>[{'max': '15.0', 'min': '0.0'}]</t>
+          <t>[{'max': '105.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>10.21966/jj9p-d309</t>
+          <t>10.21966/529y-sh57</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtF5vh1GUMdwtJdYjoJ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG736nDr1-1b51V4ZIc</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
@@ -23257,12 +23253,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
+          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
+          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -23272,7 +23268,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
+          <t>Understory kelp biomass data from BC Central Coast</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -23290,12 +23286,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -23318,45 +23314,45 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>[{'max': '105.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>10.21966/529y-sh57</t>
+          <t>10.21966/wmsy-5g39</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG736nDr1-1b51V4ZIc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtGQFN6AV5bNminNtYH</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
@@ -23367,12 +23363,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
+          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -23382,7 +23378,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Understory kelp biomass data from BC Central Coast</t>
+          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -23400,12 +23396,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -23428,37 +23424,37 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>10.21966/wmsy-5g39</t>
+          <t>10.21966/8yp1-7m94</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtGQFN6AV5bNminNtYH</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKR1jead4rZb1ooVa6</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V210" t="n">
@@ -23477,12 +23473,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
+          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -23492,7 +23488,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
+          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -23510,7 +23506,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -23538,12 +23534,12 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
@@ -23553,22 +23549,22 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>10.21966/8yp1-7m94</t>
+          <t>10.21966/g64t-ec45</t>
         </is>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKR1jead4rZb1ooVa6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICfZ5e-2vhf5NUtDZS</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="V211" t="n">
@@ -23587,12 +23583,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
+          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
+          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -23602,7 +23598,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
+          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -23640,7 +23636,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N212" t="n">
@@ -23648,12 +23644,12 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -23663,12 +23659,12 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>10.21966/g64t-ec45</t>
+          <t>10.21966/0ydj-0t79</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICfZ5e-2vhf5NUtDZS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICMGpnoARQcIltW087</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
@@ -23697,12 +23693,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
+          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -23712,12 +23708,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
+          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -23750,7 +23746,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N213" t="n">
@@ -23758,12 +23754,12 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -23773,22 +23769,22 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>10.21966/0ydj-0t79</t>
+          <t>10.21966/6x1v-1v62</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICMGpnoARQcIltW087</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OIMCEnEEW63IyHyYZOM</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V213" t="n">
@@ -23807,12 +23803,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
+          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -23822,12 +23818,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
+          <t>Calliarthron 2023 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -23840,7 +23836,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -23860,7 +23856,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N214" t="n">
@@ -23868,37 +23864,37 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>10.21966/6x1v-1v62</t>
+          <t>10.21966/7nwn-bj60</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OIMCEnEEW63IyHyYZOM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O6XAwxhj0r9Xs-V2QSA</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="V214" t="n">
@@ -23909,7 +23905,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X214" t="inlineStr"/>
+      <c r="X214" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23917,12 +23915,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
+          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -23932,7 +23930,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Calliarthron 2023 Experiment - Environmental Data</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -23950,7 +23948,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -23970,7 +23968,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N215" t="n">
@@ -23978,27 +23976,27 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>10.21966/7nwn-bj60</t>
+          <t>10.21966/ks82-th39</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O6XAwxhj0r9Xs-V2QSA</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP2QaXeKeZ30lz51gEE</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
@@ -24008,7 +24006,7 @@
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V215" t="n">
@@ -24019,9 +24017,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X215" t="n">
-        <v>1</v>
-      </c>
+      <c r="X215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24029,12 +24025,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
+          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -24044,7 +24040,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -24062,7 +24058,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -24090,12 +24086,12 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -24105,12 +24101,12 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>10.21966/ks82-th39</t>
+          <t>10.21966/n3b4-d226</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP2QaXeKeZ30lz51gEE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NM0zdQjdjAMBZ4cN8ou</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
@@ -24128,7 +24124,7 @@
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="X216" t="inlineStr"/>
@@ -24139,12 +24135,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
+          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -24154,7 +24150,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
+          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -24200,12 +24196,12 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
@@ -24215,22 +24211,22 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>10.21966/n3b4-d226</t>
+          <t>10.21966/p6jv-pe95</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NM0zdQjdjAMBZ4cN8ou</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP86akjVj471Wit4O2y</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V217" t="n">
@@ -24238,7 +24234,7 @@
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X217" t="inlineStr"/>
@@ -24249,12 +24245,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
+          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -24264,7 +24260,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
+          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -24282,7 +24278,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -24302,7 +24298,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N218" t="n">
@@ -24310,37 +24306,37 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>inorganicCarbon, other</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>10.21966/p6jv-pe95</t>
+          <t>10.21966/q1m4-pz94</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP86akjVj471Wit4O2y</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OMsFWHXIwEWiFjwQeEo</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="V218" t="n">
@@ -24351,7 +24347,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X218" t="inlineStr"/>
+      <c r="X218" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24359,12 +24357,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
+          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -24374,7 +24372,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Sea Stars 2024 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -24412,7 +24410,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N219" t="n">
@@ -24435,12 +24433,12 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>10.21966/q1m4-pz94</t>
+          <t>10.21966/jkf5-ss08</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OMsFWHXIwEWiFjwQeEo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OIMW8OO0buhOm_kHuIz</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
@@ -24450,7 +24448,7 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="V219" t="n">
@@ -24471,12 +24469,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
+          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -24486,7 +24484,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Sea Stars 2024 Experiment - Environmental Data</t>
+          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -24504,7 +24502,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -24524,15 +24522,15 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Gulf Islands National Park Reserve</t>
         </is>
       </c>
       <c r="N220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24542,27 +24540,27 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>inorganicCarbon, other</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>10.21966/jkf5-ss08</t>
+          <t>10.21966/x3jm-p494</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OIMW8OO0buhOm_kHuIz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OUG8anVj4yBJDEHy6Wj</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V220" t="n">
@@ -24573,9 +24571,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X220" t="n">
-        <v>1</v>
-      </c>
+      <c r="X220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24583,12 +24579,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
+          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -24598,7 +24594,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
+          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -24616,12 +24612,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -24636,7 +24632,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Gulf Islands National Park Reserve</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N221" t="n">
@@ -24644,48 +24640,50 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '350.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>10.21966/x3jm-p494</t>
+          <t>10.21966/g7zf-1v08</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OUG8anVj4yBJDEHy6Wj</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-ODO1YbIGbR3Rd8hvLxT</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="V221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr"/>
+          <t>[{'year': '2026', 'total': 2}]</t>
+        </is>
+      </c>
+      <c r="X221" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24693,12 +24691,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
+          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -24708,7 +24706,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
+          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -24750,7 +24748,7 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -24769,12 +24767,12 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>10.21966/g7zf-1v08</t>
+          <t>10.21966/tcp2-mm86</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-ODO1YbIGbR3Rd8hvLxT</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NZb1YZT9Xtbc9Cp9Jc3OtSLRffT2/-OQtxgedRzyaVsL4bWUx</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
@@ -24784,7 +24782,7 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V222" t="n">
@@ -24795,9 +24793,7 @@
           <t>[{'year': '2026', 'total': 2}]</t>
         </is>
       </c>
-      <c r="X222" t="n">
-        <v>1</v>
-      </c>
+      <c r="X222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24805,12 +24801,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
+          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -24820,7 +24816,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -24838,12 +24834,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -24866,32 +24862,32 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>[{'max': '350.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>zooplanktonBiomassAndDiversity</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>10.21966/tcp2-mm86</t>
+          <t>10.21966/w08z-zk15</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NZb1YZT9Xtbc9Cp9Jc3OtSLRffT2/-OQtxgedRzyaVsL4bWUx</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPFZem68YnizN7L7l</t>
         </is>
       </c>
       <c r="T223" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="U223" t="inlineStr">
@@ -24900,11 +24896,11 @@
         </is>
       </c>
       <c r="V223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 2}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X223" t="inlineStr"/>
@@ -24915,12 +24911,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
+          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
+          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -24930,7 +24926,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -24948,7 +24944,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -24976,7 +24972,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -24991,12 +24987,12 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>10.21966/w08z-zk15</t>
+          <t>10.21966/kqzp-f639</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPFZem68YnizN7L7l</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NbzgAmVWcvz-_SOMA0E</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
@@ -25025,12 +25021,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
+          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -25040,7 +25036,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -25058,7 +25054,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -25086,7 +25082,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -25101,12 +25097,12 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>10.21966/kqzp-f639</t>
+          <t>10.21966/qs1b-g693</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NbzgAmVWcvz-_SOMA0E</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-O8Dvx_fnz1WMY_Wetch</t>
         </is>
       </c>
       <c r="T225" t="inlineStr">
@@ -25116,7 +25112,7 @@
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="V225" t="n">
@@ -25135,12 +25131,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
+          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -25150,7 +25146,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
+          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -25168,12 +25164,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -25188,7 +25184,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N226" t="n">
@@ -25196,7 +25192,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -25211,30 +25207,30 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>10.21966/qs1b-g693</t>
+          <t>10.21966/9cbv-ra30</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-O8Dvx_fnz1WMY_Wetch</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OVIwXhdGT9n7FV0wmyz</t>
         </is>
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="V226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="X226" t="inlineStr"/>
@@ -25245,12 +25241,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
+          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -25260,7 +25256,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
+          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -25278,12 +25274,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Genomics, Nearshore, Oceanography</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -25298,53 +25294,53 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N227" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>10.21966/9cbv-ra30</t>
+          <t>10.21966/8sgn-jg38</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OVIwXhdGT9n7FV0wmyz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-Nd0YqVrleM4mMLlJDSU</t>
         </is>
       </c>
       <c r="T227" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X227" t="inlineStr"/>
@@ -25355,12 +25351,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
+          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -25370,7 +25366,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
+          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -25388,7 +25384,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore, Oceanography</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -25412,41 +25408,41 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '60.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>10.21966/8sgn-jg38</t>
+          <t>10.21966/vdyq-r660</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-Nd0YqVrleM4mMLlJDSU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORCQx4QHUuJ1NV1SEig</t>
         </is>
       </c>
       <c r="T228" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V228" t="n">
@@ -25465,12 +25461,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
+          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -25480,7 +25476,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
+          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -25498,7 +25494,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Genomics, Nearshore</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -25522,41 +25518,41 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>[{'max': '60.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>10.21966/vdyq-r660</t>
+          <t>10.21966/4dvn-5y90</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORCQx4QHUuJ1NV1SEig</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/24mf0TP0vkh6bmNOOA3ynoTFPNJ2/-OX0Xm6VoYH22oc68Jfp</t>
         </is>
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V229" t="n">
@@ -25567,9 +25563,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X229" t="n">
-        <v>1</v>
-      </c>
+      <c r="X229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25577,12 +25571,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
+          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -25592,7 +25586,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -25610,7 +25604,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -25634,11 +25628,11 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25648,27 +25642,27 @@
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>microbeBiomassAndDiversity</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>10.21966/4dvn-5y90</t>
+          <t>10.21966/m93t-4181</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/24mf0TP0vkh6bmNOOA3ynoTFPNJ2/-OX0Xm6VoYH22oc68Jfp</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPEiAvbPxw16A-L6I</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V230" t="n">
@@ -25687,12 +25681,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
+          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -25702,7 +25696,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -25748,7 +25742,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -25763,12 +25757,12 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>10.21966/m93t-4181</t>
+          <t>10.21966/ntdg-e790</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPEiAvbPxw16A-L6I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8raBb8T2xZJ-oRzesS</t>
         </is>
       </c>
       <c r="T231" t="inlineStr">
@@ -25778,7 +25772,7 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V231" t="n">
@@ -25797,12 +25791,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
+          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -25812,7 +25806,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
+          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -25822,7 +25816,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H232" t="b">
@@ -25830,7 +25824,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -25858,50 +25852,48 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '475.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>10.21966/ntdg-e790</t>
+          <t>10.21966/0xex-r023</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8raBb8T2xZJ-oRzesS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OdPFhWCkXwvqjCqum30</t>
         </is>
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="V232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X232" t="n">
-        <v>1</v>
-      </c>
+          <t>[{'year': '2026', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25909,12 +25901,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
+          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -25924,7 +25916,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
+          <t>Gitga'at Territory Coastal Mapping Project</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -25942,12 +25934,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -25970,12 +25962,12 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>[{'max': '475.0', 'min': '0.0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
@@ -25985,12 +25977,12 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>10.21966/0xex-r023</t>
+          <t>10.21966/2aap-hn61</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OdPFhWCkXwvqjCqum30</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Oa5tvTh2mXFQbI3SkzK</t>
         </is>
       </c>
       <c r="T233" t="inlineStr">
@@ -26000,7 +25992,7 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V233" t="n">
@@ -26019,12 +26011,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
+          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -26034,7 +26026,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Mapping Project</t>
+          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -26044,7 +26036,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H234" t="b">
@@ -26057,7 +26049,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -26080,12 +26072,12 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
@@ -26095,17 +26087,17 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>10.21966/2aap-hn61</t>
+          <t>10.21966/fv0q-q364</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Oa5tvTh2mXFQbI3SkzK</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeY_smu3pJj8TBE9ivK</t>
         </is>
       </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="U234" t="inlineStr">
@@ -26129,12 +26121,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
+          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -26144,7 +26136,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -26162,7 +26154,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -26190,7 +26182,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -26200,17 +26192,17 @@
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>10.21966/fv0q-q364</t>
+          <t>10.21966/nwg7-fe05</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeY_smu3pJj8TBE9ivK</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeItznXpvEFI_t-jsCl</t>
         </is>
       </c>
       <c r="T235" t="inlineStr">
@@ -26224,11 +26216,11 @@
         </is>
       </c>
       <c r="V235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X235" t="inlineStr"/>
@@ -26239,12 +26231,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
+          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
+          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -26254,7 +26246,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
+          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -26272,7 +26264,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -26300,32 +26292,32 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>10.21966/nwg7-fe05</t>
+          <t>10.21966/02qp-4945</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeItznXpvEFI_t-jsCl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OeTbb0MbfTCH-YFCNGG</t>
         </is>
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="U236" t="inlineStr">
@@ -26349,12 +26341,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
+          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
+          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -26364,7 +26356,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
+          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -26410,12 +26402,12 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
+          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
@@ -26425,17 +26417,17 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>10.21966/02qp-4945</t>
+          <t>10.21966/dtt0-s264</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OeTbb0MbfTCH-YFCNGG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OgDkxI9LmB0KWXvOsZe</t>
         </is>
       </c>
       <c r="T237" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="U237" t="inlineStr">
@@ -26459,12 +26451,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
+          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -26474,7 +26466,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
+          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -26492,12 +26484,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -26520,37 +26512,37 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>10.21966/dtt0-s264</t>
+          <t>10.21966/xc7x-9207</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OgDkxI9LmB0KWXvOsZe</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OZGbDlZ5dgF0dD-ceZ7</t>
         </is>
       </c>
       <c r="T238" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V238" t="n">
@@ -26569,12 +26561,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
+          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -26584,7 +26576,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
+          <t>Hakai Institute Drone Data Index</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -26602,7 +26594,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -26630,37 +26622,37 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>10.21966/xc7x-9207</t>
+          <t>10.21966/0r8b-t282</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OZGbDlZ5dgF0dD-ceZ7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCdraToZivfj6ZZ8TqZ</t>
         </is>
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="V239" t="n">
@@ -26679,12 +26671,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
+          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -26694,7 +26686,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Hakai Institute Drone Data Index</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -26712,12 +26704,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -26740,47 +26732,37 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R240" t="inlineStr">
-        <is>
-          <t>10.21966/0r8b-t282</t>
-        </is>
-      </c>
+          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCdraToZivfj6ZZ8TqZ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OlwZ9MM8a9VqCYIJo4W</t>
         </is>
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V240" t="n">
-        <v>0</v>
-      </c>
-      <c r="W240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr"/>
+      <c r="W240" t="inlineStr"/>
       <c r="X240" t="inlineStr"/>
     </row>
     <row r="241">
@@ -26789,12 +26771,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
+          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -26804,7 +26786,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -26827,7 +26809,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -26860,13 +26842,17 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R241" t="inlineStr"/>
+          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>10.21966/4jvz-bv44</t>
+        </is>
+      </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OlwZ9MM8a9VqCYIJo4W</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OOYvTmfsWUPdHkDTTFS</t>
         </is>
       </c>
       <c r="T241" t="inlineStr">
@@ -26876,11 +26862,17 @@
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="V241" t="inlineStr"/>
-      <c r="W241" t="inlineStr"/>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="V241" t="n">
+        <v>0</v>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="X241" t="inlineStr"/>
     </row>
     <row r="242">
@@ -26889,12 +26881,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
+          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
+          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -26904,7 +26896,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
+          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -26922,12 +26914,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -26950,7 +26942,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -26960,27 +26952,27 @@
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>10.21966/4jvz-bv44</t>
+          <t>10.21966/cqrt-sk09</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OOYvTmfsWUPdHkDTTFS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-Oj8Fegu6V858hz57O8z</t>
         </is>
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="V242" t="n">
@@ -26999,12 +26991,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
+          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -27014,7 +27006,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
+          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -27060,7 +27052,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
@@ -27075,33 +27067,35 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>10.21966/cqrt-sk09</t>
+          <t>10.21966/chc3-rj93</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-Oj8Fegu6V858hz57O8z</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-OnCm7wniBlFr2gSXQhf</t>
         </is>
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X243" t="inlineStr"/>
+          <t>[{'year': '2026', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="X243" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27109,12 +27103,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
+          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -27124,7 +27118,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
+          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -27142,7 +27136,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -27170,12 +27164,12 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '850.0', 'min': '400.0'}]</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
@@ -27185,35 +27179,33 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>10.21966/chc3-rj93</t>
+          <t>10.21966/f9m6-qg12</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-OnCm7wniBlFr2gSXQhf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MibW0TZpoaJ4Ih_2ev7</t>
         </is>
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="V244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
-        </is>
-      </c>
-      <c r="X244" t="n">
-        <v>1</v>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27221,12 +27213,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
+          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -27236,7 +27228,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -27254,12 +27246,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -27278,41 +27270,41 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>[{'max': '850.0', 'min': '400.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>10.21966/f9m6-qg12</t>
+          <t>10.21966/a0v4-x512</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MibW0TZpoaJ4Ih_2ev7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
         </is>
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V245" t="n">
@@ -27331,12 +27323,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
+          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -27346,7 +27338,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
+          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -27364,12 +27356,12 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -27388,31 +27380,31 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>10.21966/a0v4-x512</t>
+          <t>10.21966/NMNG-SF35</t>
         </is>
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
         </is>
       </c>
       <c r="T246" t="inlineStr">
@@ -27422,7 +27414,7 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="V246" t="n">
@@ -27441,12 +27433,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
+          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
+          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -27456,7 +27448,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -27474,12 +27466,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -27502,37 +27494,37 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>macroalgalCanopyCoverAndComposition, other</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>10.21966/NMNG-SF35</t>
+          <t>10.21966/20ym-8826</t>
         </is>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
         </is>
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V247" t="n">
@@ -27551,12 +27543,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
+          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
+          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -27566,7 +27558,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profilers, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -27584,12 +27576,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -27608,41 +27600,41 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition, other</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>10.21966/20ym-8826</t>
+          <t>10.21966/kace-2d24</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
         </is>
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V248" t="n">
@@ -27661,12 +27653,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
+          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -27676,7 +27668,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profilers, BC, Canada (Research)</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -27694,12 +27686,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -27718,31 +27710,31 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '20.0', 'min': '20.0'}]</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>10.21966/kace-2d24</t>
+          <t>10.21966/65d8-k051</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
@@ -27752,7 +27744,7 @@
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V249" t="n">
@@ -27763,9 +27755,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X249" t="n">
-        <v>1</v>
-      </c>
+      <c r="X249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27773,12 +27763,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
+          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -27788,7 +27778,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
+          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -27811,7 +27801,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -27834,37 +27824,37 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '20.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>10.21966/65d8-k051</t>
+          <t>10.21966/175j-8k96</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
         </is>
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V250" t="n">
@@ -27875,7 +27865,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X250" t="inlineStr"/>
+      <c r="X250" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27883,12 +27875,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
+          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -27898,7 +27890,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
+          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -27959,12 +27951,12 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>10.21966/175j-8k96</t>
+          <t>10.21966/dveq-bt48</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
         </is>
       </c>
       <c r="T251" t="inlineStr">
@@ -27974,7 +27966,7 @@
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="V251" t="n">
@@ -27995,12 +27987,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
+          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -28010,7 +28002,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
+          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -28028,12 +28020,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -28052,54 +28044,52 @@
         </is>
       </c>
       <c r="N252" t="n">
+        <v>2</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>10.21966/RZVW-4A72</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="V252" t="n">
         <v>1</v>
       </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
-        </is>
-      </c>
-      <c r="P252" t="inlineStr">
-        <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
-        </is>
-      </c>
-      <c r="R252" t="inlineStr">
-        <is>
-          <t>10.21966/dveq-bt48</t>
-        </is>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="V252" t="n">
-        <v>0</v>
-      </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X252" t="n">
-        <v>2</v>
-      </c>
+          <t>[{'year': '2022', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28107,12 +28097,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
+          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -28122,7 +28112,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -28140,7 +28130,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -28168,45 +28158,45 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>10.21966/RZVW-4A72</t>
+          <t>10.21966/0xvh-1318</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
         </is>
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X253" t="inlineStr"/>
@@ -28217,12 +28207,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
+          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -28232,7 +28222,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
+          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -28250,12 +28240,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -28278,37 +28268,37 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
+          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>10.21966/0xvh-1318</t>
+          <t>10.21966/3q5j-n957</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
         </is>
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="V254" t="n">
@@ -28327,12 +28317,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
+          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -28342,7 +28332,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -28360,12 +28350,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -28384,41 +28374,41 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>10.21966/3q5j-n957</t>
+          <t>10.21966/kmc2-5r12</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="V255" t="n">
@@ -28437,12 +28427,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
+          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
+          <t>ca-cioos_7e49967a-b5ab-443d-860b-e3c0eb0f709c</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -28452,7 +28442,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
+          <t>Horne Lake Bathymetry Mapping</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -28470,7 +28460,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -28494,41 +28484,41 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.7872, 49.3105], [-124.6447, 49.3105], [-124.6447, 49.3644], [-124.7872, 49.3644], [-124.7872, 49.3105]]]}</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>10.21966/kmc2-5r12</t>
+          <t>10.21966/vwee-e004</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/G8LjsjnnPxb5TxWL730BxDTQu532/-Njn-0LeJ-Uwj4L8EmOV</t>
         </is>
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="V256" t="n">
@@ -28547,12 +28537,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
+          <t>18f56a52-11af-446a-aea9-07feca8d197e</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ca-cioos_7e49967a-b5ab-443d-860b-e3c0eb0f709c</t>
+          <t>ca-cioos_e897c9d0-3fca-4c89-b37f-e571413ffd12</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -28562,7 +28552,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Horne Lake Bathymetry Mapping</t>
+          <t>Joffre Provincial Park Aerial Surveys - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -28580,7 +28570,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -28608,12 +28598,12 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.7872, 49.3105], [-124.6447, 49.3105], [-124.6447, 49.3644], [-124.7872, 49.3644], [-124.7872, 49.3105]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.5281, 50.3147], [-122.4303, 50.3147], [-122.4303, 50.3796], [-122.5281, 50.3796], [-122.5281, 50.3147]]]}</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '475.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
@@ -28623,12 +28613,12 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>10.21966/vwee-e004</t>
+          <t>10.21966/k0z0-3z50</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/G8LjsjnnPxb5TxWL730BxDTQu532/-Njn-0LeJ-Uwj4L8EmOV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ot_OaAHxjund0-w5rXq</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
@@ -28638,7 +28628,7 @@
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="V257" t="n">
@@ -28657,12 +28647,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>18f56a52-11af-446a-aea9-07feca8d197e</t>
+          <t>6c4803cc-d1c6-4327-806a-7f6796606175</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ca-cioos_e897c9d0-3fca-4c89-b37f-e571413ffd12</t>
+          <t>ca-cioos_6c34ed6e-5a17-41f2-b83a-cd59d1ce07bd</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -28672,7 +28662,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Joffre Provincial Park Aerial Surveys - 2025 - Airborne Coastal Observatory</t>
+          <t>Knight Inlet Multibeam Bathymetry Survey</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -28690,7 +28680,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -28718,12 +28708,12 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.5281, 50.3147], [-122.4303, 50.3147], [-122.4303, 50.3796], [-122.5281, 50.3796], [-122.5281, 50.3147]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0537, 50.6529], [-125.9229, 50.6529], [-125.9229, 50.7077], [-126.0537, 50.7077], [-126.0537, 50.6529]]]}</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>[{'max': '475.0', 'min': '0.0'}]</t>
+          <t>[{'max': '288.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
@@ -28733,17 +28723,17 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>10.21966/k0z0-3z50</t>
+          <t>10.21966/8dgz-1z27</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ot_OaAHxjund0-w5rXq</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG7EOynnzSIOU7LPWgs</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
@@ -28767,12 +28757,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>6c4803cc-d1c6-4327-806a-7f6796606175</t>
+          <t>ce6f3f8c-6b57-4f18-be46-8c0b5a4baeb9</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ca-cioos_6c34ed6e-5a17-41f2-b83a-cd59d1ce07bd</t>
+          <t>ca-cioos_8755f475-2133-4205-baff-5e2937824f45</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -28782,7 +28772,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Knight Inlet Multibeam Bathymetry Survey</t>
+          <t>Poole Creek Aerial Surveys - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -28800,7 +28790,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -28828,12 +28818,12 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0537, 50.6529], [-125.9229, 50.6529], [-125.9229, 50.7077], [-126.0537, 50.7077], [-126.0537, 50.6529]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9075, 50.2436], [-122.8124, 50.2436], [-122.8124, 50.3016], [-122.9075, 50.3016], [-122.9075, 50.2436]]]}</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>[{'max': '288.0', 'min': '0.0'}]</t>
+          <t>[{'max': '450.0', 'min': '200.0'}]</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
@@ -28843,12 +28833,12 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>10.21966/8dgz-1z27</t>
+          <t>10.21966/g8f2-jw82</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG7EOynnzSIOU7LPWgs</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OtfdtO43um_1J_LdCpn</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
@@ -28877,12 +28867,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>ce6f3f8c-6b57-4f18-be46-8c0b5a4baeb9</t>
+          <t>e1247209-cc26-4788-82a2-dd8a5c971e22</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ca-cioos_8755f475-2133-4205-baff-5e2937824f45</t>
+          <t>ca-cioos_2e5ddbaa-4f0c-4339-8595-1ddbd35c3df4</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -28892,7 +28882,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Poole Creek Aerial Surveys - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Aerial Surveys in British Columbia, Washington, and Alberta - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -28938,12 +28928,12 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.9075, 50.2436], [-122.8124, 50.2436], [-122.8124, 50.3016], [-122.9075, 50.3016], [-122.9075, 50.2436]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.9263, 48.0077], [-112.7224, 48.0077], [-112.7224, 54.6673], [-127.9263, 54.6673], [-127.9263, 48.0077]]]}</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>[{'max': '450.0', 'min': '200.0'}]</t>
+          <t>[{'max': '4019.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
@@ -28953,22 +28943,22 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>10.21966/g8f2-jw82</t>
+          <t>10.21966/n6ga-nc24</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OtfdtO43um_1J_LdCpn</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ou3t_K6rGOHTMO67Xbq</t>
         </is>
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="V260" t="n">
@@ -28987,12 +28977,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>e1247209-cc26-4788-82a2-dd8a5c971e22</t>
+          <t>5ac3ac5f-702e-43d8-bcb7-79f30c4d9e08</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ca-cioos_2e5ddbaa-4f0c-4339-8595-1ddbd35c3df4</t>
+          <t>ca-cioos_656ea307-fed0-48ca-b5d8-1bc017dc52d2</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -29002,7 +28992,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Aerial Surveys in British Columbia, Washington, and Alberta - 2025 - Airborne Coastal Observatory</t>
+          <t>Botanical Beach - Juan de Fuca Provincial Park - Drone Mapping</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -29020,7 +29010,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -29048,12 +29038,12 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.9263, 48.0077], [-112.7224, 48.0077], [-112.7224, 54.6673], [-127.9263, 54.6673], [-127.9263, 48.0077]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.45265489, 48.52152402], [-124.43377214, 48.52152402], [-124.43377214, 48.53061904], [-124.45265489, 48.53061904], [-124.45265489, 48.52152402]]]}</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>[{'max': '4019.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
@@ -29063,12 +29053,12 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>10.21966/n6ga-nc24</t>
+          <t>10.21966/kn3e-fn08</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ou3t_K6rGOHTMO67Xbq</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdvcmtQME1NZmdWcDY</t>
         </is>
       </c>
       <c r="T261" t="inlineStr">
@@ -29097,12 +29087,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>5ac3ac5f-702e-43d8-bcb7-79f30c4d9e08</t>
+          <t>05dac0a6-a26c-4cb5-895d-132b5e2134cd</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ca-cioos_656ea307-fed0-48ca-b5d8-1bc017dc52d2</t>
+          <t>ca-cioos_b45dbc9d-bf7a-4734-86cd-3397e7c9ac62</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -29112,7 +29102,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Botanical Beach - Juan de Fuca Provincial Park - Drone Mapping</t>
+          <t>Sea surface temperature data in False Creek, British Columbia</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -29130,7 +29120,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -29158,37 +29148,37 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.45265489, 48.52152402], [-124.43377214, 48.52152402], [-124.43377214, 48.53061904], [-124.45265489, 48.53061904], [-124.45265489, 48.52152402]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28]]]}</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.5', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>10.21966/kn3e-fn08</t>
+          <t>10.21966/0g6d-pk30</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdvcmtQME1NZmdWcDY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NHaXDtgFZr0-Oul6FZG</t>
         </is>
       </c>
       <c r="T262" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="V262" t="n">
@@ -29207,12 +29197,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>05dac0a6-a26c-4cb5-895d-132b5e2134cd</t>
+          <t>6eb46e26-dac5-4964-8b29-8e8541381aac</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>ca-cioos_b45dbc9d-bf7a-4734-86cd-3397e7c9ac62</t>
+          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -29222,7 +29212,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Sea surface temperature data in False Creek, British Columbia</t>
+          <t>Time series of eelgrass (Zostera marina) meadow extent derived from drone surveys, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -29240,12 +29230,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -29268,37 +29258,37 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>[{'max': '0.5', 'min': '0.5'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>10.21966/0g6d-pk30</t>
+          <t>10.21966/03pw-2190</t>
         </is>
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NHaXDtgFZr0-Oul6FZG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
         </is>
       </c>
       <c r="T263" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="V263" t="n">
@@ -29317,12 +29307,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>6eb46e26-dac5-4964-8b29-8e8541381aac</t>
+          <t>67b81524-e385-439e-9bc1-03bd4652eba6</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
+          <t>ca-cioos_79368bf3-8f02-4355-837e-3a6cef0d2886</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -29332,7 +29322,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Time series of eelgrass (Zostera marina) meadow extent derived from drone surveys, Central Coast, British Columbia</t>
+          <t>Watersheds Stream Stations Timeseries, Calvert and Hecate Islands, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -29350,12 +29340,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -29374,11 +29364,11 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
@@ -29388,27 +29378,27 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>10.21966/03pw-2190</t>
+          <t>10.21966/c6xs-y324</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/zBOULF9sDAgC4rkoZUFQq7sBGCf2/-OtAIe6lv3elLZd4c-V1</t>
         </is>
       </c>
       <c r="T264" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="V264" t="n">
@@ -29427,12 +29417,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>67b81524-e385-439e-9bc1-03bd4652eba6</t>
+          <t>ff456916-01f7-4eb0-961f-3658f0b4f39b</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>ca-cioos_79368bf3-8f02-4355-837e-3a6cef0d2886</t>
+          <t>ca-cioos_d986aade-6bf1-4dfa-97c2-686975f944d5</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -29442,7 +29432,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Watersheds Stream Stations Timeseries, Calvert and Hecate Islands, BC, Canada (Provisional)</t>
+          <t>Watersheds Stream Stations Timeseries, Calvert and Hecate Islands, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -29465,7 +29455,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -29488,12 +29478,12 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.1, 51.64], [-128.0, 51.64], [-128.0, 51.67], [-128.1, 51.67], [-128.1, 51.64]]]}</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q265" t="inlineStr">
@@ -29503,17 +29493,17 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>10.21966/c6xs-y324</t>
+          <t>10.21966/47m7-ev69</t>
         </is>
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/zBOULF9sDAgC4rkoZUFQq7sBGCf2/-OtAIe6lv3elLZd4c-V1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/zBOULF9sDAgC4rkoZUFQq7sBGCf2/-OHj73dBYs1okPPjDXKY</t>
         </is>
       </c>
       <c r="T265" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U265" t="inlineStr">
@@ -29537,12 +29527,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>ff456916-01f7-4eb0-961f-3658f0b4f39b</t>
+          <t>71c6db20-a521-451b-b371-a2560f6af25e</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>ca-cioos_d986aade-6bf1-4dfa-97c2-686975f944d5</t>
+          <t>ca-cioos_999da1dd-efde-4a55-868b-ce2d6ca3b983</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -29552,7 +29542,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Watersheds Stream Stations Timeseries, Calvert and Hecate Islands, BC, Canada (Research)</t>
+          <t>Observations from the 2017 Hakai MarineGEO Bioblitz</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -29570,12 +29560,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -29594,41 +29584,41 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.1, 51.64], [-128.0, 51.64], [-128.0, 51.67], [-128.1, 51.67], [-128.1, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.951, 51.48631], [-127.76165, 51.48631], [-127.76165, 52.05347], [-128.951, 52.05347], [-128.951, 51.48631]]]}</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '40.0', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>10.21966/47m7-ev69</t>
+          <t>10.21966/0jfr-7b65</t>
         </is>
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/zBOULF9sDAgC4rkoZUFQq7sBGCf2/-OHj73dBYs1okPPjDXKY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCmJU0B97JSOfOpj6J</t>
         </is>
       </c>
       <c r="T266" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="V266" t="n">
@@ -29647,12 +29637,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>71c6db20-a521-451b-b371-a2560f6af25e</t>
+          <t>f0ae5f04-2c3a-4b67-8fbf-c6dc3771257d</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>ca-cioos_999da1dd-efde-4a55-868b-ce2d6ca3b983</t>
+          <t>ca-cioos_482d2463-0c81-4d62-a22a-1c0942b3c1fa</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -29662,7 +29652,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Observations from the 2017 Hakai MarineGEO Bioblitz</t>
+          <t>Observations from the 2019 Hakai Deep Water Bioblitz</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -29708,12 +29698,12 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.951, 51.48631], [-127.76165, 51.48631], [-127.76165, 52.05347], [-128.951, 52.05347], [-128.951, 51.48631]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.14433, 51.615734], [-127.76327, 51.615734], [-127.76327, 51.787], [-128.14433, 51.787], [-128.14433, 51.615734]]]}</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>[{'max': '40.0', 'min': '0.5'}]</t>
+          <t>[{'max': '255.0', 'min': '5.0'}]</t>
         </is>
       </c>
       <c r="Q267" t="inlineStr">
@@ -29723,22 +29713,22 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>10.21966/0jfr-7b65</t>
+          <t>10.21966/3p06-vt55</t>
         </is>
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCmJU0B97JSOfOpj6J</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCoStSubGWAdV78XNC</t>
         </is>
       </c>
       <c r="T267" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="V267" t="n">
@@ -29757,12 +29747,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>f0ae5f04-2c3a-4b67-8fbf-c6dc3771257d</t>
+          <t>91d2ddf0-ea25-4ef9-b990-26d2957cb3bd</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>ca-cioos_482d2463-0c81-4d62-a22a-1c0942b3c1fa</t>
+          <t>ca-cioos_542a20b8-242e-4199-a062-5b76ea9cbf2d</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -29772,7 +29762,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Observations from the 2019 Hakai Deep Water Bioblitz</t>
+          <t>Observations from the 2018 Hakai Terrestrial Bioblitz</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -29818,27 +29808,27 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.14433, 51.615734], [-127.76327, 51.615734], [-127.76327, 51.787], [-128.14433, 51.787], [-128.14433, 51.615734]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.98366, 51.5919], [-125.0032, 51.5919], [-125.0032, 53.9998], [-128.98366, 53.9998], [-128.98366, 51.5919]]]}</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>[{'max': '255.0', 'min': '5.0'}]</t>
+          <t>[{'max': '1012.0', 'min': '50.0'}]</t>
         </is>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>10.21966/3p06-vt55</t>
+          <t>10.21966/t0h7-8g95</t>
         </is>
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCoStSubGWAdV78XNC</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCpwd5hTju8QOKVY-E</t>
         </is>
       </c>
       <c r="T268" t="inlineStr">
@@ -29848,7 +29838,7 @@
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V268" t="n">
@@ -29867,12 +29857,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>91d2ddf0-ea25-4ef9-b990-26d2957cb3bd</t>
+          <t>fa42f16a-3693-4c51-b45c-a36e709fdac3</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>ca-cioos_542a20b8-242e-4199-a062-5b76ea9cbf2d</t>
+          <t>ca-cioos_d69bf79e-b616-404e-bbfc-92932ca74087</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -29882,7 +29872,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Observations from the 2018 Hakai Terrestrial Bioblitz</t>
+          <t>Observations from the 2018 Hakai Seagrass Bioblitz</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -29900,7 +29890,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Genomics, Nearshore</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -29928,27 +29918,27 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.98366, 51.5919], [-125.0032, 51.5919], [-125.0032, 53.9998], [-128.98366, 53.9998], [-128.98366, 51.5919]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.8123, 51.8438], [-128.2105, 51.684], [-128.1968, 51.6158], [-127.8837, 51.6192], [-127.8123, 51.8438]]]}</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>[{'max': '1012.0', 'min': '50.0'}]</t>
+          <t>[{'max': '300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>10.21966/t0h7-8g95</t>
+          <t>10.21966/yf1f-jx85</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCpwd5hTju8QOKVY-E</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCnP9OAghmAmYObj0D</t>
         </is>
       </c>
       <c r="T269" t="inlineStr">
@@ -29958,7 +29948,7 @@
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="V269" t="n">
@@ -29977,12 +29967,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>fa42f16a-3693-4c51-b45c-a36e709fdac3</t>
+          <t>fc3d2ea5-b60c-42c9-97e9-542024bec9fa</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>ca-cioos_d69bf79e-b616-404e-bbfc-92932ca74087</t>
+          <t>ca-cioos_4add33cd-b182-4825-900a-5695f333125a</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -29992,7 +29982,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Observations from the 2018 Hakai Seagrass Bioblitz</t>
+          <t>Weather Station Time Series, Hyacinthe Bay, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -30010,12 +30000,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -30038,47 +30028,37 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.8123, 51.8438], [-128.2105, 51.684], [-128.1968, 51.6158], [-127.8837, 51.6192], [-127.8123, 51.8438]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2221111, 50.1162556]}</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>[{'max': '300.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution, seagrassCoverAndComposition</t>
-        </is>
-      </c>
-      <c r="R270" t="inlineStr">
-        <is>
-          <t>10.21966/yf1f-jx85</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCnP9OAghmAmYObj0D</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OyesAm4pxUK1wqBMn7x</t>
         </is>
       </c>
       <c r="T270" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="V270" t="n">
-        <v>0</v>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr"/>
+      <c r="W270" t="inlineStr"/>
       <c r="X270" t="inlineStr"/>
     </row>
     <row r="271">
@@ -30087,12 +30067,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>fc3d2ea5-b60c-42c9-97e9-542024bec9fa</t>
+          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>ca-cioos_4add33cd-b182-4825-900a-5695f333125a</t>
+          <t>ca-cioos_3f40326a-23f9-4e30-a16a-f332ace14e2f</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -30102,7 +30082,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Weather Station Time Series, Hyacinthe Bay, BC, Canada (Provisional)</t>
+          <t>Nereocystis kelp canopy productivity data from BC Central Coast</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -30120,12 +30100,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -30148,37 +30128,47 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2221111, 50.1162556]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.19], [-127.1, 51.19], [-127.1, 52.28], [-128.6, 52.28], [-128.6, 51.19]]]}</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R271" t="inlineStr"/>
+          <t>macroalgalCanopyCoverAndComposition</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>10.21966/d1s2-s530</t>
+        </is>
+      </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OyesAm4pxUK1wqBMn7x</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtG8b48aDAEdJoqNT6N</t>
         </is>
       </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="V271" t="inlineStr"/>
-      <c r="W271" t="inlineStr"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V271" t="n">
+        <v>1</v>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>[{'year': '2024', 'total': 1}]</t>
+        </is>
+      </c>
       <c r="X271" t="inlineStr"/>
     </row>
     <row r="272">
@@ -30187,12 +30177,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
+          <t>aab940b9-bb7f-49c0-ae62-4f78d26897b3</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>ca-cioos_3f40326a-23f9-4e30-a16a-f332ace14e2f</t>
+          <t>ca-cioos_0219e1d6-8dfc-4718-b89b-ea3dff06a70d</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -30202,7 +30192,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Nereocystis kelp canopy productivity data from BC Central Coast</t>
+          <t>Modeled Eelgrass Extent, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -30220,12 +30210,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -30244,49 +30234,49 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.19], [-127.1, 51.19], [-127.1, 52.28], [-128.6, 52.28], [-128.6, 51.19]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-133.7841801345348, 48.23443097294032], [-122.49023482203482, 48.23443097294032], [-122.49023482203482, 54.52958287232971], [-133.7841801345348, 54.52958287232971], [-133.7841801345348, 48.23443097294032]]]}</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>10.21966/d1s2-s530</t>
+          <t>10.21966/1ty5-e654</t>
         </is>
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtG8b48aDAEdJoqNT6N</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWtuNVpwdEdLRXZTODc</t>
         </is>
       </c>
       <c r="T272" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W272" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X272" t="inlineStr"/>
@@ -30297,12 +30287,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>aab940b9-bb7f-49c0-ae62-4f78d26897b3</t>
+          <t>3988f8e8-36ea-4cda-9bd9-a03157116ef5</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>ca-cioos_0219e1d6-8dfc-4718-b89b-ea3dff06a70d</t>
+          <t>ca-cioos_d43a79c1-a6ba-4e37-8dc2-6ced6312828e</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -30312,7 +30302,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Modeled Eelgrass Extent, British Columbia, Canada</t>
+          <t>Data from Manuscript: Parasites of the hermit crab Pagurus hirsutiusculus; distribution, prevalence, and thermal ecology</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -30330,7 +30320,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -30354,11 +30344,11 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-133.7841801345348, 48.23443097294032], [-122.49023482203482, 48.23443097294032], [-122.49023482203482, 54.52958287232971], [-133.7841801345348, 54.52958287232971], [-133.7841801345348, 48.23443097294032]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.66], [-127.9, 51.81], [-122.2, 49.03], [-123.3, 49.01], [-123.0, 48.83], [-123.0, 48.78], [-123.3, 48.7], [-123.3, 48.53], [-123.6, 48.59], [-125.2, 48.73], [-125.6, 48.95], [-125.6, 50.11], [-128.4, 51.66]]]}</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
@@ -30368,17 +30358,17 @@
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>invertebrateAbundanceAndDistribution, seaSurfaceSalinity</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>10.21966/1ty5-e654</t>
+          <t>10.21966/xb3t-qb88</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWtuNVpwdEdLRXZTODc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3eh7IMAvm8ZUtcMBeifFL0eJCIA3/-O5Kei32z9cfatfgKj5y</t>
         </is>
       </c>
       <c r="T273" t="inlineStr">
@@ -30388,7 +30378,7 @@
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V273" t="n">
@@ -30407,12 +30397,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>3988f8e8-36ea-4cda-9bd9-a03157116ef5</t>
+          <t>c4932b55-1dd8-4f2f-89da-5822056ecc37</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>ca-cioos_d43a79c1-a6ba-4e37-8dc2-6ced6312828e</t>
+          <t>ca-cioos_53189107-9df5-426b-acb4-f903468554fe</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -30422,7 +30412,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Data from Manuscript: Parasites of the hermit crab Pagurus hirsutiusculus; distribution, prevalence, and thermal ecology</t>
+          <t>Comparing invertebrate and seaweed diversity in kelp forests and urchin barrens in Owen Bay, British Columbia, using Autonomous Reef Monitoring Structures (ARMS)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -30440,7 +30430,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Sentinels of Change, Genomics</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -30464,41 +30454,41 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.66], [-127.9, 51.81], [-122.2, 49.03], [-123.3, 49.01], [-123.0, 48.83], [-123.0, 48.78], [-123.3, 48.7], [-123.3, 48.53], [-123.6, 48.59], [-125.2, 48.73], [-125.6, 48.95], [-125.6, 50.11], [-128.4, 51.66]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.2335, 50.2999], [-125.2163, 50.2999], [-125.2163, 50.313], [-125.2335, 50.313], [-125.2335, 50.2999]]]}</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '6.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, seaSurfaceSalinity</t>
+          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>10.21966/xb3t-qb88</t>
+          <t>10.21966/e5mw-tr82</t>
         </is>
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3eh7IMAvm8ZUtcMBeifFL0eJCIA3/-O5Kei32z9cfatfgKj5y</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/5Jh4rsxoBsRd4mVFqZ0XJoMtMHI2/-P-tq8uNjGhWtk4rBny0</t>
         </is>
       </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="V274" t="n">
@@ -30509,7 +30499,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X274" t="inlineStr"/>
+      <c r="X274" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30517,12 +30509,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>c4932b55-1dd8-4f2f-89da-5822056ecc37</t>
+          <t>33bb67af-4d61-4b15-93a9-f3ab2498430b</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>ca-cioos_53189107-9df5-426b-acb4-f903468554fe</t>
+          <t>ca-cioos_73abfecf-d35c-4f9c-a991-eee5cece08ea</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -30532,7 +30524,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Comparing invertebrate and seaweed diversity in kelp forests and urchin barrens in Owen Bay, British Columbia, using Autonomous Reef Monitoring Structures (ARMS)</t>
+          <t>Kelp Canopy Extent 2012 - NW Calvert Island</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -30550,7 +30542,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Sentinels of Change, Genomics</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -30574,41 +30566,41 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.2335, 50.2999], [-125.2163, 50.2999], [-125.2163, 50.313], [-125.2335, 50.313], [-125.2335, 50.2999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16959381103513, 51.63613234359897], [-128.11191558837888, 51.63613234359897], [-128.11191558837888, 51.681709494104325], [-128.16959381103513, 51.681709494104325], [-128.16959381103513, 51.63613234359897]]]}</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
+          <t>other, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>10.21966/e5mw-tr82</t>
+          <t>10.21966/63rs-yt91</t>
         </is>
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/5Jh4rsxoBsRd4mVFqZ0XJoMtMHI2/-P-tq8uNjGhWtk4rBny0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxUM01laTFaREhKbWE</t>
         </is>
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="V275" t="n">
@@ -30629,12 +30621,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>33bb67af-4d61-4b15-93a9-f3ab2498430b</t>
+          <t>bc1133da-5601-4f92-bc53-41be547c936b</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>ca-cioos_73abfecf-d35c-4f9c-a991-eee5cece08ea</t>
+          <t>ca-cioos_940218ef-d7f8-4f3f-9e69-52150ecdbec5</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -30644,7 +30636,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Kelp Canopy Extent 2012 - NW Calvert Island</t>
+          <t>North Vancouver Island Aerial Survey - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -30662,7 +30654,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -30686,31 +30678,31 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16959381103513, 51.63613234359897], [-128.11191558837888, 51.63613234359897], [-128.11191558837888, 51.681709494104325], [-128.16959381103513, 51.681709494104325], [-128.16959381103513, 51.63613234359897]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 50.35], [-125.4, 50.35], [-125.4, 50.63], [-126.7, 50.63], [-126.7, 50.35]]]}</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>other, macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>10.21966/63rs-yt91</t>
+          <t>10.21966/kdhe-hz07</t>
         </is>
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxUM01laTFaREhKbWE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCoHpqOwDbp834fqRY3</t>
         </is>
       </c>
       <c r="T276" t="inlineStr">
@@ -30720,7 +30712,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="V276" t="n">
@@ -30731,9 +30723,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X276" t="n">
-        <v>1</v>
-      </c>
+      <c r="X276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30741,12 +30731,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>bc1133da-5601-4f92-bc53-41be547c936b</t>
+          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>ca-cioos_940218ef-d7f8-4f3f-9e69-52150ecdbec5</t>
+          <t>ca-cioos_c7466354-bacc-4781-acdc-543dd03d1eab</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -30756,7 +30746,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>North Vancouver Island Aerial Survey - 2024 - Airborne Coastal Observatory</t>
+          <t>Nanwakolas LiDAR Surveys - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -30802,12 +30792,12 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 50.35], [-125.4, 50.35], [-125.4, 50.63], [-126.7, 50.63], [-126.7, 50.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.8, 49.26], [-124.5, 49.26], [-124.5, 50.83], [-126.8, 50.83], [-126.8, 49.26]]]}</t>
         </is>
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1700.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q277" t="inlineStr">
@@ -30817,12 +30807,12 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>10.21966/kdhe-hz07</t>
+          <t>10.21966/e0r7-ge27</t>
         </is>
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCoHpqOwDbp834fqRY3</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OjbuSE_uZcCs3Fit_mg</t>
         </is>
       </c>
       <c r="T277" t="inlineStr">
@@ -30832,7 +30822,7 @@
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V277" t="n">
@@ -30851,12 +30841,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
+          <t>f7433c1a-3aad-4761-81c4-c191a5e6ac92</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>ca-cioos_c7466354-bacc-4781-acdc-543dd03d1eab</t>
+          <t>ca-cioos_52e97374-bee5-4b1a-9b85-7170a5df8d6b</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -30866,7 +30856,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Nanwakolas LiDAR Surveys - Airborne Coastal Observatory</t>
+          <t>Biomass and density of Pycnopodia helianthoides from the central coast of BC</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -30884,7 +30874,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography, Nearshore</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -30912,37 +30902,37 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.8, 49.26], [-124.5, 49.26], [-124.5, 50.83], [-126.8, 50.83], [-126.8, 49.26]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.617, 51.3321], [-127.3509, 51.3321], [-127.3509, 52.3317], [-128.617, 52.3317], [-128.617, 51.3321]]]}</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>[{'max': '1700.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceSalinity, subSurfaceSalinity, seaSurfaceTemperature, subSurfaceTemperature, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>10.21966/e0r7-ge27</t>
+          <t>10.21966/xy6n-qz76</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OjbuSE_uZcCs3Fit_mg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-OteEfuBSvhg-2RySC4a</t>
         </is>
       </c>
       <c r="T278" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="V278" t="n">
@@ -30961,12 +30951,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>f7433c1a-3aad-4761-81c4-c191a5e6ac92</t>
+          <t>c7a168e8-f15e-446f-a49d-0b4a1f043ac2</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ca-cioos_52e97374-bee5-4b1a-9b85-7170a5df8d6b</t>
+          <t>ca-cioos_b4844ae2-d9c1-42f2-ae4d-a8f994c395a0</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -30976,7 +30966,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Biomass and density of Pycnopodia helianthoides from the central coast of BC</t>
+          <t>Putting fjord biodiversity on the map for British Columbia conservation planning</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -30994,7 +30984,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore</t>
+          <t>Genomics, Oceanography</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -31014,56 +31004,58 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N279" t="n">
+        <v>2</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.0471, 52.2577], [-128.9141, 51.7033], [-127.6841, 50.7687], [-123.7744, 48.9864], [-122.764, 49.331], [-122.8299, 49.9706], [-127.0471, 52.2577]]]}</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>[{'max': '595.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>fishAbundanceAndDistribution, subSurfaceTemperature, subSurfaceSalinity</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>10.21966/n141-m959</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-Ow-ZgW1jkC5-WyrtlLV</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="V279" t="n">
+        <v>0</v>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X279" t="n">
         <v>1</v>
       </c>
-      <c r="O279" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.617, 51.3321], [-127.3509, 51.3321], [-127.3509, 52.3317], [-128.617, 52.3317], [-128.617, 51.3321]]]}</t>
-        </is>
-      </c>
-      <c r="P279" t="inlineStr">
-        <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q279" t="inlineStr">
-        <is>
-          <t>seaSurfaceSalinity, subSurfaceSalinity, seaSurfaceTemperature, subSurfaceTemperature, invertebrateAbundanceAndDistribution</t>
-        </is>
-      </c>
-      <c r="R279" t="inlineStr">
-        <is>
-          <t>10.21966/xy6n-qz76</t>
-        </is>
-      </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-OteEfuBSvhg-2RySC4a</t>
-        </is>
-      </c>
-      <c r="T279" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U279" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="V279" t="n">
-        <v>0</v>
-      </c>
-      <c r="W279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31071,12 +31063,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>c7a168e8-f15e-446f-a49d-0b4a1f043ac2</t>
+          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>ca-cioos_b4844ae2-d9c1-42f2-ae4d-a8f994c395a0</t>
+          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -31086,7 +31078,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Putting fjord biodiversity on the map for Britsh Columbia conservation planning</t>
+          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -31104,7 +31096,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Genomics, Oceanography</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -31124,45 +31116,45 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N280" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.0471, 52.2577], [-128.9141, 51.7033], [-127.6841, 50.7687], [-123.7744, 48.9864], [-122.764, 49.331], [-122.8299, 49.9706], [-127.0471, 52.2577]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
         </is>
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>[{'max': '595.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2.5', 'min': '2.5'}]</t>
         </is>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, subSurfaceTemperature, subSurfaceSalinity</t>
+          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>10.21966/n141-m959</t>
+          <t>10.21966/rrzq-yw32</t>
         </is>
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-Ow-ZgW1jkC5-WyrtlLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
         </is>
       </c>
       <c r="T280" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V280" t="n">
@@ -31173,9 +31165,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X280" t="n">
-        <v>1</v>
-      </c>
+      <c r="X280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31183,12 +31173,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
+          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
+          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -31198,17 +31188,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
+          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H281" t="b">
@@ -31221,7 +31211,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -31244,27 +31234,23 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>[{'max': '2.5', 'min': '2.5'}]</t>
+          <t>[{'max': '0.0', 'min': '600.0'}]</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R281" t="inlineStr">
-        <is>
-          <t>10.21966/rrzq-yw32</t>
-        </is>
-      </c>
+          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
         </is>
       </c>
       <c r="T281" t="inlineStr">
@@ -31274,18 +31260,14 @@
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="V281" t="n">
-        <v>0</v>
-      </c>
-      <c r="W281" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X281" t="inlineStr"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr"/>
+      <c r="W281" t="inlineStr"/>
+      <c r="X281" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31293,12 +31275,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
+          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
+          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -31308,17 +31290,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
+          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H282" t="b">
@@ -31326,12 +31308,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Estuary Resilience</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -31354,40 +31336,48 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '600.0'}]</t>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R282" t="inlineStr"/>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>10.21966/r9zr-xz33</t>
+        </is>
+      </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
         </is>
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="V282" t="inlineStr"/>
-      <c r="W282" t="inlineStr"/>
-      <c r="X282" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="V282" t="n">
+        <v>0</v>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31395,12 +31385,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
+          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
+          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -31410,7 +31400,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -31456,7 +31446,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
@@ -31471,12 +31461,12 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>10.21966/r9zr-xz33</t>
+          <t>10.21966/9dbb-5d54</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
         </is>
       </c>
       <c r="T283" t="inlineStr">
@@ -31505,12 +31495,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
+          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
+          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -31520,7 +31510,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -31566,7 +31556,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
@@ -31581,12 +31571,12 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>10.21966/9dbb-5d54</t>
+          <t>10.21966/vpz7-mm73</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
         </is>
       </c>
       <c r="T284" t="inlineStr">
@@ -31615,12 +31605,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
+          <t>0ce3ee5b-425b-4eb0-a201-96bdfb795a3f</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
+          <t>ca-cioos_354b5b83-e752-4ffb-a740-d1cdc02ac8c6</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -31630,7 +31620,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Dtlaxsiwè River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -31676,7 +31666,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.1721, 50.61011], [-127.17933, 50.612], [-127.1873, 50.6098], [-127.19703, 50.61072], [-127.20524, 50.61585], [-127.19007, 50.61844], [-127.18675, 50.61393], [-127.17744, 50.61359], [-127.17161, 50.61118], [-127.17203, 50.61011], [-127.1721, 50.61011]]]}</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
@@ -31691,12 +31681,12 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>10.21966/vpz7-mm73</t>
+          <t>10.21966/ydm2-m238</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7Dng-ZtRd05hnZCq1</t>
         </is>
       </c>
       <c r="T285" t="inlineStr">
@@ -31725,12 +31715,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>0ce3ee5b-425b-4eb0-a201-96bdfb795a3f</t>
+          <t>1a2aa5c8-9a83-46f7-967d-1127436c2084</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>ca-cioos_354b5b83-e752-4ffb-a740-d1cdc02ac8c6</t>
+          <t>ca-cioos_58a5140a-0b2c-4186-a648-53d9f58e5226</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -31740,7 +31730,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Dtlaxsiwè River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kvai River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -31786,7 +31776,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.1721, 50.61011], [-127.17933, 50.612], [-127.1873, 50.6098], [-127.19703, 50.61072], [-127.20524, 50.61585], [-127.19007, 50.61844], [-127.18675, 50.61393], [-127.17744, 50.61359], [-127.17161, 50.61118], [-127.17203, 50.61011], [-127.1721, 50.61011]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.81882, 51.77547], [-127.83122, 51.77986], [-127.85192, 51.781], [-127.86785, 51.78358], [-127.8958, 51.77366], [-127.89418, 51.77118], [-127.87834, 51.77309], [-127.86508, 51.77748], [-127.84009, 51.77519], [-127.82731, 51.77452], [-127.82025, 51.77309], [-127.81853, 51.77566], [-127.81882, 51.77547]]]}</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
@@ -31801,12 +31791,12 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>10.21966/ydm2-m238</t>
+          <t>10.21966/pm9m-h431</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7Dng-ZtRd05hnZCq1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7QQE3ifLCAPcu3Jih</t>
         </is>
       </c>
       <c r="T286" t="inlineStr">
@@ -31835,12 +31825,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>1a2aa5c8-9a83-46f7-967d-1127436c2084</t>
+          <t>c035b81c-0fc3-446e-bec5-8b8933ae874b</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>ca-cioos_58a5140a-0b2c-4186-a648-53d9f58e5226</t>
+          <t>ca-cioos_7fbc28f7-ee87-4361-bbee-0ed8ce24522d</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -31850,7 +31840,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kvai River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Gwa'dzi River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -31896,7 +31886,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.81882, 51.77547], [-127.83122, 51.77986], [-127.85192, 51.781], [-127.86785, 51.78358], [-127.8958, 51.77366], [-127.89418, 51.77118], [-127.87834, 51.77309], [-127.86508, 51.77748], [-127.84009, 51.77519], [-127.82731, 51.77452], [-127.82025, 51.77309], [-127.81853, 51.77566], [-127.81882, 51.77547]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.46176, 50.74217], [-127.49022, 50.72165], [-127.49167, 50.71188], [-127.4832, 50.70356], [-127.4874, 50.69181], [-127.46443, 50.6928], [-127.47282, 50.70776], [-127.47992, 50.71424], [-127.48305, 50.72058], [-127.45901, 50.74011], [-127.46153, 50.74217], [-127.46176, 50.74217]]]}</t>
         </is>
       </c>
       <c r="P287" t="inlineStr">
@@ -31911,12 +31901,12 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>10.21966/pm9m-h431</t>
+          <t>10.21966/xq99-x273</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7QQE3ifLCAPcu3Jih</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7BCRnF2C30YPkxIyd</t>
         </is>
       </c>
       <c r="T287" t="inlineStr">
@@ -31945,12 +31935,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>c035b81c-0fc3-446e-bec5-8b8933ae874b</t>
+          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>ca-cioos_7fbc28f7-ee87-4361-bbee-0ed8ce24522d</t>
+          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -31960,7 +31950,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Gwa'dzi River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -32006,7 +31996,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.46176, 50.74217], [-127.49022, 50.72165], [-127.49167, 50.71188], [-127.4832, 50.70356], [-127.4874, 50.69181], [-127.46443, 50.6928], [-127.47282, 50.70776], [-127.47992, 50.71424], [-127.48305, 50.72058], [-127.45901, 50.74011], [-127.46153, 50.74217], [-127.46176, 50.74217]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
@@ -32021,12 +32011,12 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>10.21966/xq99-x273</t>
+          <t>10.21966/kde9-8g12</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7BCRnF2C30YPkxIyd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
         </is>
       </c>
       <c r="T288" t="inlineStr">
@@ -32055,12 +32045,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
+          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
+          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -32070,7 +32060,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -32116,7 +32106,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
@@ -32131,12 +32121,12 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>10.21966/kde9-8g12</t>
+          <t>10.21966/9a97-2j48</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
         </is>
       </c>
       <c r="T289" t="inlineStr">
@@ -32165,12 +32155,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
+          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
+          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -32180,7 +32170,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -32226,7 +32216,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
@@ -32241,12 +32231,12 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>10.21966/9a97-2j48</t>
+          <t>10.21966/ed9w-2653</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
         </is>
       </c>
       <c r="T290" t="inlineStr">
@@ -32275,12 +32265,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
+          <t>1af6a43a-e73b-4774-8e10-b9f2928ab133</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
+          <t>ca-cioos_ae7e017c-9211-4f98-b56e-90a4bbac161c</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -32290,7 +32280,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Snuneymuxw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -32336,7 +32326,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.88685, 49.19332], [-123.92494, 49.1612], [-123.92581, 49.13841], [-123.91159, 49.123], [-123.88023, 49.11117], [-123.85971, 49.12766], [-123.89792, 49.16196], [-123.88099, 49.18866], [-123.88685, 49.19332]]]}</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -32351,12 +32341,12 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>10.21966/ed9w-2653</t>
+          <t>10.21966/k01q-wb27</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt459vxCIH7YPRN9fp</t>
         </is>
       </c>
       <c r="T291" t="inlineStr">
@@ -32385,12 +32375,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>1af6a43a-e73b-4774-8e10-b9f2928ab133</t>
+          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>ca-cioos_ae7e017c-9211-4f98-b56e-90a4bbac161c</t>
+          <t>ca-cioos_bea3da72-dafe-4e25-b5b2-0176e0ffba44</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -32400,7 +32390,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Snuneymuxw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Chemainus River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -32446,7 +32436,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.88685, 49.19332], [-123.92494, 49.1612], [-123.92581, 49.13841], [-123.91159, 49.123], [-123.88023, 49.11117], [-123.85971, 49.12766], [-123.89792, 49.16196], [-123.88099, 49.18866], [-123.88685, 49.19332]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.66843, 48.91641], [-123.6484, 48.90105], [-123.6554, 48.88016], [-123.6751, 48.87641], [-123.68894, 48.88178], [-123.68329, 48.89633], [-123.67928, 48.90316], [-123.67136, 48.91722], [-123.66848, 48.91635], [-123.66843, 48.91641]]]}</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
@@ -32461,12 +32451,12 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>10.21966/k01q-wb27</t>
+          <t>10.21966/q2e0-j004</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt459vxCIH7YPRN9fp</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpszvIrt9OF8-BLQW2N</t>
         </is>
       </c>
       <c r="T292" t="inlineStr">
@@ -32495,12 +32485,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
+          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ca-cioos_bea3da72-dafe-4e25-b5b2-0176e0ffba44</t>
+          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -32510,7 +32500,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Chemainus River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -32556,7 +32546,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.66843, 48.91641], [-123.6484, 48.90105], [-123.6554, 48.88016], [-123.6751, 48.87641], [-123.68894, 48.88178], [-123.68329, 48.89633], [-123.67928, 48.90316], [-123.67136, 48.91722], [-123.66848, 48.91635], [-123.66843, 48.91641]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
@@ -32571,12 +32561,12 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>10.21966/q2e0-j004</t>
+          <t>10.21966/hjkj-6611</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpszvIrt9OF8-BLQW2N</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
         </is>
       </c>
       <c r="T293" t="inlineStr">
@@ -32605,12 +32595,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
+          <t>4c7b7347-767d-45e4-b3ad-7e0133b31e1c</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
+          <t>ca-cioos_dce15b7b-3772-4106-ab20-c3979c4c3f57</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -32620,7 +32610,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Fulmore River - Shoal Creek Estuary Complex (Provisional)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -32666,7 +32656,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.08798, 50.4777], [-126.09599, 50.48418], [-126.09046, 50.50918], [-126.0647, 50.52425], [-125.99698, 50.53569], [-125.93459, 50.56717], [-125.93173, 50.56202], [-125.93764, 50.55458], [-125.91055, 50.55134], [-125.89853, 50.54943], [-125.90063, 50.54466], [-125.96416, 50.53989], [-125.98973, 50.52043], [-126.06566, 50.5067], [-126.08779, 50.47789], [-126.08798, 50.4777]]]}</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
@@ -32681,12 +32671,12 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>10.21966/hjkj-6611</t>
+          <t>10.21966/g1cn-xs92</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptdJ8iUmLeOrdmqzrQ</t>
         </is>
       </c>
       <c r="T294" t="inlineStr">
@@ -32715,12 +32705,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>4c7b7347-767d-45e4-b3ad-7e0133b31e1c</t>
+          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>ca-cioos_dce15b7b-3772-4106-ab20-c3979c4c3f57</t>
+          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -32730,7 +32720,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Fulmore River - Shoal Creek Estuary Complex (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -32776,7 +32766,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.08798, 50.4777], [-126.09599, 50.48418], [-126.09046, 50.50918], [-126.0647, 50.52425], [-125.99698, 50.53569], [-125.93459, 50.56717], [-125.93173, 50.56202], [-125.93764, 50.55458], [-125.91055, 50.55134], [-125.89853, 50.54943], [-125.90063, 50.54466], [-125.96416, 50.53989], [-125.98973, 50.52043], [-126.06566, 50.5067], [-126.08779, 50.47789], [-126.08798, 50.4777]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
@@ -32791,12 +32781,12 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>10.21966/g1cn-xs92</t>
+          <t>10.21966/npe4-3036</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptdJ8iUmLeOrdmqzrQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
         </is>
       </c>
       <c r="T295" t="inlineStr">
@@ -32825,12 +32815,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
+          <t>35245eae-e508-47da-bcf7-54346cda086a</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
+          <t>ca-cioos_e9b72149-8cf1-4000-ae3e-6b29ad60b078</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -32840,7 +32830,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Malksope River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -32886,7 +32876,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.46569, 50.12556], [-127.45723, 50.13142], [-127.43281, 50.13338], [-127.42845, 50.13765], [-127.41181, 50.14408], [-127.40973, 50.14233], [-127.41999, 50.13627], [-127.41803, 50.13195], [-127.43106, 50.12796], [-127.46545, 50.12446], [-127.46569, 50.12548], [-127.46569, 50.12556]]]}</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
@@ -32901,12 +32891,12 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>10.21966/npe4-3036</t>
+          <t>10.21966/21sf-ey03</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq77iyWJfPg4z-FvOSb</t>
         </is>
       </c>
       <c r="T296" t="inlineStr">
@@ -32935,12 +32925,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>35245eae-e508-47da-bcf7-54346cda086a</t>
+          <t>5177d019-598e-4415-b778-9688403652c8</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>ca-cioos_e9b72149-8cf1-4000-ae3e-6b29ad60b078</t>
+          <t>ca-cioos_ed84df74-5a2d-4a7d-87c8-a7b93f11088e</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -32950,7 +32940,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Malksope River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Nalaxdlala River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -32996,7 +32986,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.46569, 50.12556], [-127.45723, 50.13142], [-127.43281, 50.13338], [-127.42845, 50.13765], [-127.41181, 50.14408], [-127.40973, 50.14233], [-127.41999, 50.13627], [-127.41803, 50.13195], [-127.43106, 50.12796], [-127.46545, 50.12446], [-127.46569, 50.12548], [-127.46569, 50.12556]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.9489, 50.70902], [-125.9696, 50.70291], [-126.00938, 50.69118], [-126.00108, 50.66848], [-125.98257, 50.68374], [-125.98152, 50.69271], [-125.95462, 50.70263], [-125.94785, 50.70768], [-125.9489, 50.70911], [-125.9489, 50.70902]]]}</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
@@ -33011,12 +33001,12 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>10.21966/21sf-ey03</t>
+          <t>10.21966/4krv-aw23</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq77iyWJfPg4z-FvOSb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptbxmpkBsfyWWfSxOJ</t>
         </is>
       </c>
       <c r="T297" t="inlineStr">
@@ -33045,12 +33035,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>5177d019-598e-4415-b778-9688403652c8</t>
+          <t>d320d90e-96bf-4993-81c5-f1f57886b0e6</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>ca-cioos_ed84df74-5a2d-4a7d-87c8-a7b93f11088e</t>
+          <t>ca-cioos_b922699f-69b6-4d63-b538-7c290086a408</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -33060,7 +33050,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Nalaxdlala River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Quw'utsun/Xwulqw'selu River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -33106,7 +33096,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.9489, 50.70902], [-125.9696, 50.70291], [-126.00938, 50.69118], [-126.00108, 50.66848], [-125.98257, 50.68374], [-125.98152, 50.69271], [-125.95462, 50.70263], [-125.94785, 50.70768], [-125.9489, 50.70911], [-125.9489, 50.70902]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.56201, 48.73508], [-123.59772, 48.75559], [-123.62127, 48.76514], [-123.63885, 48.77426], [-123.66935, 48.78033], [-123.67901, 48.75472], [-123.65155, 48.74322], [-123.63017, 48.7405], [-123.60792, 48.74289], [-123.56494, 48.72987], [-123.56179, 48.73529], [-123.56201, 48.73508]]]}</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
@@ -33121,17 +33111,17 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>10.21966/4krv-aw23</t>
+          <t>10.21966/2ha7-9p26</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptbxmpkBsfyWWfSxOJ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpsCA3ycwZ7bFTDIQxh</t>
         </is>
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
@@ -33155,12 +33145,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>d320d90e-96bf-4993-81c5-f1f57886b0e6</t>
+          <t>dd471e82-a6b8-4f32-891c-bbea26e9998e</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>ca-cioos_b922699f-69b6-4d63-b538-7c290086a408</t>
+          <t>ca-cioos_aeb30028-a7eb-462e-ac0f-6c5fe101d4a2</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -33170,7 +33160,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Quw'utsun/Xwulqw'selu River Estuary (Provisional)</t>
+          <t>DNA Metabarcoding Captures Temporal and Vertical Dynamics of Mesozooplankton Communities</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -33188,12 +33178,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Estuary Resilience</t>
+          <t>Genomics, Oceanography</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -33208,45 +33198,45 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.56201, 48.73508], [-123.59772, 48.75559], [-123.62127, 48.76514], [-123.63885, 48.77426], [-123.66935, 48.78033], [-123.67901, 48.75472], [-123.65155, 48.74322], [-123.63017, 48.7405], [-123.60792, 48.74289], [-123.56494, 48.72987], [-123.56179, 48.73529], [-123.56201, 48.73508]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.0992, 50.0307]}</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+          <t>[{'max': '260.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+          <t>zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>10.21966/2ha7-9p26</t>
+          <t>10.21966/6b20-7r76</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpsCA3ycwZ7bFTDIQxh</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OvzbmseH_syBXg1RXKd</t>
         </is>
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V299" t="n">
@@ -33265,12 +33255,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>dd471e82-a6b8-4f32-891c-bbea26e9998e</t>
+          <t>b27bb6f9-49ae-4f3a-a02a-098d8edf23e2</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>ca-cioos_aeb30028-a7eb-462e-ac0f-6c5fe101d4a2</t>
+          <t>ca-cioos_ac765dbb-8e47-415d-8685-d9090946b86b</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -33280,7 +33270,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>DNA Metabarcoding Captures Temporal and Vertical Dynamics of Mesozooplankton Communities</t>
+          <t>Micro-invertebrate DNA Barcodes from Quadra Island, BC (Biomarathon)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -33298,7 +33288,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Genomics, Oceanography</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -33318,45 +33308,45 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N300" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.0992, 50.0307]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.5461, 49.947], [-124.6642, 49.947], [-124.6642, 50.457], [-125.5461, 50.457], [-125.5461, 49.947]]]}</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>[{'max': '260.0', 'min': '0.0'}]</t>
+          <t>[{'max': '200.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>zooplanktonBiomassAndDiversity</t>
+          <t>invertebrateAbundanceAndDistribution, zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>10.21966/6b20-7r76</t>
+          <t>10.21966/qrxk-vb32</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OvzbmseH_syBXg1RXKd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxClAtvMEmxKRtywIeT</t>
         </is>
       </c>
       <c r="T300" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V300" t="n">
@@ -33375,12 +33365,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>b27bb6f9-49ae-4f3a-a02a-098d8edf23e2</t>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>ca-cioos_ac765dbb-8e47-415d-8685-d9090946b86b</t>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -33390,7 +33380,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Micro-invertebrate DNA Barcodes from Quadra Island, BC (Biomarathon)</t>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -33408,7 +33398,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -33428,7 +33418,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N301" t="n">
@@ -33436,37 +33426,33 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.5461, 49.947], [-124.6642, 49.947], [-124.6642, 50.457], [-125.5461, 50.457], [-125.5461, 49.947]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>[{'max': '200.0', 'min': '0.0'}]</t>
+          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
         </is>
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, zooplanktonBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>10.21966/qrxk-vb32</t>
+          <t>10.21966/w9n0-kn30</t>
         </is>
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxClAtvMEmxKRtywIeT</t>
-        </is>
-      </c>
-      <c r="T301" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr"/>
       <c r="U301" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="V301" t="n">
@@ -33478,112 +33464,6 @@
         </is>
       </c>
       <c r="X301" t="inlineStr"/>
-    </row>
-    <row r="302">
-      <c r="A302" t="n">
-        <v>300</v>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>CC-BY-4.0</t>
-        </is>
-      </c>
-      <c r="H302" t="b">
-        <v>0</v>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="M302" t="inlineStr">
-        <is>
-          <t>Tula Foundation</t>
-        </is>
-      </c>
-      <c r="N302" t="n">
-        <v>1</v>
-      </c>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
-        </is>
-      </c>
-      <c r="P302" t="inlineStr">
-        <is>
-          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
-        </is>
-      </c>
-      <c r="Q302" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R302" t="inlineStr">
-        <is>
-          <t>10.21966/w9n0-kn30</t>
-        </is>
-      </c>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
-        </is>
-      </c>
-      <c r="T302" t="inlineStr"/>
-      <c r="U302" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="V302" t="n">
-        <v>0</v>
-      </c>
-      <c r="W302" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X302" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -5447,12 +5447,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
+          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
+          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5518,17 +5518,17 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>10.21966/6zp4-ye07</t>
+          <t>10.21966/1.715784</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V47" t="n">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
+          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
+          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10.21966/zs6a-j496</t>
+          <t>10.21966/6zp4-ye07</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
+          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5738,17 +5738,17 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10.21966/1.715784</t>
+          <t>10.21966/zs6a-j496</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V49" t="n">
@@ -5769,9 +5769,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X49" t="n">
-        <v>1</v>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -15009,12 +15007,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15024,7 +15022,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15042,7 +15040,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15062,56 +15060,58 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N134" t="n">
+        <v>2</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>10.21966/1.135248</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X134" t="n">
         <v>1</v>
       </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
-        </is>
-      </c>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>10.21966/x6q2-me90</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="V134" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15119,12 +15119,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15172,20 +15172,20 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -15195,12 +15195,12 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>10.21966/1.135248</t>
+          <t>10.21966/x6q2-me90</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V135" t="n">
@@ -18193,7 +18193,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X162" t="inlineStr"/>
+      <c r="X162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -21281,12 +21283,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>52d607c9-46cd-4be9-a752-1b5446272f32</t>
+          <t>551bbe09-f182-478b-8d50-2f9a4dbd93ae</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ca-cioos_0507a738-cd65-4ba4-943e-42b9d022b637</t>
+          <t>ca-cioos_189dd319-d5ef-4f2a-a060-df8d47628b86</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -21296,7 +21298,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2021 - Hakai Airborne Coastal Observatory</t>
+          <t>Elliot Creek Landslide LiDAR Mapping - 2023 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -21314,7 +21316,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -21338,16 +21340,16 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.1, 50.5], [-121.7, 50.5], [-121.7, 51.12], [-122.1, 51.12], [-122.1, 50.5]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 51.0], [-124.8, 51.0], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '185.0'}]</t>
+          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
@@ -21357,12 +21359,12 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>10.21966/ytgc-6g46</t>
+          <t>10.21966/szqj-b355</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NHfqx-d8tuAroY8BWc7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRZqJivYfce75NOoBD</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
@@ -21372,7 +21374,7 @@
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V191" t="n">
@@ -21391,12 +21393,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>551bbe09-f182-478b-8d50-2f9a4dbd93ae</t>
+          <t>52d607c9-46cd-4be9-a752-1b5446272f32</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ca-cioos_189dd319-d5ef-4f2a-a060-df8d47628b86</t>
+          <t>ca-cioos_0507a738-cd65-4ba4-943e-42b9d022b637</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -21406,7 +21408,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Elliot Creek Landslide LiDAR Mapping - 2023 - Airborne Coastal Observatory</t>
+          <t>Fraser River Airborne Surveys - 2021 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -21424,7 +21426,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -21448,16 +21450,16 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 51.0], [-124.8, 51.0], [-124.8, 50.84]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.1, 50.5], [-121.7, 50.5], [-121.7, 51.12], [-122.1, 51.12], [-122.1, 50.5]]]}</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '185.0'}]</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -21467,12 +21469,12 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>10.21966/szqj-b355</t>
+          <t>10.21966/ytgc-6g46</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRZqJivYfce75NOoBD</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NHfqx-d8tuAroY8BWc7</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
@@ -21482,7 +21484,7 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V192" t="n">
@@ -21493,7 +21495,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X192" t="inlineStr"/>
+      <c r="X192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21501,12 +21505,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
+          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -21516,7 +21520,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -21558,16 +21562,16 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -21577,12 +21581,12 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>10.21966/e4b8-vp48</t>
+          <t>10.21966/thq7-0g08</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
@@ -21592,15 +21596,15 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="V193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
@@ -21611,12 +21615,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
+          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -21626,7 +21630,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -21668,16 +21672,16 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -21687,12 +21691,12 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>10.21966/bzr6-er66</t>
+          <t>10.21966/e4b8-vp48</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
@@ -21702,15 +21706,15 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
@@ -21721,12 +21725,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
+          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -21736,7 +21740,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
+          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -21754,12 +21758,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -21778,41 +21782,41 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '1.0'}]</t>
+          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>10.21966/jv5k-3k59</t>
+          <t>10.21966/bzr6-er66</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nh8VlPQ_m681tso87Gd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V195" t="n">
@@ -21831,12 +21835,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
+          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -21846,7 +21850,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
+          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -21864,12 +21868,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -21888,41 +21892,41 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '6.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>10.21966/8mpe-h081</t>
+          <t>10.21966/jv5k-3k59</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUR4a1V0N1UxYTc2U3Q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nh8VlPQ_m681tso87Gd</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="V196" t="n">
@@ -21941,12 +21945,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
+          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -21956,12 +21960,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
+          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>document</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -21974,7 +21978,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -21994,45 +21998,45 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>10.21966/xp9x-m243</t>
+          <t>10.21966/8mpe-h081</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NTLT7n49Ox3SnVoy6nW</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUR4a1V0N1UxYTc2U3Q</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V197" t="n">
@@ -22051,12 +22055,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
+          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -22066,12 +22070,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
+          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>document</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -22084,7 +22088,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -22104,7 +22108,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Hakai Geospatial</t>
         </is>
       </c>
       <c r="N198" t="n">
@@ -22112,12 +22116,12 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
@@ -22127,22 +22131,22 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>10.21966/qpe8-ay93</t>
+          <t>10.21966/xp9x-m243</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpurN_vwkhOgSJmgBh9</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NTLT7n49Ox3SnVoy6nW</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="V198" t="n">
@@ -22161,12 +22165,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
+          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -22176,7 +22180,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
+          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -22194,12 +22198,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -22222,37 +22226,37 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>[{'max': '75.0', 'min': '15.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>10.21966/fbv4-th96</t>
+          <t>10.21966/qpe8-ay93</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-O26fyGiVXoF__M22UrP</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpurN_vwkhOgSJmgBh9</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V199" t="n">
@@ -22271,12 +22275,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
+          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -22286,7 +22290,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
+          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -22304,7 +22308,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -22332,37 +22336,37 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>[{'max': '2.0', 'min': '0.0'}]</t>
+          <t>[{'max': '75.0', 'min': '15.0'}]</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>10.21966/36hp-7f40</t>
+          <t>10.21966/fbv4-th96</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-N1KAki3SSBEw0aHCoSv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-O26fyGiVXoF__M22UrP</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="V200" t="n">
@@ -22381,12 +22385,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
+          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -22396,7 +22400,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
+          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -22414,12 +22418,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -22442,37 +22446,37 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
+          <t>[{'max': '2.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>10.21966/wxph-tz51</t>
+          <t>10.21966/36hp-7f40</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKOQlOxJdTg_BFOoXb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-N1KAki3SSBEw0aHCoSv</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V201" t="n">
@@ -22491,12 +22495,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
+          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -22506,7 +22510,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
+          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -22524,12 +22528,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -22552,45 +22556,45 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>[{'max': '0.5', 'min': '0.5'}]</t>
+          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>10.21966/4kr2-jc55</t>
+          <t>10.21966/wxph-tz51</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NH0r8ddHNhVJ5bXkyqR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKOQlOxJdTg_BFOoXb</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
@@ -22601,12 +22605,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
+          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -22616,7 +22620,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Phytoplankton Pigment Time Series from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
+          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -22634,7 +22638,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -22662,45 +22666,45 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.5', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
+          <t>seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>10.21966/bw2d-tg65</t>
+          <t>10.21966/4kr2-jc55</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-O25qzW3OpioeACGpRHl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NH0r8ddHNhVJ5bXkyqR</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="V203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
@@ -22711,12 +22715,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
+          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -22726,7 +22730,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Phytoplankton Pigment Time Series from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -22744,12 +22748,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -22764,7 +22768,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N204" t="n">
@@ -22772,37 +22776,37 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>10.21966/pvy6-nw38</t>
+          <t>10.21966/bw2d-tg65</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O0G3gSlISPfB-f0u3Zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-O25qzW3OpioeACGpRHl</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V204" t="n">
@@ -22821,12 +22825,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
+          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -22836,7 +22840,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
+          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -22854,7 +22858,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -22874,7 +22878,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N205" t="n">
@@ -22882,40 +22886,48 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R205" t="inlineStr"/>
+          <t>other, inorganicCarbon</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>10.21966/pvy6-nw38</t>
+        </is>
+      </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OFhFpUJDNDF0hlFiGUV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O0G3gSlISPfB-f0u3Zz</t>
         </is>
       </c>
       <c r="T205" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="V205" t="inlineStr"/>
-      <c r="W205" t="inlineStr"/>
-      <c r="X205" t="n">
-        <v>2</v>
-      </c>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="V205" t="n">
+        <v>0</v>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22923,12 +22935,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
+          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -22938,7 +22950,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
+          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -22956,7 +22968,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -22984,12 +22996,12 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>[{'max': '254.0', 'min': '61.0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
@@ -22997,35 +23009,27 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>10.21966/zfxe-rd73</t>
-        </is>
-      </c>
+      <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCe-GBA4i93dk_I9uOR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OFhFpUJDNDF0hlFiGUV</t>
         </is>
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="V206" t="n">
-        <v>0</v>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr"/>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr"/>
+      <c r="W206" t="inlineStr"/>
+      <c r="X206" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23033,12 +23037,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
+          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -23048,7 +23052,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
+          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -23066,12 +23070,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -23094,37 +23098,37 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>[{'max': '15.0', 'min': '0.0'}]</t>
+          <t>[{'max': '254.0', 'min': '61.0'}]</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>10.21966/jj9p-d309</t>
+          <t>10.21966/zfxe-rd73</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtF5vh1GUMdwtJdYjoJ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCe-GBA4i93dk_I9uOR</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V207" t="n">
@@ -23143,12 +23147,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
+          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -23158,7 +23162,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
+          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -23176,12 +23180,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -23204,45 +23208,45 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>[{'max': '105.0', 'min': '0.0'}]</t>
+          <t>[{'max': '15.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>10.21966/529y-sh57</t>
+          <t>10.21966/jj9p-d309</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG736nDr1-1b51V4ZIc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtF5vh1GUMdwtJdYjoJ</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
@@ -23253,12 +23257,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
+          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
+          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -23268,7 +23272,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Understory kelp biomass data from BC Central Coast</t>
+          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -23286,12 +23290,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -23314,45 +23318,45 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '105.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>10.21966/wmsy-5g39</t>
+          <t>10.21966/529y-sh57</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtGQFN6AV5bNminNtYH</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG736nDr1-1b51V4ZIc</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
@@ -23363,12 +23367,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
+          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -23378,7 +23382,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
+          <t>Understory kelp biomass data from BC Central Coast</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -23396,12 +23400,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -23424,37 +23428,37 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>10.21966/8yp1-7m94</t>
+          <t>10.21966/wmsy-5g39</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKR1jead4rZb1ooVa6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtGQFN6AV5bNminNtYH</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V210" t="n">
@@ -23473,12 +23477,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
+          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -23488,7 +23492,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
+          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -23506,7 +23510,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -23534,12 +23538,12 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
@@ -23549,22 +23553,22 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>10.21966/g64t-ec45</t>
+          <t>10.21966/8yp1-7m94</t>
         </is>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICfZ5e-2vhf5NUtDZS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKR1jead4rZb1ooVa6</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V211" t="n">
@@ -23583,12 +23587,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
+          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
+          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -23598,7 +23602,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
+          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -23636,7 +23640,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N212" t="n">
@@ -23644,12 +23648,12 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
+          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -23659,12 +23663,12 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>10.21966/0ydj-0t79</t>
+          <t>10.21966/g64t-ec45</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICMGpnoARQcIltW087</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICfZ5e-2vhf5NUtDZS</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
@@ -23693,12 +23697,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
+          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -23708,12 +23712,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
+          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -23746,7 +23750,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N213" t="n">
@@ -23754,12 +23758,12 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -23769,22 +23773,22 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>10.21966/6x1v-1v62</t>
+          <t>10.21966/0ydj-0t79</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OIMCEnEEW63IyHyYZOM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICMGpnoARQcIltW087</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="V213" t="n">
@@ -23803,12 +23807,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
+          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -23818,12 +23822,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Calliarthron 2023 Experiment - Environmental Data</t>
+          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -23836,7 +23840,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -23856,7 +23860,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N214" t="n">
@@ -23864,37 +23868,37 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>10.21966/7nwn-bj60</t>
+          <t>10.21966/6x1v-1v62</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O6XAwxhj0r9Xs-V2QSA</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OIMCEnEEW63IyHyYZOM</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V214" t="n">
@@ -23905,9 +23909,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X214" t="n">
-        <v>1</v>
-      </c>
+      <c r="X214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23915,12 +23917,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
+          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -23930,7 +23932,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
+          <t>Calliarthron 2023 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -23948,7 +23950,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -23968,7 +23970,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N215" t="n">
@@ -23976,27 +23978,27 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>10.21966/ks82-th39</t>
+          <t>10.21966/7nwn-bj60</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP2QaXeKeZ30lz51gEE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O6XAwxhj0r9Xs-V2QSA</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
@@ -24006,7 +24008,7 @@
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="V215" t="n">
@@ -24017,7 +24019,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X215" t="inlineStr"/>
+      <c r="X215" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24025,12 +24029,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
+          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -24040,7 +24044,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -24058,7 +24062,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -24086,12 +24090,12 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -24101,12 +24105,12 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>10.21966/n3b4-d226</t>
+          <t>10.21966/ks82-th39</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NM0zdQjdjAMBZ4cN8ou</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP2QaXeKeZ30lz51gEE</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
@@ -24124,7 +24128,7 @@
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X216" t="inlineStr"/>
@@ -24135,12 +24139,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
+          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -24150,7 +24154,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -24196,12 +24200,12 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
+          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
@@ -24211,22 +24215,22 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>10.21966/p6jv-pe95</t>
+          <t>10.21966/n3b4-d226</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP86akjVj471Wit4O2y</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NM0zdQjdjAMBZ4cN8ou</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V217" t="n">
@@ -24234,7 +24238,7 @@
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="X217" t="inlineStr"/>
@@ -24245,12 +24249,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
+          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -24260,7 +24264,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -24278,7 +24282,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -24298,7 +24302,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N218" t="n">
@@ -24306,37 +24310,37 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>inorganicCarbon, other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>10.21966/q1m4-pz94</t>
+          <t>10.21966/p6jv-pe95</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OMsFWHXIwEWiFjwQeEo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP86akjVj471Wit4O2y</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V218" t="n">
@@ -24347,9 +24351,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X218" t="n">
-        <v>1</v>
-      </c>
+      <c r="X218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24357,12 +24359,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
+          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -24372,7 +24374,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Sea Stars 2024 Experiment - Environmental Data</t>
+          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -24410,7 +24412,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N219" t="n">
@@ -24433,12 +24435,12 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>10.21966/jkf5-ss08</t>
+          <t>10.21966/q1m4-pz94</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OIMW8OO0buhOm_kHuIz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OMsFWHXIwEWiFjwQeEo</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
@@ -24448,7 +24450,7 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="V219" t="n">
@@ -24469,12 +24471,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
+          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -24484,7 +24486,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
+          <t>Sea Stars 2024 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -24502,7 +24504,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -24522,15 +24524,15 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Gulf Islands National Park Reserve</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24540,27 +24542,27 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>inorganicCarbon, other</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>10.21966/x3jm-p494</t>
+          <t>10.21966/jkf5-ss08</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OUG8anVj4yBJDEHy6Wj</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OIMW8OO0buhOm_kHuIz</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="V220" t="n">
@@ -24571,7 +24573,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X220" t="inlineStr"/>
+      <c r="X220" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24579,12 +24583,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
+          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -24594,7 +24598,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
+          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -24612,12 +24616,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -24632,7 +24636,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Gulf Islands National Park Reserve</t>
         </is>
       </c>
       <c r="N221" t="n">
@@ -24640,50 +24644,48 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>[{'max': '350.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>zooplanktonBiomassAndDiversity</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>10.21966/g7zf-1v08</t>
+          <t>10.21966/x3jm-p494</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-ODO1YbIGbR3Rd8hvLxT</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OUG8anVj4yBJDEHy6Wj</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 2}]</t>
-        </is>
-      </c>
-      <c r="X221" t="n">
-        <v>1</v>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24691,12 +24693,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
+          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -24706,7 +24708,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
+          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -24748,7 +24750,7 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -24767,12 +24769,12 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>10.21966/tcp2-mm86</t>
+          <t>10.21966/g7zf-1v08</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NZb1YZT9Xtbc9Cp9Jc3OtSLRffT2/-OQtxgedRzyaVsL4bWUx</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-ODO1YbIGbR3Rd8hvLxT</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
@@ -24782,7 +24784,7 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="V222" t="n">
@@ -24793,7 +24795,9 @@
           <t>[{'year': '2026', 'total': 2}]</t>
         </is>
       </c>
-      <c r="X222" t="inlineStr"/>
+      <c r="X222" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24801,12 +24805,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
+          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -24816,7 +24820,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
+          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -24834,12 +24838,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -24862,32 +24866,32 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '350.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>10.21966/w08z-zk15</t>
+          <t>10.21966/tcp2-mm86</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPFZem68YnizN7L7l</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NZb1YZT9Xtbc9Cp9Jc3OtSLRffT2/-OQtxgedRzyaVsL4bWUx</t>
         </is>
       </c>
       <c r="T223" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="U223" t="inlineStr">
@@ -24896,11 +24900,11 @@
         </is>
       </c>
       <c r="V223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 2}]</t>
         </is>
       </c>
       <c r="X223" t="inlineStr"/>
@@ -24911,12 +24915,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
+          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
+          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -24926,7 +24930,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -24944,7 +24948,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -24972,7 +24976,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -24987,12 +24991,12 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>10.21966/kqzp-f639</t>
+          <t>10.21966/w08z-zk15</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NbzgAmVWcvz-_SOMA0E</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPFZem68YnizN7L7l</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
@@ -25021,12 +25025,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
+          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -25036,7 +25040,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -25054,7 +25058,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -25082,7 +25086,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -25097,12 +25101,12 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>10.21966/qs1b-g693</t>
+          <t>10.21966/kqzp-f639</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-O8Dvx_fnz1WMY_Wetch</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NbzgAmVWcvz-_SOMA0E</t>
         </is>
       </c>
       <c r="T225" t="inlineStr">
@@ -25112,7 +25116,7 @@
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V225" t="n">
@@ -25131,12 +25135,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
+          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -25146,7 +25150,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -25164,12 +25168,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -25184,7 +25188,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N226" t="n">
@@ -25192,7 +25196,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -25207,30 +25211,30 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>10.21966/9cbv-ra30</t>
+          <t>10.21966/qs1b-g693</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OVIwXhdGT9n7FV0wmyz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-O8Dvx_fnz1WMY_Wetch</t>
         </is>
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="V226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X226" t="inlineStr"/>
@@ -25241,12 +25245,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
+          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -25256,7 +25260,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
+          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -25274,12 +25278,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore, Oceanography</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -25294,53 +25298,53 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N227" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>10.21966/8sgn-jg38</t>
+          <t>10.21966/9cbv-ra30</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-Nd0YqVrleM4mMLlJDSU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OVIwXhdGT9n7FV0wmyz</t>
         </is>
       </c>
       <c r="T227" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="V227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="X227" t="inlineStr"/>
@@ -25351,12 +25355,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
+          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -25366,7 +25370,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
+          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -25384,7 +25388,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Genomics, Nearshore, Oceanography</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -25408,41 +25412,41 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>[{'max': '60.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>10.21966/vdyq-r660</t>
+          <t>10.21966/8sgn-jg38</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORCQx4QHUuJ1NV1SEig</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-Nd0YqVrleM4mMLlJDSU</t>
         </is>
       </c>
       <c r="T228" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V228" t="n">
@@ -25461,12 +25465,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
+          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -25476,7 +25480,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
+          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -25494,7 +25498,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -25518,41 +25522,41 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '60.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>microbeBiomassAndDiversity</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>10.21966/4dvn-5y90</t>
+          <t>10.21966/vdyq-r660</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/24mf0TP0vkh6bmNOOA3ynoTFPNJ2/-OX0Xm6VoYH22oc68Jfp</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORCQx4QHUuJ1NV1SEig</t>
         </is>
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V229" t="n">
@@ -25571,12 +25575,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
+          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -25586,7 +25590,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
+          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -25604,7 +25608,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Genomics, Nearshore</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -25628,11 +25632,11 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25642,27 +25646,27 @@
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>10.21966/m93t-4181</t>
+          <t>10.21966/4dvn-5y90</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPEiAvbPxw16A-L6I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/24mf0TP0vkh6bmNOOA3ynoTFPNJ2/-OX0Xm6VoYH22oc68Jfp</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V230" t="n">
@@ -25681,12 +25685,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
+          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -25696,7 +25700,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -25742,7 +25746,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -25757,12 +25761,12 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>10.21966/ntdg-e790</t>
+          <t>10.21966/m93t-4181</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8raBb8T2xZJ-oRzesS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPEiAvbPxw16A-L6I</t>
         </is>
       </c>
       <c r="T231" t="inlineStr">
@@ -25772,7 +25776,7 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V231" t="n">
@@ -25791,12 +25795,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
+          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -25806,7 +25810,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -25816,7 +25820,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H232" t="b">
@@ -25824,7 +25828,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -25852,45 +25856,45 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>[{'max': '475.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>10.21966/0xex-r023</t>
+          <t>10.21966/ntdg-e790</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OdPFhWCkXwvqjCqum30</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8raBb8T2xZJ-oRzesS</t>
         </is>
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X232" t="inlineStr"/>
@@ -25901,12 +25905,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
+          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -25916,7 +25920,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Mapping Project</t>
+          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -25934,12 +25938,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -25962,12 +25966,12 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '475.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
@@ -25977,12 +25981,12 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>10.21966/2aap-hn61</t>
+          <t>10.21966/0xex-r023</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Oa5tvTh2mXFQbI3SkzK</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OdPFhWCkXwvqjCqum30</t>
         </is>
       </c>
       <c r="T233" t="inlineStr">
@@ -25992,7 +25996,7 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="V233" t="n">
@@ -26011,12 +26015,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
+          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -26026,7 +26030,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
+          <t>Gitga'at Territory Coastal Mapping Project</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -26036,7 +26040,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H234" t="b">
@@ -26049,7 +26053,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -26072,12 +26076,12 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
@@ -26087,17 +26091,17 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>10.21966/fv0q-q364</t>
+          <t>10.21966/2aap-hn61</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeY_smu3pJj8TBE9ivK</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Oa5tvTh2mXFQbI3SkzK</t>
         </is>
       </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="U234" t="inlineStr">
@@ -26121,12 +26125,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
+          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -26136,7 +26140,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
+          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -26154,7 +26158,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -26182,7 +26186,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -26192,17 +26196,17 @@
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>10.21966/nwg7-fe05</t>
+          <t>10.21966/fv0q-q364</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeItznXpvEFI_t-jsCl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeY_smu3pJj8TBE9ivK</t>
         </is>
       </c>
       <c r="T235" t="inlineStr">
@@ -26216,11 +26220,11 @@
         </is>
       </c>
       <c r="V235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="X235" t="inlineStr"/>
@@ -26231,12 +26235,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
+          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
+          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -26246,7 +26250,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -26264,7 +26268,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -26292,32 +26296,32 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>10.21966/02qp-4945</t>
+          <t>10.21966/nwg7-fe05</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OeTbb0MbfTCH-YFCNGG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeItznXpvEFI_t-jsCl</t>
         </is>
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="U236" t="inlineStr">
@@ -26341,12 +26345,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
+          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
+          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -26356,7 +26360,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
+          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -26402,12 +26406,12 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
+          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
@@ -26417,17 +26421,17 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>10.21966/dtt0-s264</t>
+          <t>10.21966/02qp-4945</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OgDkxI9LmB0KWXvOsZe</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OeTbb0MbfTCH-YFCNGG</t>
         </is>
       </c>
       <c r="T237" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="U237" t="inlineStr">
@@ -26451,12 +26455,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
+          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -26466,7 +26470,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
+          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -26484,12 +26488,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -26512,37 +26516,37 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>10.21966/xc7x-9207</t>
+          <t>10.21966/dtt0-s264</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OZGbDlZ5dgF0dD-ceZ7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OgDkxI9LmB0KWXvOsZe</t>
         </is>
       </c>
       <c r="T238" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V238" t="n">
@@ -26561,12 +26565,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
+          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -26576,7 +26580,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Hakai Institute Drone Data Index</t>
+          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -26594,7 +26598,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -26622,37 +26626,37 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>10.21966/0r8b-t282</t>
+          <t>10.21966/xc7x-9207</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCdraToZivfj6ZZ8TqZ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OZGbDlZ5dgF0dD-ceZ7</t>
         </is>
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V239" t="n">
@@ -26671,12 +26675,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
+          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -26686,7 +26690,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Hakai Institute Drone Data Index</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -26704,12 +26708,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -26732,37 +26736,47 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R240" t="inlineStr"/>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>10.21966/0r8b-t282</t>
+        </is>
+      </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OlwZ9MM8a9VqCYIJo4W</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCdraToZivfj6ZZ8TqZ</t>
         </is>
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="V240" t="inlineStr"/>
-      <c r="W240" t="inlineStr"/>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V240" t="n">
+        <v>0</v>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="X240" t="inlineStr"/>
     </row>
     <row r="241">
@@ -26771,12 +26785,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
+          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -26786,7 +26800,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -26809,7 +26823,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -26842,17 +26856,13 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R241" t="inlineStr">
-        <is>
-          <t>10.21966/4jvz-bv44</t>
-        </is>
-      </c>
+          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OOYvTmfsWUPdHkDTTFS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OlwZ9MM8a9VqCYIJo4W</t>
         </is>
       </c>
       <c r="T241" t="inlineStr">
@@ -26862,17 +26872,11 @@
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="V241" t="n">
-        <v>0</v>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr"/>
+      <c r="W241" t="inlineStr"/>
       <c r="X241" t="inlineStr"/>
     </row>
     <row r="242">
@@ -26881,12 +26885,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
+          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
+          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -26896,7 +26900,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -26914,12 +26918,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -26942,7 +26946,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -26952,27 +26956,27 @@
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>10.21966/cqrt-sk09</t>
+          <t>10.21966/4jvz-bv44</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-Oj8Fegu6V858hz57O8z</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OOYvTmfsWUPdHkDTTFS</t>
         </is>
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="V242" t="n">
@@ -26991,12 +26995,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
+          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -27006,7 +27010,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
+          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -27052,7 +27056,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
@@ -27067,35 +27071,33 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>10.21966/chc3-rj93</t>
+          <t>10.21966/cqrt-sk09</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-OnCm7wniBlFr2gSXQhf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-Oj8Fegu6V858hz57O8z</t>
         </is>
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="V243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
-        </is>
-      </c>
-      <c r="X243" t="n">
-        <v>1</v>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27103,12 +27105,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
+          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -27118,7 +27120,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
+          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -27136,7 +27138,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -27164,12 +27166,12 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>[{'max': '850.0', 'min': '400.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
@@ -27179,33 +27181,35 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>10.21966/f9m6-qg12</t>
+          <t>10.21966/chc3-rj93</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MibW0TZpoaJ4Ih_2ev7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-OnCm7wniBlFr2gSXQhf</t>
         </is>
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr"/>
+          <t>[{'year': '2026', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="X244" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27213,12 +27217,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
+          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -27228,7 +27232,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
+          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -27246,12 +27250,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -27270,41 +27274,41 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '850.0', 'min': '400.0'}]</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>10.21966/a0v4-x512</t>
+          <t>10.21966/f9m6-qg12</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MibW0TZpoaJ4Ih_2ev7</t>
         </is>
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="V245" t="n">
@@ -27323,12 +27327,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
+          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -27338,7 +27342,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -27356,12 +27360,12 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -27380,31 +27384,31 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>10.21966/NMNG-SF35</t>
+          <t>10.21966/a0v4-x512</t>
         </is>
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
         </is>
       </c>
       <c r="T246" t="inlineStr">
@@ -27414,7 +27418,7 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V246" t="n">
@@ -27433,12 +27437,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
+          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
+          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -27448,7 +27452,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
+          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -27466,12 +27470,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -27494,37 +27498,37 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition, other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>10.21966/20ym-8826</t>
+          <t>10.21966/NMNG-SF35</t>
         </is>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
         </is>
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="V247" t="n">
@@ -27543,12 +27547,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
+          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
+          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -27558,7 +27562,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profilers, BC, Canada (Research)</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -27576,12 +27580,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -27600,41 +27604,41 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>macroalgalCanopyCoverAndComposition, other</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>10.21966/kace-2d24</t>
+          <t>10.21966/20ym-8826</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
         </is>
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V248" t="n">
@@ -27653,12 +27657,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
+          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -27668,7 +27672,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profilers, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -27686,12 +27690,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -27710,31 +27714,31 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '20.0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>10.21966/65d8-k051</t>
+          <t>10.21966/kace-2d24</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
@@ -27744,7 +27748,7 @@
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V249" t="n">
@@ -27763,12 +27767,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
+          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -27778,7 +27782,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -27801,7 +27805,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -27824,37 +27828,37 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '20.0'}]</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
+          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>10.21966/175j-8k96</t>
+          <t>10.21966/65d8-k051</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
         </is>
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V250" t="n">
@@ -27865,9 +27869,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X250" t="n">
-        <v>2</v>
-      </c>
+      <c r="X250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27875,12 +27877,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
+          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -27890,7 +27892,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
+          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -27951,12 +27953,12 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>10.21966/dveq-bt48</t>
+          <t>10.21966/175j-8k96</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
         </is>
       </c>
       <c r="T251" t="inlineStr">
@@ -27966,7 +27968,7 @@
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V251" t="n">
@@ -27987,12 +27989,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
+          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -28002,7 +28004,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -28020,12 +28022,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -28044,52 +28046,54 @@
         </is>
       </c>
       <c r="N252" t="n">
+        <v>1</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>10.21966/dveq-bt48</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="V252" t="n">
+        <v>0</v>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X252" t="n">
         <v>2</v>
       </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
-        </is>
-      </c>
-      <c r="P252" t="inlineStr">
-        <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R252" t="inlineStr">
-        <is>
-          <t>10.21966/RZVW-4A72</t>
-        </is>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="V252" t="n">
-        <v>1</v>
-      </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
-        </is>
-      </c>
-      <c r="X252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28097,12 +28101,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
+          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -28112,7 +28116,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
+          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -28130,7 +28134,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -28158,45 +28162,45 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>10.21966/0xvh-1318</t>
+          <t>10.21966/RZVW-4A72</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
         </is>
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="X253" t="inlineStr"/>
@@ -28207,12 +28211,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
+          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -28222,7 +28226,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -28240,12 +28244,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -28268,37 +28272,37 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>10.21966/3q5j-n957</t>
+          <t>10.21966/0xvh-1318</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
         </is>
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V254" t="n">
@@ -28317,12 +28321,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
+          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -28332,7 +28336,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
+          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -28350,12 +28354,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -28374,41 +28378,41 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>10.21966/kmc2-5r12</t>
+          <t>10.21966/3q5j-n957</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="V255" t="n">
@@ -28427,12 +28431,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
+          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ca-cioos_7e49967a-b5ab-443d-860b-e3c0eb0f709c</t>
+          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -28442,7 +28446,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Horne Lake Bathymetry Mapping</t>
+          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -28460,7 +28464,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -28484,41 +28488,41 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.7872, 49.3105], [-124.6447, 49.3105], [-124.6447, 49.3644], [-124.7872, 49.3644], [-124.7872, 49.3105]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>10.21966/vwee-e004</t>
+          <t>10.21966/kmc2-5r12</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/G8LjsjnnPxb5TxWL730BxDTQu532/-Njn-0LeJ-Uwj4L8EmOV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
         </is>
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="V256" t="n">
@@ -28537,12 +28541,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>18f56a52-11af-446a-aea9-07feca8d197e</t>
+          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ca-cioos_e897c9d0-3fca-4c89-b37f-e571413ffd12</t>
+          <t>ca-cioos_7e49967a-b5ab-443d-860b-e3c0eb0f709c</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -28552,7 +28556,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Joffre Provincial Park Aerial Surveys - 2025 - Airborne Coastal Observatory</t>
+          <t>Horne Lake Bathymetry Mapping</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -28570,7 +28574,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -28598,12 +28602,12 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.5281, 50.3147], [-122.4303, 50.3147], [-122.4303, 50.3796], [-122.5281, 50.3796], [-122.5281, 50.3147]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.7872, 49.3105], [-124.6447, 49.3105], [-124.6447, 49.3644], [-124.7872, 49.3644], [-124.7872, 49.3105]]]}</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>[{'max': '475.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
@@ -28613,12 +28617,12 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>10.21966/k0z0-3z50</t>
+          <t>10.21966/vwee-e004</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ot_OaAHxjund0-w5rXq</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/G8LjsjnnPxb5TxWL730BxDTQu532/-Njn-0LeJ-Uwj4L8EmOV</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
@@ -28628,7 +28632,7 @@
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="V257" t="n">
@@ -28647,12 +28651,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>6c4803cc-d1c6-4327-806a-7f6796606175</t>
+          <t>18f56a52-11af-446a-aea9-07feca8d197e</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ca-cioos_6c34ed6e-5a17-41f2-b83a-cd59d1ce07bd</t>
+          <t>ca-cioos_e897c9d0-3fca-4c89-b37f-e571413ffd12</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -28662,7 +28666,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Knight Inlet Multibeam Bathymetry Survey</t>
+          <t>Joffre Provincial Park Aerial Surveys - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -28680,7 +28684,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -28708,12 +28712,12 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0537, 50.6529], [-125.9229, 50.6529], [-125.9229, 50.7077], [-126.0537, 50.7077], [-126.0537, 50.6529]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.5281, 50.3147], [-122.4303, 50.3147], [-122.4303, 50.3796], [-122.5281, 50.3796], [-122.5281, 50.3147]]]}</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>[{'max': '288.0', 'min': '0.0'}]</t>
+          <t>[{'max': '475.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
@@ -28723,17 +28727,17 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>10.21966/8dgz-1z27</t>
+          <t>10.21966/k0z0-3z50</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG7EOynnzSIOU7LPWgs</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ot_OaAHxjund0-w5rXq</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
@@ -28757,12 +28761,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ce6f3f8c-6b57-4f18-be46-8c0b5a4baeb9</t>
+          <t>6c4803cc-d1c6-4327-806a-7f6796606175</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ca-cioos_8755f475-2133-4205-baff-5e2937824f45</t>
+          <t>ca-cioos_6c34ed6e-5a17-41f2-b83a-cd59d1ce07bd</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -28772,7 +28776,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Poole Creek Aerial Surveys - Airborne Coastal Observatory</t>
+          <t>Knight Inlet Multibeam Bathymetry Survey</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -28790,7 +28794,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -28818,12 +28822,12 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.9075, 50.2436], [-122.8124, 50.2436], [-122.8124, 50.3016], [-122.9075, 50.3016], [-122.9075, 50.2436]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0537, 50.6529], [-125.9229, 50.6529], [-125.9229, 50.7077], [-126.0537, 50.7077], [-126.0537, 50.6529]]]}</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>[{'max': '450.0', 'min': '200.0'}]</t>
+          <t>[{'max': '288.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
@@ -28833,12 +28837,12 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>10.21966/g8f2-jw82</t>
+          <t>10.21966/8dgz-1z27</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OtfdtO43um_1J_LdCpn</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG7EOynnzSIOU7LPWgs</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
@@ -28867,12 +28871,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>e1247209-cc26-4788-82a2-dd8a5c971e22</t>
+          <t>ce6f3f8c-6b57-4f18-be46-8c0b5a4baeb9</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ca-cioos_2e5ddbaa-4f0c-4339-8595-1ddbd35c3df4</t>
+          <t>ca-cioos_8755f475-2133-4205-baff-5e2937824f45</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -28882,7 +28886,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Aerial Surveys in British Columbia, Washington, and Alberta - 2025 - Airborne Coastal Observatory</t>
+          <t>Poole Creek Aerial Surveys - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -28928,12 +28932,12 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.9263, 48.0077], [-112.7224, 48.0077], [-112.7224, 54.6673], [-127.9263, 54.6673], [-127.9263, 48.0077]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9075, 50.2436], [-122.8124, 50.2436], [-122.8124, 50.3016], [-122.9075, 50.3016], [-122.9075, 50.2436]]]}</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>[{'max': '4019.0', 'min': '0.0'}]</t>
+          <t>[{'max': '450.0', 'min': '200.0'}]</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
@@ -28943,22 +28947,22 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>10.21966/n6ga-nc24</t>
+          <t>10.21966/g8f2-jw82</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ou3t_K6rGOHTMO67Xbq</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OtfdtO43um_1J_LdCpn</t>
         </is>
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="V260" t="n">
@@ -28977,12 +28981,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>5ac3ac5f-702e-43d8-bcb7-79f30c4d9e08</t>
+          <t>e1247209-cc26-4788-82a2-dd8a5c971e22</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ca-cioos_656ea307-fed0-48ca-b5d8-1bc017dc52d2</t>
+          <t>ca-cioos_2e5ddbaa-4f0c-4339-8595-1ddbd35c3df4</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -28992,7 +28996,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Botanical Beach - Juan de Fuca Provincial Park - Drone Mapping</t>
+          <t>Glacier and Icefield Aerial Surveys in British Columbia, Washington, and Alberta - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -29010,7 +29014,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -29038,12 +29042,12 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.45265489, 48.52152402], [-124.43377214, 48.52152402], [-124.43377214, 48.53061904], [-124.45265489, 48.53061904], [-124.45265489, 48.52152402]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.9263, 48.0077], [-112.7224, 48.0077], [-112.7224, 54.6673], [-127.9263, 54.6673], [-127.9263, 48.0077]]]}</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+          <t>[{'max': '4019.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
@@ -29053,12 +29057,12 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>10.21966/kn3e-fn08</t>
+          <t>10.21966/n6ga-nc24</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdvcmtQME1NZmdWcDY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ou3t_K6rGOHTMO67Xbq</t>
         </is>
       </c>
       <c r="T261" t="inlineStr">
@@ -29087,12 +29091,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>05dac0a6-a26c-4cb5-895d-132b5e2134cd</t>
+          <t>5ac3ac5f-702e-43d8-bcb7-79f30c4d9e08</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ca-cioos_b45dbc9d-bf7a-4734-86cd-3397e7c9ac62</t>
+          <t>ca-cioos_656ea307-fed0-48ca-b5d8-1bc017dc52d2</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -29102,7 +29106,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Sea surface temperature data in False Creek, British Columbia</t>
+          <t>Botanical Beach - Juan de Fuca Provincial Park - Drone Mapping</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -29120,7 +29124,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -29148,37 +29152,37 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.45265489, 48.52152402], [-124.43377214, 48.52152402], [-124.43377214, 48.53061904], [-124.45265489, 48.53061904], [-124.45265489, 48.52152402]]]}</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>[{'max': '0.5', 'min': '0.5'}]</t>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>10.21966/0g6d-pk30</t>
+          <t>10.21966/kn3e-fn08</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NHaXDtgFZr0-Oul6FZG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdvcmtQME1NZmdWcDY</t>
         </is>
       </c>
       <c r="T262" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="V262" t="n">
@@ -29197,12 +29201,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>6eb46e26-dac5-4964-8b29-8e8541381aac</t>
+          <t>05dac0a6-a26c-4cb5-895d-132b5e2134cd</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
+          <t>ca-cioos_b45dbc9d-bf7a-4734-86cd-3397e7c9ac62</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -29212,7 +29216,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Time series of eelgrass (Zostera marina) meadow extent derived from drone surveys, Central Coast, British Columbia</t>
+          <t>Sea surface temperature data in False Creek, British Columbia</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -29230,12 +29234,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -29258,37 +29262,37 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28]]]}</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.5', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>10.21966/03pw-2190</t>
+          <t>10.21966/0g6d-pk30</t>
         </is>
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NHaXDtgFZr0-Oul6FZG</t>
         </is>
       </c>
       <c r="T263" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="V263" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X302"/>
+  <dimension ref="A1:X301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8462,16 +8462,16 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>10.21966/5rp3-3207</t>
+          <t>10.21966/awsk-my87</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V74" t="n">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8572,16 +8572,16 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10.21966/awsk-my87</t>
+          <t>10.21966/5rp3-3207</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V75" t="n">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ca-cioos_7e0f0bbc-507a-4ca0-bafc-1cc3e56db028</t>
+          <t>ca-cioos_7de69ca8-b3f3-4761-b441-dfc9e63b1fbc</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hakai physical plan and utility lines – Calvert Island Field Station - 2006</t>
+          <t>Rocky Intertidal RPAS Mapping Project - BC Central Coast - Canada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -11652,16 +11652,16 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13541603114572, 51.65216411387959], [-128.12786293055976, 51.65216411387959], [-128.12786293055976, 51.6557318761607], [-128.13541603114572, 51.6557318761607], [-128.13541603114572, 51.65216411387959]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6286, 48.1332], [-122.8941, 48.1332], [-122.8941, 51.9689], [-128.6286, 51.9689], [-128.6286, 48.1332]]]}</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>10.21966/3yew-5r94</t>
+          <t>10.21966/mc7v-dx06</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU9IR0RmSHlkRW1sd2k</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBVWDBQSFpnWjBBS0Q</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V103" t="n">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ca-cioos_7de69ca8-b3f3-4761-b441-dfc9e63b1fbc</t>
+          <t>ca-cioos_7e0f0bbc-507a-4ca0-bafc-1cc3e56db028</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rocky Intertidal RPAS Mapping Project - BC Central Coast - Canada</t>
+          <t>Hakai physical plan and utility lines – Calvert Island Field Station - 2006</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11762,16 +11762,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6286, 48.1332], [-122.8941, 48.1332], [-122.8941, 51.9689], [-128.6286, 51.9689], [-128.6286, 48.1332]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13541603114572, 51.65216411387959], [-128.12786293055976, 51.65216411387959], [-128.12786293055976, 51.6557318761607], [-128.13541603114572, 51.6557318761607], [-128.13541603114572, 51.65216411387959]]]}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>10.21966/mc7v-dx06</t>
+          <t>10.21966/3yew-5r94</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBVWDBQSFpnWjBBS0Q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU9IR0RmSHlkRW1sd2k</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V104" t="n">
@@ -15005,12 +15005,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15058,20 +15058,20 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/1.135248</t>
+          <t>10.21966/x6q2-me90</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V134" t="n">
@@ -15115,12 +15115,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15168,20 +15168,20 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>10.21966/x6q2-me90</t>
+          <t>10.21966/1.135248</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="V135" t="n">
@@ -20609,9 +20609,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X184" t="n">
-        <v>1</v>
-      </c>
+      <c r="X184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -27431,12 +27429,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
+          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
+          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -27446,7 +27444,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -27464,12 +27462,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -27492,37 +27490,37 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>macroalgalCanopyCoverAndComposition, other</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>10.21966/NMNG-SF35</t>
+          <t>10.21966/20ym-8826</t>
         </is>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
         </is>
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V247" t="n">
@@ -27541,12 +27539,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
+          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
+          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -27556,7 +27554,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profilers, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -27574,12 +27572,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -27598,41 +27596,41 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition, other</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>10.21966/20ym-8826</t>
+          <t>10.21966/kace-2d24</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
         </is>
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V248" t="n">
@@ -27651,12 +27649,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
+          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -27666,7 +27664,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profilers, BC, Canada (Research)</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -27684,12 +27682,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -27708,31 +27706,31 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '20.0', 'min': '20.0'}]</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>10.21966/kace-2d24</t>
+          <t>10.21966/65d8-k051</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
@@ -27742,7 +27740,7 @@
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V249" t="n">
@@ -27761,12 +27759,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
+          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -27776,7 +27774,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
+          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -27799,7 +27797,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -27822,37 +27820,37 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '20.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>10.21966/65d8-k051</t>
+          <t>10.21966/175j-8k96</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
         </is>
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V250" t="n">
@@ -27863,7 +27861,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X250" t="inlineStr"/>
+      <c r="X250" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27871,12 +27871,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
+          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
+          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -27947,12 +27947,12 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>10.21966/175j-8k96</t>
+          <t>10.21966/dveq-bt48</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
         </is>
       </c>
       <c r="T251" t="inlineStr">
@@ -27962,7 +27962,7 @@
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="V251" t="n">
@@ -27983,12 +27983,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
+          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -27998,7 +27998,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
+          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -28016,12 +28016,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -28040,54 +28040,52 @@
         </is>
       </c>
       <c r="N252" t="n">
+        <v>2</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>10.21966/RZVW-4A72</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="V252" t="n">
         <v>1</v>
       </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
-        </is>
-      </c>
-      <c r="P252" t="inlineStr">
-        <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
-        </is>
-      </c>
-      <c r="R252" t="inlineStr">
-        <is>
-          <t>10.21966/dveq-bt48</t>
-        </is>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="V252" t="n">
-        <v>0</v>
-      </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X252" t="n">
-        <v>2</v>
-      </c>
+          <t>[{'year': '2022', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28095,12 +28093,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
+          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -28110,7 +28108,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -28128,7 +28126,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -28156,45 +28154,45 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>10.21966/RZVW-4A72</t>
+          <t>10.21966/0xvh-1318</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
         </is>
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X253" t="inlineStr"/>
@@ -28205,12 +28203,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
+          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -28220,7 +28218,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
+          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -28238,12 +28236,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -28266,37 +28264,37 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
+          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>10.21966/0xvh-1318</t>
+          <t>10.21966/3q5j-n957</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
         </is>
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="V254" t="n">
@@ -28315,12 +28313,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
+          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -28330,7 +28328,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -28348,12 +28346,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -28372,41 +28370,41 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>10.21966/3q5j-n957</t>
+          <t>10.21966/kmc2-5r12</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="V255" t="n">
@@ -28425,12 +28423,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
+          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
+          <t>ca-cioos_7e49967a-b5ab-443d-860b-e3c0eb0f709c</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -28440,7 +28438,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
+          <t>Horne Lake Bathymetry Mapping</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -28458,7 +28456,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -28482,41 +28480,41 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.7872, 49.3105], [-124.6447, 49.3105], [-124.6447, 49.3644], [-124.7872, 49.3644], [-124.7872, 49.3105]]]}</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>10.21966/kmc2-5r12</t>
+          <t>10.21966/vwee-e004</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/G8LjsjnnPxb5TxWL730BxDTQu532/-Njn-0LeJ-Uwj4L8EmOV</t>
         </is>
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="V256" t="n">
@@ -28535,12 +28533,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
+          <t>18f56a52-11af-446a-aea9-07feca8d197e</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ca-cioos_7e49967a-b5ab-443d-860b-e3c0eb0f709c</t>
+          <t>ca-cioos_e897c9d0-3fca-4c89-b37f-e571413ffd12</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -28550,7 +28548,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Horne Lake Bathymetry Mapping</t>
+          <t>Joffre Provincial Park Aerial Surveys - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -28568,7 +28566,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -28596,12 +28594,12 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.7872, 49.3105], [-124.6447, 49.3105], [-124.6447, 49.3644], [-124.7872, 49.3644], [-124.7872, 49.3105]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.5281, 50.3147], [-122.4303, 50.3147], [-122.4303, 50.3796], [-122.5281, 50.3796], [-122.5281, 50.3147]]]}</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '475.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
@@ -28611,12 +28609,12 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>10.21966/vwee-e004</t>
+          <t>10.21966/k0z0-3z50</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/G8LjsjnnPxb5TxWL730BxDTQu532/-Njn-0LeJ-Uwj4L8EmOV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ot_OaAHxjund0-w5rXq</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
@@ -28626,7 +28624,7 @@
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="V257" t="n">
@@ -28645,12 +28643,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>18f56a52-11af-446a-aea9-07feca8d197e</t>
+          <t>6c4803cc-d1c6-4327-806a-7f6796606175</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ca-cioos_e897c9d0-3fca-4c89-b37f-e571413ffd12</t>
+          <t>ca-cioos_6c34ed6e-5a17-41f2-b83a-cd59d1ce07bd</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -28660,7 +28658,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Joffre Provincial Park Aerial Surveys - 2025 - Airborne Coastal Observatory</t>
+          <t>Knight Inlet Multibeam Bathymetry Survey</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -28678,7 +28676,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -28706,12 +28704,12 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.5281, 50.3147], [-122.4303, 50.3147], [-122.4303, 50.3796], [-122.5281, 50.3796], [-122.5281, 50.3147]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0537, 50.6529], [-125.9229, 50.6529], [-125.9229, 50.7077], [-126.0537, 50.7077], [-126.0537, 50.6529]]]}</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>[{'max': '475.0', 'min': '0.0'}]</t>
+          <t>[{'max': '288.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
@@ -28721,17 +28719,17 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>10.21966/k0z0-3z50</t>
+          <t>10.21966/8dgz-1z27</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ot_OaAHxjund0-w5rXq</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG7EOynnzSIOU7LPWgs</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
@@ -28755,12 +28753,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>6c4803cc-d1c6-4327-806a-7f6796606175</t>
+          <t>ce6f3f8c-6b57-4f18-be46-8c0b5a4baeb9</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ca-cioos_6c34ed6e-5a17-41f2-b83a-cd59d1ce07bd</t>
+          <t>ca-cioos_8755f475-2133-4205-baff-5e2937824f45</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -28770,7 +28768,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Knight Inlet Multibeam Bathymetry Survey</t>
+          <t>Poole Creek Aerial Surveys - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -28788,7 +28786,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -28816,12 +28814,12 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0537, 50.6529], [-125.9229, 50.6529], [-125.9229, 50.7077], [-126.0537, 50.7077], [-126.0537, 50.6529]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9075, 50.2436], [-122.8124, 50.2436], [-122.8124, 50.3016], [-122.9075, 50.3016], [-122.9075, 50.2436]]]}</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>[{'max': '288.0', 'min': '0.0'}]</t>
+          <t>[{'max': '450.0', 'min': '200.0'}]</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
@@ -28831,12 +28829,12 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>10.21966/8dgz-1z27</t>
+          <t>10.21966/g8f2-jw82</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG7EOynnzSIOU7LPWgs</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OtfdtO43um_1J_LdCpn</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
@@ -28865,12 +28863,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>ce6f3f8c-6b57-4f18-be46-8c0b5a4baeb9</t>
+          <t>e1247209-cc26-4788-82a2-dd8a5c971e22</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ca-cioos_8755f475-2133-4205-baff-5e2937824f45</t>
+          <t>ca-cioos_2e5ddbaa-4f0c-4339-8595-1ddbd35c3df4</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -28880,7 +28878,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Poole Creek Aerial Surveys - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Aerial Surveys in British Columbia, Washington, and Alberta - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -28926,12 +28924,12 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.9075, 50.2436], [-122.8124, 50.2436], [-122.8124, 50.3016], [-122.9075, 50.3016], [-122.9075, 50.2436]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.9263, 48.0077], [-112.7224, 48.0077], [-112.7224, 54.6673], [-127.9263, 54.6673], [-127.9263, 48.0077]]]}</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>[{'max': '450.0', 'min': '200.0'}]</t>
+          <t>[{'max': '4019.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
@@ -28941,22 +28939,22 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>10.21966/g8f2-jw82</t>
+          <t>10.21966/n6ga-nc24</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OtfdtO43um_1J_LdCpn</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ou3t_K6rGOHTMO67Xbq</t>
         </is>
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="V260" t="n">
@@ -28975,12 +28973,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>e1247209-cc26-4788-82a2-dd8a5c971e22</t>
+          <t>5ac3ac5f-702e-43d8-bcb7-79f30c4d9e08</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ca-cioos_2e5ddbaa-4f0c-4339-8595-1ddbd35c3df4</t>
+          <t>ca-cioos_656ea307-fed0-48ca-b5d8-1bc017dc52d2</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -28990,7 +28988,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Aerial Surveys in British Columbia, Washington, and Alberta - 2025 - Airborne Coastal Observatory</t>
+          <t>Botanical Beach - Juan de Fuca Provincial Park - Drone Mapping</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -29008,7 +29006,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -29036,12 +29034,12 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.9263, 48.0077], [-112.7224, 48.0077], [-112.7224, 54.6673], [-127.9263, 54.6673], [-127.9263, 48.0077]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.45265489, 48.52152402], [-124.43377214, 48.52152402], [-124.43377214, 48.53061904], [-124.45265489, 48.53061904], [-124.45265489, 48.52152402]]]}</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>[{'max': '4019.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
@@ -29051,12 +29049,12 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>10.21966/n6ga-nc24</t>
+          <t>10.21966/kn3e-fn08</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ou3t_K6rGOHTMO67Xbq</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdvcmtQME1NZmdWcDY</t>
         </is>
       </c>
       <c r="T261" t="inlineStr">
@@ -29085,12 +29083,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>5ac3ac5f-702e-43d8-bcb7-79f30c4d9e08</t>
+          <t>05dac0a6-a26c-4cb5-895d-132b5e2134cd</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ca-cioos_656ea307-fed0-48ca-b5d8-1bc017dc52d2</t>
+          <t>ca-cioos_b45dbc9d-bf7a-4734-86cd-3397e7c9ac62</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -29100,7 +29098,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Botanical Beach - Juan de Fuca Provincial Park - Drone Mapping</t>
+          <t>Sea surface temperature data in False Creek, British Columbia</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -29118,7 +29116,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -29146,37 +29144,37 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.45265489, 48.52152402], [-124.43377214, 48.52152402], [-124.43377214, 48.53061904], [-124.45265489, 48.53061904], [-124.45265489, 48.52152402]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28]]]}</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.5', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>10.21966/kn3e-fn08</t>
+          <t>10.21966/0g6d-pk30</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdvcmtQME1NZmdWcDY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NHaXDtgFZr0-Oul6FZG</t>
         </is>
       </c>
       <c r="T262" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="V262" t="n">
@@ -29195,12 +29193,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>05dac0a6-a26c-4cb5-895d-132b5e2134cd</t>
+          <t>6eb46e26-dac5-4964-8b29-8e8541381aac</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>ca-cioos_b45dbc9d-bf7a-4734-86cd-3397e7c9ac62</t>
+          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -29210,7 +29208,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Sea surface temperature data in False Creek, British Columbia</t>
+          <t>Time series of eelgrass (Zostera marina) meadow extent derived from drone surveys, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -29228,12 +29226,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -29256,37 +29254,37 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>[{'max': '0.5', 'min': '0.5'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>10.21966/0g6d-pk30</t>
+          <t>10.21966/03pw-2190</t>
         </is>
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NHaXDtgFZr0-Oul6FZG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
         </is>
       </c>
       <c r="T263" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="V263" t="n">
@@ -29305,12 +29303,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>6eb46e26-dac5-4964-8b29-8e8541381aac</t>
+          <t>67b81524-e385-439e-9bc1-03bd4652eba6</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
+          <t>ca-cioos_79368bf3-8f02-4355-837e-3a6cef0d2886</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -29320,7 +29318,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Time series of eelgrass (Zostera marina) meadow extent derived from drone surveys, Central Coast, British Columbia</t>
+          <t>Watersheds Stream Stations Timeseries, Calvert and Hecate Islands, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -29338,12 +29336,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -29362,11 +29360,11 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
@@ -29376,27 +29374,27 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>10.21966/03pw-2190</t>
+          <t>10.21966/c6xs-y324</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/zBOULF9sDAgC4rkoZUFQq7sBGCf2/-OtAIe6lv3elLZd4c-V1</t>
         </is>
       </c>
       <c r="T264" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="V264" t="n">
@@ -29415,12 +29413,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>67b81524-e385-439e-9bc1-03bd4652eba6</t>
+          <t>ff456916-01f7-4eb0-961f-3658f0b4f39b</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>ca-cioos_79368bf3-8f02-4355-837e-3a6cef0d2886</t>
+          <t>ca-cioos_d986aade-6bf1-4dfa-97c2-686975f944d5</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -29430,7 +29428,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Watersheds Stream Stations Timeseries, Calvert and Hecate Islands, BC, Canada (Provisional)</t>
+          <t>Watersheds Stream Stations Timeseries, Calvert and Hecate Islands, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -29453,7 +29451,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -29476,12 +29474,12 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.1, 51.64], [-128.0, 51.64], [-128.0, 51.67], [-128.1, 51.67], [-128.1, 51.64]]]}</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q265" t="inlineStr">
@@ -29491,17 +29489,17 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>10.21966/c6xs-y324</t>
+          <t>10.21966/47m7-ev69</t>
         </is>
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/zBOULF9sDAgC4rkoZUFQq7sBGCf2/-OtAIe6lv3elLZd4c-V1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/zBOULF9sDAgC4rkoZUFQq7sBGCf2/-OHj73dBYs1okPPjDXKY</t>
         </is>
       </c>
       <c r="T265" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U265" t="inlineStr">
@@ -29525,12 +29523,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>ff456916-01f7-4eb0-961f-3658f0b4f39b</t>
+          <t>71c6db20-a521-451b-b371-a2560f6af25e</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>ca-cioos_d986aade-6bf1-4dfa-97c2-686975f944d5</t>
+          <t>ca-cioos_999da1dd-efde-4a55-868b-ce2d6ca3b983</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -29540,7 +29538,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Watersheds Stream Stations Timeseries, Calvert and Hecate Islands, BC, Canada (Research)</t>
+          <t>Observations from the 2017 Hakai MarineGEO Bioblitz</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -29558,12 +29556,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -29582,41 +29580,41 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.1, 51.64], [-128.0, 51.64], [-128.0, 51.67], [-128.1, 51.67], [-128.1, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.951, 51.48631], [-127.76165, 51.48631], [-127.76165, 52.05347], [-128.951, 52.05347], [-128.951, 51.48631]]]}</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '40.0', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>10.21966/47m7-ev69</t>
+          <t>10.21966/0jfr-7b65</t>
         </is>
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/zBOULF9sDAgC4rkoZUFQq7sBGCf2/-OHj73dBYs1okPPjDXKY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCmJU0B97JSOfOpj6J</t>
         </is>
       </c>
       <c r="T266" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="V266" t="n">
@@ -29635,12 +29633,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>71c6db20-a521-451b-b371-a2560f6af25e</t>
+          <t>f0ae5f04-2c3a-4b67-8fbf-c6dc3771257d</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>ca-cioos_999da1dd-efde-4a55-868b-ce2d6ca3b983</t>
+          <t>ca-cioos_482d2463-0c81-4d62-a22a-1c0942b3c1fa</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -29650,7 +29648,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Observations from the 2017 Hakai MarineGEO Bioblitz</t>
+          <t>Observations from the 2019 Hakai Deep Water Bioblitz</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -29696,12 +29694,12 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.951, 51.48631], [-127.76165, 51.48631], [-127.76165, 52.05347], [-128.951, 52.05347], [-128.951, 51.48631]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.14433, 51.615734], [-127.76327, 51.615734], [-127.76327, 51.787], [-128.14433, 51.787], [-128.14433, 51.615734]]]}</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>[{'max': '40.0', 'min': '0.5'}]</t>
+          <t>[{'max': '255.0', 'min': '5.0'}]</t>
         </is>
       </c>
       <c r="Q267" t="inlineStr">
@@ -29711,22 +29709,22 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>10.21966/0jfr-7b65</t>
+          <t>10.21966/3p06-vt55</t>
         </is>
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCmJU0B97JSOfOpj6J</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCoStSubGWAdV78XNC</t>
         </is>
       </c>
       <c r="T267" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="V267" t="n">
@@ -29745,12 +29743,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>f0ae5f04-2c3a-4b67-8fbf-c6dc3771257d</t>
+          <t>91d2ddf0-ea25-4ef9-b990-26d2957cb3bd</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>ca-cioos_482d2463-0c81-4d62-a22a-1c0942b3c1fa</t>
+          <t>ca-cioos_542a20b8-242e-4199-a062-5b76ea9cbf2d</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -29760,7 +29758,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Observations from the 2019 Hakai Deep Water Bioblitz</t>
+          <t>Observations from the 2018 Hakai Terrestrial Bioblitz</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -29806,27 +29804,27 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.14433, 51.615734], [-127.76327, 51.615734], [-127.76327, 51.787], [-128.14433, 51.787], [-128.14433, 51.615734]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.98366, 51.5919], [-125.0032, 51.5919], [-125.0032, 53.9998], [-128.98366, 53.9998], [-128.98366, 51.5919]]]}</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>[{'max': '255.0', 'min': '5.0'}]</t>
+          <t>[{'max': '1012.0', 'min': '50.0'}]</t>
         </is>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>10.21966/3p06-vt55</t>
+          <t>10.21966/t0h7-8g95</t>
         </is>
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCoStSubGWAdV78XNC</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCpwd5hTju8QOKVY-E</t>
         </is>
       </c>
       <c r="T268" t="inlineStr">
@@ -29836,7 +29834,7 @@
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V268" t="n">
@@ -29855,12 +29853,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>91d2ddf0-ea25-4ef9-b990-26d2957cb3bd</t>
+          <t>fa42f16a-3693-4c51-b45c-a36e709fdac3</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>ca-cioos_542a20b8-242e-4199-a062-5b76ea9cbf2d</t>
+          <t>ca-cioos_d69bf79e-b616-404e-bbfc-92932ca74087</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -29870,7 +29868,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Observations from the 2018 Hakai Terrestrial Bioblitz</t>
+          <t>Observations from the 2018 Hakai Seagrass Bioblitz</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -29888,7 +29886,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Genomics, Nearshore</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -29916,27 +29914,27 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.98366, 51.5919], [-125.0032, 51.5919], [-125.0032, 53.9998], [-128.98366, 53.9998], [-128.98366, 51.5919]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.8123, 51.8438], [-128.2105, 51.684], [-128.1968, 51.6158], [-127.8837, 51.6192], [-127.8123, 51.8438]]]}</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>[{'max': '1012.0', 'min': '50.0'}]</t>
+          <t>[{'max': '300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>10.21966/t0h7-8g95</t>
+          <t>10.21966/yf1f-jx85</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCpwd5hTju8QOKVY-E</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCnP9OAghmAmYObj0D</t>
         </is>
       </c>
       <c r="T269" t="inlineStr">
@@ -29946,7 +29944,7 @@
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="V269" t="n">
@@ -29965,12 +29963,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>fa42f16a-3693-4c51-b45c-a36e709fdac3</t>
+          <t>fc3d2ea5-b60c-42c9-97e9-542024bec9fa</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>ca-cioos_d69bf79e-b616-404e-bbfc-92932ca74087</t>
+          <t>ca-cioos_4add33cd-b182-4825-900a-5695f333125a</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -29980,7 +29978,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Observations from the 2018 Hakai Seagrass Bioblitz</t>
+          <t>Weather Station Time Series, Hyacinthe Bay, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -29998,12 +29996,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -30026,47 +30024,37 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.8123, 51.8438], [-128.2105, 51.684], [-128.1968, 51.6158], [-127.8837, 51.6192], [-127.8123, 51.8438]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2221111, 50.1162556]}</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>[{'max': '300.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution, seagrassCoverAndComposition</t>
-        </is>
-      </c>
-      <c r="R270" t="inlineStr">
-        <is>
-          <t>10.21966/yf1f-jx85</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCnP9OAghmAmYObj0D</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OyesAm4pxUK1wqBMn7x</t>
         </is>
       </c>
       <c r="T270" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="V270" t="n">
-        <v>0</v>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr"/>
+      <c r="W270" t="inlineStr"/>
       <c r="X270" t="inlineStr"/>
     </row>
     <row r="271">
@@ -30075,12 +30063,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>fc3d2ea5-b60c-42c9-97e9-542024bec9fa</t>
+          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>ca-cioos_4add33cd-b182-4825-900a-5695f333125a</t>
+          <t>ca-cioos_3f40326a-23f9-4e30-a16a-f332ace14e2f</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -30090,7 +30078,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Weather Station Time Series, Hyacinthe Bay, BC, Canada (Provisional)</t>
+          <t>Nereocystis kelp canopy productivity data from BC Central Coast</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -30108,12 +30096,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -30136,37 +30124,47 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2221111, 50.1162556]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.19], [-127.1, 51.19], [-127.1, 52.28], [-128.6, 52.28], [-128.6, 51.19]]]}</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R271" t="inlineStr"/>
+          <t>macroalgalCanopyCoverAndComposition</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>10.21966/d1s2-s530</t>
+        </is>
+      </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OyesAm4pxUK1wqBMn7x</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtG8b48aDAEdJoqNT6N</t>
         </is>
       </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="V271" t="inlineStr"/>
-      <c r="W271" t="inlineStr"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V271" t="n">
+        <v>1</v>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>[{'year': '2024', 'total': 1}]</t>
+        </is>
+      </c>
       <c r="X271" t="inlineStr"/>
     </row>
     <row r="272">
@@ -30175,12 +30173,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
+          <t>aab940b9-bb7f-49c0-ae62-4f78d26897b3</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>ca-cioos_3f40326a-23f9-4e30-a16a-f332ace14e2f</t>
+          <t>ca-cioos_0219e1d6-8dfc-4718-b89b-ea3dff06a70d</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -30190,7 +30188,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Nereocystis kelp canopy productivity data from BC Central Coast</t>
+          <t>Modeled Eelgrass Extent, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -30208,12 +30206,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -30232,49 +30230,49 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.19], [-127.1, 51.19], [-127.1, 52.28], [-128.6, 52.28], [-128.6, 51.19]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-133.7841801345348, 48.23443097294032], [-122.49023482203482, 48.23443097294032], [-122.49023482203482, 54.52958287232971], [-133.7841801345348, 54.52958287232971], [-133.7841801345348, 48.23443097294032]]]}</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>10.21966/d1s2-s530</t>
+          <t>10.21966/1ty5-e654</t>
         </is>
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtG8b48aDAEdJoqNT6N</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWtuNVpwdEdLRXZTODc</t>
         </is>
       </c>
       <c r="T272" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W272" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X272" t="inlineStr"/>
@@ -30285,12 +30283,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>aab940b9-bb7f-49c0-ae62-4f78d26897b3</t>
+          <t>3988f8e8-36ea-4cda-9bd9-a03157116ef5</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>ca-cioos_0219e1d6-8dfc-4718-b89b-ea3dff06a70d</t>
+          <t>ca-cioos_d43a79c1-a6ba-4e37-8dc2-6ced6312828e</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -30300,7 +30298,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Modeled Eelgrass Extent, British Columbia, Canada</t>
+          <t>Data from Manuscript: Parasites of the hermit crab Pagurus hirsutiusculus; distribution, prevalence, and thermal ecology</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -30318,7 +30316,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -30342,11 +30340,11 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-133.7841801345348, 48.23443097294032], [-122.49023482203482, 48.23443097294032], [-122.49023482203482, 54.52958287232971], [-133.7841801345348, 54.52958287232971], [-133.7841801345348, 48.23443097294032]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.66], [-127.9, 51.81], [-122.2, 49.03], [-123.3, 49.01], [-123.0, 48.83], [-123.0, 48.78], [-123.3, 48.7], [-123.3, 48.53], [-123.6, 48.59], [-125.2, 48.73], [-125.6, 48.95], [-125.6, 50.11], [-128.4, 51.66]]]}</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
@@ -30356,17 +30354,17 @@
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>invertebrateAbundanceAndDistribution, seaSurfaceSalinity</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>10.21966/1ty5-e654</t>
+          <t>10.21966/xb3t-qb88</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWtuNVpwdEdLRXZTODc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3eh7IMAvm8ZUtcMBeifFL0eJCIA3/-O5Kei32z9cfatfgKj5y</t>
         </is>
       </c>
       <c r="T273" t="inlineStr">
@@ -30376,7 +30374,7 @@
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V273" t="n">
@@ -30395,12 +30393,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>3988f8e8-36ea-4cda-9bd9-a03157116ef5</t>
+          <t>c4932b55-1dd8-4f2f-89da-5822056ecc37</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>ca-cioos_d43a79c1-a6ba-4e37-8dc2-6ced6312828e</t>
+          <t>ca-cioos_53189107-9df5-426b-acb4-f903468554fe</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -30410,7 +30408,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Data from Manuscript: Parasites of the hermit crab Pagurus hirsutiusculus; distribution, prevalence, and thermal ecology</t>
+          <t>Comparing invertebrate and seaweed diversity in kelp forests and urchin barrens in Owen Bay, British Columbia, using Autonomous Reef Monitoring Structures (ARMS)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -30428,7 +30426,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Sentinels of Change, Genomics</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -30452,41 +30450,41 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.66], [-127.9, 51.81], [-122.2, 49.03], [-123.3, 49.01], [-123.0, 48.83], [-123.0, 48.78], [-123.3, 48.7], [-123.3, 48.53], [-123.6, 48.59], [-125.2, 48.73], [-125.6, 48.95], [-125.6, 50.11], [-128.4, 51.66]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.2335, 50.2999], [-125.2163, 50.2999], [-125.2163, 50.313], [-125.2335, 50.313], [-125.2335, 50.2999]]]}</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '6.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, seaSurfaceSalinity</t>
+          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>10.21966/xb3t-qb88</t>
+          <t>10.21966/e5mw-tr82</t>
         </is>
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3eh7IMAvm8ZUtcMBeifFL0eJCIA3/-O5Kei32z9cfatfgKj5y</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/5Jh4rsxoBsRd4mVFqZ0XJoMtMHI2/-P-tq8uNjGhWtk4rBny0</t>
         </is>
       </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="V274" t="n">
@@ -30497,7 +30495,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X274" t="inlineStr"/>
+      <c r="X274" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30505,12 +30505,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>c4932b55-1dd8-4f2f-89da-5822056ecc37</t>
+          <t>33bb67af-4d61-4b15-93a9-f3ab2498430b</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>ca-cioos_53189107-9df5-426b-acb4-f903468554fe</t>
+          <t>ca-cioos_73abfecf-d35c-4f9c-a991-eee5cece08ea</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -30520,7 +30520,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Comparing invertebrate and seaweed diversity in kelp forests and urchin barrens in Owen Bay, British Columbia, using Autonomous Reef Monitoring Structures (ARMS)</t>
+          <t>Kelp Canopy Extent 2012 - NW Calvert Island</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Sentinels of Change, Genomics</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -30562,41 +30562,41 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.2335, 50.2999], [-125.2163, 50.2999], [-125.2163, 50.313], [-125.2335, 50.313], [-125.2335, 50.2999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16959381103513, 51.63613234359897], [-128.11191558837888, 51.63613234359897], [-128.11191558837888, 51.681709494104325], [-128.16959381103513, 51.681709494104325], [-128.16959381103513, 51.63613234359897]]]}</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
+          <t>other, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>10.21966/e5mw-tr82</t>
+          <t>10.21966/63rs-yt91</t>
         </is>
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/5Jh4rsxoBsRd4mVFqZ0XJoMtMHI2/-P-tq8uNjGhWtk4rBny0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxUM01laTFaREhKbWE</t>
         </is>
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="V275" t="n">
@@ -30617,12 +30617,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>33bb67af-4d61-4b15-93a9-f3ab2498430b</t>
+          <t>bc1133da-5601-4f92-bc53-41be547c936b</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>ca-cioos_73abfecf-d35c-4f9c-a991-eee5cece08ea</t>
+          <t>ca-cioos_940218ef-d7f8-4f3f-9e69-52150ecdbec5</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -30632,7 +30632,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Kelp Canopy Extent 2012 - NW Calvert Island</t>
+          <t>North Vancouver Island Aerial Survey - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -30650,7 +30650,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -30674,31 +30674,31 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16959381103513, 51.63613234359897], [-128.11191558837888, 51.63613234359897], [-128.11191558837888, 51.681709494104325], [-128.16959381103513, 51.681709494104325], [-128.16959381103513, 51.63613234359897]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 50.35], [-125.4, 50.35], [-125.4, 50.63], [-126.7, 50.63], [-126.7, 50.35]]]}</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>other, macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>10.21966/63rs-yt91</t>
+          <t>10.21966/kdhe-hz07</t>
         </is>
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxUM01laTFaREhKbWE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCoHpqOwDbp834fqRY3</t>
         </is>
       </c>
       <c r="T276" t="inlineStr">
@@ -30708,7 +30708,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="V276" t="n">
@@ -30729,12 +30729,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>bc1133da-5601-4f92-bc53-41be547c936b</t>
+          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>ca-cioos_940218ef-d7f8-4f3f-9e69-52150ecdbec5</t>
+          <t>ca-cioos_c7466354-bacc-4781-acdc-543dd03d1eab</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>North Vancouver Island Aerial Survey - 2024 - Airborne Coastal Observatory</t>
+          <t>Nanwakolas LiDAR Surveys - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -30790,12 +30790,12 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 50.35], [-125.4, 50.35], [-125.4, 50.63], [-126.7, 50.63], [-126.7, 50.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.8, 49.26], [-124.5, 49.26], [-124.5, 50.83], [-126.8, 50.83], [-126.8, 49.26]]]}</t>
         </is>
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1700.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q277" t="inlineStr">
@@ -30805,12 +30805,12 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>10.21966/kdhe-hz07</t>
+          <t>10.21966/e0r7-ge27</t>
         </is>
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCoHpqOwDbp834fqRY3</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OjbuSE_uZcCs3Fit_mg</t>
         </is>
       </c>
       <c r="T277" t="inlineStr">
@@ -30820,7 +30820,7 @@
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V277" t="n">
@@ -30839,12 +30839,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
+          <t>f7433c1a-3aad-4761-81c4-c191a5e6ac92</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>ca-cioos_c7466354-bacc-4781-acdc-543dd03d1eab</t>
+          <t>ca-cioos_52e97374-bee5-4b1a-9b85-7170a5df8d6b</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -30854,7 +30854,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Nanwakolas LiDAR Surveys - Airborne Coastal Observatory</t>
+          <t>Biomass and density of Pycnopodia helianthoides from the central coast of BC</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography, Nearshore</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -30900,37 +30900,37 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.8, 49.26], [-124.5, 49.26], [-124.5, 50.83], [-126.8, 50.83], [-126.8, 49.26]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.617, 51.3321], [-127.3509, 51.3321], [-127.3509, 52.3317], [-128.617, 52.3317], [-128.617, 51.3321]]]}</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>[{'max': '1700.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceSalinity, subSurfaceSalinity, seaSurfaceTemperature, subSurfaceTemperature, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>10.21966/e0r7-ge27</t>
+          <t>10.21966/xy6n-qz76</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OjbuSE_uZcCs3Fit_mg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-OteEfuBSvhg-2RySC4a</t>
         </is>
       </c>
       <c r="T278" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="V278" t="n">
@@ -30949,12 +30949,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>f7433c1a-3aad-4761-81c4-c191a5e6ac92</t>
+          <t>c7a168e8-f15e-446f-a49d-0b4a1f043ac2</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ca-cioos_52e97374-bee5-4b1a-9b85-7170a5df8d6b</t>
+          <t>ca-cioos_b4844ae2-d9c1-42f2-ae4d-a8f994c395a0</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -30964,7 +30964,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Biomass and density of Pycnopodia helianthoides from the central coast of BC</t>
+          <t>Putting fjord biodiversity on the map for British Columbia conservation planning</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -30982,7 +30982,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore</t>
+          <t>Genomics, Oceanography</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -31002,56 +31002,58 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N279" t="n">
+        <v>2</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.0471, 52.2577], [-128.9141, 51.7033], [-127.6841, 50.7687], [-123.7744, 48.9864], [-122.764, 49.331], [-122.8299, 49.9706], [-127.0471, 52.2577]]]}</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>[{'max': '595.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>fishAbundanceAndDistribution, subSurfaceTemperature, subSurfaceSalinity</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>10.21966/n141-m959</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-Ow-ZgW1jkC5-WyrtlLV</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="V279" t="n">
+        <v>0</v>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X279" t="n">
         <v>1</v>
       </c>
-      <c r="O279" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.617, 51.3321], [-127.3509, 51.3321], [-127.3509, 52.3317], [-128.617, 52.3317], [-128.617, 51.3321]]]}</t>
-        </is>
-      </c>
-      <c r="P279" t="inlineStr">
-        <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q279" t="inlineStr">
-        <is>
-          <t>seaSurfaceSalinity, subSurfaceSalinity, seaSurfaceTemperature, subSurfaceTemperature, invertebrateAbundanceAndDistribution</t>
-        </is>
-      </c>
-      <c r="R279" t="inlineStr">
-        <is>
-          <t>10.21966/xy6n-qz76</t>
-        </is>
-      </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-OteEfuBSvhg-2RySC4a</t>
-        </is>
-      </c>
-      <c r="T279" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U279" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="V279" t="n">
-        <v>0</v>
-      </c>
-      <c r="W279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31059,12 +31061,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>c7a168e8-f15e-446f-a49d-0b4a1f043ac2</t>
+          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>ca-cioos_b4844ae2-d9c1-42f2-ae4d-a8f994c395a0</t>
+          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -31074,7 +31076,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Putting fjord biodiversity on the map for British Columbia conservation planning</t>
+          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -31092,7 +31094,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Genomics, Oceanography</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -31112,45 +31114,45 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N280" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.0471, 52.2577], [-128.9141, 51.7033], [-127.6841, 50.7687], [-123.7744, 48.9864], [-122.764, 49.331], [-122.8299, 49.9706], [-127.0471, 52.2577]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
         </is>
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>[{'max': '595.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2.5', 'min': '2.5'}]</t>
         </is>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, subSurfaceTemperature, subSurfaceSalinity</t>
+          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>10.21966/n141-m959</t>
+          <t>10.21966/rrzq-yw32</t>
         </is>
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-Ow-ZgW1jkC5-WyrtlLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
         </is>
       </c>
       <c r="T280" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V280" t="n">
@@ -31161,9 +31163,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X280" t="n">
-        <v>1</v>
-      </c>
+      <c r="X280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31171,12 +31171,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
+          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
+          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -31186,17 +31186,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
+          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H281" t="b">
@@ -31209,7 +31209,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -31232,27 +31232,23 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>[{'max': '2.5', 'min': '2.5'}]</t>
+          <t>[{'max': '0.0', 'min': '600.0'}]</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R281" t="inlineStr">
-        <is>
-          <t>10.21966/rrzq-yw32</t>
-        </is>
-      </c>
+          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
         </is>
       </c>
       <c r="T281" t="inlineStr">
@@ -31262,17 +31258,11 @@
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="V281" t="n">
-        <v>0</v>
-      </c>
-      <c r="W281" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr"/>
+      <c r="W281" t="inlineStr"/>
       <c r="X281" t="inlineStr"/>
     </row>
     <row r="282">
@@ -31281,12 +31271,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
+          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
+          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -31296,17 +31286,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
+          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H282" t="b">
@@ -31314,12 +31304,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Estuary Resilience</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -31342,40 +31332,48 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '600.0'}]</t>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R282" t="inlineStr"/>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>10.21966/r9zr-xz33</t>
+        </is>
+      </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
         </is>
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="V282" t="inlineStr"/>
-      <c r="W282" t="inlineStr"/>
-      <c r="X282" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="V282" t="n">
+        <v>0</v>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31383,12 +31381,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
+          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
+          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -31398,7 +31396,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -31444,7 +31442,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
@@ -31459,12 +31457,12 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>10.21966/r9zr-xz33</t>
+          <t>10.21966/9dbb-5d54</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
         </is>
       </c>
       <c r="T283" t="inlineStr">
@@ -31493,12 +31491,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
+          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
+          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -31508,7 +31506,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -31554,7 +31552,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
@@ -31569,12 +31567,12 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>10.21966/9dbb-5d54</t>
+          <t>10.21966/vpz7-mm73</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
         </is>
       </c>
       <c r="T284" t="inlineStr">
@@ -31603,12 +31601,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
+          <t>0ce3ee5b-425b-4eb0-a201-96bdfb795a3f</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
+          <t>ca-cioos_354b5b83-e752-4ffb-a740-d1cdc02ac8c6</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -31618,7 +31616,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Dtlaxsiwè River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -31664,7 +31662,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.1721, 50.61011], [-127.17933, 50.612], [-127.1873, 50.6098], [-127.19703, 50.61072], [-127.20524, 50.61585], [-127.19007, 50.61844], [-127.18675, 50.61393], [-127.17744, 50.61359], [-127.17161, 50.61118], [-127.17203, 50.61011], [-127.1721, 50.61011]]]}</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
@@ -31679,12 +31677,12 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>10.21966/vpz7-mm73</t>
+          <t>10.21966/ydm2-m238</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7Dng-ZtRd05hnZCq1</t>
         </is>
       </c>
       <c r="T285" t="inlineStr">
@@ -31713,12 +31711,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>0ce3ee5b-425b-4eb0-a201-96bdfb795a3f</t>
+          <t>1a2aa5c8-9a83-46f7-967d-1127436c2084</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>ca-cioos_354b5b83-e752-4ffb-a740-d1cdc02ac8c6</t>
+          <t>ca-cioos_58a5140a-0b2c-4186-a648-53d9f58e5226</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -31728,7 +31726,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Dtlaxsiwè River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kvai River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -31774,7 +31772,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.1721, 50.61011], [-127.17933, 50.612], [-127.1873, 50.6098], [-127.19703, 50.61072], [-127.20524, 50.61585], [-127.19007, 50.61844], [-127.18675, 50.61393], [-127.17744, 50.61359], [-127.17161, 50.61118], [-127.17203, 50.61011], [-127.1721, 50.61011]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.81882, 51.77547], [-127.83122, 51.77986], [-127.85192, 51.781], [-127.86785, 51.78358], [-127.8958, 51.77366], [-127.89418, 51.77118], [-127.87834, 51.77309], [-127.86508, 51.77748], [-127.84009, 51.77519], [-127.82731, 51.77452], [-127.82025, 51.77309], [-127.81853, 51.77566], [-127.81882, 51.77547]]]}</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
@@ -31789,12 +31787,12 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>10.21966/ydm2-m238</t>
+          <t>10.21966/pm9m-h431</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7Dng-ZtRd05hnZCq1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7QQE3ifLCAPcu3Jih</t>
         </is>
       </c>
       <c r="T286" t="inlineStr">
@@ -31823,12 +31821,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>1a2aa5c8-9a83-46f7-967d-1127436c2084</t>
+          <t>c035b81c-0fc3-446e-bec5-8b8933ae874b</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>ca-cioos_58a5140a-0b2c-4186-a648-53d9f58e5226</t>
+          <t>ca-cioos_7fbc28f7-ee87-4361-bbee-0ed8ce24522d</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -31838,7 +31836,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kvai River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Gwa'dzi River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -31884,7 +31882,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.81882, 51.77547], [-127.83122, 51.77986], [-127.85192, 51.781], [-127.86785, 51.78358], [-127.8958, 51.77366], [-127.89418, 51.77118], [-127.87834, 51.77309], [-127.86508, 51.77748], [-127.84009, 51.77519], [-127.82731, 51.77452], [-127.82025, 51.77309], [-127.81853, 51.77566], [-127.81882, 51.77547]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.46176, 50.74217], [-127.49022, 50.72165], [-127.49167, 50.71188], [-127.4832, 50.70356], [-127.4874, 50.69181], [-127.46443, 50.6928], [-127.47282, 50.70776], [-127.47992, 50.71424], [-127.48305, 50.72058], [-127.45901, 50.74011], [-127.46153, 50.74217], [-127.46176, 50.74217]]]}</t>
         </is>
       </c>
       <c r="P287" t="inlineStr">
@@ -31899,12 +31897,12 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>10.21966/pm9m-h431</t>
+          <t>10.21966/xq99-x273</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7QQE3ifLCAPcu3Jih</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7BCRnF2C30YPkxIyd</t>
         </is>
       </c>
       <c r="T287" t="inlineStr">
@@ -31933,12 +31931,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>c035b81c-0fc3-446e-bec5-8b8933ae874b</t>
+          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>ca-cioos_7fbc28f7-ee87-4361-bbee-0ed8ce24522d</t>
+          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -31948,7 +31946,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Gwa'dzi River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -31994,7 +31992,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.46176, 50.74217], [-127.49022, 50.72165], [-127.49167, 50.71188], [-127.4832, 50.70356], [-127.4874, 50.69181], [-127.46443, 50.6928], [-127.47282, 50.70776], [-127.47992, 50.71424], [-127.48305, 50.72058], [-127.45901, 50.74011], [-127.46153, 50.74217], [-127.46176, 50.74217]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
@@ -32009,12 +32007,12 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>10.21966/xq99-x273</t>
+          <t>10.21966/kde9-8g12</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7BCRnF2C30YPkxIyd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
         </is>
       </c>
       <c r="T288" t="inlineStr">
@@ -32043,12 +32041,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
+          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
+          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -32058,7 +32056,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -32104,7 +32102,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
@@ -32119,12 +32117,12 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>10.21966/kde9-8g12</t>
+          <t>10.21966/9a97-2j48</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
         </is>
       </c>
       <c r="T289" t="inlineStr">
@@ -32153,12 +32151,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
+          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
+          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -32168,7 +32166,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -32214,7 +32212,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
@@ -32229,12 +32227,12 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>10.21966/9a97-2j48</t>
+          <t>10.21966/ed9w-2653</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
         </is>
       </c>
       <c r="T290" t="inlineStr">
@@ -32263,12 +32261,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
+          <t>1af6a43a-e73b-4774-8e10-b9f2928ab133</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
+          <t>ca-cioos_ae7e017c-9211-4f98-b56e-90a4bbac161c</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -32278,7 +32276,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Snuneymuxw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -32324,7 +32322,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.88685, 49.19332], [-123.92494, 49.1612], [-123.92581, 49.13841], [-123.91159, 49.123], [-123.88023, 49.11117], [-123.85971, 49.12766], [-123.89792, 49.16196], [-123.88099, 49.18866], [-123.88685, 49.19332]]]}</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -32339,12 +32337,12 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>10.21966/ed9w-2653</t>
+          <t>10.21966/k01q-wb27</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt459vxCIH7YPRN9fp</t>
         </is>
       </c>
       <c r="T291" t="inlineStr">
@@ -32373,12 +32371,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>1af6a43a-e73b-4774-8e10-b9f2928ab133</t>
+          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>ca-cioos_ae7e017c-9211-4f98-b56e-90a4bbac161c</t>
+          <t>ca-cioos_bea3da72-dafe-4e25-b5b2-0176e0ffba44</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -32388,7 +32386,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Snuneymuxw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Chemainus River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -32434,7 +32432,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.88685, 49.19332], [-123.92494, 49.1612], [-123.92581, 49.13841], [-123.91159, 49.123], [-123.88023, 49.11117], [-123.85971, 49.12766], [-123.89792, 49.16196], [-123.88099, 49.18866], [-123.88685, 49.19332]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.66843, 48.91641], [-123.6484, 48.90105], [-123.6554, 48.88016], [-123.6751, 48.87641], [-123.68894, 48.88178], [-123.68329, 48.89633], [-123.67928, 48.90316], [-123.67136, 48.91722], [-123.66848, 48.91635], [-123.66843, 48.91641]]]}</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
@@ -32449,12 +32447,12 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>10.21966/k01q-wb27</t>
+          <t>10.21966/q2e0-j004</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt459vxCIH7YPRN9fp</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpszvIrt9OF8-BLQW2N</t>
         </is>
       </c>
       <c r="T292" t="inlineStr">
@@ -32483,12 +32481,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
+          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ca-cioos_bea3da72-dafe-4e25-b5b2-0176e0ffba44</t>
+          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -32498,7 +32496,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Chemainus River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -32544,7 +32542,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.66843, 48.91641], [-123.6484, 48.90105], [-123.6554, 48.88016], [-123.6751, 48.87641], [-123.68894, 48.88178], [-123.68329, 48.89633], [-123.67928, 48.90316], [-123.67136, 48.91722], [-123.66848, 48.91635], [-123.66843, 48.91641]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
@@ -32559,12 +32557,12 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>10.21966/q2e0-j004</t>
+          <t>10.21966/hjkj-6611</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpszvIrt9OF8-BLQW2N</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
         </is>
       </c>
       <c r="T293" t="inlineStr">
@@ -32593,12 +32591,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
+          <t>4c7b7347-767d-45e4-b3ad-7e0133b31e1c</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
+          <t>ca-cioos_dce15b7b-3772-4106-ab20-c3979c4c3f57</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -32608,7 +32606,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Fulmore River - Shoal Creek Estuary Complex (Provisional)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -32654,7 +32652,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.08798, 50.4777], [-126.09599, 50.48418], [-126.09046, 50.50918], [-126.0647, 50.52425], [-125.99698, 50.53569], [-125.93459, 50.56717], [-125.93173, 50.56202], [-125.93764, 50.55458], [-125.91055, 50.55134], [-125.89853, 50.54943], [-125.90063, 50.54466], [-125.96416, 50.53989], [-125.98973, 50.52043], [-126.06566, 50.5067], [-126.08779, 50.47789], [-126.08798, 50.4777]]]}</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
@@ -32669,12 +32667,12 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>10.21966/hjkj-6611</t>
+          <t>10.21966/g1cn-xs92</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptdJ8iUmLeOrdmqzrQ</t>
         </is>
       </c>
       <c r="T294" t="inlineStr">
@@ -32703,12 +32701,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>4c7b7347-767d-45e4-b3ad-7e0133b31e1c</t>
+          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>ca-cioos_dce15b7b-3772-4106-ab20-c3979c4c3f57</t>
+          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -32718,7 +32716,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Fulmore River - Shoal Creek Estuary Complex (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -32764,7 +32762,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.08798, 50.4777], [-126.09599, 50.48418], [-126.09046, 50.50918], [-126.0647, 50.52425], [-125.99698, 50.53569], [-125.93459, 50.56717], [-125.93173, 50.56202], [-125.93764, 50.55458], [-125.91055, 50.55134], [-125.89853, 50.54943], [-125.90063, 50.54466], [-125.96416, 50.53989], [-125.98973, 50.52043], [-126.06566, 50.5067], [-126.08779, 50.47789], [-126.08798, 50.4777]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
@@ -32779,12 +32777,12 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>10.21966/g1cn-xs92</t>
+          <t>10.21966/npe4-3036</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptdJ8iUmLeOrdmqzrQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
         </is>
       </c>
       <c r="T295" t="inlineStr">
@@ -32813,12 +32811,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
+          <t>35245eae-e508-47da-bcf7-54346cda086a</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
+          <t>ca-cioos_e9b72149-8cf1-4000-ae3e-6b29ad60b078</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -32828,7 +32826,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Malksope River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -32874,7 +32872,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.46569, 50.12556], [-127.45723, 50.13142], [-127.43281, 50.13338], [-127.42845, 50.13765], [-127.41181, 50.14408], [-127.40973, 50.14233], [-127.41999, 50.13627], [-127.41803, 50.13195], [-127.43106, 50.12796], [-127.46545, 50.12446], [-127.46569, 50.12548], [-127.46569, 50.12556]]]}</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
@@ -32889,12 +32887,12 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>10.21966/npe4-3036</t>
+          <t>10.21966/21sf-ey03</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq77iyWJfPg4z-FvOSb</t>
         </is>
       </c>
       <c r="T296" t="inlineStr">
@@ -32923,12 +32921,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>35245eae-e508-47da-bcf7-54346cda086a</t>
+          <t>5177d019-598e-4415-b778-9688403652c8</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>ca-cioos_e9b72149-8cf1-4000-ae3e-6b29ad60b078</t>
+          <t>ca-cioos_ed84df74-5a2d-4a7d-87c8-a7b93f11088e</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -32938,7 +32936,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Malksope River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Nalaxdlala River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -32984,7 +32982,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.46569, 50.12556], [-127.45723, 50.13142], [-127.43281, 50.13338], [-127.42845, 50.13765], [-127.41181, 50.14408], [-127.40973, 50.14233], [-127.41999, 50.13627], [-127.41803, 50.13195], [-127.43106, 50.12796], [-127.46545, 50.12446], [-127.46569, 50.12548], [-127.46569, 50.12556]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.9489, 50.70902], [-125.9696, 50.70291], [-126.00938, 50.69118], [-126.00108, 50.66848], [-125.98257, 50.68374], [-125.98152, 50.69271], [-125.95462, 50.70263], [-125.94785, 50.70768], [-125.9489, 50.70911], [-125.9489, 50.70902]]]}</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
@@ -32999,12 +32997,12 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>10.21966/21sf-ey03</t>
+          <t>10.21966/4krv-aw23</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq77iyWJfPg4z-FvOSb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptbxmpkBsfyWWfSxOJ</t>
         </is>
       </c>
       <c r="T297" t="inlineStr">
@@ -33033,12 +33031,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>5177d019-598e-4415-b778-9688403652c8</t>
+          <t>d320d90e-96bf-4993-81c5-f1f57886b0e6</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>ca-cioos_ed84df74-5a2d-4a7d-87c8-a7b93f11088e</t>
+          <t>ca-cioos_b922699f-69b6-4d63-b538-7c290086a408</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -33048,7 +33046,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Nalaxdlala River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Quw'utsun/Xwulqw'selu River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -33094,7 +33092,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.9489, 50.70902], [-125.9696, 50.70291], [-126.00938, 50.69118], [-126.00108, 50.66848], [-125.98257, 50.68374], [-125.98152, 50.69271], [-125.95462, 50.70263], [-125.94785, 50.70768], [-125.9489, 50.70911], [-125.9489, 50.70902]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.56201, 48.73508], [-123.59772, 48.75559], [-123.62127, 48.76514], [-123.63885, 48.77426], [-123.66935, 48.78033], [-123.67901, 48.75472], [-123.65155, 48.74322], [-123.63017, 48.7405], [-123.60792, 48.74289], [-123.56494, 48.72987], [-123.56179, 48.73529], [-123.56201, 48.73508]]]}</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
@@ -33109,17 +33107,17 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>10.21966/4krv-aw23</t>
+          <t>10.21966/2ha7-9p26</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptbxmpkBsfyWWfSxOJ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpsCA3ycwZ7bFTDIQxh</t>
         </is>
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
@@ -33143,12 +33141,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>d320d90e-96bf-4993-81c5-f1f57886b0e6</t>
+          <t>dd471e82-a6b8-4f32-891c-bbea26e9998e</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>ca-cioos_b922699f-69b6-4d63-b538-7c290086a408</t>
+          <t>ca-cioos_aeb30028-a7eb-462e-ac0f-6c5fe101d4a2</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -33158,7 +33156,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Quw'utsun/Xwulqw'selu River Estuary (Provisional)</t>
+          <t>DNA Metabarcoding Captures Temporal and Vertical Dynamics of Mesozooplankton Communities</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -33176,12 +33174,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Estuary Resilience</t>
+          <t>Genomics, Oceanography</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -33196,45 +33194,45 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.56201, 48.73508], [-123.59772, 48.75559], [-123.62127, 48.76514], [-123.63885, 48.77426], [-123.66935, 48.78033], [-123.67901, 48.75472], [-123.65155, 48.74322], [-123.63017, 48.7405], [-123.60792, 48.74289], [-123.56494, 48.72987], [-123.56179, 48.73529], [-123.56201, 48.73508]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.0992, 50.0307]}</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+          <t>[{'max': '260.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
+          <t>zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>10.21966/2ha7-9p26</t>
+          <t>10.21966/6b20-7r76</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpsCA3ycwZ7bFTDIQxh</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OvzbmseH_syBXg1RXKd</t>
         </is>
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V299" t="n">
@@ -33253,12 +33251,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>dd471e82-a6b8-4f32-891c-bbea26e9998e</t>
+          <t>b27bb6f9-49ae-4f3a-a02a-098d8edf23e2</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>ca-cioos_aeb30028-a7eb-462e-ac0f-6c5fe101d4a2</t>
+          <t>ca-cioos_ac765dbb-8e47-415d-8685-d9090946b86b</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -33268,7 +33266,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>DNA Metabarcoding Captures Temporal and Vertical Dynamics of Mesozooplankton Communities</t>
+          <t>Micro-invertebrate DNA Barcodes from Quadra Island, BC (Biomarathon)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -33286,7 +33284,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Genomics, Oceanography</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -33306,45 +33304,45 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N300" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.0992, 50.0307]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.5461, 49.947], [-124.6642, 49.947], [-124.6642, 50.457], [-125.5461, 50.457], [-125.5461, 49.947]]]}</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>[{'max': '260.0', 'min': '0.0'}]</t>
+          <t>[{'max': '200.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>zooplanktonBiomassAndDiversity</t>
+          <t>invertebrateAbundanceAndDistribution, zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>10.21966/6b20-7r76</t>
+          <t>10.21966/qrxk-vb32</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OvzbmseH_syBXg1RXKd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxClAtvMEmxKRtywIeT</t>
         </is>
       </c>
       <c r="T300" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V300" t="n">
@@ -33363,12 +33361,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>b27bb6f9-49ae-4f3a-a02a-098d8edf23e2</t>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>ca-cioos_ac765dbb-8e47-415d-8685-d9090946b86b</t>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -33378,7 +33376,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Micro-invertebrate DNA Barcodes from Quadra Island, BC (Biomarathon)</t>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -33396,7 +33394,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -33416,7 +33414,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N301" t="n">
@@ -33424,37 +33422,33 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.5461, 49.947], [-124.6642, 49.947], [-124.6642, 50.457], [-125.5461, 50.457], [-125.5461, 49.947]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>[{'max': '200.0', 'min': '0.0'}]</t>
+          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
         </is>
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, zooplanktonBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>10.21966/qrxk-vb32</t>
+          <t>10.21966/w9n0-kn30</t>
         </is>
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxClAtvMEmxKRtywIeT</t>
-        </is>
-      </c>
-      <c r="T301" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr"/>
       <c r="U301" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="V301" t="n">
@@ -33466,112 +33460,6 @@
         </is>
       </c>
       <c r="X301" t="inlineStr"/>
-    </row>
-    <row r="302">
-      <c r="A302" t="n">
-        <v>300</v>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>CC-BY-4.0</t>
-        </is>
-      </c>
-      <c r="H302" t="b">
-        <v>0</v>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="M302" t="inlineStr">
-        <is>
-          <t>Tula Foundation</t>
-        </is>
-      </c>
-      <c r="N302" t="n">
-        <v>1</v>
-      </c>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
-        </is>
-      </c>
-      <c r="P302" t="inlineStr">
-        <is>
-          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
-        </is>
-      </c>
-      <c r="Q302" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R302" t="inlineStr">
-        <is>
-          <t>10.21966/w9n0-kn30</t>
-        </is>
-      </c>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
-        </is>
-      </c>
-      <c r="T302" t="inlineStr"/>
-      <c r="U302" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="V302" t="n">
-        <v>0</v>
-      </c>
-      <c r="W302" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X302" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X301"/>
+  <dimension ref="A1:X302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8462,16 +8462,16 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>10.21966/awsk-my87</t>
+          <t>10.21966/5rp3-3207</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V74" t="n">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8572,16 +8572,16 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10.21966/5rp3-3207</t>
+          <t>10.21966/awsk-my87</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V75" t="n">
@@ -27429,12 +27429,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
+          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
+          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -27444,7 +27444,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
+          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -27462,12 +27462,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -27490,37 +27490,37 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition, other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>10.21966/20ym-8826</t>
+          <t>10.21966/NMNG-SF35</t>
         </is>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
         </is>
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="V247" t="n">
@@ -27539,12 +27539,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
+          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
+          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -27554,7 +27554,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profilers, BC, Canada (Research)</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -27572,12 +27572,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -27596,41 +27596,41 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>macroalgalCanopyCoverAndComposition, other</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>10.21966/kace-2d24</t>
+          <t>10.21966/20ym-8826</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
         </is>
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V248" t="n">
@@ -27649,12 +27649,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
+          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profilers, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -27682,12 +27682,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -27706,31 +27706,31 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '20.0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>10.21966/65d8-k051</t>
+          <t>10.21966/kace-2d24</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V249" t="n">
@@ -27759,12 +27759,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
+          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -27774,7 +27774,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -27797,7 +27797,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -27820,37 +27820,37 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '20.0'}]</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
+          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>10.21966/175j-8k96</t>
+          <t>10.21966/65d8-k051</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
         </is>
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V250" t="n">
@@ -27861,9 +27861,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X250" t="n">
-        <v>2</v>
-      </c>
+      <c r="X250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27871,12 +27869,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
+          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -27886,7 +27884,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
+          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -27947,12 +27945,12 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>10.21966/dveq-bt48</t>
+          <t>10.21966/175j-8k96</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
         </is>
       </c>
       <c r="T251" t="inlineStr">
@@ -27962,7 +27960,7 @@
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V251" t="n">
@@ -27983,12 +27981,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
+          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -27998,7 +27996,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -28016,12 +28014,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -28040,52 +28038,54 @@
         </is>
       </c>
       <c r="N252" t="n">
+        <v>1</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>10.21966/dveq-bt48</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="V252" t="n">
+        <v>0</v>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X252" t="n">
         <v>2</v>
       </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
-        </is>
-      </c>
-      <c r="P252" t="inlineStr">
-        <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R252" t="inlineStr">
-        <is>
-          <t>10.21966/RZVW-4A72</t>
-        </is>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="V252" t="n">
-        <v>1</v>
-      </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
-        </is>
-      </c>
-      <c r="X252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28093,12 +28093,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
+          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -28108,7 +28108,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
+          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -28126,7 +28126,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -28154,45 +28154,45 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>10.21966/0xvh-1318</t>
+          <t>10.21966/RZVW-4A72</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
         </is>
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="X253" t="inlineStr"/>
@@ -28203,12 +28203,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
+          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -28264,37 +28264,37 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>10.21966/3q5j-n957</t>
+          <t>10.21966/0xvh-1318</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
         </is>
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V254" t="n">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
+          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
+          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -28346,12 +28346,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -28370,41 +28370,41 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>10.21966/kmc2-5r12</t>
+          <t>10.21966/3q5j-n957</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="V255" t="n">
@@ -28423,12 +28423,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
+          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ca-cioos_7e49967a-b5ab-443d-860b-e3c0eb0f709c</t>
+          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -28438,7 +28438,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Horne Lake Bathymetry Mapping</t>
+          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -28456,7 +28456,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -28480,41 +28480,41 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.7872, 49.3105], [-124.6447, 49.3105], [-124.6447, 49.3644], [-124.7872, 49.3644], [-124.7872, 49.3105]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>10.21966/vwee-e004</t>
+          <t>10.21966/kmc2-5r12</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/G8LjsjnnPxb5TxWL730BxDTQu532/-Njn-0LeJ-Uwj4L8EmOV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
         </is>
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="V256" t="n">
@@ -28533,12 +28533,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>18f56a52-11af-446a-aea9-07feca8d197e</t>
+          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ca-cioos_e897c9d0-3fca-4c89-b37f-e571413ffd12</t>
+          <t>ca-cioos_7e49967a-b5ab-443d-860b-e3c0eb0f709c</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Joffre Provincial Park Aerial Surveys - 2025 - Airborne Coastal Observatory</t>
+          <t>Horne Lake Bathymetry Mapping</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -28566,7 +28566,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -28594,12 +28594,12 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.5281, 50.3147], [-122.4303, 50.3147], [-122.4303, 50.3796], [-122.5281, 50.3796], [-122.5281, 50.3147]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.7872, 49.3105], [-124.6447, 49.3105], [-124.6447, 49.3644], [-124.7872, 49.3644], [-124.7872, 49.3105]]]}</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>[{'max': '475.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
@@ -28609,12 +28609,12 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>10.21966/k0z0-3z50</t>
+          <t>10.21966/vwee-e004</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ot_OaAHxjund0-w5rXq</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/G8LjsjnnPxb5TxWL730BxDTQu532/-Njn-0LeJ-Uwj4L8EmOV</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="V257" t="n">
@@ -28643,12 +28643,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>6c4803cc-d1c6-4327-806a-7f6796606175</t>
+          <t>18f56a52-11af-446a-aea9-07feca8d197e</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ca-cioos_6c34ed6e-5a17-41f2-b83a-cd59d1ce07bd</t>
+          <t>ca-cioos_e897c9d0-3fca-4c89-b37f-e571413ffd12</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Knight Inlet Multibeam Bathymetry Survey</t>
+          <t>Joffre Provincial Park Aerial Surveys - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -28704,12 +28704,12 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0537, 50.6529], [-125.9229, 50.6529], [-125.9229, 50.7077], [-126.0537, 50.7077], [-126.0537, 50.6529]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.5281, 50.3147], [-122.4303, 50.3147], [-122.4303, 50.3796], [-122.5281, 50.3796], [-122.5281, 50.3147]]]}</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>[{'max': '288.0', 'min': '0.0'}]</t>
+          <t>[{'max': '475.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
@@ -28719,17 +28719,17 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>10.21966/8dgz-1z27</t>
+          <t>10.21966/k0z0-3z50</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG7EOynnzSIOU7LPWgs</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ot_OaAHxjund0-w5rXq</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
@@ -28753,12 +28753,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ce6f3f8c-6b57-4f18-be46-8c0b5a4baeb9</t>
+          <t>6c4803cc-d1c6-4327-806a-7f6796606175</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ca-cioos_8755f475-2133-4205-baff-5e2937824f45</t>
+          <t>ca-cioos_6c34ed6e-5a17-41f2-b83a-cd59d1ce07bd</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -28768,7 +28768,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Poole Creek Aerial Surveys - Airborne Coastal Observatory</t>
+          <t>Knight Inlet Multibeam Bathymetry Survey</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -28786,7 +28786,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -28814,12 +28814,12 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.9075, 50.2436], [-122.8124, 50.2436], [-122.8124, 50.3016], [-122.9075, 50.3016], [-122.9075, 50.2436]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0537, 50.6529], [-125.9229, 50.6529], [-125.9229, 50.7077], [-126.0537, 50.7077], [-126.0537, 50.6529]]]}</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>[{'max': '450.0', 'min': '200.0'}]</t>
+          <t>[{'max': '288.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
@@ -28829,12 +28829,12 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>10.21966/g8f2-jw82</t>
+          <t>10.21966/8dgz-1z27</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OtfdtO43um_1J_LdCpn</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG7EOynnzSIOU7LPWgs</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
@@ -28863,12 +28863,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>e1247209-cc26-4788-82a2-dd8a5c971e22</t>
+          <t>ce6f3f8c-6b57-4f18-be46-8c0b5a4baeb9</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ca-cioos_2e5ddbaa-4f0c-4339-8595-1ddbd35c3df4</t>
+          <t>ca-cioos_8755f475-2133-4205-baff-5e2937824f45</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -28878,7 +28878,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Aerial Surveys in British Columbia, Washington, and Alberta - 2025 - Airborne Coastal Observatory</t>
+          <t>Poole Creek Aerial Surveys - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -28924,12 +28924,12 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.9263, 48.0077], [-112.7224, 48.0077], [-112.7224, 54.6673], [-127.9263, 54.6673], [-127.9263, 48.0077]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9075, 50.2436], [-122.8124, 50.2436], [-122.8124, 50.3016], [-122.9075, 50.3016], [-122.9075, 50.2436]]]}</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>[{'max': '4019.0', 'min': '0.0'}]</t>
+          <t>[{'max': '450.0', 'min': '200.0'}]</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
@@ -28939,22 +28939,22 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>10.21966/n6ga-nc24</t>
+          <t>10.21966/g8f2-jw82</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ou3t_K6rGOHTMO67Xbq</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OtfdtO43um_1J_LdCpn</t>
         </is>
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="V260" t="n">
@@ -28973,12 +28973,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>5ac3ac5f-702e-43d8-bcb7-79f30c4d9e08</t>
+          <t>e1247209-cc26-4788-82a2-dd8a5c971e22</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ca-cioos_656ea307-fed0-48ca-b5d8-1bc017dc52d2</t>
+          <t>ca-cioos_2e5ddbaa-4f0c-4339-8595-1ddbd35c3df4</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -28988,7 +28988,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Botanical Beach - Juan de Fuca Provincial Park - Drone Mapping</t>
+          <t>Glacier and Icefield Aerial Surveys in British Columbia, Washington, and Alberta - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -29006,7 +29006,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -29034,12 +29034,12 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.45265489, 48.52152402], [-124.43377214, 48.52152402], [-124.43377214, 48.53061904], [-124.45265489, 48.53061904], [-124.45265489, 48.52152402]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.9263, 48.0077], [-112.7224, 48.0077], [-112.7224, 54.6673], [-127.9263, 54.6673], [-127.9263, 48.0077]]]}</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+          <t>[{'max': '4019.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
@@ -29049,12 +29049,12 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>10.21966/kn3e-fn08</t>
+          <t>10.21966/n6ga-nc24</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdvcmtQME1NZmdWcDY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ou3t_K6rGOHTMO67Xbq</t>
         </is>
       </c>
       <c r="T261" t="inlineStr">
@@ -29083,12 +29083,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>05dac0a6-a26c-4cb5-895d-132b5e2134cd</t>
+          <t>5ac3ac5f-702e-43d8-bcb7-79f30c4d9e08</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ca-cioos_b45dbc9d-bf7a-4734-86cd-3397e7c9ac62</t>
+          <t>ca-cioos_656ea307-fed0-48ca-b5d8-1bc017dc52d2</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -29098,7 +29098,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Sea surface temperature data in False Creek, British Columbia</t>
+          <t>Botanical Beach - Juan de Fuca Provincial Park - Drone Mapping</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -29144,37 +29144,37 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.45265489, 48.52152402], [-124.43377214, 48.52152402], [-124.43377214, 48.53061904], [-124.45265489, 48.53061904], [-124.45265489, 48.52152402]]]}</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>[{'max': '0.5', 'min': '0.5'}]</t>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>10.21966/0g6d-pk30</t>
+          <t>10.21966/kn3e-fn08</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NHaXDtgFZr0-Oul6FZG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdvcmtQME1NZmdWcDY</t>
         </is>
       </c>
       <c r="T262" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="V262" t="n">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>6eb46e26-dac5-4964-8b29-8e8541381aac</t>
+          <t>05dac0a6-a26c-4cb5-895d-132b5e2134cd</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
+          <t>ca-cioos_b45dbc9d-bf7a-4734-86cd-3397e7c9ac62</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -29208,7 +29208,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Time series of eelgrass (Zostera marina) meadow extent derived from drone surveys, Central Coast, British Columbia</t>
+          <t>Sea surface temperature data in False Creek, British Columbia</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -29226,12 +29226,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -29254,37 +29254,37 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28], [-123.1, 49.28]]]}</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.5', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>10.21966/03pw-2190</t>
+          <t>10.21966/0g6d-pk30</t>
         </is>
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NHaXDtgFZr0-Oul6FZG</t>
         </is>
       </c>
       <c r="T263" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="V263" t="n">
@@ -29303,12 +29303,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>67b81524-e385-439e-9bc1-03bd4652eba6</t>
+          <t>6eb46e26-dac5-4964-8b29-8e8541381aac</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>ca-cioos_79368bf3-8f02-4355-837e-3a6cef0d2886</t>
+          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Watersheds Stream Stations Timeseries, Calvert and Hecate Islands, BC, Canada (Provisional)</t>
+          <t>Time series of eelgrass (Zostera marina) meadow extent derived from drone surveys, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -29336,12 +29336,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -29360,11 +29360,11 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
@@ -29374,27 +29374,27 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>10.21966/c6xs-y324</t>
+          <t>10.21966/03pw-2190</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/zBOULF9sDAgC4rkoZUFQq7sBGCf2/-OtAIe6lv3elLZd4c-V1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
         </is>
       </c>
       <c r="T264" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="V264" t="n">
@@ -29413,12 +29413,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>ff456916-01f7-4eb0-961f-3658f0b4f39b</t>
+          <t>67b81524-e385-439e-9bc1-03bd4652eba6</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>ca-cioos_d986aade-6bf1-4dfa-97c2-686975f944d5</t>
+          <t>ca-cioos_79368bf3-8f02-4355-837e-3a6cef0d2886</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -29428,7 +29428,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Watersheds Stream Stations Timeseries, Calvert and Hecate Islands, BC, Canada (Research)</t>
+          <t>Watersheds Stream Stations Timeseries, Calvert and Hecate Islands, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -29451,7 +29451,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -29474,12 +29474,12 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.1, 51.64], [-128.0, 51.64], [-128.0, 51.67], [-128.1, 51.67], [-128.1, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q265" t="inlineStr">
@@ -29489,17 +29489,17 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>10.21966/47m7-ev69</t>
+          <t>10.21966/c6xs-y324</t>
         </is>
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/zBOULF9sDAgC4rkoZUFQq7sBGCf2/-OHj73dBYs1okPPjDXKY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/zBOULF9sDAgC4rkoZUFQq7sBGCf2/-OtAIe6lv3elLZd4c-V1</t>
         </is>
       </c>
       <c r="T265" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U265" t="inlineStr">
@@ -29523,12 +29523,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>71c6db20-a521-451b-b371-a2560f6af25e</t>
+          <t>ff456916-01f7-4eb0-961f-3658f0b4f39b</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>ca-cioos_999da1dd-efde-4a55-868b-ce2d6ca3b983</t>
+          <t>ca-cioos_d986aade-6bf1-4dfa-97c2-686975f944d5</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -29538,7 +29538,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Observations from the 2017 Hakai MarineGEO Bioblitz</t>
+          <t>Watersheds Stream Stations Timeseries, Calvert and Hecate Islands, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -29556,12 +29556,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -29580,41 +29580,41 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.951, 51.48631], [-127.76165, 51.48631], [-127.76165, 52.05347], [-128.951, 52.05347], [-128.951, 51.48631]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.1, 51.64], [-128.0, 51.64], [-128.0, 51.67], [-128.1, 51.67], [-128.1, 51.64]]]}</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>[{'max': '40.0', 'min': '0.5'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>10.21966/0jfr-7b65</t>
+          <t>10.21966/47m7-ev69</t>
         </is>
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCmJU0B97JSOfOpj6J</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/zBOULF9sDAgC4rkoZUFQq7sBGCf2/-OHj73dBYs1okPPjDXKY</t>
         </is>
       </c>
       <c r="T266" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="V266" t="n">
@@ -29633,12 +29633,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>f0ae5f04-2c3a-4b67-8fbf-c6dc3771257d</t>
+          <t>71c6db20-a521-451b-b371-a2560f6af25e</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>ca-cioos_482d2463-0c81-4d62-a22a-1c0942b3c1fa</t>
+          <t>ca-cioos_999da1dd-efde-4a55-868b-ce2d6ca3b983</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -29648,7 +29648,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Observations from the 2019 Hakai Deep Water Bioblitz</t>
+          <t>Observations from the 2017 Hakai MarineGEO Bioblitz</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -29694,12 +29694,12 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.14433, 51.615734], [-127.76327, 51.615734], [-127.76327, 51.787], [-128.14433, 51.787], [-128.14433, 51.615734]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.951, 51.48631], [-127.76165, 51.48631], [-127.76165, 52.05347], [-128.951, 52.05347], [-128.951, 51.48631]]]}</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>[{'max': '255.0', 'min': '5.0'}]</t>
+          <t>[{'max': '40.0', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q267" t="inlineStr">
@@ -29709,22 +29709,22 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>10.21966/3p06-vt55</t>
+          <t>10.21966/0jfr-7b65</t>
         </is>
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCoStSubGWAdV78XNC</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCmJU0B97JSOfOpj6J</t>
         </is>
       </c>
       <c r="T267" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="V267" t="n">
@@ -29743,12 +29743,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>91d2ddf0-ea25-4ef9-b990-26d2957cb3bd</t>
+          <t>f0ae5f04-2c3a-4b67-8fbf-c6dc3771257d</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>ca-cioos_542a20b8-242e-4199-a062-5b76ea9cbf2d</t>
+          <t>ca-cioos_482d2463-0c81-4d62-a22a-1c0942b3c1fa</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -29758,7 +29758,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Observations from the 2018 Hakai Terrestrial Bioblitz</t>
+          <t>Observations from the 2019 Hakai Deep Water Bioblitz</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -29804,27 +29804,27 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.98366, 51.5919], [-125.0032, 51.5919], [-125.0032, 53.9998], [-128.98366, 53.9998], [-128.98366, 51.5919]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.14433, 51.615734], [-127.76327, 51.615734], [-127.76327, 51.787], [-128.14433, 51.787], [-128.14433, 51.615734]]]}</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>[{'max': '1012.0', 'min': '50.0'}]</t>
+          <t>[{'max': '255.0', 'min': '5.0'}]</t>
         </is>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>10.21966/t0h7-8g95</t>
+          <t>10.21966/3p06-vt55</t>
         </is>
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCpwd5hTju8QOKVY-E</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCoStSubGWAdV78XNC</t>
         </is>
       </c>
       <c r="T268" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="V268" t="n">
@@ -29853,12 +29853,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>fa42f16a-3693-4c51-b45c-a36e709fdac3</t>
+          <t>91d2ddf0-ea25-4ef9-b990-26d2957cb3bd</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>ca-cioos_d69bf79e-b616-404e-bbfc-92932ca74087</t>
+          <t>ca-cioos_542a20b8-242e-4199-a062-5b76ea9cbf2d</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -29868,7 +29868,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Observations from the 2018 Hakai Seagrass Bioblitz</t>
+          <t>Observations from the 2018 Hakai Terrestrial Bioblitz</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -29886,7 +29886,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -29914,27 +29914,27 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.8123, 51.8438], [-128.2105, 51.684], [-128.1968, 51.6158], [-127.8837, 51.6192], [-127.8123, 51.8438]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.98366, 51.5919], [-125.0032, 51.5919], [-125.0032, 53.9998], [-128.98366, 53.9998], [-128.98366, 51.5919]]]}</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>[{'max': '300.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1012.0', 'min': '50.0'}]</t>
         </is>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution, seagrassCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>10.21966/yf1f-jx85</t>
+          <t>10.21966/t0h7-8g95</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCnP9OAghmAmYObj0D</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCpwd5hTju8QOKVY-E</t>
         </is>
       </c>
       <c r="T269" t="inlineStr">
@@ -29944,7 +29944,7 @@
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V269" t="n">
@@ -29963,12 +29963,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>fc3d2ea5-b60c-42c9-97e9-542024bec9fa</t>
+          <t>fa42f16a-3693-4c51-b45c-a36e709fdac3</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>ca-cioos_4add33cd-b182-4825-900a-5695f333125a</t>
+          <t>ca-cioos_d69bf79e-b616-404e-bbfc-92932ca74087</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -29978,7 +29978,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Weather Station Time Series, Hyacinthe Bay, BC, Canada (Provisional)</t>
+          <t>Observations from the 2018 Hakai Seagrass Bioblitz</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -29996,12 +29996,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Genomics, Nearshore</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -30024,37 +30024,47 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2221111, 50.1162556]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.8123, 51.8438], [-128.2105, 51.684], [-128.1968, 51.6158], [-127.8837, 51.6192], [-127.8123, 51.8438]]]}</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R270" t="inlineStr"/>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution, seagrassCoverAndComposition</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>10.21966/yf1f-jx85</t>
+        </is>
+      </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OyesAm4pxUK1wqBMn7x</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxCnP9OAghmAmYObj0D</t>
         </is>
       </c>
       <c r="T270" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="V270" t="inlineStr"/>
-      <c r="W270" t="inlineStr"/>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="V270" t="n">
+        <v>0</v>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="X270" t="inlineStr"/>
     </row>
     <row r="271">
@@ -30063,12 +30073,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
+          <t>fc3d2ea5-b60c-42c9-97e9-542024bec9fa</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>ca-cioos_3f40326a-23f9-4e30-a16a-f332ace14e2f</t>
+          <t>ca-cioos_4add33cd-b182-4825-900a-5695f333125a</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -30078,7 +30088,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Nereocystis kelp canopy productivity data from BC Central Coast</t>
+          <t>Weather Station Time Series, Hyacinthe Bay, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -30096,12 +30106,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -30124,47 +30134,37 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.19], [-127.1, 51.19], [-127.1, 52.28], [-128.6, 52.28], [-128.6, 51.19]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2221111, 50.1162556]}</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
-        </is>
-      </c>
-      <c r="R271" t="inlineStr">
-        <is>
-          <t>10.21966/d1s2-s530</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr"/>
       <c r="S271" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtG8b48aDAEdJoqNT6N</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OyesAm4pxUK1wqBMn7x</t>
         </is>
       </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="V271" t="n">
-        <v>1</v>
-      </c>
-      <c r="W271" t="inlineStr">
-        <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
-        </is>
-      </c>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr"/>
+      <c r="W271" t="inlineStr"/>
       <c r="X271" t="inlineStr"/>
     </row>
     <row r="272">
@@ -30173,12 +30173,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>aab940b9-bb7f-49c0-ae62-4f78d26897b3</t>
+          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>ca-cioos_0219e1d6-8dfc-4718-b89b-ea3dff06a70d</t>
+          <t>ca-cioos_3f40326a-23f9-4e30-a16a-f332ace14e2f</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -30188,7 +30188,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Modeled Eelgrass Extent, British Columbia, Canada</t>
+          <t>Nereocystis kelp canopy productivity data from BC Central Coast</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -30206,12 +30206,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -30230,49 +30230,49 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-133.7841801345348, 48.23443097294032], [-122.49023482203482, 48.23443097294032], [-122.49023482203482, 54.52958287232971], [-133.7841801345348, 54.52958287232971], [-133.7841801345348, 48.23443097294032]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.19], [-127.1, 51.19], [-127.1, 52.28], [-128.6, 52.28], [-128.6, 51.19]]]}</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>10.21966/1ty5-e654</t>
+          <t>10.21966/d1s2-s530</t>
         </is>
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWtuNVpwdEdLRXZTODc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtG8b48aDAEdJoqNT6N</t>
         </is>
       </c>
       <c r="T272" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W272" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="X272" t="inlineStr"/>
@@ -30283,12 +30283,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>3988f8e8-36ea-4cda-9bd9-a03157116ef5</t>
+          <t>aab940b9-bb7f-49c0-ae62-4f78d26897b3</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>ca-cioos_d43a79c1-a6ba-4e37-8dc2-6ced6312828e</t>
+          <t>ca-cioos_0219e1d6-8dfc-4718-b89b-ea3dff06a70d</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -30298,7 +30298,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Data from Manuscript: Parasites of the hermit crab Pagurus hirsutiusculus; distribution, prevalence, and thermal ecology</t>
+          <t>Modeled Eelgrass Extent, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -30316,7 +30316,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -30340,11 +30340,11 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.66], [-127.9, 51.81], [-122.2, 49.03], [-123.3, 49.01], [-123.0, 48.83], [-123.0, 48.78], [-123.3, 48.7], [-123.3, 48.53], [-123.6, 48.59], [-125.2, 48.73], [-125.6, 48.95], [-125.6, 50.11], [-128.4, 51.66]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-133.7841801345348, 48.23443097294032], [-122.49023482203482, 48.23443097294032], [-122.49023482203482, 54.52958287232971], [-133.7841801345348, 54.52958287232971], [-133.7841801345348, 48.23443097294032]]]}</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
@@ -30354,17 +30354,17 @@
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, seaSurfaceSalinity</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>10.21966/xb3t-qb88</t>
+          <t>10.21966/1ty5-e654</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3eh7IMAvm8ZUtcMBeifFL0eJCIA3/-O5Kei32z9cfatfgKj5y</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWtuNVpwdEdLRXZTODc</t>
         </is>
       </c>
       <c r="T273" t="inlineStr">
@@ -30374,7 +30374,7 @@
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V273" t="n">
@@ -30393,12 +30393,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>c4932b55-1dd8-4f2f-89da-5822056ecc37</t>
+          <t>3988f8e8-36ea-4cda-9bd9-a03157116ef5</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>ca-cioos_53189107-9df5-426b-acb4-f903468554fe</t>
+          <t>ca-cioos_d43a79c1-a6ba-4e37-8dc2-6ced6312828e</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -30408,7 +30408,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Comparing invertebrate and seaweed diversity in kelp forests and urchin barrens in Owen Bay, British Columbia, using Autonomous Reef Monitoring Structures (ARMS)</t>
+          <t>Data from Manuscript: Parasites of the hermit crab Pagurus hirsutiusculus; distribution, prevalence, and thermal ecology</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -30426,7 +30426,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Sentinels of Change, Genomics</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -30450,41 +30450,41 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.2335, 50.2999], [-125.2163, 50.2999], [-125.2163, 50.313], [-125.2335, 50.313], [-125.2335, 50.2999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.66], [-127.9, 51.81], [-122.2, 49.03], [-123.3, 49.01], [-123.0, 48.83], [-123.0, 48.78], [-123.3, 48.7], [-123.3, 48.53], [-123.6, 48.59], [-125.2, 48.73], [-125.6, 48.95], [-125.6, 50.11], [-128.4, 51.66]]]}</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
+          <t>invertebrateAbundanceAndDistribution, seaSurfaceSalinity</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>10.21966/e5mw-tr82</t>
+          <t>10.21966/xb3t-qb88</t>
         </is>
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/5Jh4rsxoBsRd4mVFqZ0XJoMtMHI2/-P-tq8uNjGhWtk4rBny0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3eh7IMAvm8ZUtcMBeifFL0eJCIA3/-O5Kei32z9cfatfgKj5y</t>
         </is>
       </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V274" t="n">
@@ -30495,9 +30495,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X274" t="n">
-        <v>1</v>
-      </c>
+      <c r="X274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30505,12 +30503,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>33bb67af-4d61-4b15-93a9-f3ab2498430b</t>
+          <t>c4932b55-1dd8-4f2f-89da-5822056ecc37</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>ca-cioos_73abfecf-d35c-4f9c-a991-eee5cece08ea</t>
+          <t>ca-cioos_53189107-9df5-426b-acb4-f903468554fe</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -30520,7 +30518,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Kelp Canopy Extent 2012 - NW Calvert Island</t>
+          <t>Comparing invertebrate and seaweed diversity in kelp forests and urchin barrens in Owen Bay, British Columbia, using Autonomous Reef Monitoring Structures (ARMS)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -30538,7 +30536,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Sentinels of Change, Genomics</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -30562,41 +30560,41 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16959381103513, 51.63613234359897], [-128.11191558837888, 51.63613234359897], [-128.11191558837888, 51.681709494104325], [-128.16959381103513, 51.681709494104325], [-128.16959381103513, 51.63613234359897]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.2335, 50.2999], [-125.2163, 50.2999], [-125.2163, 50.313], [-125.2335, 50.313], [-125.2335, 50.2999]]]}</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '6.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>other, macroalgalCanopyCoverAndComposition</t>
+          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>10.21966/63rs-yt91</t>
+          <t>10.21966/e5mw-tr82</t>
         </is>
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxUM01laTFaREhKbWE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/5Jh4rsxoBsRd4mVFqZ0XJoMtMHI2/-P-tq8uNjGhWtk4rBny0</t>
         </is>
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="V275" t="n">
@@ -30617,12 +30615,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>bc1133da-5601-4f92-bc53-41be547c936b</t>
+          <t>33bb67af-4d61-4b15-93a9-f3ab2498430b</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>ca-cioos_940218ef-d7f8-4f3f-9e69-52150ecdbec5</t>
+          <t>ca-cioos_73abfecf-d35c-4f9c-a991-eee5cece08ea</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -30632,7 +30630,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>North Vancouver Island Aerial Survey - 2024 - Airborne Coastal Observatory</t>
+          <t>Kelp Canopy Extent 2012 - NW Calvert Island</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -30650,7 +30648,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -30674,31 +30672,31 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 50.35], [-125.4, 50.35], [-125.4, 50.63], [-126.7, 50.63], [-126.7, 50.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16959381103513, 51.63613234359897], [-128.11191558837888, 51.63613234359897], [-128.11191558837888, 51.681709494104325], [-128.16959381103513, 51.681709494104325], [-128.16959381103513, 51.63613234359897]]]}</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>10.21966/kdhe-hz07</t>
+          <t>10.21966/63rs-yt91</t>
         </is>
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCoHpqOwDbp834fqRY3</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxUM01laTFaREhKbWE</t>
         </is>
       </c>
       <c r="T276" t="inlineStr">
@@ -30708,7 +30706,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="V276" t="n">
@@ -30729,12 +30727,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
+          <t>bc1133da-5601-4f92-bc53-41be547c936b</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>ca-cioos_c7466354-bacc-4781-acdc-543dd03d1eab</t>
+          <t>ca-cioos_940218ef-d7f8-4f3f-9e69-52150ecdbec5</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -30744,7 +30742,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Nanwakolas LiDAR Surveys - Airborne Coastal Observatory</t>
+          <t>North Vancouver Island Aerial Survey - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -30790,12 +30788,12 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.8, 49.26], [-124.5, 49.26], [-124.5, 50.83], [-126.8, 50.83], [-126.8, 49.26]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 50.35], [-125.4, 50.35], [-125.4, 50.63], [-126.7, 50.63], [-126.7, 50.35]]]}</t>
         </is>
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>[{'max': '1700.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q277" t="inlineStr">
@@ -30805,12 +30803,12 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>10.21966/e0r7-ge27</t>
+          <t>10.21966/kdhe-hz07</t>
         </is>
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OjbuSE_uZcCs3Fit_mg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCoHpqOwDbp834fqRY3</t>
         </is>
       </c>
       <c r="T277" t="inlineStr">
@@ -30820,7 +30818,7 @@
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="V277" t="n">
@@ -30839,12 +30837,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>f7433c1a-3aad-4761-81c4-c191a5e6ac92</t>
+          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>ca-cioos_52e97374-bee5-4b1a-9b85-7170a5df8d6b</t>
+          <t>ca-cioos_c7466354-bacc-4781-acdc-543dd03d1eab</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -30854,7 +30852,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Biomass and density of Pycnopodia helianthoides from the central coast of BC</t>
+          <t>Nanwakolas LiDAR Surveys - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -30872,7 +30870,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -30900,37 +30898,37 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.617, 51.3321], [-127.3509, 51.3321], [-127.3509, 52.3317], [-128.617, 52.3317], [-128.617, 51.3321]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.8, 49.26], [-124.5, 49.26], [-124.5, 50.83], [-126.8, 50.83], [-126.8, 49.26]]]}</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1700.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>seaSurfaceSalinity, subSurfaceSalinity, seaSurfaceTemperature, subSurfaceTemperature, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>10.21966/xy6n-qz76</t>
+          <t>10.21966/e0r7-ge27</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-OteEfuBSvhg-2RySC4a</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OjbuSE_uZcCs3Fit_mg</t>
         </is>
       </c>
       <c r="T278" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V278" t="n">
@@ -30949,12 +30947,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>c7a168e8-f15e-446f-a49d-0b4a1f043ac2</t>
+          <t>f7433c1a-3aad-4761-81c4-c191a5e6ac92</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ca-cioos_b4844ae2-d9c1-42f2-ae4d-a8f994c395a0</t>
+          <t>ca-cioos_52e97374-bee5-4b1a-9b85-7170a5df8d6b</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -30964,7 +30962,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Putting fjord biodiversity on the map for British Columbia conservation planning</t>
+          <t>Biomass and density of Pycnopodia helianthoides from the central coast of BC</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -30982,7 +30980,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Genomics, Oceanography</t>
+          <t>Oceanography, Nearshore</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -31002,45 +31000,45 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.0471, 52.2577], [-128.9141, 51.7033], [-127.6841, 50.7687], [-123.7744, 48.9864], [-122.764, 49.331], [-122.8299, 49.9706], [-127.0471, 52.2577]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.617, 51.3321], [-127.3509, 51.3321], [-127.3509, 52.3317], [-128.617, 52.3317], [-128.617, 51.3321]]]}</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>[{'max': '595.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, subSurfaceTemperature, subSurfaceSalinity</t>
+          <t>seaSurfaceSalinity, subSurfaceSalinity, seaSurfaceTemperature, subSurfaceTemperature, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>10.21966/n141-m959</t>
+          <t>10.21966/xy6n-qz76</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-Ow-ZgW1jkC5-WyrtlLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-OteEfuBSvhg-2RySC4a</t>
         </is>
       </c>
       <c r="T279" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U279" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="V279" t="n">
@@ -31051,9 +31049,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X279" t="n">
-        <v>1</v>
-      </c>
+      <c r="X279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31061,12 +31057,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
+          <t>c7a168e8-f15e-446f-a49d-0b4a1f043ac2</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
+          <t>ca-cioos_b4844ae2-d9c1-42f2-ae4d-a8f994c395a0</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -31076,7 +31072,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
+          <t>Putting fjord biodiversity on the map for British Columbia conservation planning</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -31094,7 +31090,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Genomics, Oceanography</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -31114,56 +31110,58 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N280" t="n">
+        <v>2</v>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.0471, 52.2577], [-128.9141, 51.7033], [-127.6841, 50.7687], [-123.7744, 48.9864], [-122.764, 49.331], [-122.8299, 49.9706], [-127.0471, 52.2577]]]}</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>[{'max': '595.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>fishAbundanceAndDistribution, subSurfaceTemperature, subSurfaceSalinity</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>10.21966/n141-m959</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-Ow-ZgW1jkC5-WyrtlLV</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="V280" t="n">
+        <v>0</v>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X280" t="n">
         <v>1</v>
       </c>
-      <c r="O280" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
-        </is>
-      </c>
-      <c r="P280" t="inlineStr">
-        <is>
-          <t>[{'max': '2.5', 'min': '2.5'}]</t>
-        </is>
-      </c>
-      <c r="Q280" t="inlineStr">
-        <is>
-          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R280" t="inlineStr">
-        <is>
-          <t>10.21966/rrzq-yw32</t>
-        </is>
-      </c>
-      <c r="S280" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
-        </is>
-      </c>
-      <c r="T280" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="V280" t="n">
-        <v>0</v>
-      </c>
-      <c r="W280" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31171,12 +31169,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
+          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
+          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -31186,17 +31184,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
+          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H281" t="b">
@@ -31209,7 +31207,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -31232,23 +31230,27 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '600.0'}]</t>
+          <t>[{'max': '2.5', 'min': '2.5'}]</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R281" t="inlineStr"/>
+          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>10.21966/rrzq-yw32</t>
+        </is>
+      </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
         </is>
       </c>
       <c r="T281" t="inlineStr">
@@ -31258,11 +31260,17 @@
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="V281" t="inlineStr"/>
-      <c r="W281" t="inlineStr"/>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="V281" t="n">
+        <v>0</v>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="X281" t="inlineStr"/>
     </row>
     <row r="282">
@@ -31271,12 +31279,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
+          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
+          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -31286,17 +31294,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
+          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H282" t="b">
@@ -31304,12 +31312,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Estuary Resilience</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -31332,47 +31340,37 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+          <t>[{'max': '0.0', 'min': '600.0'}]</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
-        </is>
-      </c>
-      <c r="R282" t="inlineStr">
-        <is>
-          <t>10.21966/r9zr-xz33</t>
-        </is>
-      </c>
+          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
         </is>
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="V282" t="n">
-        <v>0</v>
-      </c>
-      <c r="W282" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr"/>
+      <c r="W282" t="inlineStr"/>
       <c r="X282" t="inlineStr"/>
     </row>
     <row r="283">
@@ -31381,12 +31379,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
+          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
+          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -31396,7 +31394,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -31442,7 +31440,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
@@ -31457,12 +31455,12 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>10.21966/9dbb-5d54</t>
+          <t>10.21966/r9zr-xz33</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
         </is>
       </c>
       <c r="T283" t="inlineStr">
@@ -31491,12 +31489,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
+          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
+          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -31506,7 +31504,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -31552,7 +31550,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
@@ -31567,12 +31565,12 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>10.21966/vpz7-mm73</t>
+          <t>10.21966/9dbb-5d54</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
         </is>
       </c>
       <c r="T284" t="inlineStr">
@@ -31601,12 +31599,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>0ce3ee5b-425b-4eb0-a201-96bdfb795a3f</t>
+          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>ca-cioos_354b5b83-e752-4ffb-a740-d1cdc02ac8c6</t>
+          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -31616,7 +31614,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Dtlaxsiwè River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -31662,7 +31660,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.1721, 50.61011], [-127.17933, 50.612], [-127.1873, 50.6098], [-127.19703, 50.61072], [-127.20524, 50.61585], [-127.19007, 50.61844], [-127.18675, 50.61393], [-127.17744, 50.61359], [-127.17161, 50.61118], [-127.17203, 50.61011], [-127.1721, 50.61011]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
@@ -31677,12 +31675,12 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>10.21966/ydm2-m238</t>
+          <t>10.21966/vpz7-mm73</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7Dng-ZtRd05hnZCq1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
         </is>
       </c>
       <c r="T285" t="inlineStr">
@@ -31711,12 +31709,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>1a2aa5c8-9a83-46f7-967d-1127436c2084</t>
+          <t>0ce3ee5b-425b-4eb0-a201-96bdfb795a3f</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>ca-cioos_58a5140a-0b2c-4186-a648-53d9f58e5226</t>
+          <t>ca-cioos_354b5b83-e752-4ffb-a740-d1cdc02ac8c6</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -31726,7 +31724,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kvai River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Dtlaxsiwè River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -31772,7 +31770,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.81882, 51.77547], [-127.83122, 51.77986], [-127.85192, 51.781], [-127.86785, 51.78358], [-127.8958, 51.77366], [-127.89418, 51.77118], [-127.87834, 51.77309], [-127.86508, 51.77748], [-127.84009, 51.77519], [-127.82731, 51.77452], [-127.82025, 51.77309], [-127.81853, 51.77566], [-127.81882, 51.77547]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.1721, 50.61011], [-127.17933, 50.612], [-127.1873, 50.6098], [-127.19703, 50.61072], [-127.20524, 50.61585], [-127.19007, 50.61844], [-127.18675, 50.61393], [-127.17744, 50.61359], [-127.17161, 50.61118], [-127.17203, 50.61011], [-127.1721, 50.61011]]]}</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
@@ -31787,12 +31785,12 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>10.21966/pm9m-h431</t>
+          <t>10.21966/ydm2-m238</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7QQE3ifLCAPcu3Jih</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7Dng-ZtRd05hnZCq1</t>
         </is>
       </c>
       <c r="T286" t="inlineStr">
@@ -31821,12 +31819,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>c035b81c-0fc3-446e-bec5-8b8933ae874b</t>
+          <t>1a2aa5c8-9a83-46f7-967d-1127436c2084</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>ca-cioos_7fbc28f7-ee87-4361-bbee-0ed8ce24522d</t>
+          <t>ca-cioos_58a5140a-0b2c-4186-a648-53d9f58e5226</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -31836,7 +31834,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Gwa'dzi River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kvai River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -31882,7 +31880,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.46176, 50.74217], [-127.49022, 50.72165], [-127.49167, 50.71188], [-127.4832, 50.70356], [-127.4874, 50.69181], [-127.46443, 50.6928], [-127.47282, 50.70776], [-127.47992, 50.71424], [-127.48305, 50.72058], [-127.45901, 50.74011], [-127.46153, 50.74217], [-127.46176, 50.74217]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.81882, 51.77547], [-127.83122, 51.77986], [-127.85192, 51.781], [-127.86785, 51.78358], [-127.8958, 51.77366], [-127.89418, 51.77118], [-127.87834, 51.77309], [-127.86508, 51.77748], [-127.84009, 51.77519], [-127.82731, 51.77452], [-127.82025, 51.77309], [-127.81853, 51.77566], [-127.81882, 51.77547]]]}</t>
         </is>
       </c>
       <c r="P287" t="inlineStr">
@@ -31897,12 +31895,12 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>10.21966/xq99-x273</t>
+          <t>10.21966/pm9m-h431</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7BCRnF2C30YPkxIyd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7QQE3ifLCAPcu3Jih</t>
         </is>
       </c>
       <c r="T287" t="inlineStr">
@@ -31931,12 +31929,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
+          <t>c035b81c-0fc3-446e-bec5-8b8933ae874b</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
+          <t>ca-cioos_7fbc28f7-ee87-4361-bbee-0ed8ce24522d</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -31946,7 +31944,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Gwa'dzi River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -31992,7 +31990,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.46176, 50.74217], [-127.49022, 50.72165], [-127.49167, 50.71188], [-127.4832, 50.70356], [-127.4874, 50.69181], [-127.46443, 50.6928], [-127.47282, 50.70776], [-127.47992, 50.71424], [-127.48305, 50.72058], [-127.45901, 50.74011], [-127.46153, 50.74217], [-127.46176, 50.74217]]]}</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
@@ -32007,12 +32005,12 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>10.21966/kde9-8g12</t>
+          <t>10.21966/xq99-x273</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7BCRnF2C30YPkxIyd</t>
         </is>
       </c>
       <c r="T288" t="inlineStr">
@@ -32041,12 +32039,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
+          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
+          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -32056,7 +32054,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -32102,7 +32100,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
@@ -32117,12 +32115,12 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>10.21966/9a97-2j48</t>
+          <t>10.21966/kde9-8g12</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
         </is>
       </c>
       <c r="T289" t="inlineStr">
@@ -32151,12 +32149,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
+          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
+          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -32166,7 +32164,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -32212,7 +32210,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
@@ -32227,12 +32225,12 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>10.21966/ed9w-2653</t>
+          <t>10.21966/9a97-2j48</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
         </is>
       </c>
       <c r="T290" t="inlineStr">
@@ -32261,12 +32259,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>1af6a43a-e73b-4774-8e10-b9f2928ab133</t>
+          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ca-cioos_ae7e017c-9211-4f98-b56e-90a4bbac161c</t>
+          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -32276,7 +32274,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Snuneymuxw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -32322,7 +32320,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.88685, 49.19332], [-123.92494, 49.1612], [-123.92581, 49.13841], [-123.91159, 49.123], [-123.88023, 49.11117], [-123.85971, 49.12766], [-123.89792, 49.16196], [-123.88099, 49.18866], [-123.88685, 49.19332]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -32337,12 +32335,12 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>10.21966/k01q-wb27</t>
+          <t>10.21966/ed9w-2653</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt459vxCIH7YPRN9fp</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
         </is>
       </c>
       <c r="T291" t="inlineStr">
@@ -32371,12 +32369,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
+          <t>1af6a43a-e73b-4774-8e10-b9f2928ab133</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>ca-cioos_bea3da72-dafe-4e25-b5b2-0176e0ffba44</t>
+          <t>ca-cioos_ae7e017c-9211-4f98-b56e-90a4bbac161c</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -32386,7 +32384,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Chemainus River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Snuneymuxw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -32432,7 +32430,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.66843, 48.91641], [-123.6484, 48.90105], [-123.6554, 48.88016], [-123.6751, 48.87641], [-123.68894, 48.88178], [-123.68329, 48.89633], [-123.67928, 48.90316], [-123.67136, 48.91722], [-123.66848, 48.91635], [-123.66843, 48.91641]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.88685, 49.19332], [-123.92494, 49.1612], [-123.92581, 49.13841], [-123.91159, 49.123], [-123.88023, 49.11117], [-123.85971, 49.12766], [-123.89792, 49.16196], [-123.88099, 49.18866], [-123.88685, 49.19332]]]}</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
@@ -32447,12 +32445,12 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>10.21966/q2e0-j004</t>
+          <t>10.21966/k01q-wb27</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpszvIrt9OF8-BLQW2N</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt459vxCIH7YPRN9fp</t>
         </is>
       </c>
       <c r="T292" t="inlineStr">
@@ -32481,12 +32479,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
+          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
+          <t>ca-cioos_bea3da72-dafe-4e25-b5b2-0176e0ffba44</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -32496,7 +32494,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Chemainus River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -32542,7 +32540,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.66843, 48.91641], [-123.6484, 48.90105], [-123.6554, 48.88016], [-123.6751, 48.87641], [-123.68894, 48.88178], [-123.68329, 48.89633], [-123.67928, 48.90316], [-123.67136, 48.91722], [-123.66848, 48.91635], [-123.66843, 48.91641]]]}</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
@@ -32557,12 +32555,12 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>10.21966/hjkj-6611</t>
+          <t>10.21966/q2e0-j004</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpszvIrt9OF8-BLQW2N</t>
         </is>
       </c>
       <c r="T293" t="inlineStr">
@@ -32591,12 +32589,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>4c7b7347-767d-45e4-b3ad-7e0133b31e1c</t>
+          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>ca-cioos_dce15b7b-3772-4106-ab20-c3979c4c3f57</t>
+          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -32606,7 +32604,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Fulmore River - Shoal Creek Estuary Complex (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -32652,7 +32650,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.08798, 50.4777], [-126.09599, 50.48418], [-126.09046, 50.50918], [-126.0647, 50.52425], [-125.99698, 50.53569], [-125.93459, 50.56717], [-125.93173, 50.56202], [-125.93764, 50.55458], [-125.91055, 50.55134], [-125.89853, 50.54943], [-125.90063, 50.54466], [-125.96416, 50.53989], [-125.98973, 50.52043], [-126.06566, 50.5067], [-126.08779, 50.47789], [-126.08798, 50.4777]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
@@ -32667,12 +32665,12 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>10.21966/g1cn-xs92</t>
+          <t>10.21966/hjkj-6611</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptdJ8iUmLeOrdmqzrQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
         </is>
       </c>
       <c r="T294" t="inlineStr">
@@ -32701,12 +32699,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
+          <t>4c7b7347-767d-45e4-b3ad-7e0133b31e1c</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
+          <t>ca-cioos_dce15b7b-3772-4106-ab20-c3979c4c3f57</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -32716,7 +32714,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Fulmore River - Shoal Creek Estuary Complex (Provisional)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -32762,7 +32760,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.08798, 50.4777], [-126.09599, 50.48418], [-126.09046, 50.50918], [-126.0647, 50.52425], [-125.99698, 50.53569], [-125.93459, 50.56717], [-125.93173, 50.56202], [-125.93764, 50.55458], [-125.91055, 50.55134], [-125.89853, 50.54943], [-125.90063, 50.54466], [-125.96416, 50.53989], [-125.98973, 50.52043], [-126.06566, 50.5067], [-126.08779, 50.47789], [-126.08798, 50.4777]]]}</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
@@ -32777,12 +32775,12 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>10.21966/npe4-3036</t>
+          <t>10.21966/g1cn-xs92</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptdJ8iUmLeOrdmqzrQ</t>
         </is>
       </c>
       <c r="T295" t="inlineStr">
@@ -32811,12 +32809,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>35245eae-e508-47da-bcf7-54346cda086a</t>
+          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>ca-cioos_e9b72149-8cf1-4000-ae3e-6b29ad60b078</t>
+          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -32826,7 +32824,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Malksope River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -32872,7 +32870,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.46569, 50.12556], [-127.45723, 50.13142], [-127.43281, 50.13338], [-127.42845, 50.13765], [-127.41181, 50.14408], [-127.40973, 50.14233], [-127.41999, 50.13627], [-127.41803, 50.13195], [-127.43106, 50.12796], [-127.46545, 50.12446], [-127.46569, 50.12548], [-127.46569, 50.12556]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
@@ -32887,12 +32885,12 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>10.21966/21sf-ey03</t>
+          <t>10.21966/npe4-3036</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq77iyWJfPg4z-FvOSb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
         </is>
       </c>
       <c r="T296" t="inlineStr">
@@ -32921,12 +32919,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>5177d019-598e-4415-b778-9688403652c8</t>
+          <t>35245eae-e508-47da-bcf7-54346cda086a</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>ca-cioos_ed84df74-5a2d-4a7d-87c8-a7b93f11088e</t>
+          <t>ca-cioos_e9b72149-8cf1-4000-ae3e-6b29ad60b078</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -32936,7 +32934,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Nalaxdlala River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Malksope River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -32982,7 +32980,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.9489, 50.70902], [-125.9696, 50.70291], [-126.00938, 50.69118], [-126.00108, 50.66848], [-125.98257, 50.68374], [-125.98152, 50.69271], [-125.95462, 50.70263], [-125.94785, 50.70768], [-125.9489, 50.70911], [-125.9489, 50.70902]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.46569, 50.12556], [-127.45723, 50.13142], [-127.43281, 50.13338], [-127.42845, 50.13765], [-127.41181, 50.14408], [-127.40973, 50.14233], [-127.41999, 50.13627], [-127.41803, 50.13195], [-127.43106, 50.12796], [-127.46545, 50.12446], [-127.46569, 50.12548], [-127.46569, 50.12556]]]}</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
@@ -32997,12 +32995,12 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>10.21966/4krv-aw23</t>
+          <t>10.21966/21sf-ey03</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptbxmpkBsfyWWfSxOJ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq77iyWJfPg4z-FvOSb</t>
         </is>
       </c>
       <c r="T297" t="inlineStr">
@@ -33031,12 +33029,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>d320d90e-96bf-4993-81c5-f1f57886b0e6</t>
+          <t>5177d019-598e-4415-b778-9688403652c8</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>ca-cioos_b922699f-69b6-4d63-b538-7c290086a408</t>
+          <t>ca-cioos_ed84df74-5a2d-4a7d-87c8-a7b93f11088e</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -33046,7 +33044,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Quw'utsun/Xwulqw'selu River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Nalaxdlala River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -33092,7 +33090,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.56201, 48.73508], [-123.59772, 48.75559], [-123.62127, 48.76514], [-123.63885, 48.77426], [-123.66935, 48.78033], [-123.67901, 48.75472], [-123.65155, 48.74322], [-123.63017, 48.7405], [-123.60792, 48.74289], [-123.56494, 48.72987], [-123.56179, 48.73529], [-123.56201, 48.73508]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.9489, 50.70902], [-125.9696, 50.70291], [-126.00938, 50.69118], [-126.00108, 50.66848], [-125.98257, 50.68374], [-125.98152, 50.69271], [-125.95462, 50.70263], [-125.94785, 50.70768], [-125.9489, 50.70911], [-125.9489, 50.70902]]]}</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
@@ -33107,17 +33105,17 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>10.21966/2ha7-9p26</t>
+          <t>10.21966/4krv-aw23</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpsCA3ycwZ7bFTDIQxh</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptbxmpkBsfyWWfSxOJ</t>
         </is>
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
@@ -33141,12 +33139,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>dd471e82-a6b8-4f32-891c-bbea26e9998e</t>
+          <t>d320d90e-96bf-4993-81c5-f1f57886b0e6</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>ca-cioos_aeb30028-a7eb-462e-ac0f-6c5fe101d4a2</t>
+          <t>ca-cioos_b922699f-69b6-4d63-b538-7c290086a408</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -33156,7 +33154,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>DNA Metabarcoding Captures Temporal and Vertical Dynamics of Mesozooplankton Communities</t>
+          <t>BC Estuary Water Quality Monitoring Data - Quw'utsun/Xwulqw'selu River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -33174,12 +33172,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Genomics, Oceanography</t>
+          <t>Estuary Resilience</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -33194,45 +33192,45 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N299" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.0992, 50.0307]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.56201, 48.73508], [-123.59772, 48.75559], [-123.62127, 48.76514], [-123.63885, 48.77426], [-123.66935, 48.78033], [-123.67901, 48.75472], [-123.65155, 48.74322], [-123.63017, 48.7405], [-123.60792, 48.74289], [-123.56494, 48.72987], [-123.56179, 48.73529], [-123.56201, 48.73508]]]}</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>[{'max': '260.0', 'min': '0.0'}]</t>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
         </is>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>zooplanktonBiomassAndDiversity</t>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>10.21966/6b20-7r76</t>
+          <t>10.21966/2ha7-9p26</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OvzbmseH_syBXg1RXKd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpsCA3ycwZ7bFTDIQxh</t>
         </is>
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V299" t="n">
@@ -33251,12 +33249,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>b27bb6f9-49ae-4f3a-a02a-098d8edf23e2</t>
+          <t>dd471e82-a6b8-4f32-891c-bbea26e9998e</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>ca-cioos_ac765dbb-8e47-415d-8685-d9090946b86b</t>
+          <t>ca-cioos_aeb30028-a7eb-462e-ac0f-6c5fe101d4a2</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -33266,7 +33264,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Micro-invertebrate DNA Barcodes from Quadra Island, BC (Biomarathon)</t>
+          <t>DNA Metabarcoding Captures Temporal and Vertical Dynamics of Mesozooplankton Communities</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -33284,7 +33282,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Genomics, Oceanography</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -33304,45 +33302,45 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.5461, 49.947], [-124.6642, 49.947], [-124.6642, 50.457], [-125.5461, 50.457], [-125.5461, 49.947]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.0992, 50.0307]}</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>[{'max': '200.0', 'min': '0.0'}]</t>
+          <t>[{'max': '260.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, zooplanktonBiomassAndDiversity</t>
+          <t>zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>10.21966/qrxk-vb32</t>
+          <t>10.21966/6b20-7r76</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxClAtvMEmxKRtywIeT</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OvzbmseH_syBXg1RXKd</t>
         </is>
       </c>
       <c r="T300" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V300" t="n">
@@ -33361,12 +33359,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+          <t>b27bb6f9-49ae-4f3a-a02a-098d8edf23e2</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+          <t>ca-cioos_ac765dbb-8e47-415d-8685-d9090946b86b</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -33376,7 +33374,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+          <t>Micro-invertebrate DNA Barcodes from Quadra Island, BC (Biomarathon)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -33394,7 +33392,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -33414,7 +33412,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N301" t="n">
@@ -33422,44 +33420,154 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.5461, 49.947], [-124.6642, 49.947], [-124.6642, 50.457], [-125.5461, 50.457], [-125.5461, 49.947]]]}</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>[{'max': '200.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>invertebrateAbundanceAndDistribution, zooplanktonBiomassAndDiversity</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>10.21966/qrxk-vb32</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OxClAtvMEmxKRtywIeT</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="V301" t="n">
+        <v>0</v>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>300</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H302" t="b">
+        <v>0</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory, Geospatial</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Tula Foundation</t>
+        </is>
+      </c>
+      <c r="N302" t="n">
+        <v>1</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
           <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
         </is>
       </c>
-      <c r="P301" t="inlineStr">
+      <c r="P302" t="inlineStr">
         <is>
           <t>[{'max': '3954.0', 'min': '800.0'}]</t>
         </is>
       </c>
-      <c r="Q301" t="inlineStr">
+      <c r="Q302" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="R301" t="inlineStr">
+      <c r="R302" t="inlineStr">
         <is>
           <t>10.21966/w9n0-kn30</t>
         </is>
       </c>
-      <c r="S301" t="inlineStr">
+      <c r="S302" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
         </is>
       </c>
-      <c r="T301" t="inlineStr"/>
-      <c r="U301" t="inlineStr">
+      <c r="T302" t="inlineStr"/>
+      <c r="U302" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="V301" t="n">
-        <v>0</v>
-      </c>
-      <c r="W301" t="inlineStr">
+      <c r="V302" t="n">
+        <v>0</v>
+      </c>
+      <c r="W302" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X301" t="inlineStr"/>
+      <c r="X302" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -8075,12 +8075,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ca-cioos_77a256cd-baf7-434e-9f62-53ba809e48cb</t>
+          <t>ca-cioos_804b5b42-5550-4620-b789-7c2fe9572c03</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>High-resolution record of 8-m seawater CO2 content entering Fanny Bay Oysters in Baynes Sound, British Columbia, Canada from March 2017 to November 2017</t>
+          <t>Zooplankton - Taxonomy – Northern Strait of Georgia, Discovery Islands, Johnstone Strait, and Queen Charlotte Strait – April to July 2015 and 2016</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -8132,11 +8132,11 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.88983154296876, 49.44759314103575], [-124.70993041992188, 49.44759314103575], [-124.70993041992188, 49.56975910961884], [-124.88983154296876, 49.56975910961884], [-124.88983154296876, 49.44759314103575]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.93452704, 49.56730131], [-124.18481219, 49.56730131], [-124.18481219, 50.90762515], [-126.93452704, 50.90762515], [-126.93452704, 49.56730131]]]}</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>10.21966/1.622315</t>
+          <t>10.21966/bhqd-9361</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTV4aEZoVWsyRXpHWno</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZhamNPb0U3cThnR0o</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -8166,15 +8166,15 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="X71" t="inlineStr"/>
@@ -8185,12 +8185,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ca-cioos_804b5b42-5550-4620-b789-7c2fe9572c03</t>
+          <t>ca-cioos_77a256cd-baf7-434e-9f62-53ba809e48cb</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Zooplankton - Taxonomy – Northern Strait of Georgia, Discovery Islands, Johnstone Strait, and Queen Charlotte Strait – April to July 2015 and 2016</t>
+          <t>High-resolution record of 8-m seawater CO2 content entering Fanny Bay Oysters in Baynes Sound, British Columbia, Canada from March 2017 to November 2017</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8242,52 +8242,54 @@
         </is>
       </c>
       <c r="N72" t="n">
+        <v>2</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.88983154296876, 49.44759314103575], [-124.70993041992188, 49.44759314103575], [-124.70993041992188, 49.56975910961884], [-124.88983154296876, 49.56975910961884], [-124.88983154296876, 49.44759314103575]]]}</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>other, inorganicCarbon</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>10.21966/1.622315</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTV4aEZoVWsyRXpHWno</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X72" t="n">
         <v>1</v>
       </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.93452704, 49.56730131], [-124.18481219, 49.56730131], [-124.18481219, 50.90762515], [-126.93452704, 50.90762515], [-126.93452704, 49.56730131]]]}</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>other, zooplanktonBiomassAndDiversity</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>10.21966/bhqd-9361</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZhamNPb0U3cThnR0o</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>2022-02-04</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="V72" t="n">
-        <v>1</v>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9175,12 +9177,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
+          <t>ca-cioos_d2e83e40-9e95-4a47-a899-b37c744be3ab</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9190,7 +9192,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
+          <t>Fin Island &amp; K'yel - 2020 - Airborne Coastal Observatory Data</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9208,7 +9210,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9236,7 +9238,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.4, 53.03], [-129.1, 53.03], [-129.1, 53.29], [-129.4, 53.29], [-129.4, 53.03]]]}</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9251,12 +9253,12 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>10.21966/eysg-7a26</t>
+          <t>10.21966/q4c4-wx08</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNm5cwomXVNI6vWU-R</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -9266,7 +9268,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V81" t="n">
@@ -9285,12 +9287,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ca-cioos_d2e83e40-9e95-4a47-a899-b37c744be3ab</t>
+          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9300,7 +9302,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fin Island &amp; K'yel - 2020 - Airborne Coastal Observatory Data</t>
+          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9318,7 +9320,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9346,7 +9348,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.4, 53.03], [-129.1, 53.03], [-129.1, 53.29], [-129.4, 53.29], [-129.4, 53.03]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9361,12 +9363,12 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>10.21966/q4c4-wx08</t>
+          <t>10.21966/eysg-7a26</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNm5cwomXVNI6vWU-R</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -9376,7 +9378,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="V82" t="n">
@@ -9387,7 +9389,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr"/>
+      <c r="X82" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -13025,12 +13029,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -13040,7 +13044,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -13063,7 +13067,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -13082,11 +13086,11 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13101,12 +13105,12 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -13116,7 +13120,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V116" t="n">
@@ -13124,7 +13128,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -13135,12 +13139,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -13150,7 +13154,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -13173,7 +13177,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -13192,11 +13196,11 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13211,12 +13215,12 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -13226,7 +13230,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V117" t="n">
@@ -13234,7 +13238,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -15005,12 +15009,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15020,7 +15024,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15038,7 +15042,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15058,20 +15062,20 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -15081,12 +15085,12 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/x6q2-me90</t>
+          <t>10.21966/1.135248</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -15096,7 +15100,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="V134" t="n">
@@ -15115,12 +15119,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -15130,7 +15134,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -15148,7 +15152,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15168,20 +15172,20 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -15191,12 +15195,12 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>10.21966/1.135248</t>
+          <t>10.21966/x6q2-me90</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -15206,7 +15210,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V135" t="n">
@@ -31371,7 +31375,9 @@
       </c>
       <c r="V282" t="inlineStr"/>
       <c r="W282" t="inlineStr"/>
-      <c r="X282" t="inlineStr"/>
+      <c r="X282" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -8075,12 +8075,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ca-cioos_804b5b42-5550-4620-b789-7c2fe9572c03</t>
+          <t>ca-cioos_77a256cd-baf7-434e-9f62-53ba809e48cb</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zooplankton - Taxonomy – Northern Strait of Georgia, Discovery Islands, Johnstone Strait, and Queen Charlotte Strait – April to July 2015 and 2016</t>
+          <t>High-resolution record of 8-m seawater CO2 content entering Fanny Bay Oysters in Baynes Sound, British Columbia, Canada from March 2017 to November 2017</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -8132,11 +8132,11 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.93452704, 49.56730131], [-124.18481219, 49.56730131], [-124.18481219, 50.90762515], [-126.93452704, 50.90762515], [-126.93452704, 49.56730131]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.88983154296876, 49.44759314103575], [-124.70993041992188, 49.44759314103575], [-124.70993041992188, 49.56975910961884], [-124.88983154296876, 49.56975910961884], [-124.88983154296876, 49.44759314103575]]]}</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>other, zooplanktonBiomassAndDiversity</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>10.21966/bhqd-9361</t>
+          <t>10.21966/1.622315</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZhamNPb0U3cThnR0o</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTV4aEZoVWsyRXpHWno</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -8166,15 +8166,15 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X71" t="inlineStr"/>
@@ -8185,12 +8185,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ca-cioos_77a256cd-baf7-434e-9f62-53ba809e48cb</t>
+          <t>ca-cioos_804b5b42-5550-4620-b789-7c2fe9572c03</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>High-resolution record of 8-m seawater CO2 content entering Fanny Bay Oysters in Baynes Sound, British Columbia, Canada from March 2017 to November 2017</t>
+          <t>Zooplankton - Taxonomy – Northern Strait of Georgia, Discovery Islands, Johnstone Strait, and Queen Charlotte Strait – April to July 2015 and 2016</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8242,11 +8242,11 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.88983154296876, 49.44759314103575], [-124.70993041992188, 49.44759314103575], [-124.70993041992188, 49.56975910961884], [-124.88983154296876, 49.56975910961884], [-124.88983154296876, 49.44759314103575]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.93452704, 49.56730131], [-124.18481219, 49.56730131], [-124.18481219, 50.90762515], [-126.93452704, 50.90762515], [-126.93452704, 49.56730131]]]}</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8256,17 +8256,17 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>10.21966/1.622315</t>
+          <t>10.21966/bhqd-9361</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTV4aEZoVWsyRXpHWno</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZhamNPb0U3cThnR0o</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -8276,20 +8276,18 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X72" t="n">
-        <v>1</v>
-      </c>
+          <t>[{'year': '2026', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8407,12 +8405,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8422,7 +8420,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8464,16 +8462,16 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8483,12 +8481,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>10.21966/5rp3-3207</t>
+          <t>10.21966/awsk-my87</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -8498,7 +8496,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V74" t="n">
@@ -8517,12 +8515,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8532,7 +8530,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8574,16 +8572,16 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -8593,12 +8591,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10.21966/awsk-my87</t>
+          <t>10.21966/5rp3-3207</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8608,7 +8606,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V75" t="n">
@@ -9177,12 +9175,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ca-cioos_d2e83e40-9e95-4a47-a899-b37c744be3ab</t>
+          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9192,7 +9190,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fin Island &amp; K'yel - 2020 - Airborne Coastal Observatory Data</t>
+          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9210,7 +9208,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9238,7 +9236,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.4, 53.03], [-129.1, 53.03], [-129.1, 53.29], [-129.4, 53.29], [-129.4, 53.03]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9253,12 +9251,12 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>10.21966/q4c4-wx08</t>
+          <t>10.21966/eysg-7a26</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNm5cwomXVNI6vWU-R</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -9268,7 +9266,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="V81" t="n">
@@ -9287,12 +9285,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
+          <t>ca-cioos_d2e83e40-9e95-4a47-a899-b37c744be3ab</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9302,7 +9300,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
+          <t>Fin Island &amp; K'yel - 2020 - Airborne Coastal Observatory Data</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9320,7 +9318,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9348,7 +9346,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.4, 53.03], [-129.1, 53.03], [-129.1, 53.29], [-129.4, 53.29], [-129.4, 53.03]]]}</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9363,12 +9361,12 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>10.21966/eysg-7a26</t>
+          <t>10.21966/q4c4-wx08</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNm5cwomXVNI6vWU-R</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -9378,7 +9376,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V82" t="n">
@@ -9389,9 +9387,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X82" t="n">
-        <v>1</v>
-      </c>
+      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9839,12 +9835,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ca-cioos_94cdfcba-bbd4-4053-8976-75de69460c14</t>
+          <t>ca-cioos_6ae1b131-d903-44ca-92a9-64cf6487ddc2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -9854,7 +9850,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sea wrack wet to dry biomass calibrations for macroalgae of the Central Coast of British Columbia - 2018</t>
+          <t>Geology - Calvert Island</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9872,7 +9868,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9900,27 +9896,27 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16116765, 51.64326925], [-128.11481908, 51.64326925], [-128.11481908, 51.66904109], [-128.16116765, 51.66904109], [-128.16116765, 51.64326925]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.402632657661314], [-127.8204345703125, 51.402632657661314], [-127.8204345703125, 51.7644403180351], [-128.2489013671875, 51.7644403180351], [-128.2489013671875, 51.402632657661314]]]}</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>other, microbeBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>10.21966/ez7j-cy15</t>
+          <t>10.21966/f6bn-9773</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFWNFc0dmtoV0UyT2k</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFhaHEzRGxZdnRTMUM</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -9930,7 +9926,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V87" t="n">
@@ -9949,12 +9945,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ca-cioos_6ae1b131-d903-44ca-92a9-64cf6487ddc2</t>
+          <t>ca-cioos_94cdfcba-bbd4-4053-8976-75de69460c14</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9964,7 +9960,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Geology - Calvert Island</t>
+          <t>Sea wrack wet to dry biomass calibrations for macroalgae of the Central Coast of British Columbia - 2018</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -9982,7 +9978,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10010,27 +10006,27 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.402632657661314], [-127.8204345703125, 51.402632657661314], [-127.8204345703125, 51.7644403180351], [-128.2489013671875, 51.7644403180351], [-128.2489013671875, 51.402632657661314]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16116765, 51.64326925], [-128.11481908, 51.64326925], [-128.11481908, 51.66904109], [-128.16116765, 51.66904109], [-128.16116765, 51.64326925]]]}</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>10.21966/f6bn-9773</t>
+          <t>10.21966/ez7j-cy15</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFhaHEzRGxZdnRTMUM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFWNFc0dmtoV0UyT2k</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -10040,7 +10036,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="V88" t="n">
@@ -13029,12 +13025,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -13044,7 +13040,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -13067,7 +13063,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -13086,11 +13082,11 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13105,12 +13101,12 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -13120,7 +13116,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V116" t="n">
@@ -13128,7 +13124,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -13139,12 +13135,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -13154,7 +13150,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -13177,7 +13173,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -13196,11 +13192,11 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13215,12 +13211,12 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -13230,7 +13226,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V117" t="n">
@@ -13238,7 +13234,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -22923,7 +22919,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X205" t="inlineStr"/>
+      <c r="X205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -31375,9 +31373,7 @@
       </c>
       <c r="V282" t="inlineStr"/>
       <c r="W282" t="inlineStr"/>
-      <c r="X282" t="n">
-        <v>1</v>
-      </c>
+      <c r="X282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31385,12 +31381,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
+          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
+          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -31400,7 +31396,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -31446,7 +31442,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
@@ -31461,12 +31457,12 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>10.21966/r9zr-xz33</t>
+          <t>10.21966/vpz7-mm73</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
         </is>
       </c>
       <c r="T283" t="inlineStr">
@@ -31495,12 +31491,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
+          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
+          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -31510,7 +31506,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -31556,7 +31552,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
@@ -31571,12 +31567,12 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>10.21966/9dbb-5d54</t>
+          <t>10.21966/r9zr-xz33</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
         </is>
       </c>
       <c r="T284" t="inlineStr">
@@ -31605,12 +31601,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
+          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
+          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -31620,7 +31616,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -31666,7 +31662,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
@@ -31681,12 +31677,12 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>10.21966/vpz7-mm73</t>
+          <t>10.21966/9dbb-5d54</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
         </is>
       </c>
       <c r="T285" t="inlineStr">
@@ -32045,12 +32041,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
+          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
+          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -32060,7 +32056,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -32106,7 +32102,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
@@ -32121,12 +32117,12 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>10.21966/kde9-8g12</t>
+          <t>10.21966/9a97-2j48</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
         </is>
       </c>
       <c r="T289" t="inlineStr">
@@ -32155,12 +32151,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
+          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
+          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -32170,7 +32166,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -32216,7 +32212,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
@@ -32231,12 +32227,12 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>10.21966/9a97-2j48</t>
+          <t>10.21966/ed9w-2653</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
         </is>
       </c>
       <c r="T290" t="inlineStr">
@@ -32265,12 +32261,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
+          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
+          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -32280,7 +32276,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -32326,7 +32322,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -32341,12 +32337,12 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>10.21966/ed9w-2653</t>
+          <t>10.21966/kde9-8g12</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
         </is>
       </c>
       <c r="T291" t="inlineStr">
@@ -32595,12 +32591,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
+          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
+          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -32610,7 +32606,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -32656,7 +32652,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
@@ -32671,12 +32667,12 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>10.21966/hjkj-6611</t>
+          <t>10.21966/npe4-3036</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
         </is>
       </c>
       <c r="T294" t="inlineStr">
@@ -32815,12 +32811,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
+          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
+          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -32830,7 +32826,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -32876,7 +32872,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
@@ -32891,12 +32887,12 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>10.21966/npe4-3036</t>
+          <t>10.21966/hjkj-6611</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
         </is>
       </c>
       <c r="T296" t="inlineStr">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X302"/>
+  <dimension ref="A1:X304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ca-cioos_6ae1b131-d903-44ca-92a9-64cf6487ddc2</t>
+          <t>ca-cioos_94cdfcba-bbd4-4053-8976-75de69460c14</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Geology - Calvert Island</t>
+          <t>Sea wrack wet to dry biomass calibrations for macroalgae of the Central Coast of British Columbia - 2018</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9896,27 +9896,27 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.402632657661314], [-127.8204345703125, 51.402632657661314], [-127.8204345703125, 51.7644403180351], [-128.2489013671875, 51.7644403180351], [-128.2489013671875, 51.402632657661314]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16116765, 51.64326925], [-128.11481908, 51.64326925], [-128.11481908, 51.66904109], [-128.16116765, 51.66904109], [-128.16116765, 51.64326925]]]}</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>10.21966/f6bn-9773</t>
+          <t>10.21966/ez7j-cy15</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFhaHEzRGxZdnRTMUM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFWNFc0dmtoV0UyT2k</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="V87" t="n">
@@ -9945,12 +9945,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ca-cioos_94cdfcba-bbd4-4053-8976-75de69460c14</t>
+          <t>ca-cioos_6ae1b131-d903-44ca-92a9-64cf6487ddc2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sea wrack wet to dry biomass calibrations for macroalgae of the Central Coast of British Columbia - 2018</t>
+          <t>Geology - Calvert Island</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10006,27 +10006,27 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16116765, 51.64326925], [-128.11481908, 51.64326925], [-128.11481908, 51.66904109], [-128.16116765, 51.66904109], [-128.16116765, 51.64326925]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.402632657661314], [-127.8204345703125, 51.402632657661314], [-127.8204345703125, 51.7644403180351], [-128.2489013671875, 51.7644403180351], [-128.2489013671875, 51.402632657661314]]]}</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>other, microbeBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>10.21966/ez7j-cy15</t>
+          <t>10.21966/f6bn-9773</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFWNFc0dmtoV0UyT2k</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFhaHEzRGxZdnRTMUM</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V88" t="n">
@@ -15107,7 +15107,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr"/>
+      <c r="X134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -19399,7 +19401,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X173" t="inlineStr"/>
+      <c r="X173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20609,7 +20613,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X184" t="inlineStr"/>
+      <c r="X184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -22908,7 +22914,7 @@
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="V205" t="n">
@@ -30708,7 +30714,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="V276" t="n">
@@ -30719,9 +30725,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X276" t="n">
-        <v>1</v>
-      </c>
+      <c r="X276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -31381,12 +31385,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
+          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
+          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -31396,7 +31400,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -31442,7 +31446,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
@@ -31457,12 +31461,12 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>10.21966/vpz7-mm73</t>
+          <t>10.21966/r9zr-xz33</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
         </is>
       </c>
       <c r="T283" t="inlineStr">
@@ -31491,12 +31495,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
+          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
+          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -31506,7 +31510,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -31552,7 +31556,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
@@ -31567,12 +31571,12 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>10.21966/r9zr-xz33</t>
+          <t>10.21966/9dbb-5d54</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
         </is>
       </c>
       <c r="T284" t="inlineStr">
@@ -31601,12 +31605,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
+          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
+          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -31616,7 +31620,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -31662,7 +31666,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
@@ -31677,12 +31681,12 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>10.21966/9dbb-5d54</t>
+          <t>10.21966/vpz7-mm73</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
         </is>
       </c>
       <c r="T285" t="inlineStr">
@@ -32041,12 +32045,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
+          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
+          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -32056,7 +32060,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -32102,7 +32106,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
@@ -32117,12 +32121,12 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>10.21966/9a97-2j48</t>
+          <t>10.21966/kde9-8g12</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
         </is>
       </c>
       <c r="T289" t="inlineStr">
@@ -32151,12 +32155,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
+          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
+          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -32166,7 +32170,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -32212,7 +32216,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
@@ -32227,12 +32231,12 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>10.21966/ed9w-2653</t>
+          <t>10.21966/9a97-2j48</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
         </is>
       </c>
       <c r="T290" t="inlineStr">
@@ -32261,12 +32265,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
+          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
+          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -32276,7 +32280,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -32322,7 +32326,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -32337,12 +32341,12 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>10.21966/kde9-8g12</t>
+          <t>10.21966/ed9w-2653</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
         </is>
       </c>
       <c r="T291" t="inlineStr">
@@ -32591,12 +32595,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
+          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
+          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -32606,7 +32610,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -32652,7 +32656,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
@@ -32667,12 +32671,12 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>10.21966/npe4-3036</t>
+          <t>10.21966/hjkj-6611</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
         </is>
       </c>
       <c r="T294" t="inlineStr">
@@ -32811,12 +32815,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
+          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
+          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -32826,7 +32830,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -32872,7 +32876,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
@@ -32887,12 +32891,12 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>10.21966/hjkj-6611</t>
+          <t>10.21966/npe4-3036</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
         </is>
       </c>
       <c r="T296" t="inlineStr">
@@ -33471,105 +33475,317 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
+          <t>d269f354-8527-4e94-bb32-9de4fe3fabdf</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>ca-cioos_da232383-781d-4852-8542-cf0cb8aa5f26</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Data for Paper: Detection differences between eDNA and mid-water trawls are driven by fish biomass and habitat preferences</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>CC-BY-NC-ND-4.0</t>
+        </is>
+      </c>
+      <c r="H302" t="b">
+        <v>0</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Genomics</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N302" t="n">
+        <v>3</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.6289, 50.7424], [-127.321, 50.6868], [-124.8052, 48.3262], [-123.2452, 48.1432], [-122.9596, 49.0945], [-126.6289, 50.7424]]]}</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>fishAbundanceAndDistribution</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>10.21966/hky6-1022</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-P1l_Wv09HnWD1is-Yik</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="V302" t="n">
+        <v>0</v>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X302" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>301</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>098c52a1-6dde-4e64-8b27-5a34e40870e6</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>ca-cioos_e5e61f93-db9b-48d0-b779-45e73fabfd0a</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>High Resolution Coastal Carbon Monitoring in the Northeast Pacific</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>collection</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H303" t="b">
+        <v>0</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Oceanography</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>onGoing</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N303" t="n">
+        <v>1</v>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-160.4964, 46.7847], [-118.6667, 46.7847], [-118.6667, 62.7421], [-160.4964, 62.7421], [-160.4964, 46.7847]]]}</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>[{'max': '0', 'min': '0'}]</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>inorganicCarbon</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr"/>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-P0csr75piiewsICpJu8</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr"/>
+      <c r="W303" t="inlineStr"/>
+      <c r="X303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>302</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
           <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
+      <c r="C304" t="inlineStr">
         <is>
           <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
         <is>
           <t>Mount Robson Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
         <is>
           <t>CC-BY-4.0</t>
         </is>
       </c>
-      <c r="H302" t="b">
-        <v>0</v>
-      </c>
-      <c r="I302" t="inlineStr">
+      <c r="H304" t="b">
+        <v>0</v>
+      </c>
+      <c r="I304" t="inlineStr">
         <is>
           <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
-      <c r="J302" t="inlineStr">
+      <c r="J304" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
+      <c r="K304" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="M302" t="inlineStr">
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
         <is>
           <t>Tula Foundation</t>
         </is>
       </c>
-      <c r="N302" t="n">
+      <c r="N304" t="n">
         <v>1</v>
       </c>
-      <c r="O302" t="inlineStr">
+      <c r="O304" t="inlineStr">
         <is>
           <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
         </is>
       </c>
-      <c r="P302" t="inlineStr">
+      <c r="P304" t="inlineStr">
         <is>
           <t>[{'max': '3954.0', 'min': '800.0'}]</t>
         </is>
       </c>
-      <c r="Q302" t="inlineStr">
+      <c r="Q304" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="R302" t="inlineStr">
+      <c r="R304" t="inlineStr">
         <is>
           <t>10.21966/w9n0-kn30</t>
         </is>
       </c>
-      <c r="S302" t="inlineStr">
+      <c r="S304" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
         </is>
       </c>
-      <c r="T302" t="inlineStr"/>
-      <c r="U302" t="inlineStr">
+      <c r="T304" t="inlineStr"/>
+      <c r="U304" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="V302" t="n">
-        <v>0</v>
-      </c>
-      <c r="W302" t="inlineStr">
+      <c r="V304" t="n">
+        <v>0</v>
+      </c>
+      <c r="W304" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X302" t="inlineStr"/>
+      <c r="X304" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X304"/>
+  <dimension ref="A1:X305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2163,7 +2163,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -13355,12 +13357,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>e1b86825-d43b-47e1-bf45-ab791f44772d</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ca-cioos_0e4f324c-6498-4c89-9e19-f2f9f474a1df</t>
+          <t>ca-cioos_0e446321-34f3-4d5a-8c7d-79c89eb76373</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -13370,7 +13372,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LiDAR-derived Drainage Network for Calvert Island - British Columbia - Canada</t>
+          <t>Stream temperature time-series – Calvert Island – 2013 - 2019</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -13388,12 +13390,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -13412,16 +13414,16 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16, 51.41], [-127.88, 51.41], [-127.88, 51.73], [-128.16, 51.73], [-128.16, 51.41]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.25940955, 51.55841821], [-127.87488807, 51.55841821], [-127.87488807, 51.75224257], [-128.25940955, 51.75224257], [-128.25940955, 51.55841821]]]}</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -13431,12 +13433,12 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>10.21966/vavm-b152</t>
+          <t>10.21966/7nb6-zk37</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW5MeGIydVA3U1VKdWo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFDT2lYSlBQZ0VNdDg</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -13465,12 +13467,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>e1b86825-d43b-47e1-bf45-ab791f44772d</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_0e446321-34f3-4d5a-8c7d-79c89eb76373</t>
+          <t>ca-cioos_0e4f324c-6498-4c89-9e19-f2f9f474a1df</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13480,7 +13482,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stream temperature time-series – Calvert Island – 2013 - 2019</t>
+          <t>LiDAR-derived Drainage Network for Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13498,12 +13500,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13522,16 +13524,16 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.25940955, 51.55841821], [-127.87488807, 51.55841821], [-127.87488807, 51.75224257], [-128.25940955, 51.75224257], [-128.25940955, 51.55841821]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16, 51.41], [-127.88, 51.41], [-127.88, 51.73], [-128.16, 51.73], [-128.16, 51.41]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -13541,12 +13543,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/7nb6-zk37</t>
+          <t>10.21966/vavm-b152</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFDT2lYSlBQZ0VNdDg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW5MeGIydVA3U1VKdWo</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -14455,12 +14457,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -14470,7 +14472,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14488,7 +14490,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14508,7 +14510,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Skeena Fisheries Commission</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N129" t="n">
@@ -14516,27 +14518,27 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -14546,7 +14548,7 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="V129" t="n">
@@ -14565,12 +14567,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -14580,7 +14582,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -14598,7 +14600,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14618,7 +14620,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Skeena Fisheries Commission</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -14626,27 +14628,27 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -14656,7 +14658,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V130" t="n">
@@ -19401,9 +19403,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X173" t="n">
-        <v>1</v>
-      </c>
+      <c r="X173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20613,9 +20613,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X184" t="n">
-        <v>1</v>
-      </c>
+      <c r="X184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -22914,7 +22912,7 @@
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="V205" t="n">
@@ -22925,9 +22923,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X205" t="n">
-        <v>1</v>
-      </c>
+      <c r="X205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -32045,12 +32041,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
+          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
+          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -32060,7 +32056,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -32106,7 +32102,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
@@ -32121,12 +32117,12 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>10.21966/kde9-8g12</t>
+          <t>10.21966/9a97-2j48</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
         </is>
       </c>
       <c r="T289" t="inlineStr">
@@ -32155,12 +32151,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
+          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
+          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -32170,7 +32166,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -32216,7 +32212,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
@@ -32231,12 +32227,12 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>10.21966/9a97-2j48</t>
+          <t>10.21966/kde9-8g12</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
         </is>
       </c>
       <c r="T290" t="inlineStr">
@@ -33578,7 +33574,7 @@
         </is>
       </c>
       <c r="X302" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -33679,7 +33675,9 @@
       </c>
       <c r="V303" t="inlineStr"/>
       <c r="W303" t="inlineStr"/>
-      <c r="X303" t="inlineStr"/>
+      <c r="X303" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -33687,12 +33685,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+          <t>1e13d2ee-580f-4785-838b-908a449781a3</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+          <t>ca-cioos_741bd412-6387-4dcd-8d61-7046b949f406</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -33702,7 +33700,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+          <t>Global Eutrophication Monitoring Dataset of Trinidad and Tobago</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -33720,12 +33718,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -33740,7 +33738,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N304" t="n">
@@ -33748,44 +33746,156 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-61.59, 10.35], [-61.46, 10.35], [-61.46, 10.68], [-61.59, 10.68], [-61.59, 10.35]]]}</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>[{'max': '1.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>nutrients, particulateMatter, oxygen, phytoplanktonBiomassAndDiversity, zooplanktonBiomassAndDiversity, seaSurfaceTemperature, subSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>10.21966/nrrn-rr63</t>
+        </is>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/P3VNaxsDaISmZcvgBvJIKlt634d2/-Op0_nycnfen8FFkS3Ti</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="V304" t="n">
+        <v>0</v>
+      </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X304" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>303</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H305" t="b">
+        <v>0</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory, Geospatial</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Tula Foundation</t>
+        </is>
+      </c>
+      <c r="N305" t="n">
+        <v>1</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
           <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
         </is>
       </c>
-      <c r="P304" t="inlineStr">
+      <c r="P305" t="inlineStr">
         <is>
           <t>[{'max': '3954.0', 'min': '800.0'}]</t>
         </is>
       </c>
-      <c r="Q304" t="inlineStr">
+      <c r="Q305" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="R304" t="inlineStr">
+      <c r="R305" t="inlineStr">
         <is>
           <t>10.21966/w9n0-kn30</t>
         </is>
       </c>
-      <c r="S304" t="inlineStr">
+      <c r="S305" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
         </is>
       </c>
-      <c r="T304" t="inlineStr"/>
-      <c r="U304" t="inlineStr">
+      <c r="T305" t="inlineStr"/>
+      <c r="U305" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="V304" t="n">
-        <v>0</v>
-      </c>
-      <c r="W304" t="inlineStr">
+      <c r="V305" t="n">
+        <v>0</v>
+      </c>
+      <c r="W305" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X304" t="inlineStr"/>
+      <c r="X305" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -6105,12 +6105,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8462,16 +8462,16 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>10.21966/5rp3-3207</t>
+          <t>10.21966/awsk-my87</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V74" t="n">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8572,16 +8572,16 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10.21966/awsk-my87</t>
+          <t>10.21966/5rp3-3207</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V75" t="n">
@@ -15005,12 +15005,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15058,20 +15058,20 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/x6q2-me90</t>
+          <t>10.21966/1.135248</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="V134" t="n">
@@ -15115,12 +15115,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15168,20 +15168,20 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>10.21966/1.135248</t>
+          <t>10.21966/x6q2-me90</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V135" t="n">
@@ -19399,7 +19399,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X173" t="inlineStr"/>
+      <c r="X173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -2391,12 +2391,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ca-cioos_7ddae37a-e706-45d2-8060-8306300a98c8</t>
+          <t>ca-cioos_1769a04e-b77b-409b-8e48-bc2098bbad3e</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oceanographic Mooring Time Series, Hyacinthe Bay, BC, Canada (Provisional)</t>
+          <t>Juvenile Salmon Migration Dynamics in the Discovery Islands and Johnstone Strait; 2015–2017</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2448,44 +2448,52 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.11545814, 49.78433133], [-124.85227454, 49.78433133], [-124.85227454, 50.81587848], [-127.11545814, 50.81587848], [-127.11545814, 49.78433133]]]}</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>[{'max': '9.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>10.21966/C7NA-Z171</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU55UGp2QldnVmU5V2U</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2021-11-19</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
         <v>1</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>{'type': 'Point', 'coordinates': [-125.212195, 50.12001367]}</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>[{'max': '60.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>oxygen, subSurfaceTemperature, seaSurfaceTemperature, seaSurfaceSalinity, subSurfaceSalinity</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MW0Az3HzggNmnqgHDw3</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2021-10-20</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>[{'year': '2024', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2493,12 +2501,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ca-cioos_1769a04e-b77b-409b-8e48-bc2098bbad3e</t>
+          <t>ca-cioos_eb1feb98-b11a-4663-b7ab-2216df8187bd</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2508,7 +2516,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Migration Dynamics in the Discovery Islands and Johnstone Strait; 2015–2017</t>
+          <t>Juvenile Salmon Migration Observations from the Hakai Institute Juvenile Salmon Program in the Discovery Islands in British Columbia, Canada in 2020</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2546,7 +2554,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -2554,7 +2562,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.11545814, 49.78433133], [-124.85227454, 49.78433133], [-124.85227454, 50.81587848], [-127.11545814, 50.81587848], [-127.11545814, 49.78433133]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.2, 49.94], [-125.0, 50.31], [-125.3, 50.54], [-125.6, 50.44], [-125.2, 49.94]]]}</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2569,12 +2577,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>10.21966/C7NA-Z171</t>
+          <t>10.21966/e5c1-c396</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU55UGp2QldnVmU5V2U</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/UTb9hNU3GJRK302QyaKNIvj2OiJ2/-MotsOF-96liGFn57nbC</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2584,15 +2592,15 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[{'year': '2023', 'total': 1}, {'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2603,12 +2611,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ca-cioos_eb1feb98-b11a-4663-b7ab-2216df8187bd</t>
+          <t>ca-cioos_64f74489-b9a3-4e6f-9f25-be141b8e285c</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2618,7 +2626,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Migration Observations from the Hakai Institute Juvenile Salmon Program in the Discovery Islands in British Columbia, Canada in 2020</t>
+          <t>Juvenile Sockeye Diets Hakai 2015-2016</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2660,11 +2668,11 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.2, 49.94], [-125.0, 50.31], [-125.3, 50.54], [-125.6, 50.44], [-125.2, 49.94]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.17472969, 49.90441037], [-124.63570169, 49.90441037], [-124.63570169, 50.69624063], [-127.17472969, 50.69624063], [-127.17472969, 49.90441037]]]}</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2679,22 +2687,22 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>10.21966/e5c1-c396</t>
+          <t>10.21966/3s9g-w013</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/UTb9hNU3GJRK302QyaKNIvj2OiJ2/-MotsOF-96liGFn57nbC</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTd0Y1A1ZVhoYVR0dEY</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2021-11-19</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="V21" t="n">
@@ -2702,7 +2710,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>[{'year': '2023', 'total': 1}, {'year': '2024', 'total': 1}]</t>
+          <t>[{'year': '2023', 'total': 2}]</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2713,12 +2721,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ca-cioos_64f74489-b9a3-4e6f-9f25-be141b8e285c</t>
+          <t>ca-cioos_ee2791c3-3d99-41e5-8cdf-fa5d1d19944d</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2728,7 +2736,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juvenile Sockeye Diets Hakai 2015-2016</t>
+          <t>Fatty acids of particulate matter collected from 2015 to 2018 near Quadra Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2746,7 +2754,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2774,45 +2782,45 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.17472969, 49.90441037], [-124.63570169, 49.90441037], [-124.63570169, 50.69624063], [-127.17472969, 50.69624063], [-127.17472969, 49.90441037]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.099, 50.03], [-125.08, 50.03], [-125.08, 50.0307], [-125.099, 50.0307], [-125.099, 50.03]]]}</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>[{'max': '9.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, stableCarbonIsotopes</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>10.21966/3s9g-w013</t>
+          <t>10.21966/RR8V-6Y52</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTd0Y1A1ZVhoYVR0dEY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-Mn6jhjE3XFwoFx2b-9G</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2021-12-02</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>[{'year': '2023', 'total': 2}]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2823,12 +2831,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ca-cioos_ee2791c3-3d99-41e5-8cdf-fa5d1d19944d</t>
+          <t>ca-cioos_66ad87d2-bb96-4515-a907-6367ca6c0a2b</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2838,7 +2846,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fatty acids of particulate matter collected from 2015 to 2018 near Quadra Island, British Columbia, Canada</t>
+          <t>Pruth Bay Thermistor String Oceanographic Mooring on Calvert Island (Provisional)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2861,7 +2869,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2876,7 +2884,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -2884,47 +2892,37 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.099, 50.03], [-125.08, 50.03], [-125.08, 50.0307], [-125.099, 50.0307], [-125.099, 50.03]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-128.0853667, 51.6521]}</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '60.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, stableCarbonIsotopes</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>10.21966/RR8V-6Y52</t>
-        </is>
-      </c>
+          <t>subSurfaceTemperature, seaSurfaceTemperature, other</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-Mn6jhjE3XFwoFx2b-9G</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MW079KN2Z_OrMh7Zk6T</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2021-12-02</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
-        </is>
-      </c>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -2933,12 +2931,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>2adbc714-fde2-436b-a5bd-ec51457a275c</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ca-cioos_66ad87d2-bb96-4515-a907-6367ca6c0a2b</t>
+          <t>ca-cioos_288ea4b2-3706-4256-8146-02bd0265585b</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2948,7 +2946,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pruth Bay Thermistor String Oceanographic Mooring on Calvert Island (Provisional)</t>
+          <t>Nearshore Macrophyte Stable Isotopes - BC Central Coast</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2966,12 +2964,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2994,37 +2992,47 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-128.0853667, 51.6521]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.62224808, 51.28805197], [-127.44960574, 51.28805197], [-127.44960574, 52.00866824], [-128.62224808, 52.00866824], [-128.62224808, 51.28805197]]]}</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>[{'max': '60.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>subSurfaceTemperature, seaSurfaceTemperature, other</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
+          <t>stableCarbonIsotopes, macroalgalCanopyCoverAndComposition, seagrassCoverAndComposition</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>10.21966/q31x-qg72</t>
+        </is>
+      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MW079KN2Z_OrMh7Zk6T</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVJMTWZWQmhmRHpnSjk</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2021-12-03</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>[{'year': '2024', 'total': 1}]</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -3033,12 +3041,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2adbc714-fde2-436b-a5bd-ec51457a275c</t>
+          <t>98bc62c7-d6a4-42bd-9110-c8021380d8a5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ca-cioos_288ea4b2-3706-4256-8146-02bd0265585b</t>
+          <t>ca-cioos_3bc02dd8-7654-44f0-8c7c-02739937bdf4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3048,7 +3056,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nearshore Macrophyte Stable Isotopes - BC Central Coast</t>
+          <t>Seastar &amp; Macroinvertebrate Dynamics - BC Central Coast</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3071,7 +3079,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3090,31 +3098,31 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.62224808, 51.28805197], [-127.44960574, 51.28805197], [-127.44960574, 52.00866824], [-128.62224808, 52.00866824], [-128.62224808, 51.28805197]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '-5.0'}]</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>stableCarbonIsotopes, macroalgalCanopyCoverAndComposition, seagrassCoverAndComposition</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10.21966/q31x-qg72</t>
+          <t>10.21966/5n09-aq76</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVJMTWZWQmhmRHpnSjk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MopDTzbqRUp1a4M25L6</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -3124,15 +3132,15 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -3143,12 +3151,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>98bc62c7-d6a4-42bd-9110-c8021380d8a5</t>
+          <t>6a6908af-8856-431e-8277-458fee82e534</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ca-cioos_3bc02dd8-7654-44f0-8c7c-02739937bdf4</t>
+          <t>ca-cioos_d87de5ca-a18a-406d-a4c1-74e6f8f28e5b</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3158,7 +3166,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Seastar &amp; Macroinvertebrate Dynamics - BC Central Coast</t>
+          <t>Surfgrass Community Structure - Monitoring - BC Central Coast - 2016-2017</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3181,7 +3189,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3200,7 +3208,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -3214,17 +3222,17 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>10.21966/5n09-aq76</t>
+          <t>10.21966/nrmz-a516</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MopDTzbqRUp1a4M25L6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MooQxV2q0Y_rOjI40Fq</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3234,7 +3242,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="V26" t="n">
@@ -3253,12 +3261,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6a6908af-8856-431e-8277-458fee82e534</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ca-cioos_d87de5ca-a18a-406d-a4c1-74e6f8f28e5b</t>
+          <t>ca-cioos_ea6c0e20-9b99-48f7-adfb-6c1b70f6bd2a</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3268,7 +3276,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Surfgrass Community Structure - Monitoring - BC Central Coast - 2016-2017</t>
+          <t>Barnacle Dynamics: Point Intercept Surveys - BC Central Coast - 2016-2018</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3324,17 +3332,17 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>10.21966/nrmz-a516</t>
+          <t>10.21966/kg0p-mt85</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MooQxV2q0Y_rOjI40Fq</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MooXcyKt1ay-sIZkq00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3344,7 +3352,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V27" t="n">
@@ -3363,12 +3371,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ca-cioos_ea6c0e20-9b99-48f7-adfb-6c1b70f6bd2a</t>
+          <t>ca-cioos_1347af6c-aedf-4ec6-bd37-ed508df6c40a</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3378,7 +3386,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Barnacle Dynamics: Point Intercept Surveys - BC Central Coast - 2016-2018</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3396,7 +3404,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3424,32 +3432,32 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.1383514404297, 51.60223926037915], [-127.96669006347653, 51.60223926037915], [-127.96669006347653, 51.68660524501087], [-128.1383514404297, 51.68660524501087], [-128.1383514404297, 51.60223926037915]]]}</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '-5.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>10.21966/kg0p-mt85</t>
+          <t>10.21966/1.243102</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MooXcyKt1ay-sIZkq00</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUVFTFdKeHlaQ29nNTQ</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3473,12 +3481,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ca-cioos_1347af6c-aedf-4ec6-bd37-ed508df6c40a</t>
+          <t>ca-cioos_62336906-31e6-4c32-968c-2312e703e08f</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3488,7 +3496,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
+          <t>Underwater Video Transects - Calvert Island - 2016</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3506,7 +3514,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3534,12 +3542,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.1383514404297, 51.60223926037915], [-127.96669006347653, 51.60223926037915], [-127.96669006347653, 51.68660524501087], [-128.1383514404297, 51.68660524501087], [-128.1383514404297, 51.60223926037915]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085938, 51.64870258356993], [-128.06350708007812, 51.64870258356993], [-128.06350708007812, 51.69958706405643], [-128.13217163085938, 51.69958706405643], [-128.13217163085938, 51.64870258356993]]]}</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '100.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3549,12 +3557,12 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10.21966/1.243102</t>
+          <t>10.21966/b0xc-8m25</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUVFTFdKeHlaQ29nNTQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVZqUmI5R3RHdGxYVXQ</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3583,12 +3591,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ca-cioos_62336906-31e6-4c32-968c-2312e703e08f</t>
+          <t>ca-cioos_94b4992f-19e2-46d4-875e-f0c952ea62f7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3598,7 +3606,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Underwater Video Transects - Calvert Island - 2016</t>
+          <t>Kelp Field Data for Remote Sensing - BC Central Coast</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3616,7 +3624,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3644,12 +3652,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085938, 51.64870258356993], [-128.06350708007812, 51.64870258356993], [-128.06350708007812, 51.69958706405643], [-128.13217163085938, 51.69958706405643], [-128.13217163085938, 51.64870258356993]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.50708007812503, 51.62824753375085], [-128.02917480468753, 51.62824753375085], [-128.02917480468753, 52.08288179572668], [-128.50708007812503, 52.08288179572668], [-128.50708007812503, 51.62824753375085]]]}</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>[{'max': '100.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3659,12 +3667,12 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>10.21966/b0xc-8m25</t>
+          <t>10.21966/tqj2-wh77</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVZqUmI5R3RHdGxYVXQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW5QQm5jeUJ4MDJReHY</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3674,7 +3682,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="V30" t="n">
@@ -3693,12 +3701,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ca-cioos_94b4992f-19e2-46d4-875e-f0c952ea62f7</t>
+          <t>ca-cioos_15caa6c8-be9b-4f19-81ae-bb82321eafd6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3708,7 +3716,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kelp Field Data for Remote Sensing - BC Central Coast</t>
+          <t>Mean Tidal Current - Coastal British Columbia - Canada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3726,7 +3734,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial, Oceanography</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3754,48 +3762,40 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.50708007812503, 51.62824753375085], [-128.02917480468753, 51.62824753375085], [-128.02917480468753, 52.08288179572668], [-128.50708007812503, 52.08288179572668], [-128.50708007812503, 51.62824753375085]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.74853515624997, 49.72447918871299], [-124.14550781249997, 49.72447918871299], [-124.14550781249997, 52.9883372533954], [-129.74853515624997, 52.9883372533954], [-129.74853515624997, 49.72447918871299]]]}</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>10.21966/tqj2-wh77</t>
-        </is>
-      </c>
+          <t>other, subSurfaceCurrents</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW5QQm5jeUJ4MDJReHY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXZtOVowU1p6eWZsSUE</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2022-01-19</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ca-cioos_15caa6c8-be9b-4f19-81ae-bb82321eafd6</t>
+          <t>ca-cioos_3dc0d46c-7afe-4379-901d-37a787c1c204</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mean Tidal Current - Coastal British Columbia - Canada</t>
+          <t>Snow Depth Measurements from Remotely Piloted Aerial Systems - Mt. Cain - 2018 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Geospatial, Oceanography</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3974,23 +3974,27 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.74853515624997, 49.72447918871299], [-124.14550781249997, 49.72447918871299], [-124.14550781249997, 52.9883372533954], [-129.74853515624997, 52.9883372533954], [-129.74853515624997, 49.72447918871299]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.45157077, 50.17895647], [-126.25015464, 50.17895647], [-126.25015464, 50.29841121], [-126.45157077, 50.29841121], [-126.45157077, 50.17895647]]]}</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '2200.0', 'min': '500.0'}]</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>other, subSurfaceCurrents</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>10.21966/1amj-rw65</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXZtOVowU1p6eWZsSUE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWN2Tzh0TTllTGVIU0M</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -4000,14 +4004,18 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4015,12 +4023,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ca-cioos_3dc0d46c-7afe-4379-901d-37a787c1c204</t>
+          <t>ca-cioos_e8c8ed7d-51fa-45e0-b4eb-d21ddc55526a</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4030,7 +4038,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Snow Depth Measurements from Remotely Piloted Aerial Systems - Mt. Cain - 2018 - British Columbia - Canada</t>
+          <t>Clam Garden Geospatial Data - Quadra Island - 2016</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4076,12 +4084,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.45157077, 50.17895647], [-126.25015464, 50.17895647], [-126.25015464, 50.29841121], [-126.45157077, 50.29841121], [-126.45157077, 50.17895647]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.34725189558227, 50.23307863302776], [-125.21060943952757, 50.23307863302776], [-125.21060943952757, 50.28641446558299], [-125.34725189558227, 50.28641446558299], [-125.34725189558227, 50.23307863302776]]]}</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>[{'max': '2200.0', 'min': '500.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4091,12 +4099,12 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>10.21966/1amj-rw65</t>
+          <t>10.21966/1.346775</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWN2Tzh0TTllTGVIU0M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWU1ek9Mc1IwTVhWcEo</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -4106,7 +4114,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="V34" t="n">
@@ -4125,12 +4133,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ca-cioos_e8c8ed7d-51fa-45e0-b4eb-d21ddc55526a</t>
+          <t>ca-cioos_f68be641-0017-4311-b4de-5d0aed9e2b57</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4140,7 +4148,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Clam Garden Geospatial Data - Quadra Island - 2016</t>
+          <t>100 Islands Project - Island Spatial Data -2017 - Coastal British Columbia - Canada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4158,7 +4166,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, 100 Islands</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4182,16 +4190,16 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.34725189558227, 50.23307863302776], [-125.21060943952757, 50.23307863302776], [-125.21060943952757, 50.28641446558299], [-125.34725189558227, 50.28641446558299], [-125.34725189558227, 50.23307863302776]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61694335937497, 51.3854950692232], [-127.61718749999997, 51.3854950692232], [-127.61718749999997, 52.0322181041453], [-128.61694335937497, 52.0322181041453], [-128.61694335937497, 51.3854950692232]]]}</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -4201,12 +4209,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>10.21966/1.346775</t>
+          <t>10.21966/gsbw-bz85</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWU1ek9Mc1IwTVhWcEo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFJMkk4eTgwRkNDeno</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4216,7 +4224,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="V35" t="n">
@@ -4235,12 +4243,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ca-cioos_f68be641-0017-4311-b4de-5d0aed9e2b57</t>
+          <t>ca-cioos_769311e9-1b1f-41f4-9023-38acf37a6690</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4250,7 +4258,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>100 Islands Project - Island Spatial Data -2017 - Coastal British Columbia - Canada</t>
+          <t>30m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4268,7 +4276,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Geospatial, 100 Islands</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4296,12 +4304,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61694335937497, 51.3854950692232], [-127.61718749999997, 51.3854950692232], [-127.61718749999997, 52.0322181041453], [-128.61694335937497, 52.0322181041453], [-128.61694335937497, 51.3854950692232]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.164675, 51.408207], [-127.868994, 51.408207], [-127.868994, 51.734813], [-128.164675, 51.734813], [-128.164675, 51.408207]]]}</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>[{'max': '300.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4311,22 +4319,22 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>10.21966/gsbw-bz85</t>
+          <t>10.21966/nwf1-8x95</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFJMkk4eTgwRkNDeno</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW1iT1oxc3AwR2Mxb24</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2022-01-19</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V36" t="n">
@@ -4345,12 +4353,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ca-cioos_769311e9-1b1f-41f4-9023-38acf37a6690</t>
+          <t>ca-cioos_1946cc53-6e11-4428-a2c9-43b34e1dcaa1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4360,7 +4368,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Orthophoto High Compression 0.25m resolution Mosaic - 2012 - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4378,7 +4386,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4402,16 +4410,16 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.164675, 51.408207], [-127.868994, 51.408207], [-127.868994, 51.734813], [-128.164675, 51.734813], [-128.164675, 51.408207]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16651, 51.402002], [-127.854745, 51.402002], [-127.854745, 51.74304], [-128.16651, 51.74304], [-128.16651, 51.402002]]]}</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -4421,22 +4429,22 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>10.21966/nwf1-8x95</t>
+          <t>10.21966/6xx9-1y19</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW1iT1oxc3AwR2Mxb24</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJRYXNXRFlMbURuMjU</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
+          <t>2022-01-21</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="V37" t="n">
@@ -4455,12 +4463,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ca-cioos_1946cc53-6e11-4428-a2c9-43b34e1dcaa1</t>
+          <t>ca-cioos_26a09a27-7f16-4944-b88d-8c3bf2d36f03</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4470,7 +4478,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Orthophoto High Compression 0.25m resolution Mosaic - 2012 - Calvert Island - British Columbia - Canada</t>
+          <t>Wind Fetch - BC Central Coast - Canada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4488,7 +4496,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4516,12 +4524,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16651, 51.402002], [-127.854745, 51.402002], [-127.854745, 51.74304], [-128.16651, 51.74304], [-128.16651, 51.402002]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.7578125, 50.16193379], [-126.22070312, 50.16193379], [-126.22070312, 52.84175491], [-131.7578125, 52.84175491], [-131.7578125, 50.16193379]]]}</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4531,12 +4539,12 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>10.21966/6xx9-1y19</t>
+          <t>10.21966/845b-yn81</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJRYXNXRFlMbURuMjU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXNDOU8zYXhRdDA3RWM</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -4546,7 +4554,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V38" t="n">
@@ -4565,12 +4573,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ca-cioos_26a09a27-7f16-4944-b88d-8c3bf2d36f03</t>
+          <t>ca-cioos_33c870b8-3b4c-429d-bc10-99dd4c7f4c7d</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4580,7 +4588,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wind Fetch - BC Central Coast - Canada</t>
+          <t>Nearshore elevation and imagery models - Quadra Island Hakai Institute Facility Shoreline - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4622,16 +4630,16 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.7578125, 50.16193379], [-126.22070312, 50.16193379], [-126.22070312, 52.84175491], [-131.7578125, 52.84175491], [-131.7578125, 50.16193379]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.2229327, 50.11245881], [-125.21821201, 50.11245881], [-125.21821201, 50.1172472], [-125.2229327, 50.1172472], [-125.2229327, 50.11245881]]]}</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4641,12 +4649,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>10.21966/845b-yn81</t>
+          <t>10.21966/ebd6-yd93</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXNDOU8zYXhRdDA3RWM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXN1MUhmRE9GRndsSko</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4656,7 +4664,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V39" t="n">
@@ -4675,12 +4683,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ca-cioos_33c870b8-3b4c-429d-bc10-99dd4c7f4c7d</t>
+          <t>ca-cioos_5feb907e-e63e-4172-94ae-831fbe92aee5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4690,7 +4698,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nearshore elevation and imagery models - Quadra Island Hakai Institute Facility Shoreline - British Columbia - Canada</t>
+          <t>25m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4736,12 +4744,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.2229327, 50.11245881], [-125.21821201, 50.11245881], [-125.21821201, 50.1172472], [-125.2229327, 50.1172472], [-125.2229327, 50.11245881]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868915, 51.408116], [-127.868915, 51.735084], [-128.16482, 51.735084], [-128.16482, 51.408116]]]}</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4751,12 +4759,12 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>10.21966/ebd6-yd93</t>
+          <t>10.21966/pggc-zh06</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXN1MUhmRE9GRndsSko</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWtqcjFNTUo0aFJWUkI</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -4766,7 +4774,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V40" t="n">
@@ -4785,12 +4793,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>401a599c-d74d-4a44-930a-8c0c90659e92</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ca-cioos_5feb907e-e63e-4172-94ae-831fbe92aee5</t>
+          <t>ca-cioos_7d3f525a-6ba2-494b-893a-147e2a812306</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4800,7 +4808,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>25m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Macrocystis kelp canopy productivity data from BC Central Coast</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4818,12 +4826,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4842,31 +4850,31 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868915, 51.408116], [-127.868915, 51.735084], [-128.16482, 51.735084], [-128.16482, 51.408116]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.2, 51.33], [-127.2, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>10.21966/pggc-zh06</t>
+          <t>10.21966/k88j-1k50</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWtqcjFNTUo0aFJWUkI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtFxWh-RyO-TnboGr5A</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -4876,7 +4884,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V41" t="n">
@@ -4895,12 +4903,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>401a599c-d74d-4a44-930a-8c0c90659e92</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ca-cioos_7d3f525a-6ba2-494b-893a-147e2a812306</t>
+          <t>ca-cioos_be16603d-e383-4af4-9e93-7a36a086688e</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4910,7 +4918,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Macrocystis kelp canopy productivity data from BC Central Coast</t>
+          <t>Imagery and elevation models monitoring algae research sites - 2017 - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4928,12 +4936,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4952,31 +4960,31 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.2, 51.33], [-127.2, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.15757751464844, 51.64358968607138], [-128.089599609375, 51.64358968607138], [-128.089599609375, 51.68021937787972], [-128.15757751464844, 51.68021937787972], [-128.15757751464844, 51.64358968607138]]]}</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>10.21966/k88j-1k50</t>
+          <t>10.21966/ykm3-ah04</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtFxWh-RyO-TnboGr5A</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVlwc1pEdzNqdGdOSGM</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -4986,7 +4994,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V42" t="n">
@@ -5005,12 +5013,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ca-cioos_be16603d-e383-4af4-9e93-7a36a086688e</t>
+          <t>ca-cioos_d342e016-1e9a-448a-bc1a-af53fe8d5dfd</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5020,7 +5028,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Imagery and elevation models monitoring algae research sites - 2017 - Calvert Island - British Columbia - Canada</t>
+          <t>Herring Survey Data - 2016 - BC Central Coast</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5038,7 +5046,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5066,27 +5074,27 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.15757751464844, 51.64358968607138], [-128.089599609375, 51.64358968607138], [-128.089599609375, 51.68021937787972], [-128.15757751464844, 51.68021937787972], [-128.15757751464844, 51.64358968607138]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.54187017306685, 51.58844754923095], [-127.72888189181685, 51.58844754923095], [-127.72888189181685, 52.26927804083806], [-128.54187017306685, 52.26927804083806], [-128.54187017306685, 51.58844754923095]]]}</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, fishAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>10.21966/ykm3-ah04</t>
+          <t>10.21966/xywe-mt82</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVlwc1pEdzNqdGdOSGM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhzYmdPTzl2elpwWFM</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -5096,7 +5104,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="V43" t="n">
@@ -5115,12 +5123,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ca-cioos_d342e016-1e9a-448a-bc1a-af53fe8d5dfd</t>
+          <t>ca-cioos_f462be7f-ab53-409e-8f8c-9b9fecc5e16e</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5130,7 +5138,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Herring Survey Data - 2016 - BC Central Coast</t>
+          <t>Hakai Marine Sampling Survey - 2014 - BC Central Coast - Canada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5148,7 +5156,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5176,27 +5184,27 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.54187017306685, 51.58844754923095], [-127.72888189181685, 51.58844754923095], [-127.72888189181685, 52.26927804083806], [-128.54187017306685, 52.26927804083806], [-128.54187017306685, 51.58844754923095]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61968994140625, 51.395778392663175], [-127.24639892578124, 51.395778392663175], [-127.24639892578124, 52.08625733233839], [-128.61968994140625, 52.08625733233839], [-128.61968994140625, 51.395778392663175]]]}</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '400.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>other, fishAbundanceAndDistribution</t>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, subSurfaceTemperature, oxygen, particulateMatter</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>10.21966/xywe-mt82</t>
+          <t>10.21966/xg0y-1z76</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhzYmdPTzl2elpwWFM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXRPMVRReFQ2YlJDYUY</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -5206,7 +5214,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="V44" t="n">
@@ -5225,12 +5233,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ca-cioos_f462be7f-ab53-409e-8f8c-9b9fecc5e16e</t>
+          <t>ca-cioos_154e88e6-2300-4ca0-b3f8-ee822d32a9a4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5240,7 +5248,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hakai Marine Sampling Survey - 2014 - BC Central Coast - Canada</t>
+          <t>Seastar &amp; Macroinvertebrate Dynamics - BC Central Coast - 2016-2017</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5258,7 +5266,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5282,41 +5290,41 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61968994140625, 51.395778392663175], [-127.24639892578124, 51.395778392663175], [-127.24639892578124, 52.08625733233839], [-128.61968994140625, 52.08625733233839], [-128.61968994140625, 51.395778392663175]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>[{'max': '400.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '-5.0'}]</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>other, seaSurfaceTemperature, subSurfaceSalinity, subSurfaceTemperature, oxygen, particulateMatter</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>10.21966/xg0y-1z76</t>
+          <t>10.21966/7rx8-dk31</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXRPMVRReFQ2YlJDYUY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MooEJK092sXt8j4VEAp</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2022-01-21</t>
+          <t>2022-01-22</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="V45" t="n">
@@ -5335,12 +5343,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ca-cioos_154e88e6-2300-4ca0-b3f8-ee822d32a9a4</t>
+          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5350,7 +5358,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Seastar &amp; Macroinvertebrate Dynamics - BC Central Coast - 2016-2017</t>
+          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5368,7 +5376,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5396,37 +5404,37 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '-5.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>10.21966/7rx8-dk31</t>
+          <t>10.21966/1.715784</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MooEJK092sXt8j4VEAp</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2022-01-22</t>
+          <t>2022-01-24</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V46" t="n">
@@ -5445,12 +5453,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
+          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5460,7 +5468,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
+          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5478,7 +5486,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5506,7 +5514,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5516,17 +5524,17 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>10.21966/1.715784</t>
+          <t>10.21966/6zp4-ye07</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -5536,7 +5544,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V47" t="n">
@@ -5555,12 +5563,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
+          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5570,7 +5578,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5616,7 +5624,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5631,12 +5639,12 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10.21966/6zp4-ye07</t>
+          <t>10.21966/zs6a-j496</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5665,12 +5673,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
+          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5680,7 +5688,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
+          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5698,7 +5706,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5726,7 +5734,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5736,17 +5744,17 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10.21966/zs6a-j496</t>
+          <t>10.21966/1.715740</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -5756,7 +5764,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V49" t="n">
@@ -5775,12 +5783,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ca-cioos_3d7d93d0-73be-4c1b-af09-307e60a3576d</t>
+          <t>ca-cioos_4624baf9-ec39-4538-83fe-1563511b722c</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5790,7 +5798,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Water column carbonate system measurements from the Pacific Salmon Foundation Citizen Science Program stations from July 2016 to October 2017 in the northern Salish Sea, British Columbia, Canada</t>
+          <t>High-resolution record of surface seawater CO2 content from June 2017 to April 2019 collected in Sitka Harbor, Alaska, USA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5836,7 +5844,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.35968411, 49.4351949], [-124.37299598, 49.4351949], [-124.37299598, 50.10196506], [-125.35968411, 50.10196506], [-125.35968411, 49.4351949]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-135.62915433, 56.79541908], [-135.02059329, 56.79541908], [-135.02059329, 57.22157626], [-135.62915433, 57.22157626], [-135.62915433, 56.79541908]]]}</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5846,17 +5854,17 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10.21966/1.715740</t>
+          <t>10.21966/fwk1-a364</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9ENGY0VHBJTUd6blo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXFtYXJjVDZ5V3UxcTk</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -5866,7 +5874,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V50" t="n">
@@ -5885,12 +5893,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>7149f4c2-1e3d-4df7-8e37-fab3d36eba58</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ca-cioos_4624baf9-ec39-4538-83fe-1563511b722c</t>
+          <t>ca-cioos_48c8f830-f281-4ca1-9a81-ea690e70cb7a</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5900,7 +5908,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>High-resolution record of surface seawater CO2 content from June 2017 to April 2019 collected in Sitka Harbor, Alaska, USA</t>
+          <t>Water column CO2 system measurements from Hakai Oceanographic station QU39 from January 2016 to December 2017 in northern Salish Sea, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5946,7 +5954,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-135.62915433, 56.79541908], [-135.02059329, 56.79541908], [-135.02059329, 57.22157626], [-135.62915433, 57.22157626], [-135.62915433, 56.79541908]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.27772275, 49.99240786], [-124.97941819, 49.99240786], [-124.97941819, 50.16368976], [-125.27772275, 50.16368976], [-125.27772275, 49.99240786]]]}</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5961,12 +5969,12 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>10.21966/fwk1-a364</t>
+          <t>10.21966/1.715738</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXFtYXJjVDZ5V3UxcTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWZySTNVU0xzN3F1a2w</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -5976,7 +5984,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="V51" t="n">
@@ -5995,12 +6003,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7149f4c2-1e3d-4df7-8e37-fab3d36eba58</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ca-cioos_48c8f830-f281-4ca1-9a81-ea690e70cb7a</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6010,7 +6018,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements from Hakai Oceanographic station QU39 from January 2016 to December 2017 in northern Salish Sea, British Columbia, Canada</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6056,7 +6064,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.27772275, 49.99240786], [-124.97941819, 49.99240786], [-124.97941819, 50.16368976], [-125.27772275, 50.16368976], [-125.27772275, 49.99240786]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6071,12 +6079,12 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>10.21966/1.715738</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWZySTNVU0xzN3F1a2w</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6086,7 +6094,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V52" t="n">
@@ -6215,12 +6223,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6ebe47c3-6d59-4cb2-a7ba-111698445d8d</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6230,7 +6238,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Bald eagles as vectors of marine nutrients – Central Coast Islands (100 Islands study area) – May – July 2017</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6248,7 +6256,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>100 Islands</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6268,15 +6276,15 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.58323147, 51.38160352], [-127.80979387, 51.38160352], [-127.80979387, 52.09997599], [-128.58323147, 52.09997599], [-128.58323147, 51.38160352]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6286,17 +6294,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, nutrients</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/2svf-e642</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6306,7 +6314,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -6325,12 +6333,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ca-cioos_6ebe47c3-6d59-4cb2-a7ba-111698445d8d</t>
+          <t>ca-cioos_94ded8f9-4ee7-407d-80eb-bf217ce7d260</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6340,7 +6348,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bald eagles as vectors of marine nutrients – Central Coast Islands (100 Islands study area) – May – July 2017</t>
+          <t>High-resolution record of surface seawater CO2 content from August 2016 to August 2017 collected at the OceansAlaska shellfish hatchery in Ketchikan, Alaska, USA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6358,7 +6366,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>100 Islands</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6378,15 +6386,15 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.58323147, 51.38160352], [-127.80979387, 51.38160352], [-127.80979387, 52.09997599], [-128.58323147, 52.09997599], [-128.58323147, 51.38160352]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.96137029, 55.13698451], [-131.23813946, 55.13698451], [-131.23813946, 55.39922677], [-131.96137029, 55.39922677], [-131.96137029, 55.13698451]]]}</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6396,17 +6404,17 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>other, nutrients</t>
+          <t>other, dissolvedOrganicCarbon, oceanSurfaceStress</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10.21966/2svf-e642</t>
+          <t>10.21966/pk18-z035</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpwbzVZa0F3ZXd1YW0</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6416,7 +6424,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V55" t="n">
@@ -6435,12 +6443,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ca-cioos_94ded8f9-4ee7-407d-80eb-bf217ce7d260</t>
+          <t>ca-cioos_b4cac70e-a6fa-4d77-8fdb-1d3612006bc4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6450,7 +6458,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>High-resolution record of surface seawater CO2 content from August 2016 to August 2017 collected at the OceansAlaska shellfish hatchery in Ketchikan, Alaska, USA</t>
+          <t>Pacific Northwest Eelgrass Sediment Carbon Data</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6468,7 +6476,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6496,7 +6504,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.96137029, 55.13698451], [-131.23813946, 55.13698451], [-131.23813946, 55.39922677], [-131.96137029, 55.39922677], [-131.96137029, 55.13698451]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-143.1666738, 39.75452039], [-118.41060343, 39.75452039], [-118.41060343, 59.04838928], [-143.1666738, 59.04838928], [-143.1666738, 39.75452039]]]}</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6506,17 +6514,17 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon, oceanSurfaceStress</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>10.21966/pk18-z035</t>
+          <t>10.21966/20SJ-J017</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpwbzVZa0F3ZXd1YW0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVlYNnVCWW5yQ3RrUkM</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -6526,7 +6534,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="V56" t="n">
@@ -6545,12 +6553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>9e4a38d6-eb29-44a8-b495-c56ce74a227c</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ca-cioos_b4cac70e-a6fa-4d77-8fdb-1d3612006bc4</t>
+          <t>ca-cioos_c113d7a8-6a46-46fc-b49c-a4e69afedfbc</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6560,7 +6568,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pacific Northwest Eelgrass Sediment Carbon Data</t>
+          <t>Hakai Institute’s Burke-o-Lator TCO2/pCO2 Analyzer Discrete Sample Analysis Protocols</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6578,7 +6586,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6602,31 +6610,31 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-143.1666738, 39.75452039], [-118.41060343, 39.75452039], [-118.41060343, 59.04838928], [-143.1666738, 59.04838928], [-143.1666738, 39.75452039]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.200851030026, 47.5931373865871], [-133.329762644444, 58.3685518859093], [-138.778981394444, 57.2923559868765], [-128.407887644444, 50.1363698995369], [-122.519210405026, 46.8770323398551], [-121.200851030026, 47.5931373865871]]]}</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.15267028510888', 'min': '50.15091039641325'}]</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>10.21966/20SJ-J017</t>
+          <t>10.21966/1.521066</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVlYNnVCWW5yQ3RrUkM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUQyQ3F1WFBEZ2FkTnI</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -6636,15 +6644,15 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}, {'year': '2025', 'total': 2}]</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
@@ -6655,12 +6663,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9e4a38d6-eb29-44a8-b495-c56ce74a227c</t>
+          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ca-cioos_c113d7a8-6a46-46fc-b49c-a4e69afedfbc</t>
+          <t>ca-cioos_d200376b-7dd8-4778-b3f5-379243bf93b8</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6670,7 +6678,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hakai Institute’s Burke-o-Lator TCO2/pCO2 Analyzer Discrete Sample Analysis Protocols</t>
+          <t>High-resolution record of surface water pH at Sentry Shoal in the Northern Strait of Georgia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6712,31 +6720,31 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.200851030026, 47.5931373865871], [-133.329762644444, 58.3685518859093], [-138.778981394444, 57.2923559868765], [-128.407887644444, 50.1363698995369], [-122.519210405026, 46.8770323398551], [-121.200851030026, 47.5931373865871]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.9855, 49.9066], [-124.9854, 49.9066], [-124.9854, 49.9067], [-124.9855, 49.9067], [-124.9855, 49.9066]]]}</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>[{'max': '50.15267028510888', 'min': '50.15091039641325'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>10.21966/1.521066</t>
+          <t>10.21966/1.715693</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUQyQ3F1WFBEZ2FkTnI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUlpdWJIYjdIVDZJWTk</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -6746,15 +6754,15 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}, {'year': '2025', 'total': 2}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
@@ -6765,12 +6773,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
+          <t>24c3b914-33d7-4267-a1aa-8ce7523b296d</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ca-cioos_d200376b-7dd8-4778-b3f5-379243bf93b8</t>
+          <t>ca-cioos_dc50a22a-44c0-478c-aa19-a46343bc764a</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6780,7 +6788,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>High-resolution record of surface water pH at Sentry Shoal in the Northern Strait of Georgia</t>
+          <t>Barnacle Dynamics: Point Intercept Surveys - BC Central Coast - 2019</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6798,7 +6806,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6826,7 +6834,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.9855, 49.9066], [-124.9854, 49.9066], [-124.9854, 49.9067], [-124.9855, 49.9067], [-124.9855, 49.9066]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.1518199, 51.64582999], [-128.12195082, 51.64582999], [-128.12195082, 51.66861942], [-128.1518199, 51.66861942], [-128.1518199, 51.64582999]]]}</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6841,12 +6849,12 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>10.21966/1.715693</t>
+          <t>10.21966/m8kp-gy81</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUlpdWJIYjdIVDZJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUFaZGRYOURGWVg5UzA</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -6856,7 +6864,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="V59" t="n">
@@ -6875,12 +6883,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>24c3b914-33d7-4267-a1aa-8ce7523b296d</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ca-cioos_dc50a22a-44c0-478c-aa19-a46343bc764a</t>
+          <t>ca-cioos_f00b9c87-190e-4b89-a864-7c012b989e49</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6890,7 +6898,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Barnacle Dynamics: Point Intercept Surveys - BC Central Coast - 2019</t>
+          <t>High-resolution record of surface seawater CO2 content from December 2014 to April 2016 collected in Hyacinthe Bay, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6908,7 +6916,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6936,27 +6944,27 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.1518199, 51.64582999], [-128.12195082, 51.64582999], [-128.12195082, 51.66861942], [-128.1518199, 51.66861942], [-128.1518199, 51.64582999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.2229619026184, 50.116395452024676], [-125.22092342376709, 50.116395452024676], [-125.22092342376709, 50.11764753238538], [-125.2229619026184, 50.11764753238538], [-125.2229619026184, 50.116395452024676]]]}</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>10.21966/m8kp-gy81</t>
+          <t>10.21966/1.437736</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUFaZGRYOURGWVg5UzA</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXg3Yk10WFU2UGRwYkY</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -6966,7 +6974,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="V60" t="n">
@@ -6985,12 +6993,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ca-cioos_f00b9c87-190e-4b89-a864-7c012b989e49</t>
+          <t>ca-cioos_fcb4dfb6-606b-4b4b-bdcb-90f3f480fc33</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7000,7 +7008,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>High-resolution record of surface seawater CO2 content from December 2014 to April 2016 collected in Hyacinthe Bay, British Columbia, Canada</t>
+          <t>Data on invasion of Calvert Island by Orthione griffenis</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7018,7 +7026,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7046,27 +7054,27 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.2229619026184, 50.116395452024676], [-125.22092342376709, 50.116395452024676], [-125.22092342376709, 50.11764753238538], [-125.2229619026184, 50.11764753238538], [-125.2229619026184, 50.116395452024676]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17334953, 51.61670267], [-127.92753044, 51.61670267], [-127.92753044, 51.73677458], [-128.17334953, 51.73677458], [-128.17334953, 51.61670267]]]}</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>[{'max': '1.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>10.21966/1.437736</t>
+          <t>10.21966/kddh-gj22</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXg3Yk10WFU2UGRwYkY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWpwT0Z6RlAySHp6cU0</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -7076,7 +7084,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V61" t="n">
@@ -7095,12 +7103,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ca-cioos_fcb4dfb6-606b-4b4b-bdcb-90f3f480fc33</t>
+          <t>ca-cioos_41b0137d-6ac0-407d-a550-dd375475b2b0</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7110,7 +7118,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Data on invasion of Calvert Island by Orthione griffenis</t>
+          <t>Seafloor Observatory in Hyacinthe Bay, Quadra Island, British Columbia, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7128,12 +7136,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -7156,47 +7164,37 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17334953, 51.61670267], [-127.92753044, 51.61670267], [-127.92753044, 51.73677458], [-128.17334953, 51.73677458], [-128.17334953, 51.61670267]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.22003, 50.11736]}</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '10.0'}]</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>10.21966/kddh-gj22</t>
-        </is>
-      </c>
+          <t>oxygen, dissolvedOrganicCarbon, subSurfaceSalinity, subSurfaceTemperature, seaSurfaceHeight</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWpwT0Z6RlAySHp6cU0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MW5xCIKrrtNHbrGqNTx</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2022-01-24</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -7205,12 +7203,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ca-cioos_41b0137d-6ac0-407d-a550-dd375475b2b0</t>
+          <t>ca-cioos_87a845e3-e71a-43cc-a75f-ec6a3b812a0e</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7220,7 +7218,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Seafloor Observatory in Hyacinthe Bay, Quadra Island, British Columbia, Canada (Provisional)</t>
+          <t>Acoustic Doppler Current Profiler Time Series from Fixed Platform on the British Columbia Central Coast (Provisional)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7266,23 +7264,27 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.22003, 50.11736]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.61], [-128.6, 51.95], [-128.2, 52.04], [-127.8, 51.61], [-125.0, 50.12], [-125.2, 50.04], [-125.2, 50.04], [-125.2, 50.04], [-128.2, 51.61]]]}</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '10.0'}]</t>
+          <t>[{'max': '90.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>oxygen, dissolvedOrganicCarbon, subSurfaceSalinity, subSurfaceTemperature, seaSurfaceHeight</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
+          <t>subSurfaceCurrents, subSurfaceTemperature, seaSurfaceHeight</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>10.21966/1cgt-q249</t>
+        </is>
+      </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MW5xCIKrrtNHbrGqNTx</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MsbCMOYj2L_7dgICnzw</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -7292,11 +7294,17 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -7305,12 +7313,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ca-cioos_87a845e3-e71a-43cc-a75f-ec6a3b812a0e</t>
+          <t>ca-cioos_e09522d7-24f7-4c0e-afac-6cafd22a54f6</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7320,7 +7328,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Acoustic Doppler Current Profiler Time Series from Fixed Platform on the British Columbia Central Coast (Provisional)</t>
+          <t>High-resolution record of CO2 content from October 2013 to December 2018 measured in seawater entering the Alutiiq Pride Shellfish Hatchery in Seward, Alaska, USA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7343,7 +7351,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -7366,27 +7374,27 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.61], [-128.6, 51.95], [-128.2, 52.04], [-127.8, 51.61], [-125.0, 50.12], [-125.2, 50.04], [-125.2, 50.04], [-125.2, 50.04], [-128.2, 51.61]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-150.14476634, 59.68961051], [-148.42177964, 59.68961051], [-148.42177964, 60.2984757], [-150.14476634, 60.2984757], [-150.14476634, 59.68961051]]]}</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>[{'max': '90.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>subSurfaceCurrents, subSurfaceTemperature, seaSurfaceHeight</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>10.21966/1cgt-q249</t>
+          <t>10.21966/nkcy-8c07</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MsbCMOYj2L_7dgICnzw</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVZUYVNsZXAyTXh5bnQ</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -7396,7 +7404,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V64" t="n">
@@ -7415,12 +7423,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ca-cioos_e09522d7-24f7-4c0e-afac-6cafd22a54f6</t>
+          <t>ca-cioos_a0ca5d26-b457-4726-97d4-ed0c8dd6cd99</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7430,7 +7438,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>High-resolution record of CO2 content from October 2013 to December 2018 measured in seawater entering the Alutiiq Pride Shellfish Hatchery in Seward, Alaska, USA</t>
+          <t>Seascape connectivity data from a sub-tidal Zostera marina meadow, Choked Passage, Calvert Island, 2015</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7448,7 +7456,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7476,7 +7484,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-150.14476634, 59.68961051], [-148.42177964, 59.68961051], [-148.42177964, 60.2984757], [-150.14476634, 60.2984757], [-150.14476634, 59.68961051]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7486,27 +7494,27 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>10.21966/nkcy-8c07</t>
+          <t>10.21966/exy6-1k58</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVZUYVNsZXAyTXh5bnQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUoydUo4NEl3VEtGdU0</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2022-02-02</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V65" t="n">
@@ -7525,12 +7533,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>4becb6c2-ebdb-43f2-8f15-dee50aaa19d8</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ca-cioos_a0ca5d26-b457-4726-97d4-ed0c8dd6cd99</t>
+          <t>ca-cioos_fd5ada9a-5719-4ca1-89d2-17adb48d1493</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7540,7 +7548,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Seascape connectivity data from a sub-tidal Zostera marina meadow, Choked Passage, Calvert Island, 2015</t>
+          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2017, 2018)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7558,7 +7566,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7586,27 +7594,27 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.81789453, 48.48393505], [-122.96096027, 48.48393505], [-122.96096027, 49.05595865], [-123.81789453, 49.05595865], [-123.81789453, 48.48393505]]]}</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '100.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>10.21966/exy6-1k58</t>
+          <t>10.21966/t8hm-ge90</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUoydUo4NEl3VEtGdU0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBNZnZGekFJcFFDcm8</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -7616,7 +7624,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V66" t="n">
@@ -7635,12 +7643,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4becb6c2-ebdb-43f2-8f15-dee50aaa19d8</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ca-cioos_fd5ada9a-5719-4ca1-89d2-17adb48d1493</t>
+          <t>ca-cioos_63765cc6-5730-4a28-9d96-3de38066312f</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7650,7 +7658,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2017, 2018)</t>
+          <t>High-resolution record of surface seawater CO2 content from April 2016 to November 2017 collected in Hyacinthe Bay, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7668,7 +7676,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7692,41 +7700,41 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.81789453, 48.48393505], [-122.96096027, 48.48393505], [-122.96096027, 49.05595865], [-123.81789453, 49.05595865], [-123.81789453, 48.48393505]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.22364854812619, 50.116106505752896], [-125.22126674652097, 50.116106505752896], [-125.22126674652097, 50.11770256813347], [-125.22364854812619, 50.11770256813347], [-125.22364854812619, 50.116106505752896]]]}</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>[{'max': '100.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>10.21966/t8hm-ge90</t>
+          <t>10.21966/1.614670</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBNZnZGekFJcFFDcm8</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVpjRzlIZEFLbE9tSnA</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2022-02-02</t>
+          <t>2022-02-03</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V67" t="n">
@@ -7745,12 +7753,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ca-cioos_63765cc6-5730-4a28-9d96-3de38066312f</t>
+          <t>ca-cioos_7c47472a-b16c-446c-89d5-eefa23e07922</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7760,7 +7768,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>High-resolution record of surface seawater CO2 content from April 2016 to November 2017 collected in Hyacinthe Bay, British Columbia, Canada</t>
+          <t>High-resolution record of surface seawater CO2 content from November 2017 to June 2018 collected in Hyacinthe Bay, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7802,7 +7810,7 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -7821,12 +7829,12 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>10.21966/1.614670</t>
+          <t>10.21966/1.715729</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVpjRzlIZEFLbE9tSnA</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUhwbUdDUUlVTWtHYzE</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -7836,7 +7844,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V68" t="n">
@@ -7855,12 +7863,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ca-cioos_7c47472a-b16c-446c-89d5-eefa23e07922</t>
+          <t>ca-cioos_a72c43e2-5b4d-4d56-89d4-464b4c513710</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7870,7 +7878,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>High-resolution record of surface seawater CO2 content from November 2017 to June 2018 collected in Hyacinthe Bay, British Columbia, Canada</t>
+          <t>Surface water CO2 parameters collected by shellfish growers and partners in the northern Salish Sea from 2016 to 2018</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7916,7 +7924,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.22364854812619, 50.116106505752896], [-125.22126674652097, 50.116106505752896], [-125.22126674652097, 50.11770256813347], [-125.22364854812619, 50.11770256813347], [-125.22364854812619, 50.116106505752896]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.57747949, 49.70969514], [-124.52984083, 49.70969514], [-124.52984083, 50.11496976], [-125.57747949, 50.11496976], [-125.57747949, 49.70969514]]]}</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7931,12 +7939,12 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>10.21966/1.715729</t>
+          <t>10.21966/1.715756</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUhwbUdDUUlVTWtHYzE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWYwNjRsV2piMFJOR08</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -7965,12 +7973,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ca-cioos_a72c43e2-5b4d-4d56-89d4-464b4c513710</t>
+          <t>ca-cioos_77a256cd-baf7-434e-9f62-53ba809e48cb</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7980,7 +7988,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by shellfish growers and partners in the northern Salish Sea from 2016 to 2018</t>
+          <t>High-resolution record of 8-m seawater CO2 content entering Fanny Bay Oysters in Baynes Sound, British Columbia, Canada from March 2017 to November 2017</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8022,11 +8030,11 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.57747949, 49.70969514], [-124.52984083, 49.70969514], [-124.52984083, 50.11496976], [-125.57747949, 50.11496976], [-125.57747949, 49.70969514]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.88983154296876, 49.44759314103575], [-124.70993041992188, 49.44759314103575], [-124.70993041992188, 49.56975910961884], [-124.88983154296876, 49.56975910961884], [-124.88983154296876, 49.44759314103575]]]}</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8041,22 +8049,22 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>10.21966/1.715756</t>
+          <t>10.21966/1.622315</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWYwNjRsV2piMFJOR08</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTV4aEZoVWsyRXpHWno</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2022-02-03</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V70" t="n">
@@ -8075,12 +8083,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ca-cioos_77a256cd-baf7-434e-9f62-53ba809e48cb</t>
+          <t>ca-cioos_804b5b42-5550-4620-b789-7c2fe9572c03</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8090,7 +8098,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>High-resolution record of 8-m seawater CO2 content entering Fanny Bay Oysters in Baynes Sound, British Columbia, Canada from March 2017 to November 2017</t>
+          <t>Zooplankton - Taxonomy – Northern Strait of Georgia, Discovery Islands, Johnstone Strait, and Queen Charlotte Strait – April to July 2015 and 2016</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8113,7 +8121,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -8132,11 +8140,11 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.88983154296876, 49.44759314103575], [-124.70993041992188, 49.44759314103575], [-124.70993041992188, 49.56975910961884], [-124.88983154296876, 49.56975910961884], [-124.88983154296876, 49.44759314103575]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.93452704, 49.56730131], [-124.18481219, 49.56730131], [-124.18481219, 50.90762515], [-126.93452704, 50.90762515], [-126.93452704, 49.56730131]]]}</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8146,17 +8154,17 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>10.21966/1.622315</t>
+          <t>10.21966/bhqd-9361</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTV4aEZoVWsyRXpHWno</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZhamNPb0U3cThnR0o</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -8166,15 +8174,15 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="X71" t="inlineStr"/>
@@ -8185,12 +8193,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ca-cioos_804b5b42-5550-4620-b789-7c2fe9572c03</t>
+          <t>ca-cioos_a0263680-f0d5-46d5-85ea-483fa58c74b6</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8200,7 +8208,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Zooplankton - Taxonomy – Northern Strait of Georgia, Discovery Islands, Johnstone Strait, and Queen Charlotte Strait – April to July 2015 and 2016</t>
+          <t>High-resolution record of sea surface nitrate at Sentry Shoal in the Northern Strait of Georgia, British Columbia, Canada from 2015 to 2017</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8223,7 +8231,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8246,7 +8254,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.93452704, 49.56730131], [-124.18481219, 49.56730131], [-124.18481219, 50.90762515], [-126.93452704, 50.90762515], [-126.93452704, 49.56730131]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.2942704, 49.83702595], [-124.90571487, 49.83702595], [-124.90571487, 50.05976151], [-125.2942704, 50.05976151], [-125.2942704, 49.83702595]]]}</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8256,17 +8264,17 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>other, zooplanktonBiomassAndDiversity</t>
+          <t>nutrients</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>10.21966/bhqd-9361</t>
+          <t>10.21966/yk87-4x24</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZhamNPb0U3cThnR0o</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZ1QmZ1a3ZiZWEwM24</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -8276,15 +8284,15 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X72" t="inlineStr"/>
@@ -8295,12 +8303,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ca-cioos_a0263680-f0d5-46d5-85ea-483fa58c74b6</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8310,7 +8318,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>High-resolution record of sea surface nitrate at Sentry Shoal in the Northern Strait of Georgia, British Columbia, Canada from 2015 to 2017</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8328,7 +8336,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8352,41 +8360,41 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.2942704, 49.83702595], [-124.90571487, 49.83702595], [-124.90571487, 50.05976151], [-125.2942704, 50.05976151], [-125.2942704, 49.83702595]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>nutrients</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>10.21966/yk87-4x24</t>
+          <t>10.21966/awsk-my87</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZ1QmZ1a3ZiZWEwM24</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V73" t="n">
@@ -8405,12 +8413,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8420,7 +8428,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8462,16 +8470,16 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8481,12 +8489,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>10.21966/awsk-my87</t>
+          <t>10.21966/5rp3-3207</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -8496,7 +8504,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V74" t="n">
@@ -8515,12 +8523,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_62de21ed-90fb-422a-9c55-29c513a00f95</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8530,7 +8538,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Kilbella River Estuary LiDAR Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8576,12 +8584,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 51.72], [-127.3, 51.72], [-127.3, 51.74], [-127.4, 51.74], [-127.4, 51.72]]]}</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -8591,12 +8599,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10.21966/5rp3-3207</t>
+          <t>10.21966/s2c0-k006</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6CPeL2BfoPN85rGFk</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8606,7 +8614,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="V75" t="n">
@@ -8625,12 +8633,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ca-cioos_62de21ed-90fb-422a-9c55-29c513a00f95</t>
+          <t>ca-cioos_95bee6a0-ae38-4427-b5b2-5cc5835df70d</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -8640,7 +8648,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kilbella River Estuary LiDAR Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>North Vancouver Island Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8682,16 +8690,16 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 51.72], [-127.3, 51.72], [-127.3, 51.74], [-127.4, 51.74], [-127.4, 51.72]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 50.33], [-127.6, 50.33], [-127.6, 50.63], [-128.3, 50.63], [-128.3, 50.33]]]}</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -8701,12 +8709,12 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>10.21966/s2c0-k006</t>
+          <t>10.21966/ag60-st44</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6CPeL2BfoPN85rGFk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6hTZuLZ6h5NLfVXzz</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -8716,7 +8724,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V76" t="n">
@@ -8735,12 +8743,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_95bee6a0-ae38-4427-b5b2-5cc5835df70d</t>
+          <t>ca-cioos_a60a0468-3f56-4f22-abd4-5268fcfb9744</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8750,7 +8758,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>North Vancouver Island Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Owikeno Basin LiDAR Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8796,12 +8804,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 50.33], [-127.6, 50.33], [-127.6, 50.63], [-128.3, 50.63], [-128.3, 50.33]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 51.46], [-125.9, 51.46], [-125.9, 51.92], [-127.3, 51.92], [-127.3, 51.46]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8811,12 +8819,12 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>10.21966/ag60-st44</t>
+          <t>10.21966/03xf-hc34</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6hTZuLZ6h5NLfVXzz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MjBOaZ2eyXo9wQ38kdy</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8826,7 +8834,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="V77" t="n">
@@ -8845,12 +8853,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_a60a0468-3f56-4f22-abd4-5268fcfb9744</t>
+          <t>ca-cioos_bb59cb9e-887a-40a3-b41a-f4a5b2263ce6</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8860,7 +8868,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Owikeno Basin LiDAR Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Fountain Valley LiDAR Data - 2019 &amp; 2020 - Hakai Airborne Coastal Observatory - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8906,12 +8914,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 51.46], [-125.9, 51.46], [-125.9, 51.92], [-127.3, 51.92], [-127.3, 51.46]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.0, 50.56], [-121.7, 50.56], [-121.7, 50.8], [-122.0, 50.8], [-122.0, 50.56]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8921,12 +8929,12 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>10.21966/03xf-hc34</t>
+          <t>10.21966/8f0v-t572</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MjBOaZ2eyXo9wQ38kdy</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MmUnbGWVNvtiQAsYVPj</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8936,7 +8944,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="V78" t="n">
@@ -8955,12 +8963,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ca-cioos_bb59cb9e-887a-40a3-b41a-f4a5b2263ce6</t>
+          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8970,7 +8978,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fountain Valley LiDAR Data - 2019 &amp; 2020 - Hakai Airborne Coastal Observatory - British Columbia - Canada</t>
+          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9016,12 +9024,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.0, 50.56], [-121.7, 50.56], [-121.7, 50.8], [-122.0, 50.8], [-122.0, 50.56]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -9031,12 +9039,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>10.21966/8f0v-t572</t>
+          <t>10.21966/wfcv-n753</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MmUnbGWVNvtiQAsYVPj</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -9046,7 +9054,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="V79" t="n">
@@ -9065,12 +9073,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
+          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9080,7 +9088,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9098,7 +9106,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9126,12 +9134,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -9141,12 +9149,12 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>10.21966/wfcv-n753</t>
+          <t>10.21966/eysg-7a26</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -9175,12 +9183,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
+          <t>ca-cioos_d2e83e40-9e95-4a47-a899-b37c744be3ab</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9190,7 +9198,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
+          <t>Fin Island &amp; K'yel - 2020 - Airborne Coastal Observatory Data</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9208,7 +9216,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9236,7 +9244,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.4, 53.03], [-129.1, 53.03], [-129.1, 53.29], [-129.4, 53.29], [-129.4, 53.03]]]}</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9251,12 +9259,12 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>10.21966/eysg-7a26</t>
+          <t>10.21966/q4c4-wx08</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNm5cwomXVNI6vWU-R</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -9266,7 +9274,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V81" t="n">
@@ -9285,12 +9293,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ca-cioos_d2e83e40-9e95-4a47-a899-b37c744be3ab</t>
+          <t>ca-cioos_e0c768fc-5c37-455f-b2a3-604f766f4148</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9300,7 +9308,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fin Island &amp; K'yel - 2020 - Airborne Coastal Observatory Data</t>
+          <t>Nanwakolas Watershed Surveys - Knight Inlet - 2019 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9318,7 +9326,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9346,12 +9354,12 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.4, 53.03], [-129.1, 53.03], [-129.1, 53.29], [-129.4, 53.29], [-129.4, 53.03]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.1, 50.54], [-125.3, 50.54], [-125.3, 51.02], [-126.1, 51.02], [-126.1, 50.54]]]}</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -9361,12 +9369,12 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>10.21966/q4c4-wx08</t>
+          <t>10.21966/yvjm-gp93</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNm5cwomXVNI6vWU-R</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkEoax-I-IalULFPmu9</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -9376,7 +9384,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="V82" t="n">
@@ -9395,12 +9403,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ca-cioos_e0c768fc-5c37-455f-b2a3-604f766f4148</t>
+          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9410,7 +9418,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nanwakolas Watershed Surveys - Knight Inlet - 2019 - Hakai Airborne Coastal Observatory</t>
+          <t>Owikeno Lake Bathymetric Survey</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9428,7 +9436,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Watersheds, Airborne Coastal Observatory</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9456,12 +9464,12 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.1, 50.54], [-125.3, 50.54], [-125.3, 51.02], [-126.1, 51.02], [-126.1, 50.54]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -9471,22 +9479,22 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>10.21966/yvjm-gp93</t>
+          <t>10.21966/31db-5090</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkEoax-I-IalULFPmu9</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-03-02</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V83" t="n">
@@ -9505,12 +9513,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
+          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -9520,12 +9528,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Owikeno Lake Bathymetric Survey</t>
+          <t>Google Earth Engine Kelp Tool - Central Coast Output</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>software</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -9566,7 +9574,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9581,12 +9589,12 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>10.21966/31db-5090</t>
+          <t>10.21966/yff8-2w22</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -9596,7 +9604,7 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V84" t="n">
@@ -9615,12 +9623,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
+          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -9630,12 +9638,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Google Earth Engine Kelp Tool - Central Coast Output</t>
+          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -9648,7 +9656,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9672,11 +9680,11 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9686,17 +9694,17 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>10.21966/yff8-2w22</t>
+          <t>10.21966/82bd-ks94</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFIWmZWeEE0RkZrZVc</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -9706,7 +9714,7 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="V85" t="n">
@@ -9725,12 +9733,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
+          <t>ca-cioos_94cdfcba-bbd4-4053-8976-75de69460c14</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -9740,7 +9748,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
+          <t>Sea wrack wet to dry biomass calibrations for macroalgae of the Central Coast of British Columbia - 2018</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9758,7 +9766,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9782,31 +9790,31 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16116765, 51.64326925], [-128.11481908, 51.64326925], [-128.11481908, 51.66904109], [-128.16116765, 51.66904109], [-128.16116765, 51.64326925]]]}</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>other, macroalgalCanopyCoverAndComposition</t>
+          <t>other, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>10.21966/82bd-ks94</t>
+          <t>10.21966/ez7j-cy15</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFIWmZWeEE0RkZrZVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFWNFc0dmtoV0UyT2k</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -9835,12 +9843,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ca-cioos_94cdfcba-bbd4-4053-8976-75de69460c14</t>
+          <t>ca-cioos_6ae1b131-d903-44ca-92a9-64cf6487ddc2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -9850,7 +9858,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sea wrack wet to dry biomass calibrations for macroalgae of the Central Coast of British Columbia - 2018</t>
+          <t>Geology - Calvert Island</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9868,7 +9876,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9896,27 +9904,27 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16116765, 51.64326925], [-128.11481908, 51.64326925], [-128.11481908, 51.66904109], [-128.16116765, 51.66904109], [-128.16116765, 51.64326925]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.402632657661314], [-127.8204345703125, 51.402632657661314], [-127.8204345703125, 51.7644403180351], [-128.2489013671875, 51.7644403180351], [-128.2489013671875, 51.402632657661314]]]}</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>other, microbeBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>10.21966/ez7j-cy15</t>
+          <t>10.21966/f6bn-9773</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFWNFc0dmtoV0UyT2k</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFhaHEzRGxZdnRTMUM</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -9926,7 +9934,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V87" t="n">
@@ -9945,12 +9953,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ca-cioos_6ae1b131-d903-44ca-92a9-64cf6487ddc2</t>
+          <t>ca-cioos_1b517e6f-4f0a-4577-b7c2-c37f95d5b413</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9960,7 +9968,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Geology - Calvert Island</t>
+          <t>Field Station Structures - Calvert Island</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -10006,7 +10014,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.402632657661314], [-127.8204345703125, 51.402632657661314], [-127.8204345703125, 51.7644403180351], [-128.2489013671875, 51.7644403180351], [-128.2489013671875, 51.402632657661314]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13388824462888, 51.65280313672477], [-128.12830924987793, 51.65280313672477], [-128.12830924987793, 51.65589162014166], [-128.13388824462888, 51.65589162014166], [-128.13388824462888, 51.65280313672477]]]}</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10021,22 +10029,22 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>10.21966/f6bn-9773</t>
+          <t>10.21966/s2m2-0386</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFhaHEzRGxZdnRTMUM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTJ1U1NFN0xDSVNBT0k</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>2022-03-02</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="V88" t="n">
@@ -10055,12 +10063,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ca-cioos_1b517e6f-4f0a-4577-b7c2-c37f95d5b413</t>
+          <t>ca-cioos_4be1cc5e-8846-4fba-bd94-16ca933faab8</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10070,7 +10078,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Field Station Structures - Calvert Island</t>
+          <t>Hyperspectral Imagery - Calvert Island - 2012</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10088,7 +10096,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10112,16 +10120,16 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13388824462888, 51.65280313672477], [-128.12830924987793, 51.65280313672477], [-128.12830924987793, 51.65589162014166], [-128.13388824462888, 51.65589162014166], [-128.13388824462888, 51.65280313672477]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.21594238281247, 51.40948589555509], [-127.8094482421875, 51.40948589555509], [-127.8094482421875, 51.78993084774129], [-128.21594238281247, 51.78993084774129], [-128.21594238281247, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '3000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -10131,12 +10139,12 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>10.21966/s2m2-0386</t>
+          <t>10.21966/64tt-jh34</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTJ1U1NFN0xDSVNBT0k</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1SSXd3cG5UbzVYVW8</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -10146,7 +10154,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="V89" t="n">
@@ -10165,12 +10173,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ca-cioos_4be1cc5e-8846-4fba-bd94-16ca933faab8</t>
+          <t>ca-cioos_7381aff7-a4fe-4309-81f1-8eebe183b4d8</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -10180,7 +10188,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hyperspectral Imagery - Calvert Island - 2012</t>
+          <t>Summer sea wrack spatial data; Central Coast, British Columbia, Canada (2015 - 2017)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10198,7 +10206,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10222,16 +10230,16 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.21594238281247, 51.40948589555509], [-127.8094482421875, 51.40948589555509], [-127.8094482421875, 51.78993084774129], [-128.21594238281247, 51.78993084774129], [-128.21594238281247, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6224365234375, 51.399205653553764], [-127.650146484375, 51.399205653553764], [-127.650146484375, 52.08625733233839], [-128.6224365234375, 52.08625733233839], [-128.6224365234375, 51.399205653553764]]]}</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>[{'max': '3000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -10241,12 +10249,12 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>10.21966/64tt-jh34</t>
+          <t>10.21966/rwwv-na68</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1SSXd3cG5UbzVYVW8</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1BMXVHcFJ0d1ZVbjg</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -10256,7 +10264,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V90" t="n">
@@ -10275,12 +10283,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ca-cioos_7381aff7-a4fe-4309-81f1-8eebe183b4d8</t>
+          <t>ca-cioos_82a3f5ec-95c5-4aeb-a0c0-bf168c985676</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -10290,12 +10298,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Summer sea wrack spatial data; Central Coast, British Columbia, Canada (2015 - 2017)</t>
+          <t>Time-lapse Camera Imagery of Calvert Island Beaches (2012-Present)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -10308,12 +10316,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -10336,7 +10344,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6224365234375, 51.399205653553764], [-127.650146484375, 51.399205653553764], [-127.650146484375, 52.08625733233839], [-128.6224365234375, 52.08625733233839], [-128.6224365234375, 51.399205653553764]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.33441451, 51.56044969], [-128.01581099, 51.56044969], [-128.01581099, 51.75809075], [-128.33441451, 51.75809075], [-128.33441451, 51.56044969]]]}</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10351,12 +10359,12 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>10.21966/rwwv-na68</t>
+          <t>10.21966/r0nk-cz60</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1BMXVHcFJ0d1ZVbjg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTRPT3Q4SUJwZDBDazY</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
@@ -10366,7 +10374,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V91" t="n">
@@ -10385,12 +10393,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ca-cioos_82a3f5ec-95c5-4aeb-a0c0-bf168c985676</t>
+          <t>ca-cioos_c5bf06e7-29f9-404a-a454-36a5d67b2e69</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -10400,12 +10408,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Time-lapse Camera Imagery of Calvert Island Beaches (2012-Present)</t>
+          <t>Hakai Topographic Basemap</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -10423,7 +10431,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -10442,16 +10450,16 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.33441451, 51.56044969], [-128.01581099, 51.56044969], [-128.01581099, 51.75809075], [-128.33441451, 51.75809075], [-128.33441451, 51.56044969]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.000024, 49.750005], [-123.500016, 49.750005], [-123.500016, 53.00001], [-130.000024, 53.00001], [-130.000024, 49.750005]]]}</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -10461,12 +10469,12 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>10.21966/r0nk-cz60</t>
+          <t>10.21966/3aa8-3347</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTRPT3Q4SUJwZDBDazY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTdQU1J3ejBLVmp5MGY</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -10476,7 +10484,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="V92" t="n">
@@ -10495,12 +10503,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ca-cioos_c5bf06e7-29f9-404a-a454-36a5d67b2e69</t>
+          <t>ca-cioos_d61f51c3-7614-465f-bf27-c78986ca07c3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -10510,7 +10518,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hakai Topographic Basemap</t>
+          <t>McMullin Group Kelp Extent - Based on UAS Imagery - 2017</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -10556,12 +10564,12 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.000024, 49.750005], [-123.500016, 49.750005], [-123.500016, 53.00001], [-130.000024, 53.00001], [-130.000024, 49.750005]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.44315751, 52.02620636], [-128.37559157, 52.02620636], [-128.37559157, 52.07215005], [-128.44315751, 52.07215005], [-128.44315751, 52.02620636]]]}</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -10571,12 +10579,12 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>10.21966/3aa8-3347</t>
+          <t>10.21966/36b8-hq30</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTdQU1J3ejBLVmp5MGY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTNoNHEyQ0g1c3VIbGE</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -10586,7 +10594,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="V93" t="n">
@@ -10605,12 +10613,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ca-cioos_d61f51c3-7614-465f-bf27-c78986ca07c3</t>
+          <t>ca-cioos_e2d3d616-9ee2-451f-8584-14801b4c6fd0</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -10620,7 +10628,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>McMullin Group Kelp Extent - Based on UAS Imagery - 2017</t>
+          <t>Bathymetric Survey - Northwest Calvert Island</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10662,11 +10670,11 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.44315751, 52.02620636], [-128.37559157, 52.02620636], [-128.37559157, 52.07215005], [-128.44315751, 52.07215005], [-128.44315751, 52.02620636]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.1933734, 51.63078777], [-128.05776091, 51.63078777], [-128.05776091, 51.70744235], [-128.1933734, 51.70744235], [-128.1933734, 51.63078777]]]}</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10681,12 +10689,12 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>10.21966/36b8-hq30</t>
+          <t>10.21966/xtp4-7p91</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTNoNHEyQ0g1c3VIbGE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTlsYnhwcFE5NFpnejQ</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -10696,7 +10704,7 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V94" t="n">
@@ -10715,12 +10723,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ca-cioos_e2d3d616-9ee2-451f-8584-14801b4c6fd0</t>
+          <t>ca-cioos_fe20660b-ef3d-4f6b-90f8-5936d9c96cb5</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -10730,7 +10738,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bathymetric Survey - Northwest Calvert Island</t>
+          <t>20m Digital Elevation Model - Calvert Island</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10772,11 +10780,11 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.1933734, 51.63078777], [-128.05776091, 51.63078777], [-128.05776091, 51.70744235], [-128.1933734, 51.70744235], [-128.1933734, 51.63078777]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.164675, 51.408206], [-127.868845, 51.408206], [-127.868845, 51.734993], [-128.164675, 51.734993], [-128.164675, 51.408206]]]}</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10791,12 +10799,12 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>10.21966/xtp4-7p91</t>
+          <t>10.21966/zk1j-y602</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTlsYnhwcFE5NFpnejQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTJRNjNXMTFqUE5Semc</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -10806,7 +10814,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V95" t="n">
@@ -10825,12 +10833,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ca-cioos_fe20660b-ef3d-4f6b-90f8-5936d9c96cb5</t>
+          <t>ca-cioos_82a543b1-686c-45c9-a03d-4f93e0ab8e8a</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -10840,7 +10848,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20m Digital Elevation Model - Calvert Island</t>
+          <t>Big Bar Slide - 2020 - Airborne Coastal Observatory Data</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10858,7 +10866,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -10882,16 +10890,16 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.164675, 51.408206], [-127.868845, 51.408206], [-127.868845, 51.734993], [-128.164675, 51.734993], [-128.164675, 51.408206]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.0, 51.16], [-122.1, 51.13], [-122.2, 51.24], [-122.3, 51.35], [-122.2, 51.35], [-122.1, 51.21], [-122.1, 51.21], [-122.0, 51.16]]]}</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '300.0'}]</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -10901,22 +10909,22 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>10.21966/zk1j-y602</t>
+          <t>10.21966/42r2-pz17</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTJRNjNXMTFqUE5Semc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNRfeBqfw0-lialpkO</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2022-03-08</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="V96" t="n">
@@ -10935,12 +10943,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ca-cioos_82a543b1-686c-45c9-a03d-4f93e0ab8e8a</t>
+          <t>ca-cioos_0c8692f0-a103-4681-9247-9bb69c6e222e</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -10950,7 +10958,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Big Bar Slide - 2020 - Airborne Coastal Observatory Data</t>
+          <t>Kelp Canopy Extent - 2015 - NW Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -10968,7 +10976,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -10996,12 +11004,12 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.0, 51.16], [-122.1, 51.13], [-122.2, 51.24], [-122.3, 51.35], [-122.2, 51.35], [-122.1, 51.21], [-122.1, 51.21], [-122.0, 51.16]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17543029785156, 51.63272286429384], [-128.10916900634766, 51.63272286429384], [-128.10916900634766, 51.68149662336026], [-128.17543029785156, 51.68149662336026], [-128.17543029785156, 51.63272286429384]]]}</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '300.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -11011,22 +11019,22 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>10.21966/42r2-pz17</t>
+          <t>10.21966/q0wm-zk34</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNRfeBqfw0-lialpkO</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUV1QlY5N1AwYk42TFo</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>2022-03-08</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="V97" t="n">
@@ -11045,12 +11053,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ca-cioos_0c8692f0-a103-4681-9247-9bb69c6e222e</t>
+          <t>ca-cioos_14bf37c7-5eb6-4194-a992-c039fd7fb38b</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -11060,7 +11068,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kelp Canopy Extent - 2015 - NW Calvert Island - British Columbia - Canada</t>
+          <t>Hunter Island Hauyat Village Site Elevation Point Data - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -11078,7 +11086,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11102,16 +11110,16 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17543029785156, 51.63272286429384], [-128.10916900634766, 51.63272286429384], [-128.10916900634766, 51.68149662336026], [-128.17543029785156, 51.68149662336026], [-128.17543029785156, 51.63272286429384]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.1802368164062, 51.98995445995024], [-127.91656494140622, 51.98995445995024], [-127.91656494140622, 52.104818220233255], [-128.1802368164062, 52.104818220233255], [-128.1802368164062, 51.98995445995024]]]}</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -11121,12 +11129,12 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>10.21966/q0wm-zk34</t>
+          <t>10.21966/cj75-kw28</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUV1QlY5N1AwYk42TFo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWwydGZacjhXVkowZ0g</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -11136,7 +11144,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="V98" t="n">
@@ -14997,9 +15005,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X133" t="n">
-        <v>1</v>
-      </c>
+      <c r="X133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -25568,7 +25574,7 @@
         </is>
       </c>
       <c r="X229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -31062,7 +31068,7 @@
         </is>
       </c>
       <c r="X279" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -33797,9 +33803,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X304" t="n">
-        <v>1</v>
-      </c>
+      <c r="X304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -6105,12 +6105,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V54" t="n">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
+          <t>ca-cioos_bb59cb9e-887a-40a3-b41a-f4a5b2263ce6</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Fountain Valley LiDAR Data - 2019 &amp; 2020 - Hakai Airborne Coastal Observatory - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.0, 50.56], [-121.7, 50.56], [-121.7, 50.8], [-122.0, 50.8], [-122.0, 50.56]]]}</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>10.21966/wfcv-n753</t>
+          <t>10.21966/8f0v-t572</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MmUnbGWVNvtiQAsYVPj</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="V79" t="n">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
+          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
+          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>10.21966/eysg-7a26</t>
+          <t>10.21966/wfcv-n753</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ca-cioos_bb59cb9e-887a-40a3-b41a-f4a5b2263ce6</t>
+          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fountain Valley LiDAR Data - 2019 &amp; 2020 - Hakai Airborne Coastal Observatory - British Columbia - Canada</t>
+          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.0, 50.56], [-121.7, 50.56], [-121.7, 50.8], [-122.0, 50.8], [-122.0, 50.56]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>10.21966/8f0v-t572</t>
+          <t>10.21966/eysg-7a26</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MmUnbGWVNvtiQAsYVPj</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="V81" t="n">
@@ -9497,9 +9497,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X83" t="n">
-        <v>1</v>
-      </c>
+      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -14009,7 +14007,9 @@
           <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
         </is>
       </c>
-      <c r="X124" t="inlineStr"/>
+      <c r="X124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ca-cioos_24f1c230-6c37-470c-907d-25b9b022f5c2</t>
+          <t>ca-cioos_476204a7-0714-4755-953d-61fa3c5df497</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -18874,7 +18874,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada</t>
+          <t>Hakai Institute Nutrients (Dosser et al., 2021)</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -18892,7 +18892,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -18920,27 +18920,27 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.87477074, 49.80151064], [-124.30109865, 49.80151064], [-124.30109865, 50.66883255], [-126.87477074, 50.66883255], [-126.87477074, 49.80151064]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.6, 50.69], [-126.3, 50.8], [-124.8, 50.44], [-123.9, 49.65], [-125.1, 49.65], [-127.6, 50.69]]]}</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>[{'max': '9.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>nutrients</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>10.21966/54tw-kh93</t>
+          <t>10.21966/j3j5-wt70</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZDeElXT3dpUFNlOGQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/oOseiEWez6TzqPUIisEXczg6G8y2/-MoZtzH-n9LBy9Bn29Hl</t>
         </is>
       </c>
       <c r="T169" t="inlineStr">
@@ -18950,7 +18950,7 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="V169" t="n">
@@ -18969,12 +18969,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ca-cioos_476204a7-0714-4755-953d-61fa3c5df497</t>
+          <t>ca-cioos_24f1c230-6c37-470c-907d-25b9b022f5c2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Hakai Institute Nutrients (Dosser et al., 2021)</t>
+          <t>Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -19030,27 +19030,27 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.6, 50.69], [-126.3, 50.8], [-124.8, 50.44], [-123.9, 49.65], [-125.1, 49.65], [-127.6, 50.69]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.87477074, 49.80151064], [-124.30109865, 49.80151064], [-124.30109865, 50.66883255], [-126.87477074, 50.66883255], [-126.87477074, 49.80151064]]]}</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '9.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>nutrients</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>10.21966/j3j5-wt70</t>
+          <t>10.21966/54tw-kh93</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/oOseiEWez6TzqPUIisEXczg6G8y2/-MoZtzH-n9LBy9Bn29Hl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZDeElXT3dpUFNlOGQ</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="V170" t="n">
@@ -19181,7 +19181,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X171" t="inlineStr"/>
+      <c r="X171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19401,9 +19403,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X173" t="n">
-        <v>1</v>
-      </c>
+      <c r="X173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -21823,9 +21823,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X195" t="n">
-        <v>1</v>
-      </c>
+      <c r="X195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -28311,7 +28309,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X254" t="inlineStr"/>
+      <c r="X254" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28531,7 +28531,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X256" t="inlineStr"/>
+      <c r="X256" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -30399,12 +30401,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>c4932b55-1dd8-4f2f-89da-5822056ecc37</t>
+          <t>3988f8e8-36ea-4cda-9bd9-a03157116ef5</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>ca-cioos_53189107-9df5-426b-acb4-f903468554fe</t>
+          <t>ca-cioos_d43a79c1-a6ba-4e37-8dc2-6ced6312828e</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -30414,7 +30416,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Comparing invertebrate and seaweed diversity in kelp forests and urchin barrens in Owen Bay, British Columbia, using Autonomous Reef Monitoring Structures (ARMS)</t>
+          <t>Data from Manuscript: Parasites of the hermit crab Pagurus hirsutiusculus; distribution, prevalence, and thermal ecology</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -30432,7 +30434,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Sentinels of Change, Genomics</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -30456,41 +30458,41 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.2335, 50.2999], [-125.2163, 50.2999], [-125.2163, 50.313], [-125.2335, 50.313], [-125.2335, 50.2999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.66], [-127.9, 51.81], [-122.2, 49.03], [-123.3, 49.01], [-123.0, 48.83], [-123.0, 48.78], [-123.3, 48.7], [-123.3, 48.53], [-123.6, 48.59], [-125.2, 48.73], [-125.6, 48.95], [-125.6, 50.11], [-128.4, 51.66]]]}</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
+          <t>invertebrateAbundanceAndDistribution, seaSurfaceSalinity</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>10.21966/e5mw-tr82</t>
+          <t>10.21966/xb3t-qb88</t>
         </is>
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/5Jh4rsxoBsRd4mVFqZ0XJoMtMHI2/-P-tq8uNjGhWtk4rBny0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3eh7IMAvm8ZUtcMBeifFL0eJCIA3/-O5Kei32z9cfatfgKj5y</t>
         </is>
       </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V274" t="n">
@@ -30501,9 +30503,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X274" t="n">
-        <v>1</v>
-      </c>
+      <c r="X274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30511,12 +30511,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>33bb67af-4d61-4b15-93a9-f3ab2498430b</t>
+          <t>c4932b55-1dd8-4f2f-89da-5822056ecc37</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>ca-cioos_73abfecf-d35c-4f9c-a991-eee5cece08ea</t>
+          <t>ca-cioos_53189107-9df5-426b-acb4-f903468554fe</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -30526,7 +30526,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Kelp Canopy Extent 2012 - NW Calvert Island</t>
+          <t>Comparing invertebrate and seaweed diversity in kelp forests and urchin barrens in Owen Bay, British Columbia, using Autonomous Reef Monitoring Structures (ARMS)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -30544,7 +30544,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Sentinels of Change, Genomics</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -30568,41 +30568,41 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16959381103513, 51.63613234359897], [-128.11191558837888, 51.63613234359897], [-128.11191558837888, 51.681709494104325], [-128.16959381103513, 51.681709494104325], [-128.16959381103513, 51.63613234359897]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.2335, 50.2999], [-125.2163, 50.2999], [-125.2163, 50.313], [-125.2335, 50.313], [-125.2335, 50.2999]]]}</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '6.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>other, macroalgalCanopyCoverAndComposition</t>
+          <t>invertebrateAbundanceAndDistribution, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>10.21966/63rs-yt91</t>
+          <t>10.21966/e5mw-tr82</t>
         </is>
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxUM01laTFaREhKbWE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/5Jh4rsxoBsRd4mVFqZ0XJoMtMHI2/-P-tq8uNjGhWtk4rBny0</t>
         </is>
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="V275" t="n">
@@ -30613,7 +30613,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X275" t="inlineStr"/>
+      <c r="X275" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30621,12 +30623,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>bc1133da-5601-4f92-bc53-41be547c936b</t>
+          <t>33bb67af-4d61-4b15-93a9-f3ab2498430b</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>ca-cioos_940218ef-d7f8-4f3f-9e69-52150ecdbec5</t>
+          <t>ca-cioos_73abfecf-d35c-4f9c-a991-eee5cece08ea</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -30636,7 +30638,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>North Vancouver Island Aerial Survey - 2024 - Airborne Coastal Observatory</t>
+          <t>Kelp Canopy Extent 2012 - NW Calvert Island</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -30654,7 +30656,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -30678,31 +30680,31 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 50.35], [-125.4, 50.35], [-125.4, 50.63], [-126.7, 50.63], [-126.7, 50.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16959381103513, 51.63613234359897], [-128.11191558837888, 51.63613234359897], [-128.11191558837888, 51.681709494104325], [-128.16959381103513, 51.681709494104325], [-128.16959381103513, 51.63613234359897]]]}</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>10.21966/kdhe-hz07</t>
+          <t>10.21966/63rs-yt91</t>
         </is>
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCoHpqOwDbp834fqRY3</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxUM01laTFaREhKbWE</t>
         </is>
       </c>
       <c r="T276" t="inlineStr">
@@ -30712,7 +30714,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="V276" t="n">
@@ -30731,12 +30733,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
+          <t>bc1133da-5601-4f92-bc53-41be547c936b</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>ca-cioos_c7466354-bacc-4781-acdc-543dd03d1eab</t>
+          <t>ca-cioos_940218ef-d7f8-4f3f-9e69-52150ecdbec5</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -30746,7 +30748,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Nanwakolas LiDAR Surveys - Airborne Coastal Observatory</t>
+          <t>North Vancouver Island Aerial Survey - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -30792,12 +30794,12 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.8, 49.26], [-124.5, 49.26], [-124.5, 50.83], [-126.8, 50.83], [-126.8, 49.26]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 50.35], [-125.4, 50.35], [-125.4, 50.63], [-126.7, 50.63], [-126.7, 50.35]]]}</t>
         </is>
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>[{'max': '1700.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q277" t="inlineStr">
@@ -30807,12 +30809,12 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>10.21966/e0r7-ge27</t>
+          <t>10.21966/kdhe-hz07</t>
         </is>
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OjbuSE_uZcCs3Fit_mg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCoHpqOwDbp834fqRY3</t>
         </is>
       </c>
       <c r="T277" t="inlineStr">
@@ -30822,7 +30824,7 @@
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="V277" t="n">
@@ -30841,12 +30843,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>f7433c1a-3aad-4761-81c4-c191a5e6ac92</t>
+          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>ca-cioos_52e97374-bee5-4b1a-9b85-7170a5df8d6b</t>
+          <t>ca-cioos_c7466354-bacc-4781-acdc-543dd03d1eab</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -30856,7 +30858,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Biomass and density of Pycnopodia helianthoides from the central coast of BC</t>
+          <t>Nanwakolas LiDAR Surveys - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -30874,7 +30876,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -30902,37 +30904,37 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.617, 51.3321], [-127.3509, 51.3321], [-127.3509, 52.3317], [-128.617, 52.3317], [-128.617, 51.3321]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.8, 49.26], [-124.5, 49.26], [-124.5, 50.83], [-126.8, 50.83], [-126.8, 49.26]]]}</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1700.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>seaSurfaceSalinity, subSurfaceSalinity, seaSurfaceTemperature, subSurfaceTemperature, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>10.21966/xy6n-qz76</t>
+          <t>10.21966/e0r7-ge27</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-OteEfuBSvhg-2RySC4a</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OjbuSE_uZcCs3Fit_mg</t>
         </is>
       </c>
       <c r="T278" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V278" t="n">
@@ -30951,12 +30953,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>c7a168e8-f15e-446f-a49d-0b4a1f043ac2</t>
+          <t>f7433c1a-3aad-4761-81c4-c191a5e6ac92</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ca-cioos_b4844ae2-d9c1-42f2-ae4d-a8f994c395a0</t>
+          <t>ca-cioos_52e97374-bee5-4b1a-9b85-7170a5df8d6b</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -30966,7 +30968,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Putting fjord biodiversity on the map for British Columbia conservation planning</t>
+          <t>Biomass and density of Pycnopodia helianthoides from the central coast of BC</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -30984,7 +30986,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Genomics, Oceanography</t>
+          <t>Oceanography, Nearshore</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -31004,45 +31006,45 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.0471, 52.2577], [-128.9141, 51.7033], [-127.6841, 50.7687], [-123.7744, 48.9864], [-122.764, 49.331], [-122.8299, 49.9706], [-127.0471, 52.2577]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.617, 51.3321], [-127.3509, 51.3321], [-127.3509, 52.3317], [-128.617, 52.3317], [-128.617, 51.3321]]]}</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>[{'max': '595.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, subSurfaceTemperature, subSurfaceSalinity</t>
+          <t>seaSurfaceSalinity, subSurfaceSalinity, seaSurfaceTemperature, subSurfaceTemperature, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>10.21966/n141-m959</t>
+          <t>10.21966/xy6n-qz76</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-Ow-ZgW1jkC5-WyrtlLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-OteEfuBSvhg-2RySC4a</t>
         </is>
       </c>
       <c r="T279" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U279" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="V279" t="n">
@@ -31053,9 +31055,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X279" t="n">
-        <v>1</v>
-      </c>
+      <c r="X279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31063,12 +31063,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
+          <t>c7a168e8-f15e-446f-a49d-0b4a1f043ac2</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
+          <t>ca-cioos_b4844ae2-d9c1-42f2-ae4d-a8f994c395a0</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -31078,7 +31078,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
+          <t>Putting fjord biodiversity on the map for British Columbia conservation planning</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -31096,7 +31096,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Genomics, Oceanography</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -31116,56 +31116,58 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N280" t="n">
+        <v>2</v>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.0471, 52.2577], [-128.9141, 51.7033], [-127.6841, 50.7687], [-123.7744, 48.9864], [-122.764, 49.331], [-122.8299, 49.9706], [-127.0471, 52.2577]]]}</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>[{'max': '595.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>fishAbundanceAndDistribution, subSurfaceTemperature, subSurfaceSalinity</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>10.21966/n141-m959</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-Ow-ZgW1jkC5-WyrtlLV</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="V280" t="n">
+        <v>0</v>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X280" t="n">
         <v>1</v>
       </c>
-      <c r="O280" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
-        </is>
-      </c>
-      <c r="P280" t="inlineStr">
-        <is>
-          <t>[{'max': '2.5', 'min': '2.5'}]</t>
-        </is>
-      </c>
-      <c r="Q280" t="inlineStr">
-        <is>
-          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R280" t="inlineStr">
-        <is>
-          <t>10.21966/rrzq-yw32</t>
-        </is>
-      </c>
-      <c r="S280" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
-        </is>
-      </c>
-      <c r="T280" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="V280" t="n">
-        <v>0</v>
-      </c>
-      <c r="W280" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31173,12 +31175,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
+          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
+          <t>ca-cioos_1f1774ff-7398-4099-b89f-59df7ef0749e</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -31188,17 +31190,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
+          <t>Surface underway seawater and marine boundary layer observations of partial pressure of carbon dioxide (pCO2), water temperature, salinity and other parameters made during the M/V Seaspan Royal cruises in the coastal waters of British Columbia, Canada from 2022-07-01 to 2022-12-20</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H281" t="b">
@@ -31211,7 +31213,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -31234,23 +31236,27 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.4, 48.0], [-122.6, 48.0], [-122.6, 56.0], [-134.4, 56.0], [-134.4, 48.0]]]}</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>[{'max': '600.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2.5', 'min': '2.5'}]</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R281" t="inlineStr"/>
+          <t>oxygen, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>10.21966/rrzq-yw32</t>
+        </is>
+      </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/64WELpDV0tXYqOqiWFYNzMJdW4k1/-P0d5bTNUbXdaZiFm9zI</t>
         </is>
       </c>
       <c r="T281" t="inlineStr">
@@ -31260,11 +31266,17 @@
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="V281" t="inlineStr"/>
-      <c r="W281" t="inlineStr"/>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="V281" t="n">
+        <v>0</v>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="X281" t="inlineStr"/>
     </row>
     <row r="282">
@@ -31273,12 +31285,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
+          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
+          <t>ca-cioos_a787372d-e6f0-4128-bd08-7e9f5e667e1d</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -31288,17 +31300,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
+          <t>Discrete water chemistry measurements of the carbon dioxide system, nutrients, and organic carbon in fresh and marine waters of the Northeast Pacific coast of North America</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H282" t="b">
@@ -31306,12 +31318,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Estuary Resilience</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -31334,47 +31346,37 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.5, 43.3], [-121.8, 43.3], [-121.8, 62.0], [-153.5, 62.0], [-153.5, 43.3]]]}</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>[{'max': '100.0', 'min': '0.2'}]</t>
+          <t>[{'max': '600.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
-        </is>
-      </c>
-      <c r="R282" t="inlineStr">
-        <is>
-          <t>10.21966/r9zr-xz33</t>
-        </is>
-      </c>
+          <t>dissolvedOrganicCarbon, nitrousOxide, oxygen, stableCarbonIsotopes, inorganicCarbon, nutrients, particulateMatter, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceCurrents, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-P0d-gfRwatFu4gaeuhY</t>
         </is>
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="V282" t="n">
-        <v>0</v>
-      </c>
-      <c r="W282" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr"/>
+      <c r="W282" t="inlineStr"/>
       <c r="X282" t="inlineStr"/>
     </row>
     <row r="283">
@@ -31383,12 +31385,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
+          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
+          <t>ca-cioos_05c75bd9-1953-4ab9-8573-878845854662</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -31398,7 +31400,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Glendale River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -31444,7 +31446,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.72874, 50.69623], [-125.7357, 50.67697], [-125.73637, 50.66065], [-125.72893, 50.65255], [-125.71434, 50.64835], [-125.71329, 50.65188], [-125.72626, 50.65827], [-125.72636, 50.66466], [-125.72865, 50.68116], [-125.72721, 50.69604], [-125.72855, 50.69614], [-125.72874, 50.69623]]]}</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
@@ -31459,12 +31461,12 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>10.21966/9dbb-5d54</t>
+          <t>10.21966/r9zr-xz33</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7FmsNQ6HChfyLfTcX</t>
         </is>
       </c>
       <c r="T283" t="inlineStr">
@@ -31493,12 +31495,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
+          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
+          <t>ca-cioos_0e50f5a3-6100-4f1a-b184-ba327def9f3a</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -31508,7 +31510,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kaouk River estuary (Provisional)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -31554,7 +31556,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.15825, 50.07693], [-127.15157, 50.07806], [-127.13204, 50.06944], [-127.11152, 50.06781], [-127.0959, 50.06667], [-127.04315, 50.06879], [-127.04168, 50.06455], [-127.0902, 50.05983], [-127.10062, 50.05658], [-127.11983, 50.05885], [-127.13887, 50.06423], [-127.15988, 50.0753], [-127.15874, 50.07693], [-127.15825, 50.07693]]]}</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
@@ -31569,12 +31571,12 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>10.21966/vpz7-mm73</t>
+          <t>10.21966/9dbb-5d54</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq6X1wQRkybrW6sac5D</t>
         </is>
       </c>
       <c r="T284" t="inlineStr">
@@ -31603,12 +31605,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>0ce3ee5b-425b-4eb0-a201-96bdfb795a3f</t>
+          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>ca-cioos_354b5b83-e752-4ffb-a740-d1cdc02ac8c6</t>
+          <t>ca-cioos_2ba57f02-c88b-42b8-8f8c-07cfdeab45d3</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -31618,7 +31620,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Dtlaxsiwè River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kw'a'luxw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -31664,7 +31666,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.1721, 50.61011], [-127.17933, 50.612], [-127.1873, 50.6098], [-127.19703, 50.61072], [-127.20524, 50.61585], [-127.19007, 50.61844], [-127.18675, 50.61393], [-127.17744, 50.61359], [-127.17161, 50.61118], [-127.17203, 50.61011], [-127.1721, 50.61011]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.29886, 49.3576], [-124.30659, 49.32057], [-124.28624, 49.31332], [-124.26557, 49.29566], [-124.26427, 49.29899], [-124.28624, 49.3283], [-124.29878, 49.35744], [-124.29886, 49.3576]]]}</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
@@ -31679,12 +31681,12 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>10.21966/ydm2-m238</t>
+          <t>10.21966/vpz7-mm73</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7Dng-ZtRd05hnZCq1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptH1k-7T2gjAKY814I</t>
         </is>
       </c>
       <c r="T285" t="inlineStr">
@@ -31713,12 +31715,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>1a2aa5c8-9a83-46f7-967d-1127436c2084</t>
+          <t>0ce3ee5b-425b-4eb0-a201-96bdfb795a3f</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>ca-cioos_58a5140a-0b2c-4186-a648-53d9f58e5226</t>
+          <t>ca-cioos_354b5b83-e752-4ffb-a740-d1cdc02ac8c6</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -31728,7 +31730,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Kvai River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Dtlaxsiwè River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -31774,7 +31776,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.81882, 51.77547], [-127.83122, 51.77986], [-127.85192, 51.781], [-127.86785, 51.78358], [-127.8958, 51.77366], [-127.89418, 51.77118], [-127.87834, 51.77309], [-127.86508, 51.77748], [-127.84009, 51.77519], [-127.82731, 51.77452], [-127.82025, 51.77309], [-127.81853, 51.77566], [-127.81882, 51.77547]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.1721, 50.61011], [-127.17933, 50.612], [-127.1873, 50.6098], [-127.19703, 50.61072], [-127.20524, 50.61585], [-127.19007, 50.61844], [-127.18675, 50.61393], [-127.17744, 50.61359], [-127.17161, 50.61118], [-127.17203, 50.61011], [-127.1721, 50.61011]]]}</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
@@ -31789,12 +31791,12 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>10.21966/pm9m-h431</t>
+          <t>10.21966/ydm2-m238</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7QQE3ifLCAPcu3Jih</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7Dng-ZtRd05hnZCq1</t>
         </is>
       </c>
       <c r="T286" t="inlineStr">
@@ -31823,12 +31825,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>c035b81c-0fc3-446e-bec5-8b8933ae874b</t>
+          <t>1a2aa5c8-9a83-46f7-967d-1127436c2084</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>ca-cioos_7fbc28f7-ee87-4361-bbee-0ed8ce24522d</t>
+          <t>ca-cioos_58a5140a-0b2c-4186-a648-53d9f58e5226</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -31838,7 +31840,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Gwa'dzi River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Kvai River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -31884,7 +31886,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.46176, 50.74217], [-127.49022, 50.72165], [-127.49167, 50.71188], [-127.4832, 50.70356], [-127.4874, 50.69181], [-127.46443, 50.6928], [-127.47282, 50.70776], [-127.47992, 50.71424], [-127.48305, 50.72058], [-127.45901, 50.74011], [-127.46153, 50.74217], [-127.46176, 50.74217]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.81882, 51.77547], [-127.83122, 51.77986], [-127.85192, 51.781], [-127.86785, 51.78358], [-127.8958, 51.77366], [-127.89418, 51.77118], [-127.87834, 51.77309], [-127.86508, 51.77748], [-127.84009, 51.77519], [-127.82731, 51.77452], [-127.82025, 51.77309], [-127.81853, 51.77566], [-127.81882, 51.77547]]]}</t>
         </is>
       </c>
       <c r="P287" t="inlineStr">
@@ -31899,12 +31901,12 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>10.21966/xq99-x273</t>
+          <t>10.21966/pm9m-h431</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7BCRnF2C30YPkxIyd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7QQE3ifLCAPcu3Jih</t>
         </is>
       </c>
       <c r="T287" t="inlineStr">
@@ -31933,12 +31935,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
+          <t>c035b81c-0fc3-446e-bec5-8b8933ae874b</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
+          <t>ca-cioos_7fbc28f7-ee87-4361-bbee-0ed8ce24522d</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -31948,7 +31950,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Gwa'dzi River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -31994,7 +31996,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.46176, 50.74217], [-127.49022, 50.72165], [-127.49167, 50.71188], [-127.4832, 50.70356], [-127.4874, 50.69181], [-127.46443, 50.6928], [-127.47282, 50.70776], [-127.47992, 50.71424], [-127.48305, 50.72058], [-127.45901, 50.74011], [-127.46153, 50.74217], [-127.46176, 50.74217]]]}</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
@@ -32009,12 +32011,12 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>10.21966/kde9-8g12</t>
+          <t>10.21966/xq99-x273</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7BCRnF2C30YPkxIyd</t>
         </is>
       </c>
       <c r="T288" t="inlineStr">
@@ -32043,12 +32045,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
+          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
+          <t>ca-cioos_81883927-2334-45eb-b1c5-f6deb7add791</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -32058,7 +32060,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Conuma River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -32104,7 +32106,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.40799, 49.80074], [-126.43876, 49.78731], [-126.46497, 49.7786], [-126.46147, 49.79048], [-126.41255, 49.80261], [-126.40758, 49.80074], [-126.40799, 49.80074]]]}</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
@@ -32119,12 +32121,12 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>10.21966/9a97-2j48</t>
+          <t>10.21966/kde9-8g12</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpteQ8r8Ydn0LR9h4VG</t>
         </is>
       </c>
       <c r="T289" t="inlineStr">
@@ -32153,12 +32155,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
+          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
+          <t>ca-cioos_83a949b4-99be-4a36-a910-0c81946a9bf6</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -32168,7 +32170,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Muuyaḥi River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -32214,7 +32216,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.90617, 49.43155], [-125.91545, 49.42581], [-125.92033, 49.41507], [-125.9511, 49.38039], [-125.93437, 49.37197], [-125.89701, 49.41092], [-125.8986, 49.42679], [-125.90617, 49.43168], [-125.90617, 49.43155]]]}</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
@@ -32229,12 +32231,12 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>10.21966/ed9w-2653</t>
+          <t>10.21966/9a97-2j48</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptLdNw6_h2xTcYUjkS</t>
         </is>
       </c>
       <c r="T290" t="inlineStr">
@@ -32263,12 +32265,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>1af6a43a-e73b-4774-8e10-b9f2928ab133</t>
+          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ca-cioos_ae7e017c-9211-4f98-b56e-90a4bbac161c</t>
+          <t>ca-cioos_86f1dd95-27a0-4c52-97e4-15be649ce73a</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -32278,7 +32280,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Snuneymuxw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Xwésam River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -32324,7 +32326,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.88685, 49.19332], [-123.92494, 49.1612], [-123.92581, 49.13841], [-123.91159, 49.123], [-123.88023, 49.11117], [-123.85971, 49.12766], [-123.89792, 49.16196], [-123.88099, 49.18866], [-123.88685, 49.19332]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.92043, 50.31848], [-125.94107, 50.31848], [-125.94046, 50.36243], [-125.9639, 50.38185], [-125.95731, 50.39906], [-125.94094, 50.38954], [-125.93716, 50.37831], [-125.91445, 50.37257], [-125.91994, 50.31835], [-125.92043, 50.31848]]]}</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -32339,12 +32341,12 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>10.21966/k01q-wb27</t>
+          <t>10.21966/ed9w-2653</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt459vxCIH7YPRN9fp</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptUCw9y_sktWpuppc0</t>
         </is>
       </c>
       <c r="T291" t="inlineStr">
@@ -32373,12 +32375,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
+          <t>1af6a43a-e73b-4774-8e10-b9f2928ab133</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>ca-cioos_bea3da72-dafe-4e25-b5b2-0176e0ffba44</t>
+          <t>ca-cioos_ae7e017c-9211-4f98-b56e-90a4bbac161c</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -32388,7 +32390,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Chemainus River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Snuneymuxw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -32434,7 +32436,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.66843, 48.91641], [-123.6484, 48.90105], [-123.6554, 48.88016], [-123.6751, 48.87641], [-123.68894, 48.88178], [-123.68329, 48.89633], [-123.67928, 48.90316], [-123.67136, 48.91722], [-123.66848, 48.91635], [-123.66843, 48.91641]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.88685, 49.19332], [-123.92494, 49.1612], [-123.92581, 49.13841], [-123.91159, 49.123], [-123.88023, 49.11117], [-123.85971, 49.12766], [-123.89792, 49.16196], [-123.88099, 49.18866], [-123.88685, 49.19332]]]}</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
@@ -32449,12 +32451,12 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>10.21966/q2e0-j004</t>
+          <t>10.21966/k01q-wb27</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpszvIrt9OF8-BLQW2N</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt459vxCIH7YPRN9fp</t>
         </is>
       </c>
       <c r="T292" t="inlineStr">
@@ -32483,12 +32485,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
+          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
+          <t>ca-cioos_bea3da72-dafe-4e25-b5b2-0176e0ffba44</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -32498,7 +32500,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Chemainus River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -32544,7 +32546,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.66843, 48.91641], [-123.6484, 48.90105], [-123.6554, 48.88016], [-123.6751, 48.87641], [-123.68894, 48.88178], [-123.68329, 48.89633], [-123.67928, 48.90316], [-123.67136, 48.91722], [-123.66848, 48.91635], [-123.66843, 48.91641]]]}</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
@@ -32559,12 +32561,12 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>10.21966/hjkj-6611</t>
+          <t>10.21966/q2e0-j004</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpszvIrt9OF8-BLQW2N</t>
         </is>
       </c>
       <c r="T293" t="inlineStr">
@@ -32593,12 +32595,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>4c7b7347-767d-45e4-b3ad-7e0133b31e1c</t>
+          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>ca-cioos_dce15b7b-3772-4106-ab20-c3979c4c3f57</t>
+          <t>ca-cioos_d6e2bb44-2cad-4008-8af8-268054f5dfc6</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -32608,7 +32610,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Fulmore River - Shoal Creek Estuary Complex (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Asiixw River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -32654,7 +32656,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.08798, 50.4777], [-126.09599, 50.48418], [-126.09046, 50.50918], [-126.0647, 50.52425], [-125.99698, 50.53569], [-125.93459, 50.56717], [-125.93173, 50.56202], [-125.93764, 50.55458], [-125.91055, 50.55134], [-125.89853, 50.54943], [-125.90063, 50.54466], [-125.96416, 50.53989], [-125.98973, 50.52043], [-126.06566, 50.5067], [-126.08779, 50.47789], [-126.08798, 50.4777]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.67758, 51.98241], [-126.67797, 51.9818], [-126.67794, 51.97239], [-126.67998, 51.96699], [-126.68252, 51.95773], [-126.67601, 51.95751], [-126.67021, 51.95869], [-126.66832, 51.96062], [-126.67093, 51.96366], [-126.67565, 51.96617], [-126.67379, 51.97286], [-126.67744, 51.98251], [-126.67758, 51.98241]]]}</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
@@ -32669,12 +32671,12 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>10.21966/g1cn-xs92</t>
+          <t>10.21966/hjkj-6611</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptdJ8iUmLeOrdmqzrQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq7XYdY4GReTVYPK2zz</t>
         </is>
       </c>
       <c r="T294" t="inlineStr">
@@ -32703,12 +32705,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
+          <t>4c7b7347-767d-45e4-b3ad-7e0133b31e1c</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
+          <t>ca-cioos_dce15b7b-3772-4106-ab20-c3979c4c3f57</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -32718,7 +32720,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Fulmore River - Shoal Creek Estuary Complex (Provisional)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -32764,7 +32766,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.08798, 50.4777], [-126.09599, 50.48418], [-126.09046, 50.50918], [-126.0647, 50.52425], [-125.99698, 50.53569], [-125.93459, 50.56717], [-125.93173, 50.56202], [-125.93764, 50.55458], [-125.91055, 50.55134], [-125.89853, 50.54943], [-125.90063, 50.54466], [-125.96416, 50.53989], [-125.98973, 50.52043], [-126.06566, 50.5067], [-126.08779, 50.47789], [-126.08798, 50.4777]]]}</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
@@ -32779,12 +32781,12 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>10.21966/npe4-3036</t>
+          <t>10.21966/g1cn-xs92</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptdJ8iUmLeOrdmqzrQ</t>
         </is>
       </c>
       <c r="T295" t="inlineStr">
@@ -32813,12 +32815,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>35245eae-e508-47da-bcf7-54346cda086a</t>
+          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>ca-cioos_e9b72149-8cf1-4000-ae3e-6b29ad60b078</t>
+          <t>ca-cioos_dfb93c87-300e-4843-91f9-7c51bc59422e</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -32828,7 +32830,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Malksope River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Little Qualicum River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -32874,7 +32876,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.46569, 50.12556], [-127.45723, 50.13142], [-127.43281, 50.13338], [-127.42845, 50.13765], [-127.41181, 50.14408], [-127.40973, 50.14233], [-127.41999, 50.13627], [-127.41803, 50.13195], [-127.43106, 50.12796], [-127.46545, 50.12446], [-127.46569, 50.12548], [-127.46569, 50.12556]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.50281, 49.36977], [-124.50159, 49.36509], [-124.49039, 49.36183], [-124.484, 49.35439], [-124.48233, 49.35536], [-124.49153, 49.36749], [-124.50289, 49.36977], [-124.50281, 49.36977]]]}</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
@@ -32889,12 +32891,12 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>10.21966/21sf-ey03</t>
+          <t>10.21966/npe4-3036</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq77iyWJfPg4z-FvOSb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Opt2a41JCjjQCuqrK6m</t>
         </is>
       </c>
       <c r="T296" t="inlineStr">
@@ -32923,12 +32925,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>5177d019-598e-4415-b778-9688403652c8</t>
+          <t>35245eae-e508-47da-bcf7-54346cda086a</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>ca-cioos_ed84df74-5a2d-4a7d-87c8-a7b93f11088e</t>
+          <t>ca-cioos_e9b72149-8cf1-4000-ae3e-6b29ad60b078</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -32938,7 +32940,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Nalaxdlala River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Malksope River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -32984,7 +32986,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.9489, 50.70902], [-125.9696, 50.70291], [-126.00938, 50.69118], [-126.00108, 50.66848], [-125.98257, 50.68374], [-125.98152, 50.69271], [-125.95462, 50.70263], [-125.94785, 50.70768], [-125.9489, 50.70911], [-125.9489, 50.70902]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.46569, 50.12556], [-127.45723, 50.13142], [-127.43281, 50.13338], [-127.42845, 50.13765], [-127.41181, 50.14408], [-127.40973, 50.14233], [-127.41999, 50.13627], [-127.41803, 50.13195], [-127.43106, 50.12796], [-127.46545, 50.12446], [-127.46569, 50.12548], [-127.46569, 50.12556]]]}</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
@@ -32999,12 +33001,12 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>10.21966/4krv-aw23</t>
+          <t>10.21966/21sf-ey03</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptbxmpkBsfyWWfSxOJ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-Oq77iyWJfPg4z-FvOSb</t>
         </is>
       </c>
       <c r="T297" t="inlineStr">
@@ -33033,12 +33035,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>d320d90e-96bf-4993-81c5-f1f57886b0e6</t>
+          <t>5177d019-598e-4415-b778-9688403652c8</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>ca-cioos_b922699f-69b6-4d63-b538-7c290086a408</t>
+          <t>ca-cioos_ed84df74-5a2d-4a7d-87c8-a7b93f11088e</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -33048,7 +33050,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>BC Estuary Water Quality Monitoring Data - Quw'utsun/Xwulqw'selu River Estuary (Provisional)</t>
+          <t>BC Estuary Water Quality Monitoring Data - Nalaxdlala River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -33094,7 +33096,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.56201, 48.73508], [-123.59772, 48.75559], [-123.62127, 48.76514], [-123.63885, 48.77426], [-123.66935, 48.78033], [-123.67901, 48.75472], [-123.65155, 48.74322], [-123.63017, 48.7405], [-123.60792, 48.74289], [-123.56494, 48.72987], [-123.56179, 48.73529], [-123.56201, 48.73508]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.9489, 50.70902], [-125.9696, 50.70291], [-126.00938, 50.69118], [-126.00108, 50.66848], [-125.98257, 50.68374], [-125.98152, 50.69271], [-125.95462, 50.70263], [-125.94785, 50.70768], [-125.9489, 50.70911], [-125.9489, 50.70902]]]}</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
@@ -33109,17 +33111,17 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>10.21966/2ha7-9p26</t>
+          <t>10.21966/4krv-aw23</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpsCA3ycwZ7bFTDIQxh</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OptbxmpkBsfyWWfSxOJ</t>
         </is>
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
@@ -33143,12 +33145,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>dd471e82-a6b8-4f32-891c-bbea26e9998e</t>
+          <t>d320d90e-96bf-4993-81c5-f1f57886b0e6</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>ca-cioos_aeb30028-a7eb-462e-ac0f-6c5fe101d4a2</t>
+          <t>ca-cioos_b922699f-69b6-4d63-b538-7c290086a408</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -33158,7 +33160,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>DNA Metabarcoding Captures Temporal and Vertical Dynamics of Mesozooplankton Communities</t>
+          <t>BC Estuary Water Quality Monitoring Data - Quw'utsun/Xwulqw'selu River Estuary (Provisional)</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -33176,12 +33178,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Genomics, Oceanography</t>
+          <t>Estuary Resilience</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -33196,45 +33198,45 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N299" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.0992, 50.0307]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.56201, 48.73508], [-123.59772, 48.75559], [-123.62127, 48.76514], [-123.63885, 48.77426], [-123.66935, 48.78033], [-123.67901, 48.75472], [-123.65155, 48.74322], [-123.63017, 48.7405], [-123.60792, 48.74289], [-123.56494, 48.72987], [-123.56179, 48.73529], [-123.56201, 48.73508]]]}</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>[{'max': '260.0', 'min': '0.0'}]</t>
+          <t>[{'max': '100.0', 'min': '0.2'}]</t>
         </is>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>zooplanktonBiomassAndDiversity</t>
+          <t>other, seaSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, subSurfaceTemperature, oxygen</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>10.21966/6b20-7r76</t>
+          <t>10.21966/2ha7-9p26</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OvzbmseH_syBXg1RXKd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/mALzxHvoyRXof5FCVKOlOJC585n1/-OpsCA3ycwZ7bFTDIQxh</t>
         </is>
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V299" t="n">
@@ -33363,12 +33365,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>d269f354-8527-4e94-bb32-9de4fe3fabdf</t>
+          <t>098c52a1-6dde-4e64-8b27-5a34e40870e6</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>ca-cioos_da232383-781d-4852-8542-cf0cb8aa5f26</t>
+          <t>ca-cioos_e5e61f93-db9b-48d0-b779-45e73fabfd0a</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -33378,17 +33380,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Data for Paper: Detection differences between eDNA and mid-water trawls are driven by fish biomass and habitat preferences</t>
+          <t>High Resolution Coastal Carbon Monitoring in the Northeast Pacific</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>CC-BY-NC-ND-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H301" t="b">
@@ -33396,12 +33398,12 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -33420,31 +33422,27 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.6289, 50.7424], [-127.321, 50.6868], [-124.8052, 48.3262], [-123.2452, 48.1432], [-122.9596, 49.0945], [-126.6289, 50.7424]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-160.4964, 46.7847], [-118.6667, 46.7847], [-118.6667, 62.7421], [-160.4964, 62.7421], [-160.4964, 46.7847]]]}</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution</t>
-        </is>
-      </c>
-      <c r="R301" t="inlineStr">
-        <is>
-          <t>10.21966/hky6-1022</t>
-        </is>
-      </c>
+          <t>inorganicCarbon</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr"/>
       <c r="S301" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-P1l_Wv09HnWD1is-Yik</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-P0csr75piiewsICpJu8</t>
         </is>
       </c>
       <c r="T301" t="inlineStr">
@@ -33454,17 +33452,11 @@
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="V301" t="n">
-        <v>0</v>
-      </c>
-      <c r="W301" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr"/>
+      <c r="W301" t="inlineStr"/>
       <c r="X301" t="inlineStr"/>
     </row>
     <row r="302">
@@ -33473,12 +33465,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>098c52a1-6dde-4e64-8b27-5a34e40870e6</t>
+          <t>d269f354-8527-4e94-bb32-9de4fe3fabdf</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>ca-cioos_e5e61f93-db9b-48d0-b779-45e73fabfd0a</t>
+          <t>ca-cioos_da232383-781d-4852-8542-cf0cb8aa5f26</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -33488,17 +33480,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>High Resolution Coastal Carbon Monitoring in the Northeast Pacific</t>
+          <t>Data for Paper: Detection differences between eDNA and mid-water trawls are driven by fish biomass and habitat preferences</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-NC-ND-4.0</t>
         </is>
       </c>
       <c r="H302" t="b">
@@ -33506,12 +33498,12 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -33530,42 +33522,54 @@
         </is>
       </c>
       <c r="N302" t="n">
+        <v>3</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.6289, 50.7424], [-127.321, 50.6868], [-124.8052, 48.3262], [-123.2452, 48.1432], [-122.9596, 49.0945], [-126.6289, 50.7424]]]}</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>fishAbundanceAndDistribution</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>10.21966/hky6-1022</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-P1l_Wv09HnWD1is-Yik</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="V302" t="n">
+        <v>0</v>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X302" t="n">
         <v>1</v>
       </c>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-160.4964, 46.7847], [-118.6667, 46.7847], [-118.6667, 62.7421], [-160.4964, 62.7421], [-160.4964, 46.7847]]]}</t>
-        </is>
-      </c>
-      <c r="P302" t="inlineStr">
-        <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
-        </is>
-      </c>
-      <c r="Q302" t="inlineStr">
-        <is>
-          <t>inorganicCarbon</t>
-        </is>
-      </c>
-      <c r="R302" t="inlineStr"/>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-P0csr75piiewsICpJu8</t>
-        </is>
-      </c>
-      <c r="T302" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="U302" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="V302" t="inlineStr"/>
-      <c r="W302" t="inlineStr"/>
-      <c r="X302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -33787,7 +33791,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X304" t="inlineStr"/>
+      <c r="X304" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -33997,7 +34003,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X306" t="inlineStr"/>
+      <c r="X306" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -3685,9 +3685,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -6005,12 +6003,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6020,7 +6018,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6066,7 +6064,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6076,17 +6074,17 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6096,7 +6094,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V52" t="n">
@@ -6115,12 +6113,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6130,7 +6128,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6176,7 +6174,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6186,17 +6184,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6206,7 +6204,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -8965,12 +8963,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
+          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8980,7 +8978,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
+          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8998,7 +8996,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9026,12 +9024,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -9041,12 +9039,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>10.21966/eysg-7a26</t>
+          <t>10.21966/wfcv-n753</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -9075,12 +9073,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
+          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9090,7 +9088,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9108,7 +9106,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9136,12 +9134,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -9151,12 +9149,12 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>10.21966/wfcv-n753</t>
+          <t>10.21966/eysg-7a26</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -12925,12 +12923,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -12940,7 +12938,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -12963,7 +12961,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -12982,11 +12980,11 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -13001,12 +12999,12 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -13016,7 +13014,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V115" t="n">
@@ -13024,7 +13022,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -13035,12 +13033,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -13050,7 +13048,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -13073,7 +13071,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -13092,11 +13090,11 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13111,12 +13109,12 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -13126,7 +13124,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V116" t="n">
@@ -13134,7 +13132,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -15007,9 +15005,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X133" t="n">
-        <v>1</v>
-      </c>
+      <c r="X133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16331,9 +16327,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X145" t="n">
-        <v>1</v>
-      </c>
+      <c r="X145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -18533,9 +18527,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X165" t="n">
-        <v>1</v>
-      </c>
+      <c r="X165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19305,7 +19297,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X172" t="inlineStr"/>
+      <c r="X172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20515,9 +20509,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X183" t="n">
-        <v>1</v>
-      </c>
+      <c r="X183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -23149,9 +23141,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X207" t="n">
-        <v>1</v>
-      </c>
+      <c r="X207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -5775,7 +5775,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6003,12 +6005,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6018,7 +6020,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6064,7 +6066,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6074,17 +6076,17 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6094,7 +6096,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V52" t="n">
@@ -6113,12 +6115,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6128,7 +6130,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6174,7 +6176,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6184,17 +6186,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6204,7 +6206,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -13905,7 +13907,9 @@
           <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
         </is>
       </c>
-      <c r="X123" t="inlineStr"/>
+      <c r="X123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14903,12 +14907,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -14918,7 +14922,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14936,7 +14940,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -14956,20 +14960,20 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -14979,12 +14983,12 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>10.21966/1.135248</t>
+          <t>10.21966/x6q2-me90</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14994,7 +14998,7 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V133" t="n">
@@ -15005,9 +15009,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X133" t="n">
-        <v>1</v>
-      </c>
+      <c r="X133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15015,12 +15017,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15030,7 +15032,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15048,7 +15050,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15068,20 +15070,20 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -15091,12 +15093,12 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/x6q2-me90</t>
+          <t>10.21966/1.135248</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -15106,7 +15108,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="V134" t="n">
@@ -16329,9 +16331,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X145" t="n">
-        <v>1</v>
-      </c>
+      <c r="X145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -24801,7 +24801,9 @@
           <t>[{'year': '2026', 'total': 2}]</t>
         </is>
       </c>
-      <c r="X222" t="inlineStr"/>
+      <c r="X222" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25791,9 +25793,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X231" t="n">
-        <v>1</v>
-      </c>
+      <c r="X231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -34221,9 +34221,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X308" t="n">
-        <v>1</v>
-      </c>
+      <c r="X308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -6003,12 +6003,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6074,17 +6074,17 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V52" t="n">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6184,17 +6184,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -14353,12 +14353,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -14368,7 +14368,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -14386,7 +14386,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Skeena Fisheries Commission</t>
         </is>
       </c>
       <c r="N128" t="n">
@@ -14414,27 +14414,27 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V128" t="n">
@@ -14463,12 +14463,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Skeena Fisheries Commission</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N129" t="n">
@@ -14524,27 +14524,27 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="V129" t="n">
@@ -15005,7 +15005,9 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X133" t="inlineStr"/>
+      <c r="X133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -5343,12 +5343,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
+          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
+          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>10.21966/1.715784</t>
+          <t>10.21966/6zp4-ye07</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V46" t="n">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
+          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>10.21966/6zp4-ye07</t>
+          <t>10.21966/zs6a-j496</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
+          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
+          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5634,17 +5634,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10.21966/zs6a-j496</t>
+          <t>10.21966/1.715784</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V48" t="n">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6074,17 +6074,17 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V52" t="n">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6184,17 +6184,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8360,16 +8360,16 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>10.21966/awsk-my87</t>
+          <t>10.21966/5rp3-3207</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V73" t="n">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8470,16 +8470,16 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8489,12 +8489,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>10.21966/5rp3-3207</t>
+          <t>10.21966/awsk-my87</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V74" t="n">
@@ -13905,7 +13905,9 @@
           <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
         </is>
       </c>
-      <c r="X123" t="inlineStr"/>
+      <c r="X123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15005,9 +15007,7 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="X133" t="n">
-        <v>1</v>
-      </c>
+      <c r="X133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -31269,7 +31269,9 @@
       </c>
       <c r="V281" t="inlineStr"/>
       <c r="W281" t="inlineStr"/>
-      <c r="X281" t="inlineStr"/>
+      <c r="X281" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">

--- a/docs/catalog_summary.xlsx
+++ b/docs/catalog_summary.xlsx
@@ -5343,12 +5343,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
+          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
+          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>10.21966/6zp4-ye07</t>
+          <t>10.21966/1.715784</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="V46" t="n">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
+          <t>ca-cioos_1c9b7bcd-d3cc-4856-9428-df7abb2149f0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
+          <t>Mobile Invertebrate Rocky Intertidal Surveys - BC Central Coast - 2016-2018</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>10.21966/zs6a-j496</t>
+          <t>10.21966/6zp4-ye07</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MURNVGtYRFppYzB6YWI</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ca-cioos_17396d02-88ff-4240-837b-5d3a45e70ea0</t>
+          <t>ca-cioos_2738ef2b-0c74-422d-a140-082e5f7b3793</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements collected during the 2016 National Oceanic and Atmospheric Administration West Coast Ocean Acidification survey (NOAA WCOA2016) from California to British Columbia</t>
+          <t>Surfgrass Communities - Motile Invertebrate Surveys - BC Central Coast - 2018-2019</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.40081275, 43.38978964], [-121.83893073, 43.38978964], [-121.83893073, 53.31525434], [-131.40081275, 53.31525434], [-131.40081275, 43.38978964]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17701209, 51.62693395], [-128.1138407, 51.62693395], [-128.1138407, 51.67805576], [-128.17701209, 51.67805576], [-128.17701209, 51.62693395]]]}</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5634,17 +5634,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10.21966/1.715784</t>
+          <t>10.21966/zs6a-j496</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXM3TWYzcWNJZ2p1Nk0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXd4OWhCMU42TmhvaFY</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="V48" t="n">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6074,17 +6074,17 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V52" t="n">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6184,17 +6184,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V53" t="n">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8360,16 +8360,16 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>10.21966/5rp3-3207</t>
+          <t>10.21966/awsk-my87</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V73" t="n">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8470,16 +8470,16 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8489,12 +8489,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>10.21966/awsk-my87</t>
+          <t>10.21966/5rp3-3207</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V74" t="n">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -12980,11 +12980,11 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -12999,12 +12999,12 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -13014,7 +13014,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V115" t="n">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -13033,12 +13033,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -13090,11 +13090,11 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13109,12 +13109,12 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V116" t="n">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -13905,9 +13905,7 @@
           <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
         </is>
       </c>
-      <c r="X123" t="n">
-        <v>1</v>
-      </c>
+      <c r="X123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14905,12 +14903,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -14920,7 +14918,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14938,7 +14936,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -14958,20 +14956,20 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -14981,12 +14979,12 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>10.21966/1.135248</t>
+          <t>10.21966/x6q2-me90</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14996,7 +14994,7 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="V133" t="n">
@@ -15015,12 +15013,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15030,7 +15028,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15048,7 +15046,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15068,20 +15066,20 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -15091,12 +15089,12 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/x6q2-me90</t>
+          <t>10.21966/1.135248</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -15106,7 +15104,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="V134" t="n">
@@ -31269,9 +31267,7 @@
       </c>
       <c r="V281" t="inlineStr"/>
       <c r="W281" t="inlineStr"/>
-      <c r="X281" t="n">
-        <v>1</v>
-      </c>
+      <c r="X281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
